--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -10,7 +10,7 @@
     <sheet name="labels" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$G$636</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$G$657</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="381">
   <si>
     <t>类别</t>
   </si>
@@ -1594,6 +1594,27 @@
     <t>单位：℃</t>
   </si>
   <si>
+    <t>npu_chip_info_optical_index_num_X_Y</t>
+  </si>
+  <si>
+    <t>芯片Udie Port链接的光模块Lane数量。</t>
+  </si>
+  <si>
+    <t>Atlas 850 服务器</t>
+  </si>
+  <si>
+    <t>npu_chip_optical_tx_power_Z_X_Y</t>
+  </si>
+  <si>
+    <t>光模块发送功率。Z为Lane的index，取值为[0:3]，X为Udie ID，Y为Port ID。</t>
+  </si>
+  <si>
+    <t>npu_chip_optical_rx_power_Z_X_Y</t>
+  </si>
+  <si>
+    <t>光模块接收功率。Z为Lane的index，取值为[0:3]，X为Udie ID，Y为Port ID</t>
+  </si>
+  <si>
     <t>npu_chip_info_hbm_utilization</t>
   </si>
   <si>
@@ -1630,6 +1651,302 @@
   </si>
   <si>
     <t>昇腾AI处理器片上内存的带宽利用率。</t>
+  </si>
+  <si>
+    <t>UB</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv4_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv4 UB报文数。</t>
+  </si>
+  <si>
+    <t>Atlas 350 标卡
+Atlas 850 服务器
+Atlas 950 SuperPoD 超节点</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv6_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv6 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv4_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv4 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv6_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv6 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_compact_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG6报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ctph_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG7 CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ntph_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG7 非CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_mem_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的UB mem报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unknown_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的未知报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_drop_ind_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的带drop_ind的报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_err_ind_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的ERR报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_host_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后的落地报文数量（不包含枚举配置和管理报文）。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_imp_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后落地的枚举配置和管理报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_mar_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后落地的UB memory报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_link_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后转发到同Port的TX侧的报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_noc_pkt_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后的P2P报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_route_err_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后出现路由查表错误的报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_out_err_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过校验后的错误报文总数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_length_err_cnt_rx_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过校验后的长度错误报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_rx_busi_flit_num_X_Y</t>
+  </si>
+  <si>
+    <t>RX侧报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_rx_send_ack_flit_X_Y</t>
+  </si>
+  <si>
+    <t>RX向对端返回响应的报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv4_pkt_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv4 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv6_pkt_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv6 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv4_pkt_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv4 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv6_pkt_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv6 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_compact_pkt_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG6报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ctph_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG7 CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ntph_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG7 非CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_mem_pkt_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的UB mem报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unknown_pkt_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的未知报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_drop_ind_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的带drop_ind的报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_err_ind_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的ERR报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_lpbk_ind_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送报文在NL环回的报文个数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_out_err_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的报文经过校验后的错误报文总数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_length_err_cnt_tx_X_Y</t>
+  </si>
+  <si>
+    <t>TX侧发送的报文经过校验后的长度错误报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_tx_busi_flit_num_X_Y</t>
+  </si>
+  <si>
+    <t>TX报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_tx_recv_ack_flit_X_Y</t>
+  </si>
+  <si>
+    <t>TX收到对端响应的报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_retry_req_sum_X_Y</t>
+  </si>
+  <si>
+    <t>发起重传次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_retry_ack_sum_X_Y</t>
+  </si>
+  <si>
+    <t>响应重传次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_crc_error_sum_X_Y</t>
+  </si>
+  <si>
+    <t>CRC校验错误次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxpausepkts_X_Y</t>
+  </si>
+  <si>
+    <t>RX pause帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txpausepkts_X_Y</t>
+  </si>
+  <si>
+    <t>TX pause帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxpfcpkts_X_Y</t>
+  </si>
+  <si>
+    <t>RX PFC帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txpfcpkts_X_Y</t>
+  </si>
+  <si>
+    <t>TX PFC帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxbadpkts_X_Y</t>
+  </si>
+  <si>
+    <t>RX坏包总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txbadpkts_X_Y</t>
+  </si>
+  <si>
+    <t>TX坏包总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxbadoctets_X_Y</t>
+  </si>
+  <si>
+    <t>RX坏包总报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txbadoctets_X_Y</t>
+  </si>
+  <si>
+    <t>TX坏包总报文字节数。</t>
   </si>
 </sst>
 </file>
@@ -1814,13 +2131,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="方正兰亭黑简体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
@@ -1831,6 +2141,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3082,7 +3399,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G636"/>
+  <dimension ref="A1:G993"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14.25" style="1" customWidth="1"/>
@@ -11975,13 +12292,13 @@
       <c r="G615" s="9"/>
     </row>
     <row r="616" spans="1:7">
-      <c r="A616" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B616" s="18" t="s">
+      <c r="A616" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B616" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C616" s="18" t="s">
+      <c r="C616" s="8" t="s">
         <v>270</v>
       </c>
       <c r="D616" s="8" t="s">
@@ -11990,100 +12307,100 @@
       <c r="E616" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F616" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G616" s="16" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="617" customHeight="1" spans="1:7">
-      <c r="A617" s="7"/>
-      <c r="B617" s="20"/>
-      <c r="C617" s="20"/>
+      <c r="F616" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G616" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7">
+      <c r="A617" s="8"/>
+      <c r="B617" s="8"/>
+      <c r="C617" s="8"/>
       <c r="D617" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E617" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F617" s="7"/>
-      <c r="G617" s="16"/>
-    </row>
-    <row r="618" customHeight="1" spans="1:7">
-      <c r="A618" s="7"/>
-      <c r="B618" s="20"/>
-      <c r="C618" s="20"/>
+      <c r="F617" s="35"/>
+      <c r="G617" s="9"/>
+    </row>
+    <row r="618" spans="1:7">
+      <c r="A618" s="8"/>
+      <c r="B618" s="8"/>
+      <c r="C618" s="8"/>
       <c r="D618" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E618" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F618" s="7"/>
-      <c r="G618" s="16"/>
-    </row>
-    <row r="619" customHeight="1" spans="1:7">
-      <c r="A619" s="7"/>
-      <c r="B619" s="20"/>
-      <c r="C619" s="20"/>
+      <c r="F618" s="35"/>
+      <c r="G618" s="9"/>
+    </row>
+    <row r="619" spans="1:7">
+      <c r="A619" s="8"/>
+      <c r="B619" s="8"/>
+      <c r="C619" s="8"/>
       <c r="D619" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E619" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F619" s="7"/>
-      <c r="G619" s="16"/>
-    </row>
-    <row r="620" customHeight="1" spans="1:7">
-      <c r="A620" s="7"/>
-      <c r="B620" s="20"/>
-      <c r="C620" s="20"/>
+      <c r="F619" s="35"/>
+      <c r="G619" s="9"/>
+    </row>
+    <row r="620" spans="1:7">
+      <c r="A620" s="8"/>
+      <c r="B620" s="8"/>
+      <c r="C620" s="8"/>
       <c r="D620" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E620" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F620" s="7"/>
-      <c r="G620" s="16"/>
-    </row>
-    <row r="621" customHeight="1" spans="1:7">
-      <c r="A621" s="7"/>
-      <c r="B621" s="20"/>
-      <c r="C621" s="20"/>
+      <c r="F620" s="35"/>
+      <c r="G620" s="9"/>
+    </row>
+    <row r="621" spans="1:7">
+      <c r="A621" s="8"/>
+      <c r="B621" s="8"/>
+      <c r="C621" s="8"/>
       <c r="D621" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E621" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F621" s="7"/>
-      <c r="G621" s="16"/>
-    </row>
-    <row r="622" customHeight="1" spans="1:7">
-      <c r="A622" s="7"/>
-      <c r="B622" s="25"/>
-      <c r="C622" s="25"/>
+      <c r="F621" s="35"/>
+      <c r="G621" s="9"/>
+    </row>
+    <row r="622" spans="1:7">
+      <c r="A622" s="8"/>
+      <c r="B622" s="8"/>
+      <c r="C622" s="8"/>
       <c r="D622" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E622" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F622" s="7"/>
-      <c r="G622" s="16"/>
+      <c r="F622" s="37"/>
+      <c r="G622" s="9"/>
     </row>
     <row r="623" spans="1:7">
-      <c r="A623" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="B623" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="C623" s="18" t="s">
+      <c r="A623" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B623" s="8" t="s">
         <v>272</v>
+      </c>
+      <c r="C623" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="D623" s="8" t="s">
         <v>17</v>
@@ -12091,99 +12408,99 @@
       <c r="E623" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F623" s="63" t="s">
-        <v>273</v>
-      </c>
-      <c r="G623" s="16" t="s">
-        <v>148</v>
+      <c r="F623" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G623" s="9" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="624" spans="1:7">
-      <c r="A624" s="64"/>
-      <c r="B624" s="20"/>
-      <c r="C624" s="20"/>
+      <c r="A624" s="8"/>
+      <c r="B624" s="8"/>
+      <c r="C624" s="8"/>
       <c r="D624" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E624" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F624" s="65"/>
-      <c r="G624" s="16"/>
+      <c r="F624" s="35"/>
+      <c r="G624" s="9"/>
     </row>
     <row r="625" spans="1:7">
-      <c r="A625" s="64"/>
-      <c r="B625" s="20"/>
-      <c r="C625" s="20"/>
+      <c r="A625" s="8"/>
+      <c r="B625" s="8"/>
+      <c r="C625" s="8"/>
       <c r="D625" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E625" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F625" s="65"/>
-      <c r="G625" s="16"/>
+      <c r="F625" s="35"/>
+      <c r="G625" s="9"/>
     </row>
     <row r="626" spans="1:7">
-      <c r="A626" s="64"/>
-      <c r="B626" s="20"/>
-      <c r="C626" s="20"/>
+      <c r="A626" s="8"/>
+      <c r="B626" s="8"/>
+      <c r="C626" s="8"/>
       <c r="D626" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E626" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F626" s="65"/>
-      <c r="G626" s="16"/>
+      <c r="F626" s="35"/>
+      <c r="G626" s="9"/>
     </row>
     <row r="627" spans="1:7">
-      <c r="A627" s="64"/>
-      <c r="B627" s="20"/>
-      <c r="C627" s="20"/>
+      <c r="A627" s="8"/>
+      <c r="B627" s="8"/>
+      <c r="C627" s="8"/>
       <c r="D627" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E627" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F627" s="65"/>
-      <c r="G627" s="16"/>
+      <c r="F627" s="35"/>
+      <c r="G627" s="9"/>
     </row>
     <row r="628" spans="1:7">
-      <c r="A628" s="64"/>
-      <c r="B628" s="20"/>
-      <c r="C628" s="20"/>
+      <c r="A628" s="8"/>
+      <c r="B628" s="8"/>
+      <c r="C628" s="8"/>
       <c r="D628" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E628" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F628" s="65"/>
-      <c r="G628" s="16"/>
+      <c r="F628" s="35"/>
+      <c r="G628" s="9"/>
     </row>
     <row r="629" spans="1:7">
-      <c r="A629" s="66"/>
-      <c r="B629" s="25"/>
-      <c r="C629" s="25"/>
+      <c r="A629" s="8"/>
+      <c r="B629" s="8"/>
+      <c r="C629" s="8"/>
       <c r="D629" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E629" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F629" s="65"/>
-      <c r="G629" s="16"/>
+      <c r="F629" s="37"/>
+      <c r="G629" s="9"/>
     </row>
     <row r="630" spans="1:7">
-      <c r="A630" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="B630" s="18" t="s">
+      <c r="A630" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B630" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C630" s="18" t="s">
+      <c r="C630" s="8" t="s">
         <v>275</v>
       </c>
       <c r="D630" s="8" t="s">
@@ -12192,93 +12509,5244 @@
       <c r="E630" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F630" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G630" s="16" t="s">
-        <v>148</v>
+      <c r="F630" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G630" s="9" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="631" spans="1:7">
-      <c r="A631" s="64"/>
-      <c r="B631" s="20"/>
-      <c r="C631" s="20"/>
+      <c r="A631" s="8"/>
+      <c r="B631" s="8"/>
+      <c r="C631" s="8"/>
       <c r="D631" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E631" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F631" s="20"/>
-      <c r="G631" s="16"/>
+      <c r="F631" s="35"/>
+      <c r="G631" s="9"/>
     </row>
     <row r="632" spans="1:7">
-      <c r="A632" s="64"/>
-      <c r="B632" s="20"/>
-      <c r="C632" s="20"/>
+      <c r="A632" s="8"/>
+      <c r="B632" s="8"/>
+      <c r="C632" s="8"/>
       <c r="D632" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E632" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F632" s="20"/>
-      <c r="G632" s="16"/>
+      <c r="F632" s="35"/>
+      <c r="G632" s="9"/>
     </row>
     <row r="633" spans="1:7">
-      <c r="A633" s="64"/>
-      <c r="B633" s="20"/>
-      <c r="C633" s="20"/>
+      <c r="A633" s="8"/>
+      <c r="B633" s="8"/>
+      <c r="C633" s="8"/>
       <c r="D633" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E633" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F633" s="20"/>
-      <c r="G633" s="16"/>
+      <c r="F633" s="35"/>
+      <c r="G633" s="9"/>
     </row>
     <row r="634" spans="1:7">
-      <c r="A634" s="64"/>
-      <c r="B634" s="20"/>
-      <c r="C634" s="20"/>
+      <c r="A634" s="8"/>
+      <c r="B634" s="8"/>
+      <c r="C634" s="8"/>
       <c r="D634" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E634" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F634" s="20"/>
-      <c r="G634" s="16"/>
+      <c r="F634" s="35"/>
+      <c r="G634" s="9"/>
     </row>
     <row r="635" spans="1:7">
-      <c r="A635" s="64"/>
-      <c r="B635" s="20"/>
-      <c r="C635" s="20"/>
+      <c r="A635" s="8"/>
+      <c r="B635" s="8"/>
+      <c r="C635" s="8"/>
       <c r="D635" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E635" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F635" s="20"/>
-      <c r="G635" s="16"/>
+      <c r="F635" s="35"/>
+      <c r="G635" s="9"/>
     </row>
     <row r="636" spans="1:7">
-      <c r="A636" s="66"/>
-      <c r="B636" s="25"/>
-      <c r="C636" s="25"/>
+      <c r="A636" s="8"/>
+      <c r="B636" s="8"/>
+      <c r="C636" s="8"/>
       <c r="D636" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E636" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F636" s="25"/>
-      <c r="G636" s="16"/>
+      <c r="F636" s="37"/>
+      <c r="G636" s="9"/>
+    </row>
+    <row r="637" spans="1:7">
+      <c r="A637" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B637" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="C637" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="D637" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E637" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F637" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G637" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="638" customHeight="1" spans="1:7">
+      <c r="A638" s="7"/>
+      <c r="B638" s="20"/>
+      <c r="C638" s="20"/>
+      <c r="D638" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E638" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F638" s="7"/>
+      <c r="G638" s="16"/>
+    </row>
+    <row r="639" customHeight="1" spans="1:7">
+      <c r="A639" s="7"/>
+      <c r="B639" s="20"/>
+      <c r="C639" s="20"/>
+      <c r="D639" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E639" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F639" s="7"/>
+      <c r="G639" s="16"/>
+    </row>
+    <row r="640" customHeight="1" spans="1:7">
+      <c r="A640" s="7"/>
+      <c r="B640" s="20"/>
+      <c r="C640" s="20"/>
+      <c r="D640" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E640" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F640" s="7"/>
+      <c r="G640" s="16"/>
+    </row>
+    <row r="641" customHeight="1" spans="1:7">
+      <c r="A641" s="7"/>
+      <c r="B641" s="20"/>
+      <c r="C641" s="20"/>
+      <c r="D641" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E641" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F641" s="7"/>
+      <c r="G641" s="16"/>
+    </row>
+    <row r="642" customHeight="1" spans="1:7">
+      <c r="A642" s="7"/>
+      <c r="B642" s="20"/>
+      <c r="C642" s="20"/>
+      <c r="D642" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E642" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F642" s="7"/>
+      <c r="G642" s="16"/>
+    </row>
+    <row r="643" customHeight="1" spans="1:7">
+      <c r="A643" s="7"/>
+      <c r="B643" s="25"/>
+      <c r="C643" s="25"/>
+      <c r="D643" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E643" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F643" s="7"/>
+      <c r="G643" s="16"/>
+    </row>
+    <row r="644" spans="1:7">
+      <c r="A644" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="B644" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C644" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D644" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E644" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F644" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="G644" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7">
+      <c r="A645" s="64"/>
+      <c r="B645" s="20"/>
+      <c r="C645" s="20"/>
+      <c r="D645" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E645" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F645" s="65"/>
+      <c r="G645" s="16"/>
+    </row>
+    <row r="646" spans="1:7">
+      <c r="A646" s="64"/>
+      <c r="B646" s="20"/>
+      <c r="C646" s="20"/>
+      <c r="D646" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E646" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F646" s="65"/>
+      <c r="G646" s="16"/>
+    </row>
+    <row r="647" spans="1:7">
+      <c r="A647" s="64"/>
+      <c r="B647" s="20"/>
+      <c r="C647" s="20"/>
+      <c r="D647" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E647" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F647" s="65"/>
+      <c r="G647" s="16"/>
+    </row>
+    <row r="648" spans="1:7">
+      <c r="A648" s="64"/>
+      <c r="B648" s="20"/>
+      <c r="C648" s="20"/>
+      <c r="D648" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E648" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F648" s="65"/>
+      <c r="G648" s="16"/>
+    </row>
+    <row r="649" spans="1:7">
+      <c r="A649" s="64"/>
+      <c r="B649" s="20"/>
+      <c r="C649" s="20"/>
+      <c r="D649" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E649" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F649" s="65"/>
+      <c r="G649" s="16"/>
+    </row>
+    <row r="650" spans="1:7">
+      <c r="A650" s="66"/>
+      <c r="B650" s="25"/>
+      <c r="C650" s="25"/>
+      <c r="D650" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E650" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F650" s="65"/>
+      <c r="G650" s="16"/>
+    </row>
+    <row r="651" spans="1:7">
+      <c r="A651" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="B651" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C651" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="D651" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E651" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F651" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="G651" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="652" spans="1:7">
+      <c r="A652" s="64"/>
+      <c r="B652" s="20"/>
+      <c r="C652" s="20"/>
+      <c r="D652" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E652" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F652" s="20"/>
+      <c r="G652" s="16"/>
+    </row>
+    <row r="653" spans="1:7">
+      <c r="A653" s="64"/>
+      <c r="B653" s="20"/>
+      <c r="C653" s="20"/>
+      <c r="D653" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E653" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F653" s="20"/>
+      <c r="G653" s="16"/>
+    </row>
+    <row r="654" spans="1:7">
+      <c r="A654" s="64"/>
+      <c r="B654" s="20"/>
+      <c r="C654" s="20"/>
+      <c r="D654" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E654" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F654" s="20"/>
+      <c r="G654" s="16"/>
+    </row>
+    <row r="655" spans="1:7">
+      <c r="A655" s="64"/>
+      <c r="B655" s="20"/>
+      <c r="C655" s="20"/>
+      <c r="D655" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E655" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F655" s="20"/>
+      <c r="G655" s="16"/>
+    </row>
+    <row r="656" spans="1:7">
+      <c r="A656" s="64"/>
+      <c r="B656" s="20"/>
+      <c r="C656" s="20"/>
+      <c r="D656" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E656" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F656" s="20"/>
+      <c r="G656" s="16"/>
+    </row>
+    <row r="657" spans="1:7">
+      <c r="A657" s="66"/>
+      <c r="B657" s="25"/>
+      <c r="C657" s="25"/>
+      <c r="D657" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E657" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F657" s="25"/>
+      <c r="G657" s="16"/>
+    </row>
+    <row r="658" spans="1:7">
+      <c r="A658" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B658" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C658" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D658" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E658" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F658" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G658" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7">
+      <c r="A659" s="8"/>
+      <c r="B659" s="8"/>
+      <c r="C659" s="8"/>
+      <c r="D659" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E659" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F659" s="35"/>
+      <c r="G659" s="9"/>
+    </row>
+    <row r="660" spans="1:7">
+      <c r="A660" s="8"/>
+      <c r="B660" s="8"/>
+      <c r="C660" s="8"/>
+      <c r="D660" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E660" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F660" s="35"/>
+      <c r="G660" s="9"/>
+    </row>
+    <row r="661" spans="1:7">
+      <c r="A661" s="8"/>
+      <c r="B661" s="8"/>
+      <c r="C661" s="8"/>
+      <c r="D661" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E661" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F661" s="35"/>
+      <c r="G661" s="9"/>
+    </row>
+    <row r="662" spans="1:7">
+      <c r="A662" s="8"/>
+      <c r="B662" s="8"/>
+      <c r="C662" s="8"/>
+      <c r="D662" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E662" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F662" s="35"/>
+      <c r="G662" s="9"/>
+    </row>
+    <row r="663" spans="1:7">
+      <c r="A663" s="8"/>
+      <c r="B663" s="8"/>
+      <c r="C663" s="8"/>
+      <c r="D663" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E663" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F663" s="35"/>
+      <c r="G663" s="9"/>
+    </row>
+    <row r="664" spans="1:7">
+      <c r="A664" s="8"/>
+      <c r="B664" s="8"/>
+      <c r="C664" s="8"/>
+      <c r="D664" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E664" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F664" s="37"/>
+      <c r="G664" s="9"/>
+    </row>
+    <row r="665" spans="1:7">
+      <c r="A665" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B665" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C665" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D665" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E665" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F665" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G665" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="666" spans="1:7">
+      <c r="A666" s="8"/>
+      <c r="B666" s="8"/>
+      <c r="C666" s="8"/>
+      <c r="D666" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E666" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F666" s="35"/>
+      <c r="G666" s="9"/>
+    </row>
+    <row r="667" spans="1:7">
+      <c r="A667" s="8"/>
+      <c r="B667" s="8"/>
+      <c r="C667" s="8"/>
+      <c r="D667" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E667" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F667" s="35"/>
+      <c r="G667" s="9"/>
+    </row>
+    <row r="668" spans="1:7">
+      <c r="A668" s="8"/>
+      <c r="B668" s="8"/>
+      <c r="C668" s="8"/>
+      <c r="D668" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E668" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F668" s="35"/>
+      <c r="G668" s="9"/>
+    </row>
+    <row r="669" spans="1:7">
+      <c r="A669" s="8"/>
+      <c r="B669" s="8"/>
+      <c r="C669" s="8"/>
+      <c r="D669" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E669" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F669" s="35"/>
+      <c r="G669" s="9"/>
+    </row>
+    <row r="670" spans="1:7">
+      <c r="A670" s="8"/>
+      <c r="B670" s="8"/>
+      <c r="C670" s="8"/>
+      <c r="D670" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E670" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F670" s="35"/>
+      <c r="G670" s="9"/>
+    </row>
+    <row r="671" spans="1:7">
+      <c r="A671" s="8"/>
+      <c r="B671" s="8"/>
+      <c r="C671" s="8"/>
+      <c r="D671" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E671" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F671" s="37"/>
+      <c r="G671" s="9"/>
+    </row>
+    <row r="672" spans="1:7">
+      <c r="A672" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B672" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C672" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D672" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E672" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F672" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G672" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7">
+      <c r="A673" s="8"/>
+      <c r="B673" s="8"/>
+      <c r="C673" s="8"/>
+      <c r="D673" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E673" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F673" s="35"/>
+      <c r="G673" s="9"/>
+    </row>
+    <row r="674" spans="1:7">
+      <c r="A674" s="8"/>
+      <c r="B674" s="8"/>
+      <c r="C674" s="8"/>
+      <c r="D674" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E674" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F674" s="35"/>
+      <c r="G674" s="9"/>
+    </row>
+    <row r="675" spans="1:7">
+      <c r="A675" s="8"/>
+      <c r="B675" s="8"/>
+      <c r="C675" s="8"/>
+      <c r="D675" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E675" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F675" s="35"/>
+      <c r="G675" s="9"/>
+    </row>
+    <row r="676" spans="1:7">
+      <c r="A676" s="8"/>
+      <c r="B676" s="8"/>
+      <c r="C676" s="8"/>
+      <c r="D676" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E676" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F676" s="35"/>
+      <c r="G676" s="9"/>
+    </row>
+    <row r="677" spans="1:7">
+      <c r="A677" s="8"/>
+      <c r="B677" s="8"/>
+      <c r="C677" s="8"/>
+      <c r="D677" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E677" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F677" s="35"/>
+      <c r="G677" s="9"/>
+    </row>
+    <row r="678" spans="1:7">
+      <c r="A678" s="8"/>
+      <c r="B678" s="8"/>
+      <c r="C678" s="8"/>
+      <c r="D678" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E678" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F678" s="37"/>
+      <c r="G678" s="9"/>
+    </row>
+    <row r="679" spans="1:7">
+      <c r="A679" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B679" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="C679" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D679" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E679" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F679" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G679" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="680" spans="1:7">
+      <c r="A680" s="8"/>
+      <c r="B680" s="8"/>
+      <c r="C680" s="8"/>
+      <c r="D680" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E680" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F680" s="35"/>
+      <c r="G680" s="9"/>
+    </row>
+    <row r="681" spans="1:7">
+      <c r="A681" s="8"/>
+      <c r="B681" s="8"/>
+      <c r="C681" s="8"/>
+      <c r="D681" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E681" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F681" s="35"/>
+      <c r="G681" s="9"/>
+    </row>
+    <row r="682" spans="1:7">
+      <c r="A682" s="8"/>
+      <c r="B682" s="8"/>
+      <c r="C682" s="8"/>
+      <c r="D682" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E682" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F682" s="35"/>
+      <c r="G682" s="9"/>
+    </row>
+    <row r="683" spans="1:7">
+      <c r="A683" s="8"/>
+      <c r="B683" s="8"/>
+      <c r="C683" s="8"/>
+      <c r="D683" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E683" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F683" s="35"/>
+      <c r="G683" s="9"/>
+    </row>
+    <row r="684" spans="1:7">
+      <c r="A684" s="8"/>
+      <c r="B684" s="8"/>
+      <c r="C684" s="8"/>
+      <c r="D684" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E684" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F684" s="35"/>
+      <c r="G684" s="9"/>
+    </row>
+    <row r="685" spans="1:7">
+      <c r="A685" s="8"/>
+      <c r="B685" s="8"/>
+      <c r="C685" s="8"/>
+      <c r="D685" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E685" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F685" s="37"/>
+      <c r="G685" s="9"/>
+    </row>
+    <row r="686" spans="1:7">
+      <c r="A686" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B686" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C686" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D686" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E686" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F686" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G686" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="687" spans="1:7">
+      <c r="A687" s="8"/>
+      <c r="B687" s="8"/>
+      <c r="C687" s="8"/>
+      <c r="D687" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E687" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F687" s="35"/>
+      <c r="G687" s="9"/>
+    </row>
+    <row r="688" spans="1:7">
+      <c r="A688" s="8"/>
+      <c r="B688" s="8"/>
+      <c r="C688" s="8"/>
+      <c r="D688" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E688" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F688" s="35"/>
+      <c r="G688" s="9"/>
+    </row>
+    <row r="689" spans="1:7">
+      <c r="A689" s="8"/>
+      <c r="B689" s="8"/>
+      <c r="C689" s="8"/>
+      <c r="D689" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E689" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F689" s="35"/>
+      <c r="G689" s="9"/>
+    </row>
+    <row r="690" spans="1:7">
+      <c r="A690" s="8"/>
+      <c r="B690" s="8"/>
+      <c r="C690" s="8"/>
+      <c r="D690" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E690" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F690" s="35"/>
+      <c r="G690" s="9"/>
+    </row>
+    <row r="691" spans="1:7">
+      <c r="A691" s="8"/>
+      <c r="B691" s="8"/>
+      <c r="C691" s="8"/>
+      <c r="D691" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E691" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F691" s="35"/>
+      <c r="G691" s="9"/>
+    </row>
+    <row r="692" spans="1:7">
+      <c r="A692" s="8"/>
+      <c r="B692" s="8"/>
+      <c r="C692" s="8"/>
+      <c r="D692" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E692" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F692" s="37"/>
+      <c r="G692" s="9"/>
+    </row>
+    <row r="693" spans="1:7">
+      <c r="A693" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B693" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C693" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D693" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E693" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F693" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G693" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7">
+      <c r="A694" s="8"/>
+      <c r="B694" s="8"/>
+      <c r="C694" s="8"/>
+      <c r="D694" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E694" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F694" s="35"/>
+      <c r="G694" s="9"/>
+    </row>
+    <row r="695" spans="1:7">
+      <c r="A695" s="8"/>
+      <c r="B695" s="8"/>
+      <c r="C695" s="8"/>
+      <c r="D695" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E695" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F695" s="35"/>
+      <c r="G695" s="9"/>
+    </row>
+    <row r="696" spans="1:7">
+      <c r="A696" s="8"/>
+      <c r="B696" s="8"/>
+      <c r="C696" s="8"/>
+      <c r="D696" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E696" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F696" s="35"/>
+      <c r="G696" s="9"/>
+    </row>
+    <row r="697" spans="1:7">
+      <c r="A697" s="8"/>
+      <c r="B697" s="8"/>
+      <c r="C697" s="8"/>
+      <c r="D697" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E697" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F697" s="35"/>
+      <c r="G697" s="9"/>
+    </row>
+    <row r="698" spans="1:7">
+      <c r="A698" s="8"/>
+      <c r="B698" s="8"/>
+      <c r="C698" s="8"/>
+      <c r="D698" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E698" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F698" s="35"/>
+      <c r="G698" s="9"/>
+    </row>
+    <row r="699" spans="1:7">
+      <c r="A699" s="8"/>
+      <c r="B699" s="8"/>
+      <c r="C699" s="8"/>
+      <c r="D699" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E699" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F699" s="37"/>
+      <c r="G699" s="9"/>
+    </row>
+    <row r="700" spans="1:7">
+      <c r="A700" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B700" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C700" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D700" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E700" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F700" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G700" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7">
+      <c r="A701" s="8"/>
+      <c r="B701" s="8"/>
+      <c r="C701" s="8"/>
+      <c r="D701" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E701" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F701" s="35"/>
+      <c r="G701" s="9"/>
+    </row>
+    <row r="702" spans="1:7">
+      <c r="A702" s="8"/>
+      <c r="B702" s="8"/>
+      <c r="C702" s="8"/>
+      <c r="D702" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E702" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F702" s="35"/>
+      <c r="G702" s="9"/>
+    </row>
+    <row r="703" spans="1:7">
+      <c r="A703" s="8"/>
+      <c r="B703" s="8"/>
+      <c r="C703" s="8"/>
+      <c r="D703" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E703" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F703" s="35"/>
+      <c r="G703" s="9"/>
+    </row>
+    <row r="704" spans="1:7">
+      <c r="A704" s="8"/>
+      <c r="B704" s="8"/>
+      <c r="C704" s="8"/>
+      <c r="D704" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E704" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F704" s="35"/>
+      <c r="G704" s="9"/>
+    </row>
+    <row r="705" spans="1:7">
+      <c r="A705" s="8"/>
+      <c r="B705" s="8"/>
+      <c r="C705" s="8"/>
+      <c r="D705" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E705" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F705" s="35"/>
+      <c r="G705" s="9"/>
+    </row>
+    <row r="706" spans="1:7">
+      <c r="A706" s="8"/>
+      <c r="B706" s="8"/>
+      <c r="C706" s="8"/>
+      <c r="D706" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E706" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F706" s="37"/>
+      <c r="G706" s="9"/>
+    </row>
+    <row r="707" spans="1:7">
+      <c r="A707" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B707" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C707" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D707" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E707" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F707" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G707" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="708" spans="1:7">
+      <c r="A708" s="8"/>
+      <c r="B708" s="8"/>
+      <c r="C708" s="8"/>
+      <c r="D708" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E708" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F708" s="35"/>
+      <c r="G708" s="9"/>
+    </row>
+    <row r="709" spans="1:7">
+      <c r="A709" s="8"/>
+      <c r="B709" s="8"/>
+      <c r="C709" s="8"/>
+      <c r="D709" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E709" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F709" s="35"/>
+      <c r="G709" s="9"/>
+    </row>
+    <row r="710" spans="1:7">
+      <c r="A710" s="8"/>
+      <c r="B710" s="8"/>
+      <c r="C710" s="8"/>
+      <c r="D710" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E710" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F710" s="35"/>
+      <c r="G710" s="9"/>
+    </row>
+    <row r="711" spans="1:7">
+      <c r="A711" s="8"/>
+      <c r="B711" s="8"/>
+      <c r="C711" s="8"/>
+      <c r="D711" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E711" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F711" s="35"/>
+      <c r="G711" s="9"/>
+    </row>
+    <row r="712" spans="1:7">
+      <c r="A712" s="8"/>
+      <c r="B712" s="8"/>
+      <c r="C712" s="8"/>
+      <c r="D712" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E712" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F712" s="35"/>
+      <c r="G712" s="9"/>
+    </row>
+    <row r="713" spans="1:7">
+      <c r="A713" s="8"/>
+      <c r="B713" s="8"/>
+      <c r="C713" s="8"/>
+      <c r="D713" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E713" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F713" s="37"/>
+      <c r="G713" s="9"/>
+    </row>
+    <row r="714" spans="1:7">
+      <c r="A714" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B714" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C714" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D714" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E714" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F714" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G714" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="715" spans="1:7">
+      <c r="A715" s="8"/>
+      <c r="B715" s="8"/>
+      <c r="C715" s="8"/>
+      <c r="D715" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E715" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F715" s="35"/>
+      <c r="G715" s="9"/>
+    </row>
+    <row r="716" spans="1:7">
+      <c r="A716" s="8"/>
+      <c r="B716" s="8"/>
+      <c r="C716" s="8"/>
+      <c r="D716" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E716" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F716" s="35"/>
+      <c r="G716" s="9"/>
+    </row>
+    <row r="717" spans="1:7">
+      <c r="A717" s="8"/>
+      <c r="B717" s="8"/>
+      <c r="C717" s="8"/>
+      <c r="D717" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E717" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F717" s="35"/>
+      <c r="G717" s="9"/>
+    </row>
+    <row r="718" spans="1:7">
+      <c r="A718" s="8"/>
+      <c r="B718" s="8"/>
+      <c r="C718" s="8"/>
+      <c r="D718" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E718" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F718" s="35"/>
+      <c r="G718" s="9"/>
+    </row>
+    <row r="719" spans="1:7">
+      <c r="A719" s="8"/>
+      <c r="B719" s="8"/>
+      <c r="C719" s="8"/>
+      <c r="D719" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E719" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F719" s="35"/>
+      <c r="G719" s="9"/>
+    </row>
+    <row r="720" spans="1:7">
+      <c r="A720" s="8"/>
+      <c r="B720" s="8"/>
+      <c r="C720" s="8"/>
+      <c r="D720" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E720" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F720" s="37"/>
+      <c r="G720" s="9"/>
+    </row>
+    <row r="721" spans="1:7">
+      <c r="A721" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B721" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C721" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D721" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E721" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F721" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G721" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7">
+      <c r="A722" s="8"/>
+      <c r="B722" s="8"/>
+      <c r="C722" s="8"/>
+      <c r="D722" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E722" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F722" s="35"/>
+      <c r="G722" s="9"/>
+    </row>
+    <row r="723" spans="1:7">
+      <c r="A723" s="8"/>
+      <c r="B723" s="8"/>
+      <c r="C723" s="8"/>
+      <c r="D723" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E723" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F723" s="35"/>
+      <c r="G723" s="9"/>
+    </row>
+    <row r="724" spans="1:7">
+      <c r="A724" s="8"/>
+      <c r="B724" s="8"/>
+      <c r="C724" s="8"/>
+      <c r="D724" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E724" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F724" s="35"/>
+      <c r="G724" s="9"/>
+    </row>
+    <row r="725" spans="1:7">
+      <c r="A725" s="8"/>
+      <c r="B725" s="8"/>
+      <c r="C725" s="8"/>
+      <c r="D725" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E725" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F725" s="35"/>
+      <c r="G725" s="9"/>
+    </row>
+    <row r="726" spans="1:7">
+      <c r="A726" s="8"/>
+      <c r="B726" s="8"/>
+      <c r="C726" s="8"/>
+      <c r="D726" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E726" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F726" s="35"/>
+      <c r="G726" s="9"/>
+    </row>
+    <row r="727" spans="1:7">
+      <c r="A727" s="8"/>
+      <c r="B727" s="8"/>
+      <c r="C727" s="8"/>
+      <c r="D727" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E727" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F727" s="37"/>
+      <c r="G727" s="9"/>
+    </row>
+    <row r="728" spans="1:7">
+      <c r="A728" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B728" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C728" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D728" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E728" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F728" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G728" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7">
+      <c r="A729" s="8"/>
+      <c r="B729" s="8"/>
+      <c r="C729" s="8"/>
+      <c r="D729" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E729" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F729" s="35"/>
+      <c r="G729" s="9"/>
+    </row>
+    <row r="730" spans="1:7">
+      <c r="A730" s="8"/>
+      <c r="B730" s="8"/>
+      <c r="C730" s="8"/>
+      <c r="D730" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E730" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F730" s="35"/>
+      <c r="G730" s="9"/>
+    </row>
+    <row r="731" spans="1:7">
+      <c r="A731" s="8"/>
+      <c r="B731" s="8"/>
+      <c r="C731" s="8"/>
+      <c r="D731" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E731" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F731" s="35"/>
+      <c r="G731" s="9"/>
+    </row>
+    <row r="732" spans="1:7">
+      <c r="A732" s="8"/>
+      <c r="B732" s="8"/>
+      <c r="C732" s="8"/>
+      <c r="D732" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E732" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F732" s="35"/>
+      <c r="G732" s="9"/>
+    </row>
+    <row r="733" spans="1:7">
+      <c r="A733" s="8"/>
+      <c r="B733" s="8"/>
+      <c r="C733" s="8"/>
+      <c r="D733" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E733" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F733" s="35"/>
+      <c r="G733" s="9"/>
+    </row>
+    <row r="734" spans="1:7">
+      <c r="A734" s="8"/>
+      <c r="B734" s="8"/>
+      <c r="C734" s="8"/>
+      <c r="D734" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E734" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F734" s="37"/>
+      <c r="G734" s="9"/>
+    </row>
+    <row r="735" spans="1:7">
+      <c r="A735" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B735" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C735" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D735" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E735" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F735" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G735" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="736" spans="1:7">
+      <c r="A736" s="8"/>
+      <c r="B736" s="8"/>
+      <c r="C736" s="8"/>
+      <c r="D736" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E736" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F736" s="35"/>
+      <c r="G736" s="9"/>
+    </row>
+    <row r="737" spans="1:7">
+      <c r="A737" s="8"/>
+      <c r="B737" s="8"/>
+      <c r="C737" s="8"/>
+      <c r="D737" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E737" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F737" s="35"/>
+      <c r="G737" s="9"/>
+    </row>
+    <row r="738" spans="1:7">
+      <c r="A738" s="8"/>
+      <c r="B738" s="8"/>
+      <c r="C738" s="8"/>
+      <c r="D738" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E738" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F738" s="35"/>
+      <c r="G738" s="9"/>
+    </row>
+    <row r="739" spans="1:7">
+      <c r="A739" s="8"/>
+      <c r="B739" s="8"/>
+      <c r="C739" s="8"/>
+      <c r="D739" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E739" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F739" s="35"/>
+      <c r="G739" s="9"/>
+    </row>
+    <row r="740" spans="1:7">
+      <c r="A740" s="8"/>
+      <c r="B740" s="8"/>
+      <c r="C740" s="8"/>
+      <c r="D740" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E740" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F740" s="35"/>
+      <c r="G740" s="9"/>
+    </row>
+    <row r="741" spans="1:7">
+      <c r="A741" s="8"/>
+      <c r="B741" s="8"/>
+      <c r="C741" s="8"/>
+      <c r="D741" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E741" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F741" s="37"/>
+      <c r="G741" s="9"/>
+    </row>
+    <row r="742" spans="1:7">
+      <c r="A742" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B742" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C742" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D742" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E742" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F742" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G742" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="743" spans="1:7">
+      <c r="A743" s="8"/>
+      <c r="B743" s="8"/>
+      <c r="C743" s="8"/>
+      <c r="D743" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E743" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F743" s="35"/>
+      <c r="G743" s="9"/>
+    </row>
+    <row r="744" spans="1:7">
+      <c r="A744" s="8"/>
+      <c r="B744" s="8"/>
+      <c r="C744" s="8"/>
+      <c r="D744" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E744" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F744" s="35"/>
+      <c r="G744" s="9"/>
+    </row>
+    <row r="745" spans="1:7">
+      <c r="A745" s="8"/>
+      <c r="B745" s="8"/>
+      <c r="C745" s="8"/>
+      <c r="D745" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E745" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F745" s="35"/>
+      <c r="G745" s="9"/>
+    </row>
+    <row r="746" spans="1:7">
+      <c r="A746" s="8"/>
+      <c r="B746" s="8"/>
+      <c r="C746" s="8"/>
+      <c r="D746" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E746" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F746" s="35"/>
+      <c r="G746" s="9"/>
+    </row>
+    <row r="747" spans="1:7">
+      <c r="A747" s="8"/>
+      <c r="B747" s="8"/>
+      <c r="C747" s="8"/>
+      <c r="D747" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E747" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F747" s="35"/>
+      <c r="G747" s="9"/>
+    </row>
+    <row r="748" spans="1:7">
+      <c r="A748" s="8"/>
+      <c r="B748" s="8"/>
+      <c r="C748" s="8"/>
+      <c r="D748" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E748" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F748" s="37"/>
+      <c r="G748" s="9"/>
+    </row>
+    <row r="749" spans="1:7">
+      <c r="A749" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B749" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="C749" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D749" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E749" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F749" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G749" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="750" spans="1:7">
+      <c r="A750" s="8"/>
+      <c r="B750" s="8"/>
+      <c r="C750" s="8"/>
+      <c r="D750" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E750" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F750" s="35"/>
+      <c r="G750" s="9"/>
+    </row>
+    <row r="751" spans="1:7">
+      <c r="A751" s="8"/>
+      <c r="B751" s="8"/>
+      <c r="C751" s="8"/>
+      <c r="D751" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E751" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F751" s="35"/>
+      <c r="G751" s="9"/>
+    </row>
+    <row r="752" spans="1:7">
+      <c r="A752" s="8"/>
+      <c r="B752" s="8"/>
+      <c r="C752" s="8"/>
+      <c r="D752" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E752" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F752" s="35"/>
+      <c r="G752" s="9"/>
+    </row>
+    <row r="753" spans="1:7">
+      <c r="A753" s="8"/>
+      <c r="B753" s="8"/>
+      <c r="C753" s="8"/>
+      <c r="D753" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E753" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F753" s="35"/>
+      <c r="G753" s="9"/>
+    </row>
+    <row r="754" spans="1:7">
+      <c r="A754" s="8"/>
+      <c r="B754" s="8"/>
+      <c r="C754" s="8"/>
+      <c r="D754" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E754" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F754" s="35"/>
+      <c r="G754" s="9"/>
+    </row>
+    <row r="755" spans="1:7">
+      <c r="A755" s="8"/>
+      <c r="B755" s="8"/>
+      <c r="C755" s="8"/>
+      <c r="D755" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E755" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F755" s="37"/>
+      <c r="G755" s="9"/>
+    </row>
+    <row r="756" spans="1:7">
+      <c r="A756" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B756" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C756" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="D756" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E756" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F756" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G756" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="757" spans="1:7">
+      <c r="A757" s="8"/>
+      <c r="B757" s="8"/>
+      <c r="C757" s="8"/>
+      <c r="D757" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E757" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F757" s="35"/>
+      <c r="G757" s="9"/>
+    </row>
+    <row r="758" spans="1:7">
+      <c r="A758" s="8"/>
+      <c r="B758" s="8"/>
+      <c r="C758" s="8"/>
+      <c r="D758" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E758" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F758" s="35"/>
+      <c r="G758" s="9"/>
+    </row>
+    <row r="759" spans="1:7">
+      <c r="A759" s="8"/>
+      <c r="B759" s="8"/>
+      <c r="C759" s="8"/>
+      <c r="D759" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E759" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F759" s="35"/>
+      <c r="G759" s="9"/>
+    </row>
+    <row r="760" spans="1:7">
+      <c r="A760" s="8"/>
+      <c r="B760" s="8"/>
+      <c r="C760" s="8"/>
+      <c r="D760" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E760" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F760" s="35"/>
+      <c r="G760" s="9"/>
+    </row>
+    <row r="761" spans="1:7">
+      <c r="A761" s="8"/>
+      <c r="B761" s="8"/>
+      <c r="C761" s="8"/>
+      <c r="D761" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E761" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F761" s="35"/>
+      <c r="G761" s="9"/>
+    </row>
+    <row r="762" spans="1:7">
+      <c r="A762" s="8"/>
+      <c r="B762" s="8"/>
+      <c r="C762" s="8"/>
+      <c r="D762" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E762" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F762" s="37"/>
+      <c r="G762" s="9"/>
+    </row>
+    <row r="763" spans="1:7">
+      <c r="A763" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B763" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C763" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D763" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E763" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F763" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G763" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="764" spans="1:7">
+      <c r="A764" s="8"/>
+      <c r="B764" s="8"/>
+      <c r="C764" s="8"/>
+      <c r="D764" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E764" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F764" s="35"/>
+      <c r="G764" s="9"/>
+    </row>
+    <row r="765" spans="1:7">
+      <c r="A765" s="8"/>
+      <c r="B765" s="8"/>
+      <c r="C765" s="8"/>
+      <c r="D765" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E765" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F765" s="35"/>
+      <c r="G765" s="9"/>
+    </row>
+    <row r="766" spans="1:7">
+      <c r="A766" s="8"/>
+      <c r="B766" s="8"/>
+      <c r="C766" s="8"/>
+      <c r="D766" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E766" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F766" s="35"/>
+      <c r="G766" s="9"/>
+    </row>
+    <row r="767" spans="1:7">
+      <c r="A767" s="8"/>
+      <c r="B767" s="8"/>
+      <c r="C767" s="8"/>
+      <c r="D767" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E767" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F767" s="35"/>
+      <c r="G767" s="9"/>
+    </row>
+    <row r="768" spans="1:7">
+      <c r="A768" s="8"/>
+      <c r="B768" s="8"/>
+      <c r="C768" s="8"/>
+      <c r="D768" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E768" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F768" s="35"/>
+      <c r="G768" s="9"/>
+    </row>
+    <row r="769" spans="1:7">
+      <c r="A769" s="8"/>
+      <c r="B769" s="8"/>
+      <c r="C769" s="8"/>
+      <c r="D769" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E769" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F769" s="37"/>
+      <c r="G769" s="9"/>
+    </row>
+    <row r="770" spans="1:7">
+      <c r="A770" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B770" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C770" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="D770" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E770" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F770" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G770" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="771" spans="1:7">
+      <c r="A771" s="8"/>
+      <c r="B771" s="8"/>
+      <c r="C771" s="8"/>
+      <c r="D771" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E771" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F771" s="35"/>
+      <c r="G771" s="9"/>
+    </row>
+    <row r="772" spans="1:7">
+      <c r="A772" s="8"/>
+      <c r="B772" s="8"/>
+      <c r="C772" s="8"/>
+      <c r="D772" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E772" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F772" s="35"/>
+      <c r="G772" s="9"/>
+    </row>
+    <row r="773" spans="1:7">
+      <c r="A773" s="8"/>
+      <c r="B773" s="8"/>
+      <c r="C773" s="8"/>
+      <c r="D773" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E773" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F773" s="35"/>
+      <c r="G773" s="9"/>
+    </row>
+    <row r="774" spans="1:7">
+      <c r="A774" s="8"/>
+      <c r="B774" s="8"/>
+      <c r="C774" s="8"/>
+      <c r="D774" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E774" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F774" s="35"/>
+      <c r="G774" s="9"/>
+    </row>
+    <row r="775" spans="1:7">
+      <c r="A775" s="8"/>
+      <c r="B775" s="8"/>
+      <c r="C775" s="8"/>
+      <c r="D775" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E775" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F775" s="35"/>
+      <c r="G775" s="9"/>
+    </row>
+    <row r="776" spans="1:7">
+      <c r="A776" s="8"/>
+      <c r="B776" s="8"/>
+      <c r="C776" s="8"/>
+      <c r="D776" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E776" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F776" s="37"/>
+      <c r="G776" s="9"/>
+    </row>
+    <row r="777" spans="1:7">
+      <c r="A777" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B777" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C777" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D777" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E777" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F777" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G777" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="778" spans="1:7">
+      <c r="A778" s="8"/>
+      <c r="B778" s="8"/>
+      <c r="C778" s="8"/>
+      <c r="D778" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E778" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F778" s="35"/>
+      <c r="G778" s="9"/>
+    </row>
+    <row r="779" spans="1:7">
+      <c r="A779" s="8"/>
+      <c r="B779" s="8"/>
+      <c r="C779" s="8"/>
+      <c r="D779" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E779" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F779" s="35"/>
+      <c r="G779" s="9"/>
+    </row>
+    <row r="780" spans="1:7">
+      <c r="A780" s="8"/>
+      <c r="B780" s="8"/>
+      <c r="C780" s="8"/>
+      <c r="D780" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E780" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F780" s="35"/>
+      <c r="G780" s="9"/>
+    </row>
+    <row r="781" spans="1:7">
+      <c r="A781" s="8"/>
+      <c r="B781" s="8"/>
+      <c r="C781" s="8"/>
+      <c r="D781" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E781" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F781" s="35"/>
+      <c r="G781" s="9"/>
+    </row>
+    <row r="782" spans="1:7">
+      <c r="A782" s="8"/>
+      <c r="B782" s="8"/>
+      <c r="C782" s="8"/>
+      <c r="D782" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E782" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F782" s="35"/>
+      <c r="G782" s="9"/>
+    </row>
+    <row r="783" spans="1:7">
+      <c r="A783" s="8"/>
+      <c r="B783" s="8"/>
+      <c r="C783" s="8"/>
+      <c r="D783" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E783" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F783" s="37"/>
+      <c r="G783" s="9"/>
+    </row>
+    <row r="784" spans="1:7">
+      <c r="A784" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B784" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C784" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D784" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E784" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F784" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G784" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="785" spans="1:7">
+      <c r="A785" s="8"/>
+      <c r="B785" s="8"/>
+      <c r="C785" s="8"/>
+      <c r="D785" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E785" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F785" s="35"/>
+      <c r="G785" s="9"/>
+    </row>
+    <row r="786" spans="1:7">
+      <c r="A786" s="8"/>
+      <c r="B786" s="8"/>
+      <c r="C786" s="8"/>
+      <c r="D786" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E786" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F786" s="35"/>
+      <c r="G786" s="9"/>
+    </row>
+    <row r="787" spans="1:7">
+      <c r="A787" s="8"/>
+      <c r="B787" s="8"/>
+      <c r="C787" s="8"/>
+      <c r="D787" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E787" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F787" s="35"/>
+      <c r="G787" s="9"/>
+    </row>
+    <row r="788" spans="1:7">
+      <c r="A788" s="8"/>
+      <c r="B788" s="8"/>
+      <c r="C788" s="8"/>
+      <c r="D788" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E788" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F788" s="35"/>
+      <c r="G788" s="9"/>
+    </row>
+    <row r="789" spans="1:7">
+      <c r="A789" s="8"/>
+      <c r="B789" s="8"/>
+      <c r="C789" s="8"/>
+      <c r="D789" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E789" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F789" s="35"/>
+      <c r="G789" s="9"/>
+    </row>
+    <row r="790" spans="1:7">
+      <c r="A790" s="8"/>
+      <c r="B790" s="8"/>
+      <c r="C790" s="8"/>
+      <c r="D790" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E790" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F790" s="37"/>
+      <c r="G790" s="9"/>
+    </row>
+    <row r="791" spans="1:7">
+      <c r="A791" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B791" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C791" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="D791" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E791" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F791" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G791" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="792" spans="1:7">
+      <c r="A792" s="8"/>
+      <c r="B792" s="8"/>
+      <c r="C792" s="8"/>
+      <c r="D792" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E792" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F792" s="35"/>
+      <c r="G792" s="9"/>
+    </row>
+    <row r="793" spans="1:7">
+      <c r="A793" s="8"/>
+      <c r="B793" s="8"/>
+      <c r="C793" s="8"/>
+      <c r="D793" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E793" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F793" s="35"/>
+      <c r="G793" s="9"/>
+    </row>
+    <row r="794" spans="1:7">
+      <c r="A794" s="8"/>
+      <c r="B794" s="8"/>
+      <c r="C794" s="8"/>
+      <c r="D794" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E794" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F794" s="35"/>
+      <c r="G794" s="9"/>
+    </row>
+    <row r="795" spans="1:7">
+      <c r="A795" s="8"/>
+      <c r="B795" s="8"/>
+      <c r="C795" s="8"/>
+      <c r="D795" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E795" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F795" s="35"/>
+      <c r="G795" s="9"/>
+    </row>
+    <row r="796" spans="1:7">
+      <c r="A796" s="8"/>
+      <c r="B796" s="8"/>
+      <c r="C796" s="8"/>
+      <c r="D796" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E796" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F796" s="35"/>
+      <c r="G796" s="9"/>
+    </row>
+    <row r="797" spans="1:7">
+      <c r="A797" s="8"/>
+      <c r="B797" s="8"/>
+      <c r="C797" s="8"/>
+      <c r="D797" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E797" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F797" s="37"/>
+      <c r="G797" s="9"/>
+    </row>
+    <row r="798" spans="1:7">
+      <c r="A798" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B798" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C798" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D798" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E798" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F798" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G798" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="799" spans="1:7">
+      <c r="A799" s="8"/>
+      <c r="B799" s="8"/>
+      <c r="C799" s="8"/>
+      <c r="D799" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E799" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F799" s="35"/>
+      <c r="G799" s="9"/>
+    </row>
+    <row r="800" spans="1:7">
+      <c r="A800" s="8"/>
+      <c r="B800" s="8"/>
+      <c r="C800" s="8"/>
+      <c r="D800" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E800" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F800" s="35"/>
+      <c r="G800" s="9"/>
+    </row>
+    <row r="801" spans="1:7">
+      <c r="A801" s="8"/>
+      <c r="B801" s="8"/>
+      <c r="C801" s="8"/>
+      <c r="D801" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E801" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F801" s="35"/>
+      <c r="G801" s="9"/>
+    </row>
+    <row r="802" spans="1:7">
+      <c r="A802" s="8"/>
+      <c r="B802" s="8"/>
+      <c r="C802" s="8"/>
+      <c r="D802" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E802" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F802" s="35"/>
+      <c r="G802" s="9"/>
+    </row>
+    <row r="803" spans="1:7">
+      <c r="A803" s="8"/>
+      <c r="B803" s="8"/>
+      <c r="C803" s="8"/>
+      <c r="D803" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E803" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F803" s="35"/>
+      <c r="G803" s="9"/>
+    </row>
+    <row r="804" spans="1:7">
+      <c r="A804" s="8"/>
+      <c r="B804" s="8"/>
+      <c r="C804" s="8"/>
+      <c r="D804" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E804" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F804" s="37"/>
+      <c r="G804" s="9"/>
+    </row>
+    <row r="805" spans="1:7">
+      <c r="A805" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B805" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="C805" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="D805" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E805" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F805" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G805" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="806" spans="1:7">
+      <c r="A806" s="8"/>
+      <c r="B806" s="8"/>
+      <c r="C806" s="8"/>
+      <c r="D806" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E806" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F806" s="35"/>
+      <c r="G806" s="9"/>
+    </row>
+    <row r="807" spans="1:7">
+      <c r="A807" s="8"/>
+      <c r="B807" s="8"/>
+      <c r="C807" s="8"/>
+      <c r="D807" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E807" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F807" s="35"/>
+      <c r="G807" s="9"/>
+    </row>
+    <row r="808" spans="1:7">
+      <c r="A808" s="8"/>
+      <c r="B808" s="8"/>
+      <c r="C808" s="8"/>
+      <c r="D808" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E808" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F808" s="35"/>
+      <c r="G808" s="9"/>
+    </row>
+    <row r="809" spans="1:7">
+      <c r="A809" s="8"/>
+      <c r="B809" s="8"/>
+      <c r="C809" s="8"/>
+      <c r="D809" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E809" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F809" s="35"/>
+      <c r="G809" s="9"/>
+    </row>
+    <row r="810" spans="1:7">
+      <c r="A810" s="8"/>
+      <c r="B810" s="8"/>
+      <c r="C810" s="8"/>
+      <c r="D810" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E810" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F810" s="35"/>
+      <c r="G810" s="9"/>
+    </row>
+    <row r="811" spans="1:7">
+      <c r="A811" s="8"/>
+      <c r="B811" s="8"/>
+      <c r="C811" s="8"/>
+      <c r="D811" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E811" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F811" s="37"/>
+      <c r="G811" s="9"/>
+    </row>
+    <row r="812" spans="1:7">
+      <c r="A812" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B812" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C812" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D812" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E812" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F812" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G812" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="813" spans="1:7">
+      <c r="A813" s="8"/>
+      <c r="B813" s="8"/>
+      <c r="C813" s="8"/>
+      <c r="D813" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E813" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F813" s="35"/>
+      <c r="G813" s="9"/>
+    </row>
+    <row r="814" spans="1:7">
+      <c r="A814" s="8"/>
+      <c r="B814" s="8"/>
+      <c r="C814" s="8"/>
+      <c r="D814" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E814" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F814" s="35"/>
+      <c r="G814" s="9"/>
+    </row>
+    <row r="815" spans="1:7">
+      <c r="A815" s="8"/>
+      <c r="B815" s="8"/>
+      <c r="C815" s="8"/>
+      <c r="D815" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E815" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F815" s="35"/>
+      <c r="G815" s="9"/>
+    </row>
+    <row r="816" spans="1:7">
+      <c r="A816" s="8"/>
+      <c r="B816" s="8"/>
+      <c r="C816" s="8"/>
+      <c r="D816" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E816" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F816" s="35"/>
+      <c r="G816" s="9"/>
+    </row>
+    <row r="817" spans="1:7">
+      <c r="A817" s="8"/>
+      <c r="B817" s="8"/>
+      <c r="C817" s="8"/>
+      <c r="D817" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E817" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F817" s="35"/>
+      <c r="G817" s="9"/>
+    </row>
+    <row r="818" spans="1:7">
+      <c r="A818" s="8"/>
+      <c r="B818" s="8"/>
+      <c r="C818" s="8"/>
+      <c r="D818" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E818" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F818" s="37"/>
+      <c r="G818" s="9"/>
+    </row>
+    <row r="819" spans="1:7">
+      <c r="A819" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B819" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C819" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="D819" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E819" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F819" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G819" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="820" spans="1:7">
+      <c r="A820" s="8"/>
+      <c r="B820" s="8"/>
+      <c r="C820" s="8"/>
+      <c r="D820" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E820" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F820" s="35"/>
+      <c r="G820" s="9"/>
+    </row>
+    <row r="821" spans="1:7">
+      <c r="A821" s="8"/>
+      <c r="B821" s="8"/>
+      <c r="C821" s="8"/>
+      <c r="D821" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E821" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F821" s="35"/>
+      <c r="G821" s="9"/>
+    </row>
+    <row r="822" spans="1:7">
+      <c r="A822" s="8"/>
+      <c r="B822" s="8"/>
+      <c r="C822" s="8"/>
+      <c r="D822" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E822" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F822" s="35"/>
+      <c r="G822" s="9"/>
+    </row>
+    <row r="823" spans="1:7">
+      <c r="A823" s="8"/>
+      <c r="B823" s="8"/>
+      <c r="C823" s="8"/>
+      <c r="D823" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E823" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F823" s="35"/>
+      <c r="G823" s="9"/>
+    </row>
+    <row r="824" spans="1:7">
+      <c r="A824" s="8"/>
+      <c r="B824" s="8"/>
+      <c r="C824" s="8"/>
+      <c r="D824" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E824" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F824" s="35"/>
+      <c r="G824" s="9"/>
+    </row>
+    <row r="825" spans="1:7">
+      <c r="A825" s="8"/>
+      <c r="B825" s="8"/>
+      <c r="C825" s="8"/>
+      <c r="D825" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E825" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F825" s="37"/>
+      <c r="G825" s="9"/>
+    </row>
+    <row r="826" spans="1:7">
+      <c r="A826" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B826" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C826" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D826" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E826" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F826" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G826" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="827" spans="1:7">
+      <c r="A827" s="8"/>
+      <c r="B827" s="8"/>
+      <c r="C827" s="8"/>
+      <c r="D827" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E827" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F827" s="35"/>
+      <c r="G827" s="9"/>
+    </row>
+    <row r="828" spans="1:7">
+      <c r="A828" s="8"/>
+      <c r="B828" s="8"/>
+      <c r="C828" s="8"/>
+      <c r="D828" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E828" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F828" s="35"/>
+      <c r="G828" s="9"/>
+    </row>
+    <row r="829" spans="1:7">
+      <c r="A829" s="8"/>
+      <c r="B829" s="8"/>
+      <c r="C829" s="8"/>
+      <c r="D829" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E829" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F829" s="35"/>
+      <c r="G829" s="9"/>
+    </row>
+    <row r="830" spans="1:7">
+      <c r="A830" s="8"/>
+      <c r="B830" s="8"/>
+      <c r="C830" s="8"/>
+      <c r="D830" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E830" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F830" s="35"/>
+      <c r="G830" s="9"/>
+    </row>
+    <row r="831" spans="1:7">
+      <c r="A831" s="8"/>
+      <c r="B831" s="8"/>
+      <c r="C831" s="8"/>
+      <c r="D831" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E831" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F831" s="35"/>
+      <c r="G831" s="9"/>
+    </row>
+    <row r="832" spans="1:7">
+      <c r="A832" s="8"/>
+      <c r="B832" s="8"/>
+      <c r="C832" s="8"/>
+      <c r="D832" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E832" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F832" s="37"/>
+      <c r="G832" s="9"/>
+    </row>
+    <row r="833" spans="1:7">
+      <c r="A833" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B833" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C833" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="D833" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E833" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F833" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G833" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="834" spans="1:7">
+      <c r="A834" s="8"/>
+      <c r="B834" s="8"/>
+      <c r="C834" s="8"/>
+      <c r="D834" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E834" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F834" s="35"/>
+      <c r="G834" s="9"/>
+    </row>
+    <row r="835" spans="1:7">
+      <c r="A835" s="8"/>
+      <c r="B835" s="8"/>
+      <c r="C835" s="8"/>
+      <c r="D835" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E835" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F835" s="35"/>
+      <c r="G835" s="9"/>
+    </row>
+    <row r="836" spans="1:7">
+      <c r="A836" s="8"/>
+      <c r="B836" s="8"/>
+      <c r="C836" s="8"/>
+      <c r="D836" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E836" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F836" s="35"/>
+      <c r="G836" s="9"/>
+    </row>
+    <row r="837" spans="1:7">
+      <c r="A837" s="8"/>
+      <c r="B837" s="8"/>
+      <c r="C837" s="8"/>
+      <c r="D837" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E837" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F837" s="35"/>
+      <c r="G837" s="9"/>
+    </row>
+    <row r="838" spans="1:7">
+      <c r="A838" s="8"/>
+      <c r="B838" s="8"/>
+      <c r="C838" s="8"/>
+      <c r="D838" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E838" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F838" s="35"/>
+      <c r="G838" s="9"/>
+    </row>
+    <row r="839" spans="1:7">
+      <c r="A839" s="8"/>
+      <c r="B839" s="8"/>
+      <c r="C839" s="8"/>
+      <c r="D839" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E839" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F839" s="37"/>
+      <c r="G839" s="9"/>
+    </row>
+    <row r="840" spans="1:7">
+      <c r="A840" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B840" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C840" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D840" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E840" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F840" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G840" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="841" spans="1:7">
+      <c r="A841" s="8"/>
+      <c r="B841" s="8"/>
+      <c r="C841" s="8"/>
+      <c r="D841" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E841" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F841" s="35"/>
+      <c r="G841" s="9"/>
+    </row>
+    <row r="842" spans="1:7">
+      <c r="A842" s="8"/>
+      <c r="B842" s="8"/>
+      <c r="C842" s="8"/>
+      <c r="D842" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E842" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F842" s="35"/>
+      <c r="G842" s="9"/>
+    </row>
+    <row r="843" spans="1:7">
+      <c r="A843" s="8"/>
+      <c r="B843" s="8"/>
+      <c r="C843" s="8"/>
+      <c r="D843" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E843" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F843" s="35"/>
+      <c r="G843" s="9"/>
+    </row>
+    <row r="844" spans="1:7">
+      <c r="A844" s="8"/>
+      <c r="B844" s="8"/>
+      <c r="C844" s="8"/>
+      <c r="D844" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E844" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F844" s="35"/>
+      <c r="G844" s="9"/>
+    </row>
+    <row r="845" spans="1:7">
+      <c r="A845" s="8"/>
+      <c r="B845" s="8"/>
+      <c r="C845" s="8"/>
+      <c r="D845" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E845" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F845" s="35"/>
+      <c r="G845" s="9"/>
+    </row>
+    <row r="846" spans="1:7">
+      <c r="A846" s="8"/>
+      <c r="B846" s="8"/>
+      <c r="C846" s="8"/>
+      <c r="D846" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E846" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F846" s="37"/>
+      <c r="G846" s="9"/>
+    </row>
+    <row r="847" spans="1:7">
+      <c r="A847" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B847" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="C847" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D847" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E847" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F847" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G847" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="848" spans="1:7">
+      <c r="A848" s="8"/>
+      <c r="B848" s="8"/>
+      <c r="C848" s="8"/>
+      <c r="D848" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E848" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F848" s="35"/>
+      <c r="G848" s="9"/>
+    </row>
+    <row r="849" spans="1:7">
+      <c r="A849" s="8"/>
+      <c r="B849" s="8"/>
+      <c r="C849" s="8"/>
+      <c r="D849" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E849" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F849" s="35"/>
+      <c r="G849" s="9"/>
+    </row>
+    <row r="850" spans="1:7">
+      <c r="A850" s="8"/>
+      <c r="B850" s="8"/>
+      <c r="C850" s="8"/>
+      <c r="D850" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E850" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F850" s="35"/>
+      <c r="G850" s="9"/>
+    </row>
+    <row r="851" spans="1:7">
+      <c r="A851" s="8"/>
+      <c r="B851" s="8"/>
+      <c r="C851" s="8"/>
+      <c r="D851" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E851" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F851" s="35"/>
+      <c r="G851" s="9"/>
+    </row>
+    <row r="852" spans="1:7">
+      <c r="A852" s="8"/>
+      <c r="B852" s="8"/>
+      <c r="C852" s="8"/>
+      <c r="D852" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E852" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F852" s="35"/>
+      <c r="G852" s="9"/>
+    </row>
+    <row r="853" spans="1:7">
+      <c r="A853" s="8"/>
+      <c r="B853" s="8"/>
+      <c r="C853" s="8"/>
+      <c r="D853" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E853" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F853" s="37"/>
+      <c r="G853" s="9"/>
+    </row>
+    <row r="854" spans="1:7">
+      <c r="A854" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B854" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="C854" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="D854" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E854" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F854" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G854" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="855" spans="1:7">
+      <c r="A855" s="8"/>
+      <c r="B855" s="8"/>
+      <c r="C855" s="8"/>
+      <c r="D855" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E855" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F855" s="35"/>
+      <c r="G855" s="9"/>
+    </row>
+    <row r="856" spans="1:7">
+      <c r="A856" s="8"/>
+      <c r="B856" s="8"/>
+      <c r="C856" s="8"/>
+      <c r="D856" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E856" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F856" s="35"/>
+      <c r="G856" s="9"/>
+    </row>
+    <row r="857" spans="1:7">
+      <c r="A857" s="8"/>
+      <c r="B857" s="8"/>
+      <c r="C857" s="8"/>
+      <c r="D857" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E857" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F857" s="35"/>
+      <c r="G857" s="9"/>
+    </row>
+    <row r="858" spans="1:7">
+      <c r="A858" s="8"/>
+      <c r="B858" s="8"/>
+      <c r="C858" s="8"/>
+      <c r="D858" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E858" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F858" s="35"/>
+      <c r="G858" s="9"/>
+    </row>
+    <row r="859" spans="1:7">
+      <c r="A859" s="8"/>
+      <c r="B859" s="8"/>
+      <c r="C859" s="8"/>
+      <c r="D859" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E859" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F859" s="35"/>
+      <c r="G859" s="9"/>
+    </row>
+    <row r="860" spans="1:7">
+      <c r="A860" s="8"/>
+      <c r="B860" s="8"/>
+      <c r="C860" s="8"/>
+      <c r="D860" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E860" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F860" s="37"/>
+      <c r="G860" s="9"/>
+    </row>
+    <row r="861" spans="1:7">
+      <c r="A861" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B861" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C861" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="D861" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E861" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F861" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G861" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="862" spans="1:7">
+      <c r="A862" s="8"/>
+      <c r="B862" s="8"/>
+      <c r="C862" s="8"/>
+      <c r="D862" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E862" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F862" s="35"/>
+      <c r="G862" s="9"/>
+    </row>
+    <row r="863" spans="1:7">
+      <c r="A863" s="8"/>
+      <c r="B863" s="8"/>
+      <c r="C863" s="8"/>
+      <c r="D863" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E863" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F863" s="35"/>
+      <c r="G863" s="9"/>
+    </row>
+    <row r="864" spans="1:7">
+      <c r="A864" s="8"/>
+      <c r="B864" s="8"/>
+      <c r="C864" s="8"/>
+      <c r="D864" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E864" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F864" s="35"/>
+      <c r="G864" s="9"/>
+    </row>
+    <row r="865" spans="1:7">
+      <c r="A865" s="8"/>
+      <c r="B865" s="8"/>
+      <c r="C865" s="8"/>
+      <c r="D865" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E865" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F865" s="35"/>
+      <c r="G865" s="9"/>
+    </row>
+    <row r="866" spans="1:7">
+      <c r="A866" s="8"/>
+      <c r="B866" s="8"/>
+      <c r="C866" s="8"/>
+      <c r="D866" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E866" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F866" s="35"/>
+      <c r="G866" s="9"/>
+    </row>
+    <row r="867" spans="1:7">
+      <c r="A867" s="8"/>
+      <c r="B867" s="8"/>
+      <c r="C867" s="8"/>
+      <c r="D867" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E867" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F867" s="37"/>
+      <c r="G867" s="9"/>
+    </row>
+    <row r="868" spans="1:7">
+      <c r="A868" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B868" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C868" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="D868" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E868" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F868" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G868" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="869" spans="1:7">
+      <c r="A869" s="8"/>
+      <c r="B869" s="8"/>
+      <c r="C869" s="8"/>
+      <c r="D869" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E869" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F869" s="35"/>
+      <c r="G869" s="9"/>
+    </row>
+    <row r="870" spans="1:7">
+      <c r="A870" s="8"/>
+      <c r="B870" s="8"/>
+      <c r="C870" s="8"/>
+      <c r="D870" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E870" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F870" s="35"/>
+      <c r="G870" s="9"/>
+    </row>
+    <row r="871" spans="1:7">
+      <c r="A871" s="8"/>
+      <c r="B871" s="8"/>
+      <c r="C871" s="8"/>
+      <c r="D871" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E871" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F871" s="35"/>
+      <c r="G871" s="9"/>
+    </row>
+    <row r="872" spans="1:7">
+      <c r="A872" s="8"/>
+      <c r="B872" s="8"/>
+      <c r="C872" s="8"/>
+      <c r="D872" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E872" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F872" s="35"/>
+      <c r="G872" s="9"/>
+    </row>
+    <row r="873" spans="1:7">
+      <c r="A873" s="8"/>
+      <c r="B873" s="8"/>
+      <c r="C873" s="8"/>
+      <c r="D873" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E873" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F873" s="35"/>
+      <c r="G873" s="9"/>
+    </row>
+    <row r="874" spans="1:7">
+      <c r="A874" s="8"/>
+      <c r="B874" s="8"/>
+      <c r="C874" s="8"/>
+      <c r="D874" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E874" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F874" s="37"/>
+      <c r="G874" s="9"/>
+    </row>
+    <row r="875" spans="1:7">
+      <c r="A875" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B875" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C875" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="D875" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E875" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F875" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G875" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="876" spans="1:7">
+      <c r="A876" s="8"/>
+      <c r="B876" s="8"/>
+      <c r="C876" s="8"/>
+      <c r="D876" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E876" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F876" s="35"/>
+      <c r="G876" s="9"/>
+    </row>
+    <row r="877" spans="1:7">
+      <c r="A877" s="8"/>
+      <c r="B877" s="8"/>
+      <c r="C877" s="8"/>
+      <c r="D877" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E877" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F877" s="35"/>
+      <c r="G877" s="9"/>
+    </row>
+    <row r="878" spans="1:7">
+      <c r="A878" s="8"/>
+      <c r="B878" s="8"/>
+      <c r="C878" s="8"/>
+      <c r="D878" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E878" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F878" s="35"/>
+      <c r="G878" s="9"/>
+    </row>
+    <row r="879" spans="1:7">
+      <c r="A879" s="8"/>
+      <c r="B879" s="8"/>
+      <c r="C879" s="8"/>
+      <c r="D879" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E879" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F879" s="35"/>
+      <c r="G879" s="9"/>
+    </row>
+    <row r="880" spans="1:7">
+      <c r="A880" s="8"/>
+      <c r="B880" s="8"/>
+      <c r="C880" s="8"/>
+      <c r="D880" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E880" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F880" s="35"/>
+      <c r="G880" s="9"/>
+    </row>
+    <row r="881" spans="1:7">
+      <c r="A881" s="8"/>
+      <c r="B881" s="8"/>
+      <c r="C881" s="8"/>
+      <c r="D881" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E881" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F881" s="37"/>
+      <c r="G881" s="9"/>
+    </row>
+    <row r="882" spans="1:7">
+      <c r="A882" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B882" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C882" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D882" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E882" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F882" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G882" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="883" spans="1:7">
+      <c r="A883" s="8"/>
+      <c r="B883" s="8"/>
+      <c r="C883" s="8"/>
+      <c r="D883" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E883" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F883" s="35"/>
+      <c r="G883" s="9"/>
+    </row>
+    <row r="884" spans="1:7">
+      <c r="A884" s="8"/>
+      <c r="B884" s="8"/>
+      <c r="C884" s="8"/>
+      <c r="D884" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E884" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F884" s="35"/>
+      <c r="G884" s="9"/>
+    </row>
+    <row r="885" spans="1:7">
+      <c r="A885" s="8"/>
+      <c r="B885" s="8"/>
+      <c r="C885" s="8"/>
+      <c r="D885" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E885" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F885" s="35"/>
+      <c r="G885" s="9"/>
+    </row>
+    <row r="886" spans="1:7">
+      <c r="A886" s="8"/>
+      <c r="B886" s="8"/>
+      <c r="C886" s="8"/>
+      <c r="D886" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E886" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F886" s="35"/>
+      <c r="G886" s="9"/>
+    </row>
+    <row r="887" spans="1:7">
+      <c r="A887" s="8"/>
+      <c r="B887" s="8"/>
+      <c r="C887" s="8"/>
+      <c r="D887" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E887" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F887" s="35"/>
+      <c r="G887" s="9"/>
+    </row>
+    <row r="888" spans="1:7">
+      <c r="A888" s="8"/>
+      <c r="B888" s="8"/>
+      <c r="C888" s="8"/>
+      <c r="D888" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E888" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F888" s="37"/>
+      <c r="G888" s="9"/>
+    </row>
+    <row r="889" spans="1:7">
+      <c r="A889" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B889" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C889" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D889" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E889" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F889" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G889" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="890" spans="1:7">
+      <c r="A890" s="8"/>
+      <c r="B890" s="8"/>
+      <c r="C890" s="8"/>
+      <c r="D890" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E890" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F890" s="35"/>
+      <c r="G890" s="9"/>
+    </row>
+    <row r="891" spans="1:7">
+      <c r="A891" s="8"/>
+      <c r="B891" s="8"/>
+      <c r="C891" s="8"/>
+      <c r="D891" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E891" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F891" s="35"/>
+      <c r="G891" s="9"/>
+    </row>
+    <row r="892" spans="1:7">
+      <c r="A892" s="8"/>
+      <c r="B892" s="8"/>
+      <c r="C892" s="8"/>
+      <c r="D892" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E892" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F892" s="35"/>
+      <c r="G892" s="9"/>
+    </row>
+    <row r="893" spans="1:7">
+      <c r="A893" s="8"/>
+      <c r="B893" s="8"/>
+      <c r="C893" s="8"/>
+      <c r="D893" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E893" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F893" s="35"/>
+      <c r="G893" s="9"/>
+    </row>
+    <row r="894" spans="1:7">
+      <c r="A894" s="8"/>
+      <c r="B894" s="8"/>
+      <c r="C894" s="8"/>
+      <c r="D894" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E894" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F894" s="35"/>
+      <c r="G894" s="9"/>
+    </row>
+    <row r="895" spans="1:7">
+      <c r="A895" s="8"/>
+      <c r="B895" s="8"/>
+      <c r="C895" s="8"/>
+      <c r="D895" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E895" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F895" s="37"/>
+      <c r="G895" s="9"/>
+    </row>
+    <row r="896" spans="1:7">
+      <c r="A896" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B896" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C896" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D896" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E896" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F896" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G896" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="897" spans="1:7">
+      <c r="A897" s="8"/>
+      <c r="B897" s="8"/>
+      <c r="C897" s="8"/>
+      <c r="D897" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E897" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F897" s="35"/>
+      <c r="G897" s="9"/>
+    </row>
+    <row r="898" spans="1:7">
+      <c r="A898" s="8"/>
+      <c r="B898" s="8"/>
+      <c r="C898" s="8"/>
+      <c r="D898" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E898" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F898" s="35"/>
+      <c r="G898" s="9"/>
+    </row>
+    <row r="899" spans="1:7">
+      <c r="A899" s="8"/>
+      <c r="B899" s="8"/>
+      <c r="C899" s="8"/>
+      <c r="D899" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E899" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F899" s="35"/>
+      <c r="G899" s="9"/>
+    </row>
+    <row r="900" spans="1:7">
+      <c r="A900" s="8"/>
+      <c r="B900" s="8"/>
+      <c r="C900" s="8"/>
+      <c r="D900" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E900" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F900" s="35"/>
+      <c r="G900" s="9"/>
+    </row>
+    <row r="901" spans="1:7">
+      <c r="A901" s="8"/>
+      <c r="B901" s="8"/>
+      <c r="C901" s="8"/>
+      <c r="D901" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E901" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F901" s="35"/>
+      <c r="G901" s="9"/>
+    </row>
+    <row r="902" spans="1:7">
+      <c r="A902" s="8"/>
+      <c r="B902" s="8"/>
+      <c r="C902" s="8"/>
+      <c r="D902" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E902" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F902" s="37"/>
+      <c r="G902" s="9"/>
+    </row>
+    <row r="903" spans="1:7">
+      <c r="A903" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B903" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="C903" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="D903" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E903" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F903" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G903" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="904" spans="1:7">
+      <c r="A904" s="8"/>
+      <c r="B904" s="8"/>
+      <c r="C904" s="8"/>
+      <c r="D904" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E904" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F904" s="35"/>
+      <c r="G904" s="9"/>
+    </row>
+    <row r="905" spans="1:7">
+      <c r="A905" s="8"/>
+      <c r="B905" s="8"/>
+      <c r="C905" s="8"/>
+      <c r="D905" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E905" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F905" s="35"/>
+      <c r="G905" s="9"/>
+    </row>
+    <row r="906" spans="1:7">
+      <c r="A906" s="8"/>
+      <c r="B906" s="8"/>
+      <c r="C906" s="8"/>
+      <c r="D906" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E906" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F906" s="35"/>
+      <c r="G906" s="9"/>
+    </row>
+    <row r="907" spans="1:7">
+      <c r="A907" s="8"/>
+      <c r="B907" s="8"/>
+      <c r="C907" s="8"/>
+      <c r="D907" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E907" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F907" s="35"/>
+      <c r="G907" s="9"/>
+    </row>
+    <row r="908" spans="1:7">
+      <c r="A908" s="8"/>
+      <c r="B908" s="8"/>
+      <c r="C908" s="8"/>
+      <c r="D908" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E908" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F908" s="35"/>
+      <c r="G908" s="9"/>
+    </row>
+    <row r="909" spans="1:7">
+      <c r="A909" s="8"/>
+      <c r="B909" s="8"/>
+      <c r="C909" s="8"/>
+      <c r="D909" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E909" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F909" s="37"/>
+      <c r="G909" s="9"/>
+    </row>
+    <row r="910" spans="1:7">
+      <c r="A910" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B910" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="C910" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="D910" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E910" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F910" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G910" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="911" spans="1:7">
+      <c r="A911" s="8"/>
+      <c r="B911" s="8"/>
+      <c r="C911" s="8"/>
+      <c r="D911" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E911" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F911" s="35"/>
+      <c r="G911" s="9"/>
+    </row>
+    <row r="912" spans="1:7">
+      <c r="A912" s="8"/>
+      <c r="B912" s="8"/>
+      <c r="C912" s="8"/>
+      <c r="D912" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E912" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F912" s="35"/>
+      <c r="G912" s="9"/>
+    </row>
+    <row r="913" spans="1:7">
+      <c r="A913" s="8"/>
+      <c r="B913" s="8"/>
+      <c r="C913" s="8"/>
+      <c r="D913" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E913" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F913" s="35"/>
+      <c r="G913" s="9"/>
+    </row>
+    <row r="914" spans="1:7">
+      <c r="A914" s="8"/>
+      <c r="B914" s="8"/>
+      <c r="C914" s="8"/>
+      <c r="D914" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E914" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F914" s="35"/>
+      <c r="G914" s="9"/>
+    </row>
+    <row r="915" spans="1:7">
+      <c r="A915" s="8"/>
+      <c r="B915" s="8"/>
+      <c r="C915" s="8"/>
+      <c r="D915" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E915" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F915" s="35"/>
+      <c r="G915" s="9"/>
+    </row>
+    <row r="916" spans="1:7">
+      <c r="A916" s="8"/>
+      <c r="B916" s="8"/>
+      <c r="C916" s="8"/>
+      <c r="D916" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E916" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F916" s="37"/>
+      <c r="G916" s="9"/>
+    </row>
+    <row r="917" spans="1:7">
+      <c r="A917" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B917" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="C917" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="D917" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E917" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F917" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G917" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="918" spans="1:7">
+      <c r="A918" s="8"/>
+      <c r="B918" s="8"/>
+      <c r="C918" s="8"/>
+      <c r="D918" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E918" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F918" s="35"/>
+      <c r="G918" s="9"/>
+    </row>
+    <row r="919" spans="1:7">
+      <c r="A919" s="8"/>
+      <c r="B919" s="8"/>
+      <c r="C919" s="8"/>
+      <c r="D919" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E919" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F919" s="35"/>
+      <c r="G919" s="9"/>
+    </row>
+    <row r="920" spans="1:7">
+      <c r="A920" s="8"/>
+      <c r="B920" s="8"/>
+      <c r="C920" s="8"/>
+      <c r="D920" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E920" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F920" s="35"/>
+      <c r="G920" s="9"/>
+    </row>
+    <row r="921" spans="1:7">
+      <c r="A921" s="8"/>
+      <c r="B921" s="8"/>
+      <c r="C921" s="8"/>
+      <c r="D921" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E921" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F921" s="35"/>
+      <c r="G921" s="9"/>
+    </row>
+    <row r="922" spans="1:7">
+      <c r="A922" s="8"/>
+      <c r="B922" s="8"/>
+      <c r="C922" s="8"/>
+      <c r="D922" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E922" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F922" s="35"/>
+      <c r="G922" s="9"/>
+    </row>
+    <row r="923" spans="1:7">
+      <c r="A923" s="8"/>
+      <c r="B923" s="8"/>
+      <c r="C923" s="8"/>
+      <c r="D923" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E923" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F923" s="37"/>
+      <c r="G923" s="9"/>
+    </row>
+    <row r="924" spans="1:7">
+      <c r="A924" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B924" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="C924" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D924" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E924" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F924" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G924" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="925" spans="1:7">
+      <c r="A925" s="8"/>
+      <c r="B925" s="8"/>
+      <c r="C925" s="8"/>
+      <c r="D925" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E925" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F925" s="35"/>
+      <c r="G925" s="9"/>
+    </row>
+    <row r="926" spans="1:7">
+      <c r="A926" s="8"/>
+      <c r="B926" s="8"/>
+      <c r="C926" s="8"/>
+      <c r="D926" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E926" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F926" s="35"/>
+      <c r="G926" s="9"/>
+    </row>
+    <row r="927" spans="1:7">
+      <c r="A927" s="8"/>
+      <c r="B927" s="8"/>
+      <c r="C927" s="8"/>
+      <c r="D927" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E927" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F927" s="35"/>
+      <c r="G927" s="9"/>
+    </row>
+    <row r="928" spans="1:7">
+      <c r="A928" s="8"/>
+      <c r="B928" s="8"/>
+      <c r="C928" s="8"/>
+      <c r="D928" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E928" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F928" s="35"/>
+      <c r="G928" s="9"/>
+    </row>
+    <row r="929" spans="1:7">
+      <c r="A929" s="8"/>
+      <c r="B929" s="8"/>
+      <c r="C929" s="8"/>
+      <c r="D929" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E929" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F929" s="35"/>
+      <c r="G929" s="9"/>
+    </row>
+    <row r="930" spans="1:7">
+      <c r="A930" s="8"/>
+      <c r="B930" s="8"/>
+      <c r="C930" s="8"/>
+      <c r="D930" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E930" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F930" s="37"/>
+      <c r="G930" s="9"/>
+    </row>
+    <row r="931" spans="1:7">
+      <c r="A931" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B931" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="C931" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D931" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E931" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F931" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G931" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="932" spans="1:7">
+      <c r="A932" s="8"/>
+      <c r="B932" s="8"/>
+      <c r="C932" s="8"/>
+      <c r="D932" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E932" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F932" s="35"/>
+      <c r="G932" s="9"/>
+    </row>
+    <row r="933" spans="1:7">
+      <c r="A933" s="8"/>
+      <c r="B933" s="8"/>
+      <c r="C933" s="8"/>
+      <c r="D933" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E933" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F933" s="35"/>
+      <c r="G933" s="9"/>
+    </row>
+    <row r="934" spans="1:7">
+      <c r="A934" s="8"/>
+      <c r="B934" s="8"/>
+      <c r="C934" s="8"/>
+      <c r="D934" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E934" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F934" s="35"/>
+      <c r="G934" s="9"/>
+    </row>
+    <row r="935" spans="1:7">
+      <c r="A935" s="8"/>
+      <c r="B935" s="8"/>
+      <c r="C935" s="8"/>
+      <c r="D935" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E935" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F935" s="35"/>
+      <c r="G935" s="9"/>
+    </row>
+    <row r="936" spans="1:7">
+      <c r="A936" s="8"/>
+      <c r="B936" s="8"/>
+      <c r="C936" s="8"/>
+      <c r="D936" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E936" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F936" s="35"/>
+      <c r="G936" s="9"/>
+    </row>
+    <row r="937" spans="1:7">
+      <c r="A937" s="8"/>
+      <c r="B937" s="8"/>
+      <c r="C937" s="8"/>
+      <c r="D937" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E937" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F937" s="37"/>
+      <c r="G937" s="9"/>
+    </row>
+    <row r="938" spans="1:7">
+      <c r="A938" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B938" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C938" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="D938" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E938" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F938" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G938" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="939" spans="1:7">
+      <c r="A939" s="8"/>
+      <c r="B939" s="8"/>
+      <c r="C939" s="8"/>
+      <c r="D939" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E939" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F939" s="35"/>
+      <c r="G939" s="9"/>
+    </row>
+    <row r="940" spans="1:7">
+      <c r="A940" s="8"/>
+      <c r="B940" s="8"/>
+      <c r="C940" s="8"/>
+      <c r="D940" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E940" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F940" s="35"/>
+      <c r="G940" s="9"/>
+    </row>
+    <row r="941" spans="1:7">
+      <c r="A941" s="8"/>
+      <c r="B941" s="8"/>
+      <c r="C941" s="8"/>
+      <c r="D941" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E941" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F941" s="35"/>
+      <c r="G941" s="9"/>
+    </row>
+    <row r="942" spans="1:7">
+      <c r="A942" s="8"/>
+      <c r="B942" s="8"/>
+      <c r="C942" s="8"/>
+      <c r="D942" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E942" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F942" s="35"/>
+      <c r="G942" s="9"/>
+    </row>
+    <row r="943" spans="1:7">
+      <c r="A943" s="8"/>
+      <c r="B943" s="8"/>
+      <c r="C943" s="8"/>
+      <c r="D943" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E943" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F943" s="35"/>
+      <c r="G943" s="9"/>
+    </row>
+    <row r="944" spans="1:7">
+      <c r="A944" s="8"/>
+      <c r="B944" s="8"/>
+      <c r="C944" s="8"/>
+      <c r="D944" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E944" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F944" s="37"/>
+      <c r="G944" s="9"/>
+    </row>
+    <row r="945" spans="1:7">
+      <c r="A945" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B945" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C945" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D945" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E945" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F945" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G945" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="946" spans="1:7">
+      <c r="A946" s="8"/>
+      <c r="B946" s="8"/>
+      <c r="C946" s="8"/>
+      <c r="D946" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E946" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F946" s="35"/>
+      <c r="G946" s="9"/>
+    </row>
+    <row r="947" spans="1:7">
+      <c r="A947" s="8"/>
+      <c r="B947" s="8"/>
+      <c r="C947" s="8"/>
+      <c r="D947" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E947" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F947" s="35"/>
+      <c r="G947" s="9"/>
+    </row>
+    <row r="948" spans="1:7">
+      <c r="A948" s="8"/>
+      <c r="B948" s="8"/>
+      <c r="C948" s="8"/>
+      <c r="D948" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E948" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F948" s="35"/>
+      <c r="G948" s="9"/>
+    </row>
+    <row r="949" spans="1:7">
+      <c r="A949" s="8"/>
+      <c r="B949" s="8"/>
+      <c r="C949" s="8"/>
+      <c r="D949" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E949" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F949" s="35"/>
+      <c r="G949" s="9"/>
+    </row>
+    <row r="950" spans="1:7">
+      <c r="A950" s="8"/>
+      <c r="B950" s="8"/>
+      <c r="C950" s="8"/>
+      <c r="D950" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E950" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F950" s="35"/>
+      <c r="G950" s="9"/>
+    </row>
+    <row r="951" spans="1:7">
+      <c r="A951" s="8"/>
+      <c r="B951" s="8"/>
+      <c r="C951" s="8"/>
+      <c r="D951" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E951" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F951" s="37"/>
+      <c r="G951" s="9"/>
+    </row>
+    <row r="952" spans="1:7">
+      <c r="A952" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B952" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C952" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D952" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E952" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F952" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G952" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="953" spans="1:7">
+      <c r="A953" s="8"/>
+      <c r="B953" s="8"/>
+      <c r="C953" s="8"/>
+      <c r="D953" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E953" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F953" s="35"/>
+      <c r="G953" s="9"/>
+    </row>
+    <row r="954" spans="1:7">
+      <c r="A954" s="8"/>
+      <c r="B954" s="8"/>
+      <c r="C954" s="8"/>
+      <c r="D954" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E954" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F954" s="35"/>
+      <c r="G954" s="9"/>
+    </row>
+    <row r="955" spans="1:7">
+      <c r="A955" s="8"/>
+      <c r="B955" s="8"/>
+      <c r="C955" s="8"/>
+      <c r="D955" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E955" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F955" s="35"/>
+      <c r="G955" s="9"/>
+    </row>
+    <row r="956" spans="1:7">
+      <c r="A956" s="8"/>
+      <c r="B956" s="8"/>
+      <c r="C956" s="8"/>
+      <c r="D956" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E956" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F956" s="35"/>
+      <c r="G956" s="9"/>
+    </row>
+    <row r="957" spans="1:7">
+      <c r="A957" s="8"/>
+      <c r="B957" s="8"/>
+      <c r="C957" s="8"/>
+      <c r="D957" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E957" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F957" s="35"/>
+      <c r="G957" s="9"/>
+    </row>
+    <row r="958" spans="1:7">
+      <c r="A958" s="8"/>
+      <c r="B958" s="8"/>
+      <c r="C958" s="8"/>
+      <c r="D958" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E958" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F958" s="37"/>
+      <c r="G958" s="9"/>
+    </row>
+    <row r="959" spans="1:7">
+      <c r="A959" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B959" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C959" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="D959" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E959" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F959" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G959" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="960" spans="1:7">
+      <c r="A960" s="8"/>
+      <c r="B960" s="8"/>
+      <c r="C960" s="8"/>
+      <c r="D960" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E960" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F960" s="35"/>
+      <c r="G960" s="9"/>
+    </row>
+    <row r="961" spans="1:7">
+      <c r="A961" s="8"/>
+      <c r="B961" s="8"/>
+      <c r="C961" s="8"/>
+      <c r="D961" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E961" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F961" s="35"/>
+      <c r="G961" s="9"/>
+    </row>
+    <row r="962" spans="1:7">
+      <c r="A962" s="8"/>
+      <c r="B962" s="8"/>
+      <c r="C962" s="8"/>
+      <c r="D962" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E962" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F962" s="35"/>
+      <c r="G962" s="9"/>
+    </row>
+    <row r="963" spans="1:7">
+      <c r="A963" s="8"/>
+      <c r="B963" s="8"/>
+      <c r="C963" s="8"/>
+      <c r="D963" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E963" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F963" s="35"/>
+      <c r="G963" s="9"/>
+    </row>
+    <row r="964" spans="1:7">
+      <c r="A964" s="8"/>
+      <c r="B964" s="8"/>
+      <c r="C964" s="8"/>
+      <c r="D964" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E964" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F964" s="35"/>
+      <c r="G964" s="9"/>
+    </row>
+    <row r="965" spans="1:7">
+      <c r="A965" s="8"/>
+      <c r="B965" s="8"/>
+      <c r="C965" s="8"/>
+      <c r="D965" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E965" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F965" s="37"/>
+      <c r="G965" s="9"/>
+    </row>
+    <row r="966" spans="1:7">
+      <c r="A966" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B966" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C966" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D966" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E966" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F966" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G966" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="967" spans="1:7">
+      <c r="A967" s="8"/>
+      <c r="B967" s="8"/>
+      <c r="C967" s="8"/>
+      <c r="D967" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E967" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F967" s="35"/>
+      <c r="G967" s="9"/>
+    </row>
+    <row r="968" spans="1:7">
+      <c r="A968" s="8"/>
+      <c r="B968" s="8"/>
+      <c r="C968" s="8"/>
+      <c r="D968" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E968" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F968" s="35"/>
+      <c r="G968" s="9"/>
+    </row>
+    <row r="969" spans="1:7">
+      <c r="A969" s="8"/>
+      <c r="B969" s="8"/>
+      <c r="C969" s="8"/>
+      <c r="D969" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E969" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F969" s="35"/>
+      <c r="G969" s="9"/>
+    </row>
+    <row r="970" spans="1:7">
+      <c r="A970" s="8"/>
+      <c r="B970" s="8"/>
+      <c r="C970" s="8"/>
+      <c r="D970" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E970" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F970" s="35"/>
+      <c r="G970" s="9"/>
+    </row>
+    <row r="971" spans="1:7">
+      <c r="A971" s="8"/>
+      <c r="B971" s="8"/>
+      <c r="C971" s="8"/>
+      <c r="D971" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E971" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F971" s="35"/>
+      <c r="G971" s="9"/>
+    </row>
+    <row r="972" spans="1:7">
+      <c r="A972" s="8"/>
+      <c r="B972" s="8"/>
+      <c r="C972" s="8"/>
+      <c r="D972" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E972" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F972" s="37"/>
+      <c r="G972" s="9"/>
+    </row>
+    <row r="973" spans="1:7">
+      <c r="A973" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B973" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="C973" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="D973" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E973" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F973" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G973" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="974" spans="1:7">
+      <c r="A974" s="8"/>
+      <c r="B974" s="8"/>
+      <c r="C974" s="8"/>
+      <c r="D974" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E974" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F974" s="35"/>
+      <c r="G974" s="9"/>
+    </row>
+    <row r="975" spans="1:7">
+      <c r="A975" s="8"/>
+      <c r="B975" s="8"/>
+      <c r="C975" s="8"/>
+      <c r="D975" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E975" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F975" s="35"/>
+      <c r="G975" s="9"/>
+    </row>
+    <row r="976" spans="1:7">
+      <c r="A976" s="8"/>
+      <c r="B976" s="8"/>
+      <c r="C976" s="8"/>
+      <c r="D976" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E976" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F976" s="35"/>
+      <c r="G976" s="9"/>
+    </row>
+    <row r="977" spans="1:7">
+      <c r="A977" s="8"/>
+      <c r="B977" s="8"/>
+      <c r="C977" s="8"/>
+      <c r="D977" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E977" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F977" s="35"/>
+      <c r="G977" s="9"/>
+    </row>
+    <row r="978" spans="1:7">
+      <c r="A978" s="8"/>
+      <c r="B978" s="8"/>
+      <c r="C978" s="8"/>
+      <c r="D978" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E978" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F978" s="35"/>
+      <c r="G978" s="9"/>
+    </row>
+    <row r="979" spans="1:7">
+      <c r="A979" s="8"/>
+      <c r="B979" s="8"/>
+      <c r="C979" s="8"/>
+      <c r="D979" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E979" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F979" s="37"/>
+      <c r="G979" s="9"/>
+    </row>
+    <row r="980" spans="1:7">
+      <c r="A980" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B980" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C980" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="D980" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E980" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F980" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G980" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="981" spans="1:7">
+      <c r="A981" s="8"/>
+      <c r="B981" s="8"/>
+      <c r="C981" s="8"/>
+      <c r="D981" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E981" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F981" s="35"/>
+      <c r="G981" s="9"/>
+    </row>
+    <row r="982" spans="1:7">
+      <c r="A982" s="8"/>
+      <c r="B982" s="8"/>
+      <c r="C982" s="8"/>
+      <c r="D982" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E982" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F982" s="35"/>
+      <c r="G982" s="9"/>
+    </row>
+    <row r="983" spans="1:7">
+      <c r="A983" s="8"/>
+      <c r="B983" s="8"/>
+      <c r="C983" s="8"/>
+      <c r="D983" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E983" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F983" s="35"/>
+      <c r="G983" s="9"/>
+    </row>
+    <row r="984" spans="1:7">
+      <c r="A984" s="8"/>
+      <c r="B984" s="8"/>
+      <c r="C984" s="8"/>
+      <c r="D984" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E984" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F984" s="35"/>
+      <c r="G984" s="9"/>
+    </row>
+    <row r="985" spans="1:7">
+      <c r="A985" s="8"/>
+      <c r="B985" s="8"/>
+      <c r="C985" s="8"/>
+      <c r="D985" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E985" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F985" s="35"/>
+      <c r="G985" s="9"/>
+    </row>
+    <row r="986" spans="1:7">
+      <c r="A986" s="8"/>
+      <c r="B986" s="8"/>
+      <c r="C986" s="8"/>
+      <c r="D986" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E986" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F986" s="37"/>
+      <c r="G986" s="9"/>
+    </row>
+    <row r="987" spans="1:7">
+      <c r="A987" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B987" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="C987" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="D987" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E987" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F987" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G987" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="988" spans="1:7">
+      <c r="A988" s="8"/>
+      <c r="B988" s="8"/>
+      <c r="C988" s="8"/>
+      <c r="D988" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E988" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F988" s="35"/>
+      <c r="G988" s="9"/>
+    </row>
+    <row r="989" spans="1:7">
+      <c r="A989" s="8"/>
+      <c r="B989" s="8"/>
+      <c r="C989" s="8"/>
+      <c r="D989" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E989" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F989" s="35"/>
+      <c r="G989" s="9"/>
+    </row>
+    <row r="990" spans="1:7">
+      <c r="A990" s="8"/>
+      <c r="B990" s="8"/>
+      <c r="C990" s="8"/>
+      <c r="D990" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E990" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F990" s="35"/>
+      <c r="G990" s="9"/>
+    </row>
+    <row r="991" spans="1:7">
+      <c r="A991" s="8"/>
+      <c r="B991" s="8"/>
+      <c r="C991" s="8"/>
+      <c r="D991" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E991" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F991" s="35"/>
+      <c r="G991" s="9"/>
+    </row>
+    <row r="992" spans="1:7">
+      <c r="A992" s="8"/>
+      <c r="B992" s="8"/>
+      <c r="C992" s="8"/>
+      <c r="D992" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E992" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F992" s="35"/>
+      <c r="G992" s="9"/>
+    </row>
+    <row r="993" spans="1:7">
+      <c r="A993" s="8"/>
+      <c r="B993" s="8"/>
+      <c r="C993" s="8"/>
+      <c r="D993" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E993" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F993" s="37"/>
+      <c r="G993" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="442">
+  <mergeCells count="697">
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="A10:A16"/>
     <mergeCell ref="A17:A23"/>
@@ -12367,6 +17835,57 @@
     <mergeCell ref="A616:A622"/>
     <mergeCell ref="A623:A629"/>
     <mergeCell ref="A630:A636"/>
+    <mergeCell ref="A637:A643"/>
+    <mergeCell ref="A644:A650"/>
+    <mergeCell ref="A651:A657"/>
+    <mergeCell ref="A658:A664"/>
+    <mergeCell ref="A665:A671"/>
+    <mergeCell ref="A672:A678"/>
+    <mergeCell ref="A679:A685"/>
+    <mergeCell ref="A686:A692"/>
+    <mergeCell ref="A693:A699"/>
+    <mergeCell ref="A700:A706"/>
+    <mergeCell ref="A707:A713"/>
+    <mergeCell ref="A714:A720"/>
+    <mergeCell ref="A721:A727"/>
+    <mergeCell ref="A728:A734"/>
+    <mergeCell ref="A735:A741"/>
+    <mergeCell ref="A742:A748"/>
+    <mergeCell ref="A749:A755"/>
+    <mergeCell ref="A756:A762"/>
+    <mergeCell ref="A763:A769"/>
+    <mergeCell ref="A770:A776"/>
+    <mergeCell ref="A777:A783"/>
+    <mergeCell ref="A784:A790"/>
+    <mergeCell ref="A791:A797"/>
+    <mergeCell ref="A798:A804"/>
+    <mergeCell ref="A805:A811"/>
+    <mergeCell ref="A812:A818"/>
+    <mergeCell ref="A819:A825"/>
+    <mergeCell ref="A826:A832"/>
+    <mergeCell ref="A833:A839"/>
+    <mergeCell ref="A840:A846"/>
+    <mergeCell ref="A847:A853"/>
+    <mergeCell ref="A854:A860"/>
+    <mergeCell ref="A861:A867"/>
+    <mergeCell ref="A868:A874"/>
+    <mergeCell ref="A875:A881"/>
+    <mergeCell ref="A882:A888"/>
+    <mergeCell ref="A889:A895"/>
+    <mergeCell ref="A896:A902"/>
+    <mergeCell ref="A903:A909"/>
+    <mergeCell ref="A910:A916"/>
+    <mergeCell ref="A917:A923"/>
+    <mergeCell ref="A924:A930"/>
+    <mergeCell ref="A931:A937"/>
+    <mergeCell ref="A938:A944"/>
+    <mergeCell ref="A945:A951"/>
+    <mergeCell ref="A952:A958"/>
+    <mergeCell ref="A959:A965"/>
+    <mergeCell ref="A966:A972"/>
+    <mergeCell ref="A973:A979"/>
+    <mergeCell ref="A980:A986"/>
+    <mergeCell ref="A987:A993"/>
     <mergeCell ref="B3:B9"/>
     <mergeCell ref="B10:B16"/>
     <mergeCell ref="B17:B23"/>
@@ -12455,6 +17974,57 @@
     <mergeCell ref="B616:B622"/>
     <mergeCell ref="B623:B629"/>
     <mergeCell ref="B630:B636"/>
+    <mergeCell ref="B637:B643"/>
+    <mergeCell ref="B644:B650"/>
+    <mergeCell ref="B651:B657"/>
+    <mergeCell ref="B658:B664"/>
+    <mergeCell ref="B665:B671"/>
+    <mergeCell ref="B672:B678"/>
+    <mergeCell ref="B679:B685"/>
+    <mergeCell ref="B686:B692"/>
+    <mergeCell ref="B693:B699"/>
+    <mergeCell ref="B700:B706"/>
+    <mergeCell ref="B707:B713"/>
+    <mergeCell ref="B714:B720"/>
+    <mergeCell ref="B721:B727"/>
+    <mergeCell ref="B728:B734"/>
+    <mergeCell ref="B735:B741"/>
+    <mergeCell ref="B742:B748"/>
+    <mergeCell ref="B749:B755"/>
+    <mergeCell ref="B756:B762"/>
+    <mergeCell ref="B763:B769"/>
+    <mergeCell ref="B770:B776"/>
+    <mergeCell ref="B777:B783"/>
+    <mergeCell ref="B784:B790"/>
+    <mergeCell ref="B791:B797"/>
+    <mergeCell ref="B798:B804"/>
+    <mergeCell ref="B805:B811"/>
+    <mergeCell ref="B812:B818"/>
+    <mergeCell ref="B819:B825"/>
+    <mergeCell ref="B826:B832"/>
+    <mergeCell ref="B833:B839"/>
+    <mergeCell ref="B840:B846"/>
+    <mergeCell ref="B847:B853"/>
+    <mergeCell ref="B854:B860"/>
+    <mergeCell ref="B861:B867"/>
+    <mergeCell ref="B868:B874"/>
+    <mergeCell ref="B875:B881"/>
+    <mergeCell ref="B882:B888"/>
+    <mergeCell ref="B889:B895"/>
+    <mergeCell ref="B896:B902"/>
+    <mergeCell ref="B903:B909"/>
+    <mergeCell ref="B910:B916"/>
+    <mergeCell ref="B917:B923"/>
+    <mergeCell ref="B924:B930"/>
+    <mergeCell ref="B931:B937"/>
+    <mergeCell ref="B938:B944"/>
+    <mergeCell ref="B945:B951"/>
+    <mergeCell ref="B952:B958"/>
+    <mergeCell ref="B959:B965"/>
+    <mergeCell ref="B966:B972"/>
+    <mergeCell ref="B973:B979"/>
+    <mergeCell ref="B980:B986"/>
+    <mergeCell ref="B987:B993"/>
     <mergeCell ref="C3:C9"/>
     <mergeCell ref="C10:C16"/>
     <mergeCell ref="C17:C23"/>
@@ -12543,6 +18113,57 @@
     <mergeCell ref="C616:C622"/>
     <mergeCell ref="C623:C629"/>
     <mergeCell ref="C630:C636"/>
+    <mergeCell ref="C637:C643"/>
+    <mergeCell ref="C644:C650"/>
+    <mergeCell ref="C651:C657"/>
+    <mergeCell ref="C658:C664"/>
+    <mergeCell ref="C665:C671"/>
+    <mergeCell ref="C672:C678"/>
+    <mergeCell ref="C679:C685"/>
+    <mergeCell ref="C686:C692"/>
+    <mergeCell ref="C693:C699"/>
+    <mergeCell ref="C700:C706"/>
+    <mergeCell ref="C707:C713"/>
+    <mergeCell ref="C714:C720"/>
+    <mergeCell ref="C721:C727"/>
+    <mergeCell ref="C728:C734"/>
+    <mergeCell ref="C735:C741"/>
+    <mergeCell ref="C742:C748"/>
+    <mergeCell ref="C749:C755"/>
+    <mergeCell ref="C756:C762"/>
+    <mergeCell ref="C763:C769"/>
+    <mergeCell ref="C770:C776"/>
+    <mergeCell ref="C777:C783"/>
+    <mergeCell ref="C784:C790"/>
+    <mergeCell ref="C791:C797"/>
+    <mergeCell ref="C798:C804"/>
+    <mergeCell ref="C805:C811"/>
+    <mergeCell ref="C812:C818"/>
+    <mergeCell ref="C819:C825"/>
+    <mergeCell ref="C826:C832"/>
+    <mergeCell ref="C833:C839"/>
+    <mergeCell ref="C840:C846"/>
+    <mergeCell ref="C847:C853"/>
+    <mergeCell ref="C854:C860"/>
+    <mergeCell ref="C861:C867"/>
+    <mergeCell ref="C868:C874"/>
+    <mergeCell ref="C875:C881"/>
+    <mergeCell ref="C882:C888"/>
+    <mergeCell ref="C889:C895"/>
+    <mergeCell ref="C896:C902"/>
+    <mergeCell ref="C903:C909"/>
+    <mergeCell ref="C910:C916"/>
+    <mergeCell ref="C917:C923"/>
+    <mergeCell ref="C924:C930"/>
+    <mergeCell ref="C931:C937"/>
+    <mergeCell ref="C938:C944"/>
+    <mergeCell ref="C945:C951"/>
+    <mergeCell ref="C952:C958"/>
+    <mergeCell ref="C959:C965"/>
+    <mergeCell ref="C966:C972"/>
+    <mergeCell ref="C973:C979"/>
+    <mergeCell ref="C980:C986"/>
+    <mergeCell ref="C987:C993"/>
     <mergeCell ref="D273:D274"/>
     <mergeCell ref="E273:E274"/>
     <mergeCell ref="F3:F9"/>
@@ -12633,6 +18254,57 @@
     <mergeCell ref="F616:F622"/>
     <mergeCell ref="F623:F629"/>
     <mergeCell ref="F630:F636"/>
+    <mergeCell ref="F637:F643"/>
+    <mergeCell ref="F644:F650"/>
+    <mergeCell ref="F651:F657"/>
+    <mergeCell ref="F658:F664"/>
+    <mergeCell ref="F665:F671"/>
+    <mergeCell ref="F672:F678"/>
+    <mergeCell ref="F679:F685"/>
+    <mergeCell ref="F686:F692"/>
+    <mergeCell ref="F693:F699"/>
+    <mergeCell ref="F700:F706"/>
+    <mergeCell ref="F707:F713"/>
+    <mergeCell ref="F714:F720"/>
+    <mergeCell ref="F721:F727"/>
+    <mergeCell ref="F728:F734"/>
+    <mergeCell ref="F735:F741"/>
+    <mergeCell ref="F742:F748"/>
+    <mergeCell ref="F749:F755"/>
+    <mergeCell ref="F756:F762"/>
+    <mergeCell ref="F763:F769"/>
+    <mergeCell ref="F770:F776"/>
+    <mergeCell ref="F777:F783"/>
+    <mergeCell ref="F784:F790"/>
+    <mergeCell ref="F791:F797"/>
+    <mergeCell ref="F798:F804"/>
+    <mergeCell ref="F805:F811"/>
+    <mergeCell ref="F812:F818"/>
+    <mergeCell ref="F819:F825"/>
+    <mergeCell ref="F826:F832"/>
+    <mergeCell ref="F833:F839"/>
+    <mergeCell ref="F840:F846"/>
+    <mergeCell ref="F847:F853"/>
+    <mergeCell ref="F854:F860"/>
+    <mergeCell ref="F861:F867"/>
+    <mergeCell ref="F868:F874"/>
+    <mergeCell ref="F875:F881"/>
+    <mergeCell ref="F882:F888"/>
+    <mergeCell ref="F889:F895"/>
+    <mergeCell ref="F896:F902"/>
+    <mergeCell ref="F903:F909"/>
+    <mergeCell ref="F910:F916"/>
+    <mergeCell ref="F917:F923"/>
+    <mergeCell ref="F924:F930"/>
+    <mergeCell ref="F931:F937"/>
+    <mergeCell ref="F938:F944"/>
+    <mergeCell ref="F945:F951"/>
+    <mergeCell ref="F952:F958"/>
+    <mergeCell ref="F959:F965"/>
+    <mergeCell ref="F966:F972"/>
+    <mergeCell ref="F973:F979"/>
+    <mergeCell ref="F980:F986"/>
+    <mergeCell ref="F987:F993"/>
     <mergeCell ref="G3:G9"/>
     <mergeCell ref="G10:G16"/>
     <mergeCell ref="G17:G23"/>
@@ -12721,6 +18393,57 @@
     <mergeCell ref="G616:G622"/>
     <mergeCell ref="G623:G629"/>
     <mergeCell ref="G630:G636"/>
+    <mergeCell ref="G637:G643"/>
+    <mergeCell ref="G644:G650"/>
+    <mergeCell ref="G651:G657"/>
+    <mergeCell ref="G658:G664"/>
+    <mergeCell ref="G665:G671"/>
+    <mergeCell ref="G672:G678"/>
+    <mergeCell ref="G679:G685"/>
+    <mergeCell ref="G686:G692"/>
+    <mergeCell ref="G693:G699"/>
+    <mergeCell ref="G700:G706"/>
+    <mergeCell ref="G707:G713"/>
+    <mergeCell ref="G714:G720"/>
+    <mergeCell ref="G721:G727"/>
+    <mergeCell ref="G728:G734"/>
+    <mergeCell ref="G735:G741"/>
+    <mergeCell ref="G742:G748"/>
+    <mergeCell ref="G749:G755"/>
+    <mergeCell ref="G756:G762"/>
+    <mergeCell ref="G763:G769"/>
+    <mergeCell ref="G770:G776"/>
+    <mergeCell ref="G777:G783"/>
+    <mergeCell ref="G784:G790"/>
+    <mergeCell ref="G791:G797"/>
+    <mergeCell ref="G798:G804"/>
+    <mergeCell ref="G805:G811"/>
+    <mergeCell ref="G812:G818"/>
+    <mergeCell ref="G819:G825"/>
+    <mergeCell ref="G826:G832"/>
+    <mergeCell ref="G833:G839"/>
+    <mergeCell ref="G840:G846"/>
+    <mergeCell ref="G847:G853"/>
+    <mergeCell ref="G854:G860"/>
+    <mergeCell ref="G861:G867"/>
+    <mergeCell ref="G868:G874"/>
+    <mergeCell ref="G875:G881"/>
+    <mergeCell ref="G882:G888"/>
+    <mergeCell ref="G889:G895"/>
+    <mergeCell ref="G896:G902"/>
+    <mergeCell ref="G903:G909"/>
+    <mergeCell ref="G910:G916"/>
+    <mergeCell ref="G917:G923"/>
+    <mergeCell ref="G924:G930"/>
+    <mergeCell ref="G931:G937"/>
+    <mergeCell ref="G938:G944"/>
+    <mergeCell ref="G945:G951"/>
+    <mergeCell ref="G952:G958"/>
+    <mergeCell ref="G959:G965"/>
+    <mergeCell ref="G966:G972"/>
+    <mergeCell ref="G973:G979"/>
+    <mergeCell ref="G980:G986"/>
+    <mergeCell ref="G987:G993"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -42,6 +42,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">数据信息标签字段
 </t>
     </r>
@@ -58,6 +65,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">字段类型
 </t>
     </r>
@@ -104,7 +118,7 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-推理服务器（插Atlas 350 标卡）</t>
+Atlas 350 加速卡</t>
   </si>
   <si>
     <t>Network</t>
@@ -175,6 +189,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -223,28 +243,28 @@
     <t>npu_chip_info_link_status_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口Link状态。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
-  </si>
-  <si>
-    <t>推理服务器（插Atlas 350 标卡 4Pmesh互联）</t>
+    <t>昇腾AI处理器端口Link状态。其中，X为Udie ID，Y为Port ID，在Atlas 350 加速卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
+  </si>
+  <si>
+    <t>Atlas 350 加速卡（4Pmesh互联）</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_rx_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口实时接收速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
+    <t>昇腾AI处理器端口实时接收速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 加速卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_tx_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口实时发送速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
+    <t>昇腾AI处理器端口实时发送速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 加速卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
   </si>
   <si>
     <t>npu_chip_info_link_speed_X_Y</t>
   </si>
   <si>
-    <t>物理端口的速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
+    <t>物理端口的速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 加速卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
   </si>
   <si>
     <t>单位：G</t>
@@ -272,6 +292,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -320,6 +346,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">昇腾AI处理器错误码，X表示错误码的索引。
 当昇腾AI处理器上没有错误码时，不会上报该字段。
 说明：
@@ -428,6 +460,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -486,7 +524,7 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-推理服务器（插Atlas 350 标卡）
+Atlas 350 加速卡
 说明：
 只有Atlas 推理系列产品为板卡功耗，其余产品为昇腾AI处理器功耗。</t>
   </si>
@@ -518,6 +556,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">process_id:
 </t>
     </r>
@@ -614,6 +658,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t>containerName：容器名，输出格式为“</t>
     </r>
     <r>
@@ -652,7 +702,7 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-推理服务器（插Atlas 350 标卡）</t>
+Atlas 350 加速卡</t>
   </si>
   <si>
     <t>container_npu_used_memory</t>
@@ -730,7 +780,7 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-推理服务器（插Atlas 350 标卡）</t>
+Atlas 350 加速卡</t>
   </si>
   <si>
     <t>npu_chip_info_vector_utilization</t>
@@ -745,7 +795,7 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-推理服务器（插Atlas 350 标卡）</t>
+Atlas 350 加速卡</t>
   </si>
   <si>
     <t>RoCE</t>
@@ -836,7 +886,7 @@
 Atlas A3 训练系列产品
 A200I A2 Box 异构组件
 Atlas 800I A2 推理服务器
-推理服务器（插Atlas 350 标卡）</t>
+Atlas 350 加速卡</t>
   </si>
   <si>
     <t>npu_chip_info_hbm_total_memory</t>
@@ -852,6 +902,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为1或0
 </t>
     </r>
@@ -1024,6 +1080,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">pcie_bw_type：向远端写PCIe带宽的统计值
 </t>
     </r>
@@ -1092,6 +1154,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">pcie_bw_type：从远端读PCIe带宽的统计值
 </t>
     </r>
@@ -1160,6 +1228,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">pcie_bw_type：回复远端读操作CPL的带宽的统计值
 </t>
     </r>
@@ -1228,6 +1302,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">pcie_bw_type：接收远端写的PCIe带宽的统计值
 </t>
     </r>
@@ -1296,6 +1376,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">pcie_bw_type：接收远端读的PCIe带宽的统计值
 </t>
     </r>
@@ -1364,6 +1450,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">pcie_bw_type：从远端读收到CPL回复的带宽的统计值
 </t>
     </r>
@@ -1549,7 +1641,7 @@
   </si>
   <si>
     <t>Atlas A3 训练系列产品
-推理服务器（插Atlas 350 标卡）</t>
+Atlas 350 加速卡</t>
   </si>
   <si>
     <t>npu_chip_info_sio_crc_rx_err_cnt</t>
@@ -1568,6 +1660,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -1656,7 +1754,7 @@
     <t>芯片Udie Port链接的光模块Lane数量。X为Udie ID，Y为Port ID。</t>
   </si>
   <si>
-    <t>Atlas 850 服务器</t>
+    <t>Atlas 850 系列硬件产品</t>
   </si>
   <si>
     <t>npu_chip_optical_tx_power_Z_X_Y</t>
@@ -1701,9 +1799,9 @@
     <t>RX侧接收到的IPv4 UB报文数。X为Udie ID，Y为Port ID。</t>
   </si>
   <si>
-    <t>Atlas 350 标卡
-Atlas 850 服务器
-Atlas 950 SuperPoD 超节点</t>
+    <t>Atlas 350 加速卡
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
   </si>
   <si>
     <t>npu_chip_info_ub_ipv6_pkt_cnt_rx_X_Y</t>
@@ -2164,9 +2262,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>
@@ -2177,9 +2275,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -118,7 +118,7 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 加速卡</t>
+Atlas 350 标卡</t>
   </si>
   <si>
     <t>Network</t>
@@ -243,28 +243,28 @@
     <t>npu_chip_info_link_status_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口Link状态。其中，X为Udie ID，Y为Port ID，在Atlas 350 加速卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
-  </si>
-  <si>
-    <t>Atlas 350 加速卡（4Pmesh互联）</t>
+    <t>昇腾AI处理器端口Link状态。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
+  </si>
+  <si>
+    <t>Atlas 350 标卡（4Pmesh互联）</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_rx_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口实时接收速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 加速卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
+    <t>昇腾AI处理器端口实时接收速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_tx_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口实时发送速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 加速卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
+    <t>昇腾AI处理器端口实时发送速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
   </si>
   <si>
     <t>npu_chip_info_link_speed_X_Y</t>
   </si>
   <si>
-    <t>物理端口的速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 加速卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
+    <t>物理端口的速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
   </si>
   <si>
     <t>单位：G</t>
@@ -524,7 +524,7 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 加速卡
+Atlas 350 标卡
 说明：
 只有Atlas 推理系列产品为板卡功耗，其余产品为昇腾AI处理器功耗。</t>
   </si>
@@ -702,7 +702,7 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 加速卡</t>
+Atlas 350 标卡</t>
   </si>
   <si>
     <t>container_npu_used_memory</t>
@@ -780,7 +780,7 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 加速卡</t>
+Atlas 350 标卡</t>
   </si>
   <si>
     <t>npu_chip_info_vector_utilization</t>
@@ -795,7 +795,7 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 加速卡</t>
+Atlas 350 标卡</t>
   </si>
   <si>
     <t>RoCE</t>
@@ -886,7 +886,7 @@
 Atlas A3 训练系列产品
 A200I A2 Box 异构组件
 Atlas 800I A2 推理服务器
-Atlas 350 加速卡</t>
+Atlas 350 标卡</t>
   </si>
   <si>
     <t>npu_chip_info_hbm_total_memory</t>
@@ -1641,7 +1641,7 @@
   </si>
   <si>
     <t>Atlas A3 训练系列产品
-Atlas 350 加速卡</t>
+Atlas 350 标卡</t>
   </si>
   <si>
     <t>npu_chip_info_sio_crc_rx_err_cnt</t>
@@ -1799,7 +1799,7 @@
     <t>RX侧接收到的IPv4 UB报文数。X为Udie ID，Y为Port ID。</t>
   </si>
   <si>
-    <t>Atlas 350 加速卡
+    <t>Atlas 350 标卡
 Atlas 850 系列硬件产品
 Atlas 950 SuperPoD</t>
   </si>
@@ -2262,13 +2262,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="方正兰亭黑简体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -2285,6 +2278,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>
   </fonts>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
     <sheet name="标签数据信息说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$144</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="395">
   <si>
     <t>类别</t>
   </si>
@@ -43,6 +43,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">数据信息标签字段及字段类型
 </t>
     </r>
@@ -90,6 +97,20 @@
 Atlas 350 标卡
 Atlas 850 系列硬件产品
 Atlas 950 SuperPoD</t>
+  </si>
+  <si>
+    <t>nodeBase</t>
+  </si>
+  <si>
+    <t>node_base_info</t>
+  </si>
+  <si>
+    <t>节点基本信息</t>
+  </si>
+  <si>
+    <t>exporterVersion：当前NPU Exporter版本信息。
+字段类型为string。
+driverVersion：驱动版本信息。字段类型为string。</t>
   </si>
   <si>
     <t>Network</t>
@@ -2029,19 +2050,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF252B3A"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2049,6 +2064,12 @@
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF252B3A"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2919,12 +2940,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F143"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:F144"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="42" style="7" customWidth="1"/>
-    <col min="3" max="3" width="32.625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="32.6296296296296" style="7" customWidth="1"/>
     <col min="4" max="4" width="48.25" style="7" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="7" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="7" customWidth="1"/>
@@ -2971,1669 +2992,1669 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="81" customHeight="1" spans="1:6">
-      <c r="A3" s="9" t="s">
+    <row r="3" ht="154" customHeight="1" spans="1:6">
+      <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1" spans="1:6">
+      <c r="A4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" ht="75" spans="1:6">
-      <c r="A4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="82" customHeight="1" spans="1:6">
-      <c r="A5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="5" ht="72" spans="1:6">
+      <c r="A5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="82" customHeight="1" spans="1:6">
+      <c r="A6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="75" spans="1:6">
-      <c r="A6" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="72" spans="1:6">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="75" spans="1:6">
-      <c r="A7" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="B7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" ht="60" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="72" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="5" t="s">
         <v>29</v>
       </c>
+      <c r="C8" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="D8" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="57.6" spans="1:6">
       <c r="A9" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" ht="72" spans="1:6">
+      <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" ht="75" spans="1:6">
-      <c r="A10" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="7" t="s">
+    </row>
+    <row r="11" ht="72" spans="1:6">
+      <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" ht="60" spans="1:6">
-      <c r="A11" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="B11" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" ht="118" customHeight="1" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="57.6" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" ht="118" customHeight="1" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="B13" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" ht="75" spans="1:6">
-      <c r="A13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" ht="210" spans="1:6">
+      <c r="F13" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" ht="72" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="201.6" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" ht="120" spans="1:6">
-      <c r="A15" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" ht="120" spans="1:6">
+    </row>
+    <row r="16" ht="115.2" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>53</v>
+        <v>19</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" ht="165" spans="1:6">
-      <c r="A17" s="9" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" ht="115.2" spans="1:6">
+      <c r="A17" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="9" t="s">
         <v>55</v>
       </c>
+      <c r="C17" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="D17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="18" ht="120" spans="1:6">
+      <c r="F17" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" ht="158.4" spans="1:6">
       <c r="A18" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="9" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>60</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" ht="123" customHeight="1" spans="1:6">
-      <c r="A19" s="7" t="s">
-        <v>38</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" ht="115.2" spans="1:6">
+      <c r="A19" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="5" t="s">
         <v>62</v>
       </c>
+      <c r="C19" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="D19" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>64</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" ht="132" customHeight="1" spans="1:6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" ht="123" customHeight="1" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" ht="120" spans="1:6">
-      <c r="A21" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" ht="132" customHeight="1" spans="1:6">
+      <c r="A21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" ht="115.2" spans="1:6">
+      <c r="A22" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" ht="120" spans="1:6">
-      <c r="A22" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="B22" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" ht="120" spans="1:6">
-      <c r="A23" s="9" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" ht="115.2" spans="1:6">
+      <c r="A23" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="12" t="s">
         <v>74</v>
       </c>
+      <c r="C23" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="D23" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" ht="90" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" ht="115.2" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" ht="90" spans="1:6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" ht="86.4" spans="1:6">
       <c r="A25" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" ht="120" spans="1:6">
-      <c r="A26" s="4" t="s">
-        <v>38</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" ht="86.4" spans="1:6">
+      <c r="A26" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" ht="120" spans="1:6">
+    </row>
+    <row r="27" ht="115.2" spans="1:6">
       <c r="A27" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" ht="120" spans="1:6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" ht="115.2" spans="1:6">
       <c r="A28" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" ht="115.2" spans="1:6">
+      <c r="A29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" ht="120" spans="1:6">
-      <c r="A29" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="F29" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" ht="39" customHeight="1" spans="1:6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" ht="115.2" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" ht="60" spans="1:6">
-      <c r="A31" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" ht="39" customHeight="1" spans="1:6">
+      <c r="A31" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="12" t="s">
         <v>97</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" ht="75" spans="1:6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" ht="57.6" spans="1:6">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="33" ht="105" spans="1:6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" ht="72" spans="1:6">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" ht="75" spans="1:6">
-      <c r="A34" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="7" t="s">
+    </row>
+    <row r="34" ht="100.8" spans="1:6">
+      <c r="A34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="9" t="s">
         <v>107</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>41</v>
+        <v>19</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" ht="75" spans="1:6">
-      <c r="A35" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="9" t="s">
+    </row>
+    <row r="35" ht="72" spans="1:6">
+      <c r="A35" s="7" t="s">
         <v>109</v>
       </c>
+      <c r="B35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="D35" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" ht="72" spans="1:6">
+      <c r="A36" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>112</v>
       </c>
+      <c r="C36" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="D36" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>83</v>
+        <v>19</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="12" t="s">
-        <v>110</v>
-      </c>
       <c r="B38" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="E38" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" ht="45" spans="1:6">
-      <c r="A39" s="5" t="s">
-        <v>119</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" ht="45" spans="1:6">
+      <c r="F39" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" ht="43.2" spans="1:6">
       <c r="A40" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" ht="43.2" spans="1:6">
+      <c r="A41" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" ht="90" spans="1:6">
-      <c r="A41" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="B41" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1" spans="1:6">
+    </row>
+    <row r="42" ht="86.4" spans="1:6">
       <c r="A42" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A43" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" ht="90" spans="1:6">
-      <c r="A43" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C43" s="12" t="s">
+      <c r="B43" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="44" ht="90" spans="1:6">
+    </row>
+    <row r="44" ht="86.4" spans="1:6">
       <c r="A44" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C44" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="12" t="s">
         <v>135</v>
       </c>
+      <c r="C44" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="D44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>41</v>
+        <v>19</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>137</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="45" ht="90" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" ht="86.4" spans="1:6">
       <c r="A45" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="46" ht="90" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" ht="86.4" spans="1:6">
       <c r="A46" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" ht="90" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" ht="86.4" spans="1:6">
       <c r="A47" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="48" ht="102" customHeight="1" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" ht="86.4" spans="1:6">
       <c r="A48" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" ht="90" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" ht="102" customHeight="1" spans="1:6">
       <c r="A49" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" ht="33" customHeight="1" spans="1:6">
-      <c r="A50" s="5" t="s">
-        <v>146</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" ht="86.4" spans="1:6">
+      <c r="A50" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="51" ht="29" customHeight="1" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" ht="33" customHeight="1" spans="1:6">
       <c r="A51" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" ht="29" customHeight="1" spans="1:6">
+      <c r="A52" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="52" ht="45" spans="1:6">
-      <c r="A52" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="C52" s="13" t="s">
+      <c r="B52" s="5" t="s">
         <v>154</v>
       </c>
+      <c r="C52" s="5" t="s">
+        <v>155</v>
+      </c>
       <c r="D52" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>155</v>
+        <v>19</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" ht="45" spans="1:6">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" ht="43.2" spans="1:6">
       <c r="A53" s="13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B53" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="54" ht="45" spans="1:6">
+    </row>
+    <row r="54" ht="43.2" spans="1:6">
       <c r="A54" s="13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="55" ht="29" customHeight="1" spans="1:6">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" ht="43.2" spans="1:6">
       <c r="A55" s="13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C55" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>158</v>
-      </c>
       <c r="F55" s="10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="56" ht="45" spans="1:6">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" ht="29" customHeight="1" spans="1:6">
       <c r="A56" s="13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="57" ht="35" customHeight="1" spans="1:6">
-      <c r="A57" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="C57" s="5" t="s">
         <v>167</v>
       </c>
+    </row>
+    <row r="57" ht="43.2" spans="1:6">
+      <c r="A57" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="D57" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>41</v>
+        <v>19</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>162</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="58" ht="45" spans="1:6">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" ht="35" customHeight="1" spans="1:6">
       <c r="A58" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>169</v>
+        <v>150</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" ht="43.2" spans="1:6">
+      <c r="A59" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="B59" s="5" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="59" ht="45" spans="1:6">
-      <c r="A59" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="E59" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" ht="43.2" spans="1:6">
+      <c r="A60" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="60" ht="45" spans="1:6">
-      <c r="A60" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="B60" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="F60" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E60" s="5" t="s">
+    </row>
+    <row r="61" ht="43.2" spans="1:6">
+      <c r="A61" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F60" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="61" ht="45" spans="1:6">
-      <c r="A61" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="B61" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E61" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" ht="43.2" spans="1:6">
+      <c r="A62" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="62" ht="45" spans="1:6">
-      <c r="A62" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="B62" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E62" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="63" ht="43.2" spans="1:6">
+      <c r="A63" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F62" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="63" ht="45" spans="1:6">
-      <c r="A63" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="B63" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E63" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" ht="43.2" spans="1:6">
+      <c r="A64" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="64" ht="75" spans="1:6">
-      <c r="A64" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="B64" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" ht="75" spans="1:6">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" ht="72" spans="1:6">
       <c r="A65" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" ht="72" spans="1:6">
       <c r="A66" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" ht="72" spans="1:6">
       <c r="A67" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" ht="72" spans="1:6">
       <c r="A68" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" ht="72" spans="1:6">
       <c r="A69" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" ht="72" spans="1:6">
       <c r="A70" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" ht="72" spans="1:6">
       <c r="A71" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" ht="72" spans="1:6">
       <c r="A72" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" ht="72" spans="1:6">
       <c r="A73" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" ht="75" customHeight="1" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" ht="72" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" ht="75" customHeight="1" spans="1:6">
       <c r="A75" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" ht="72" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" ht="72" spans="1:6">
       <c r="A77" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" ht="72" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" ht="72" spans="1:6">
       <c r="A79" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" ht="72" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" ht="75" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" ht="72" spans="1:6">
       <c r="A81" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" ht="27" customHeight="1" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" ht="72" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" ht="30" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" ht="27" customHeight="1" spans="1:6">
       <c r="A83" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="C83" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>224</v>
       </c>
+      <c r="C83" s="5" t="s">
+        <v>225</v>
+      </c>
       <c r="D83" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="84" ht="30" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" ht="28.8" spans="1:6">
       <c r="A84" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B84" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="85" ht="28.8" spans="1:6">
+      <c r="A85" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C84" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="85" ht="75" spans="1:6">
-      <c r="A85" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C85" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="F85" s="10" t="s">
+    </row>
+    <row r="86" ht="72" spans="1:6">
+      <c r="A86" s="5" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="86" ht="75" spans="1:6">
-      <c r="A86" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>233</v>
@@ -4642,1153 +4663,1173 @@
         <v>234</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E86" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="12" t="s">
         <v>235</v>
       </c>
       <c r="F86" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="87" ht="72" spans="1:6">
+      <c r="A87" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="87" ht="75" spans="1:6">
-      <c r="A87" s="5" t="s">
-        <v>228</v>
-      </c>
       <c r="B87" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F87" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F87" s="10" t="s">
+    </row>
+    <row r="88" ht="72" spans="1:6">
+      <c r="A88" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="88" ht="75" spans="1:6">
-      <c r="A88" s="5" t="s">
-        <v>228</v>
-      </c>
       <c r="B88" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C88" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="D88" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>240</v>
-      </c>
       <c r="F88" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="89" ht="72" spans="1:6">
+      <c r="A89" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="89" ht="75" spans="1:6">
-      <c r="A89" s="5" t="s">
-        <v>228</v>
-      </c>
       <c r="B89" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F89" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="90" ht="72" spans="1:6">
+      <c r="A90" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="90" ht="30" spans="1:6">
-      <c r="A90" s="5" t="s">
-        <v>228</v>
-      </c>
       <c r="B90" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>41</v>
+        <v>247</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="91" ht="45" spans="1:6">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="91" ht="28.8" spans="1:6">
       <c r="A91" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>235</v>
+        <v>45</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="92" ht="60" spans="1:6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="92" ht="43.2" spans="1:6">
       <c r="A92" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C92" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F92" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="93" ht="90" spans="1:6">
-      <c r="A93" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>252</v>
+    </row>
+    <row r="93" ht="57.6" spans="1:6">
+      <c r="A93" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F93" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="94" ht="90" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="94" ht="86.4" spans="1:6">
       <c r="A94" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>255</v>
+        <v>87</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="95" ht="90" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="95" ht="86.4" spans="1:6">
       <c r="A95" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>83</v>
+        <v>259</v>
       </c>
       <c r="F95" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="96" ht="45" spans="1:6">
-      <c r="A96" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C96" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="96" ht="86.4" spans="1:6">
+      <c r="A96" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B96" s="9" t="s">
         <v>260</v>
       </c>
+      <c r="C96" s="9" t="s">
+        <v>261</v>
+      </c>
       <c r="D96" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="97" ht="45" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="97" ht="43.2" spans="1:6">
       <c r="A97" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="98" ht="43.2" spans="1:6">
+      <c r="A98" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C97" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="98" ht="45" spans="1:6">
-      <c r="A98" s="5" t="s">
-        <v>258</v>
-      </c>
       <c r="B98" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C98" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F98" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="99" ht="45" spans="1:6">
+    </row>
+    <row r="99" ht="43.2" spans="1:6">
       <c r="A99" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="100" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="100" ht="43.2" spans="1:6">
       <c r="A100" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="101" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="101" ht="43.2" spans="1:6">
       <c r="A101" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="102" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="102" ht="43.2" spans="1:6">
       <c r="A102" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="103" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="103" ht="43.2" spans="1:6">
       <c r="A103" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="104" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="104" ht="43.2" spans="1:6">
       <c r="A104" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="105" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="105" ht="43.2" spans="1:6">
       <c r="A105" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="106" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="106" ht="43.2" spans="1:6">
       <c r="A106" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="107" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="107" ht="43.2" spans="1:6">
       <c r="A107" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="108" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="108" ht="57.6" spans="1:6">
       <c r="A108" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="109" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" ht="43.2" spans="1:6">
       <c r="A109" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="110" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="110" ht="43.2" spans="1:6">
       <c r="A110" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="111" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="111" ht="43.2" spans="1:6">
       <c r="A111" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="112" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="112" ht="43.2" spans="1:6">
       <c r="A112" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="113" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="113" ht="43.2" spans="1:6">
       <c r="A113" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="114" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="114" ht="43.2" spans="1:6">
       <c r="A114" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="115" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="115" ht="43.2" spans="1:6">
       <c r="A115" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="116" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="116" ht="43.2" spans="1:6">
       <c r="A116" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="117" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="117" ht="43.2" spans="1:6">
       <c r="A117" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="118" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="118" ht="43.2" spans="1:6">
       <c r="A118" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="119" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="119" ht="43.2" spans="1:6">
       <c r="A119" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="120" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="120" ht="43.2" spans="1:6">
       <c r="A120" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="121" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="121" ht="43.2" spans="1:6">
       <c r="A121" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="122" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="122" ht="43.2" spans="1:6">
       <c r="A122" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="123" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="123" ht="43.2" spans="1:6">
       <c r="A123" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="124" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="124" ht="43.2" spans="1:6">
       <c r="A124" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="125" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="125" ht="43.2" spans="1:6">
       <c r="A125" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="126" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="126" ht="43.2" spans="1:6">
       <c r="A126" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="127" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="127" ht="43.2" spans="1:6">
       <c r="A127" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="128" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="128" ht="43.2" spans="1:6">
       <c r="A128" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="129" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="129" ht="43.2" spans="1:6">
       <c r="A129" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="130" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="130" ht="43.2" spans="1:6">
       <c r="A130" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="131" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="131" ht="43.2" spans="1:6">
       <c r="A131" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="132" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="132" ht="43.2" spans="1:6">
       <c r="A132" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="133" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="133" ht="43.2" spans="1:6">
       <c r="A133" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="134" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="134" ht="43.2" spans="1:6">
       <c r="A134" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="135" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="135" ht="43.2" spans="1:6">
       <c r="A135" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="136" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="136" ht="43.2" spans="1:6">
       <c r="A136" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="137" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="137" ht="43.2" spans="1:6">
       <c r="A137" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="138" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="138" ht="43.2" spans="1:6">
       <c r="A138" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="139" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="139" ht="43.2" spans="1:6">
       <c r="A139" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="140" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="140" ht="43.2" spans="1:6">
       <c r="A140" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="141" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="141" ht="43.2" spans="1:6">
       <c r="A141" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="142" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="142" ht="43.2" spans="1:6">
       <c r="A142" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="143" ht="45" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="143" ht="43.2" spans="1:6">
       <c r="A143" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="144" ht="43.2" spans="1:6">
+      <c r="A144" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5802,550 +5843,550 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="73.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6296296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="393">
   <si>
     <t>类别</t>
   </si>
@@ -214,28 +214,81 @@
     <t>npu_chip_info_link_status_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口Link状态。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
-  </si>
-  <si>
-    <t>Atlas 350 标卡（4Pmesh互联）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口Link状态。其中，X为Udie ID，Y为Port ID。</t>
+    </r>
+  </si>
+  <si>
+    <t>Atlas 350 标卡（4Pmesh互联）
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_rx_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口实时接收速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口实时接收速率。其中，X为Udie ID，Y为Port ID。使用的-time参数为100。</t>
+    </r>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_tx_X_Y</t>
   </si>
   <si>
-    <t>昇腾AI处理器端口实时发送速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。使用的-time参数为100。</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口实时发送速率。其中，X为Udie ID，Y为Port ID。使用的-time参数为100。</t>
+    </r>
   </si>
   <si>
     <t>npu_chip_info_link_speed_X_Y</t>
   </si>
   <si>
-    <t>物理端口的速率。其中，X为Udie ID，Y为Port ID，在Atlas 350 标卡中，Udie ID为0，Port ID取值范围为[4, 6]。</t>
+    <t>物理端口的速率。其中，X为Udie ID，Y为Port ID。</t>
   </si>
   <si>
     <t>单位：G</t>
@@ -254,16 +307,6 @@
   </si>
   <si>
     <t>单位：个</t>
-  </si>
-  <si>
-    <t>Atlas 训练系列产品
-Atlas A2 训练系列产品
-Atlas A3 训练系列产品
-推理服务器（插Atlas 300I 推理卡）
-Atlas 推理系列产品
-Atlas 800I A2 推理服务器
-A200I A2 Box 异构组件
-Atlas 350 标卡</t>
   </si>
   <si>
     <t>npu_chip_info_network_status</t>
@@ -495,7 +538,8 @@
     <t>单位：瓦特（W）</t>
   </si>
   <si>
-    <t>Atlas 训练系列产品
+    <r>
+      <t>Atlas 训练系列产品
 Atlas A2 训练系列产品
 Atlas A3 训练系列产品
 推理服务器（插Atlas 300I 推理卡）
@@ -503,8 +547,29 @@
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
 Atlas 350 标卡
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD
 说明：
-只有Atlas 推理系列产品为板卡功耗，其余产品为昇腾AI处理器功耗。</t>
+只有Atlas 推理系列产品为板卡功耗，其余产品为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器功耗。</t>
+    </r>
   </si>
   <si>
     <t>npu_chip_info_temperature</t>
@@ -576,7 +641,9 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡</t>
+Atlas 350 标卡
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
   </si>
   <si>
     <t>container_npu_used_memory</t>
@@ -654,7 +721,9 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡</t>
+Atlas 350 标卡
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
   </si>
   <si>
     <t>npu_chip_info_vector_utilization</t>
@@ -669,7 +738,9 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡</t>
+Atlas 350 标卡
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
   </si>
   <si>
     <t>RoCE</t>
@@ -748,7 +819,9 @@
 Atlas A3 训练系列产品
 A200I A2 Box 异构组件
 Atlas 800I A2 推理服务器
-Atlas 350 标卡</t>
+Atlas 350 标卡
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
   </si>
   <si>
     <t>npu_chip_info_hbm_total_memory</t>
@@ -1098,7 +1171,9 @@
   </si>
   <si>
     <t>Atlas A3 训练系列产品
-Atlas 350 标卡</t>
+Atlas 350 标卡
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
   </si>
   <si>
     <t>npu_chip_info_sio_crc_rx_err_cnt</t>
@@ -1254,11 +1329,6 @@
   </si>
   <si>
     <t>RX侧接收到的IPv4 UB报文数。X为Udie ID，Y为Port ID。</t>
-  </si>
-  <si>
-    <t>Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
   </si>
   <si>
     <t>npu_chip_info_ub_ipv6_pkt_cnt_rx_X_Y</t>
@@ -1901,6 +1971,12 @@
       <sz val="11"/>
       <color rgb="FF252B3A"/>
       <name val="方正兰亭黑简体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2050,13 +2126,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
+      <color rgb="FF252B3A"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2064,12 +2140,6 @@
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF252B3A"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2279,7 +2349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -2328,6 +2398,43 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2448,137 +2555,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2615,11 +2722,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2941,11 +3060,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F144"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="42" style="7" customWidth="1"/>
-    <col min="3" max="3" width="32.6296296296296" style="7" customWidth="1"/>
+    <col min="3" max="3" width="32.6333333333333" style="7" customWidth="1"/>
     <col min="4" max="4" width="48.25" style="7" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="7" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="7" customWidth="1"/>
@@ -3032,7 +3151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="72" spans="1:6">
+    <row r="5" ht="75" spans="1:6">
       <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
@@ -3072,7 +3191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="72" spans="1:6">
+    <row r="7" ht="75" spans="1:6">
       <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
@@ -3092,7 +3211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="72" spans="1:6">
+    <row r="8" ht="75" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -3112,14 +3231,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="57.6" spans="1:6">
+    <row r="9" ht="45" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -3132,14 +3251,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="72" spans="1:6">
+    <row r="10" ht="45" spans="1:6">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="12" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -3152,14 +3271,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="72" spans="1:6">
+    <row r="11" ht="45" spans="1:6">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -3172,7 +3291,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="57.6" spans="1:6">
+    <row r="12" ht="45" spans="1:6">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -3192,11 +3311,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" ht="118" customHeight="1" spans="1:6">
+    <row r="13" ht="159" customHeight="1" spans="1:6">
       <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -3209,39 +3328,39 @@
         <v>46</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" ht="72" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" ht="75" spans="1:6">
       <c r="A14" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" ht="201.6" spans="1:6">
+    <row r="15" ht="210" spans="1:6">
       <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>52</v>
-      </c>
       <c r="D15" s="5" t="s">
         <v>19</v>
       </c>
@@ -3249,19 +3368,19 @@
         <v>45</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" ht="115.2" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" ht="149" customHeight="1" spans="1:6">
       <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="D16" s="5" t="s">
         <v>19</v>
       </c>
@@ -3269,118 +3388,118 @@
         <v>45</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" ht="115.2" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" ht="150" spans="1:6">
       <c r="A17" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="F17" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" ht="158.4" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" ht="195" spans="1:6">
       <c r="A18" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" ht="115.2" spans="1:6">
+    </row>
+    <row r="19" ht="150" spans="1:6">
       <c r="A19" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>64</v>
-      </c>
       <c r="F19" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" ht="123" customHeight="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" ht="153" customHeight="1" spans="1:6">
       <c r="A20" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>68</v>
-      </c>
       <c r="F20" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" ht="132" customHeight="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" ht="151" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="E21" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" ht="115.2" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" ht="150" spans="1:6">
       <c r="A22" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>72</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>73</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>19</v>
@@ -3388,168 +3507,168 @@
       <c r="E22" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" ht="115.2" spans="1:6">
+      <c r="F22" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" ht="150" spans="1:6">
       <c r="A23" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="F23" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" ht="115.2" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" ht="150" spans="1:6">
       <c r="A24" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="E24" s="9" t="s">
         <v>45</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" ht="86.4" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" ht="120" spans="1:6">
       <c r="A25" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="D25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" ht="86.4" spans="1:6">
+    </row>
+    <row r="26" ht="120" spans="1:6">
       <c r="A26" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>84</v>
-      </c>
       <c r="D26" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" ht="115.2" spans="1:6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" ht="150" spans="1:6">
       <c r="A27" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="D27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>87</v>
-      </c>
       <c r="F27" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" ht="115.2" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" ht="150" spans="1:6">
       <c r="A28" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="D28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>90</v>
-      </c>
       <c r="F28" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" ht="115.2" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" ht="150" spans="1:6">
       <c r="A29" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B29" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>92</v>
-      </c>
       <c r="D29" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" ht="115.2" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" ht="150" spans="1:6">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="D30" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" ht="39" customHeight="1" spans="1:6">
@@ -3557,90 +3676,90 @@
         <v>42</v>
       </c>
       <c r="B31" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="D31" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" ht="57.6" spans="1:6">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" ht="60" spans="1:6">
       <c r="A32" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="D32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="33" ht="72" spans="1:6">
+    </row>
+    <row r="33" ht="105" spans="1:6">
       <c r="A33" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B33" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="D33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F33" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" ht="100.8" spans="1:6">
+    </row>
+    <row r="34" ht="135" spans="1:6">
       <c r="A34" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B34" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="D34" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34" s="10" t="s">
+    </row>
+    <row r="35" ht="75" spans="1:6">
+      <c r="A35" s="7" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="35" ht="72" spans="1:6">
-      <c r="A35" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>19</v>
@@ -3652,15 +3771,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" ht="72" spans="1:6">
+    <row r="36" ht="75" spans="1:6">
       <c r="A36" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>19</v>
@@ -3674,274 +3793,274 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="E37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F38" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" ht="45" spans="1:6">
+      <c r="A40" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" ht="43.2" spans="1:6">
-      <c r="A40" s="5" t="s">
+      <c r="B40" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F40" s="11" t="s">
+    </row>
+    <row r="41" ht="45" spans="1:6">
+      <c r="A41" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="41" ht="43.2" spans="1:6">
-      <c r="A41" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" ht="120" spans="1:6">
+      <c r="A42" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" ht="86.4" spans="1:6">
-      <c r="A42" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F42" s="10" t="s">
+    </row>
+    <row r="43" ht="123" customHeight="1" spans="1:6">
+      <c r="A43" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A43" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" ht="120" spans="1:6">
+      <c r="A44" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="44" ht="86.4" spans="1:6">
-      <c r="A44" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="12" t="s">
+      <c r="C44" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="D44" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="12" t="s">
+      <c r="F44" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" ht="120" spans="1:6">
+      <c r="A45" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45" ht="86.4" spans="1:6">
-      <c r="A45" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" ht="120" spans="1:6">
+      <c r="A46" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" ht="86.4" spans="1:6">
-      <c r="A46" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" ht="120" spans="1:6">
+      <c r="A47" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47" ht="86.4" spans="1:6">
-      <c r="A47" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B47" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" ht="120" spans="1:6">
+      <c r="A48" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" ht="86.4" spans="1:6">
-      <c r="A48" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" ht="119" customHeight="1" spans="1:6">
+      <c r="A49" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49" ht="102" customHeight="1" spans="1:6">
-      <c r="A49" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" ht="120" spans="1:6">
+      <c r="A50" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" ht="86.4" spans="1:6">
-      <c r="A50" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="D50" s="5" t="s">
         <v>19</v>
       </c>
@@ -3949,298 +4068,298 @@
         <v>45</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" ht="33" customHeight="1" spans="1:6">
       <c r="A51" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="D51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="52" ht="29" customHeight="1" spans="1:6">
       <c r="A52" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F52" s="10" t="s">
+    </row>
+    <row r="53" ht="45" spans="1:6">
+      <c r="A53" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="14" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="53" ht="43.2" spans="1:6">
-      <c r="A53" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="D53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="9" t="s">
+      <c r="F53" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" ht="45" spans="1:6">
+      <c r="A54" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B54" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="54" ht="43.2" spans="1:6">
-      <c r="A54" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B54" s="13" t="s">
+      <c r="C54" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="D54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="9" t="s">
+      <c r="F54" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" ht="45" spans="1:6">
+      <c r="A55" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="F54" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="55" ht="43.2" spans="1:6">
-      <c r="A55" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B55" s="13" t="s">
+      <c r="C55" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="D55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="56" ht="29" customHeight="1" spans="1:6">
+      <c r="A56" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="56" ht="29" customHeight="1" spans="1:6">
-      <c r="A56" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B56" s="13" t="s">
+      <c r="C56" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="D56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F56" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F56" s="10" t="s">
+    </row>
+    <row r="57" ht="45" spans="1:6">
+      <c r="A57" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="14" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="57" ht="43.2" spans="1:6">
-      <c r="A57" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B57" s="13" t="s">
+      <c r="C57" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C57" s="13" t="s">
-        <v>169</v>
-      </c>
       <c r="D57" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" ht="35" customHeight="1" spans="1:6">
       <c r="A58" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B58" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" ht="45" spans="1:6">
+      <c r="A59" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" ht="43.2" spans="1:6">
-      <c r="A59" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="E59" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F59" s="10" t="s">
+    </row>
+    <row r="60" ht="45" spans="1:6">
+      <c r="A60" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="60" ht="43.2" spans="1:6">
-      <c r="A60" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" ht="45" spans="1:6">
+      <c r="A61" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="C61" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="F61" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F60" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="61" ht="43.2" spans="1:6">
-      <c r="A61" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C61" s="5" t="s">
+    </row>
+    <row r="62" ht="45" spans="1:6">
+      <c r="A62" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="C62" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F62" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="62" ht="43.2" spans="1:6">
-      <c r="A62" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C62" s="5" t="s">
+    </row>
+    <row r="63" ht="45" spans="1:6">
+      <c r="A63" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="C63" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="F63" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F62" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="63" ht="43.2" spans="1:6">
-      <c r="A63" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C63" s="5" t="s">
+    </row>
+    <row r="64" ht="45" spans="1:6">
+      <c r="A64" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="C64" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="F64" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="64" ht="43.2" spans="1:6">
-      <c r="A64" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C64" s="5" t="s">
+    </row>
+    <row r="65" ht="75" spans="1:6">
+      <c r="A65" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="65" ht="72" spans="1:6">
-      <c r="A65" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>19</v>
@@ -4252,15 +4371,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" ht="72" spans="1:6">
+    <row r="66" ht="75" spans="1:6">
       <c r="A66" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>191</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>19</v>
@@ -4272,15 +4391,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" ht="72" spans="1:6">
+    <row r="67" ht="75" spans="1:6">
       <c r="A67" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>19</v>
@@ -4292,15 +4411,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" ht="72" spans="1:6">
+    <row r="68" ht="75" spans="1:6">
       <c r="A68" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>19</v>
@@ -4312,15 +4431,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" ht="72" spans="1:6">
+    <row r="69" ht="75" spans="1:6">
       <c r="A69" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B69" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>197</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>19</v>
@@ -4332,15 +4451,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" ht="72" spans="1:6">
+    <row r="70" ht="75" spans="1:6">
       <c r="A70" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B70" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>19</v>
@@ -4352,15 +4471,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" ht="72" spans="1:6">
+    <row r="71" ht="75" spans="1:6">
       <c r="A71" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B71" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>19</v>
@@ -4372,15 +4491,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" ht="72" spans="1:6">
+    <row r="72" ht="75" spans="1:6">
       <c r="A72" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>19</v>
@@ -4392,15 +4511,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" ht="72" spans="1:6">
+    <row r="73" ht="75" spans="1:6">
       <c r="A73" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B73" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>19</v>
@@ -4412,15 +4531,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" ht="72" spans="1:6">
+    <row r="74" ht="75" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B74" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>19</v>
@@ -4434,13 +4553,13 @@
     </row>
     <row r="75" ht="75" customHeight="1" spans="1:6">
       <c r="A75" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B75" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>19</v>
@@ -4452,15 +4571,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" ht="72" spans="1:6">
+    <row r="76" ht="75" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B76" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>19</v>
@@ -4472,15 +4591,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" ht="72" spans="1:6">
+    <row r="77" ht="75" spans="1:6">
       <c r="A77" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B77" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>19</v>
@@ -4492,15 +4611,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" ht="72" spans="1:6">
+    <row r="78" ht="75" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B78" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>19</v>
@@ -4512,15 +4631,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" ht="72" spans="1:6">
+    <row r="79" ht="75" spans="1:6">
       <c r="A79" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B79" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>19</v>
@@ -4532,15 +4651,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" ht="72" spans="1:6">
+    <row r="80" ht="75" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B80" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>219</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>19</v>
@@ -4552,15 +4671,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" ht="72" spans="1:6">
+    <row r="81" ht="75" spans="1:6">
       <c r="A81" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B81" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>19</v>
@@ -4572,15 +4691,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" ht="72" spans="1:6">
+    <row r="82" ht="75" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B82" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>223</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>19</v>
@@ -4594,13 +4713,13 @@
     </row>
     <row r="83" ht="27" customHeight="1" spans="1:6">
       <c r="A83" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B83" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>225</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>19</v>
@@ -4612,1227 +4731,1136 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" ht="28.8" spans="1:6">
+    <row r="84" ht="60" customHeight="1" spans="1:6">
       <c r="A84" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B84" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="D84" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F84" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="D84" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F84" s="10" t="s">
+    </row>
+    <row r="85" ht="60" spans="1:6">
+      <c r="A85" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B85" s="13" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="85" ht="28.8" spans="1:6">
-      <c r="A85" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B85" s="12" t="s">
+      <c r="C85" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="D85" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="86" ht="75" spans="1:6">
+      <c r="A86" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D85" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="86" ht="72" spans="1:6">
-      <c r="A86" s="5" t="s">
+      <c r="B86" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="D86" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="12" t="s">
+      <c r="F86" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="F86" s="10" t="s">
+    </row>
+    <row r="87" ht="75" spans="1:6">
+      <c r="A87" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="87" ht="72" spans="1:6">
-      <c r="A87" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B87" s="5" t="s">
+      <c r="C87" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="D87" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D87" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87" s="5" t="s">
+      <c r="F87" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="88" ht="75" spans="1:6">
+      <c r="A88" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="88" ht="72" spans="1:6">
-      <c r="A88" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B88" s="5" t="s">
+      <c r="C88" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="D88" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="89" ht="75" spans="1:6">
+      <c r="A89" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D88" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="89" ht="72" spans="1:6">
-      <c r="A89" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B89" s="5" t="s">
+      <c r="C89" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="D89" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D89" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E89" s="5" t="s">
+      <c r="F89" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="90" ht="75" spans="1:6">
+      <c r="A90" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F89" s="10" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="90" ht="72" spans="1:6">
-      <c r="A90" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B90" s="5" t="s">
+      <c r="C90" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="D90" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D90" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="5" t="s">
+      <c r="F90" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="91" ht="30" spans="1:6">
+      <c r="A91" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F90" s="10" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="91" ht="28.8" spans="1:6">
-      <c r="A91" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="D91" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F91" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F91" s="10" t="s">
+    </row>
+    <row r="92" ht="45" spans="1:6">
+      <c r="A92" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B92" s="5" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="92" ht="43.2" spans="1:6">
-      <c r="A92" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B92" s="5" t="s">
+      <c r="C92" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="D92" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="93" ht="60" spans="1:6">
+      <c r="A93" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="93" ht="57.6" spans="1:6">
-      <c r="A93" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B93" s="5" t="s">
+      <c r="C93" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="D93" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="94" ht="120" spans="1:6">
+      <c r="A94" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B94" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="D93" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="94" ht="86.4" spans="1:6">
-      <c r="A94" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B94" s="9" t="s">
+      <c r="C94" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="D94" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="95" ht="120" spans="1:6">
+      <c r="A95" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B95" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="D94" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="95" ht="86.4" spans="1:6">
-      <c r="A95" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B95" s="9" t="s">
+      <c r="C95" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="C95" s="9" t="s">
+      <c r="D95" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="9" t="s">
+      <c r="F95" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="96" ht="120" spans="1:6">
+      <c r="A96" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B96" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="F95" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="96" ht="86.4" spans="1:6">
-      <c r="A96" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B96" s="9" t="s">
+      <c r="C96" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="C96" s="9" t="s">
+      <c r="D96" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="97" ht="30" spans="1:6">
+      <c r="A97" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="D96" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F96" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="97" ht="43.2" spans="1:6">
-      <c r="A97" s="5" t="s">
+      <c r="B97" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="C97" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="D97" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="98" ht="30" spans="1:6">
+      <c r="A98" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B98" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F97" s="10" t="s">
+      <c r="C98" s="5" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="98" ht="43.2" spans="1:6">
-      <c r="A98" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B98" s="5" t="s">
+      <c r="D98" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F98" s="16"/>
+    </row>
+    <row r="99" ht="30" spans="1:6">
+      <c r="A99" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C99" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="99" ht="43.2" spans="1:6">
-      <c r="A99" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B99" s="5" t="s">
+      <c r="D99" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F99" s="16"/>
+    </row>
+    <row r="100" ht="30" spans="1:6">
+      <c r="A100" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="C100" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="100" ht="43.2" spans="1:6">
-      <c r="A100" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B100" s="5" t="s">
+      <c r="D100" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F100" s="16"/>
+    </row>
+    <row r="101" ht="30" spans="1:6">
+      <c r="A101" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C101" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D100" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="101" ht="43.2" spans="1:6">
-      <c r="A101" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B101" s="5" t="s">
+      <c r="D101" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F101" s="16"/>
+    </row>
+    <row r="102" ht="30" spans="1:6">
+      <c r="A102" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C101" s="5" t="s">
+      <c r="C102" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D101" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F101" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="102" ht="43.2" spans="1:6">
-      <c r="A102" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B102" s="5" t="s">
+      <c r="D102" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F102" s="16"/>
+    </row>
+    <row r="103" ht="30" spans="1:6">
+      <c r="A103" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C103" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="103" ht="43.2" spans="1:6">
-      <c r="A103" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B103" s="5" t="s">
+      <c r="D103" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" s="16"/>
+    </row>
+    <row r="104" ht="30" spans="1:6">
+      <c r="A104" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="C104" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F103" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="104" ht="43.2" spans="1:6">
-      <c r="A104" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B104" s="5" t="s">
+      <c r="D104" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F104" s="16"/>
+    </row>
+    <row r="105" ht="30" spans="1:6">
+      <c r="A105" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C105" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F104" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="105" ht="43.2" spans="1:6">
-      <c r="A105" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B105" s="5" t="s">
+      <c r="D105" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F105" s="16"/>
+    </row>
+    <row r="106" ht="30" spans="1:6">
+      <c r="A106" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="C106" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D105" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F105" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="106" ht="43.2" spans="1:6">
-      <c r="A106" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B106" s="5" t="s">
+      <c r="D106" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F106" s="16"/>
+    </row>
+    <row r="107" ht="30" spans="1:6">
+      <c r="A107" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C107" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="D106" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F106" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="107" ht="43.2" spans="1:6">
-      <c r="A107" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B107" s="5" t="s">
+      <c r="D107" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F107" s="16"/>
+    </row>
+    <row r="108" ht="45" spans="1:6">
+      <c r="A108" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B108" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="C108" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="D107" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="108" ht="57.6" spans="1:6">
-      <c r="A108" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B108" s="5" t="s">
+      <c r="D108" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F108" s="16"/>
+    </row>
+    <row r="109" ht="45" spans="1:6">
+      <c r="A109" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B109" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="C109" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="D108" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F108" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="109" ht="43.2" spans="1:6">
-      <c r="A109" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B109" s="5" t="s">
+      <c r="D109" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F109" s="16"/>
+    </row>
+    <row r="110" ht="45" spans="1:6">
+      <c r="A110" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C109" s="5" t="s">
+      <c r="C110" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D109" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F109" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="110" ht="43.2" spans="1:6">
-      <c r="A110" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B110" s="5" t="s">
+      <c r="D110" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F110" s="16"/>
+    </row>
+    <row r="111" ht="45" spans="1:6">
+      <c r="A111" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="C111" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="D110" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F110" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="111" ht="43.2" spans="1:6">
-      <c r="A111" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B111" s="5" t="s">
+      <c r="D111" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F111" s="16"/>
+    </row>
+    <row r="112" ht="45" spans="1:6">
+      <c r="A112" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B112" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="C112" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F111" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="112" ht="43.2" spans="1:6">
-      <c r="A112" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B112" s="5" t="s">
+      <c r="D112" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F112" s="16"/>
+    </row>
+    <row r="113" ht="45" spans="1:6">
+      <c r="A113" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C113" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D112" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F112" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="113" ht="43.2" spans="1:6">
-      <c r="A113" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B113" s="5" t="s">
+      <c r="D113" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F113" s="16"/>
+    </row>
+    <row r="114" ht="45" spans="1:6">
+      <c r="A114" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="C114" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="D113" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F113" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="114" ht="43.2" spans="1:6">
-      <c r="A114" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B114" s="5" t="s">
+      <c r="D114" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F114" s="16"/>
+    </row>
+    <row r="115" ht="45" spans="1:6">
+      <c r="A115" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C115" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="D114" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F114" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="115" ht="43.2" spans="1:6">
-      <c r="A115" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B115" s="5" t="s">
+      <c r="D115" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F115" s="16"/>
+    </row>
+    <row r="116" ht="30" spans="1:6">
+      <c r="A116" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="C116" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="D115" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F115" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="116" ht="43.2" spans="1:6">
-      <c r="A116" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B116" s="5" t="s">
+      <c r="D116" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F116" s="16"/>
+    </row>
+    <row r="117" ht="30" spans="1:6">
+      <c r="A117" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C117" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="D116" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F116" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="117" ht="43.2" spans="1:6">
-      <c r="A117" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B117" s="5" t="s">
+      <c r="D117" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F117" s="16"/>
+    </row>
+    <row r="118" ht="30" spans="1:6">
+      <c r="A118" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="C118" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="D117" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F117" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="118" ht="43.2" spans="1:6">
-      <c r="A118" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B118" s="5" t="s">
+      <c r="D118" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F118" s="16"/>
+    </row>
+    <row r="119" ht="30" spans="1:6">
+      <c r="A119" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C119" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="D118" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F118" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="119" ht="43.2" spans="1:6">
-      <c r="A119" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B119" s="5" t="s">
+      <c r="D119" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F119" s="16"/>
+    </row>
+    <row r="120" ht="30" spans="1:6">
+      <c r="A120" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="C120" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D119" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F119" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="120" ht="43.2" spans="1:6">
-      <c r="A120" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B120" s="5" t="s">
+      <c r="D120" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F120" s="16"/>
+    </row>
+    <row r="121" ht="30" spans="1:6">
+      <c r="A121" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="C121" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="D120" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F120" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="121" ht="43.2" spans="1:6">
-      <c r="A121" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B121" s="5" t="s">
+      <c r="D121" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F121" s="16"/>
+    </row>
+    <row r="122" ht="30" spans="1:6">
+      <c r="A122" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="C121" s="5" t="s">
+      <c r="C122" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="D121" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F121" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="122" ht="43.2" spans="1:6">
-      <c r="A122" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B122" s="5" t="s">
+      <c r="D122" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F122" s="16"/>
+    </row>
+    <row r="123" ht="30" spans="1:6">
+      <c r="A123" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="C123" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="D122" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F122" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="123" ht="43.2" spans="1:6">
-      <c r="A123" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B123" s="5" t="s">
+      <c r="D123" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F123" s="16"/>
+    </row>
+    <row r="124" ht="30" spans="1:6">
+      <c r="A124" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="C124" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D123" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F123" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="124" ht="43.2" spans="1:6">
-      <c r="A124" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B124" s="5" t="s">
+      <c r="D124" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F124" s="16"/>
+    </row>
+    <row r="125" ht="30" spans="1:6">
+      <c r="A125" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="C124" s="5" t="s">
+      <c r="C125" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="D124" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F124" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="125" ht="43.2" spans="1:6">
-      <c r="A125" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B125" s="5" t="s">
+      <c r="D125" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F125" s="16"/>
+    </row>
+    <row r="126" ht="30" spans="1:6">
+      <c r="A126" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B126" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="C126" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="D125" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F125" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="126" ht="43.2" spans="1:6">
-      <c r="A126" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B126" s="5" t="s">
+      <c r="D126" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F126" s="16"/>
+    </row>
+    <row r="127" ht="30" spans="1:6">
+      <c r="A127" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="C127" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="D126" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="127" ht="43.2" spans="1:6">
-      <c r="A127" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B127" s="5" t="s">
+      <c r="D127" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F127" s="16"/>
+    </row>
+    <row r="128" ht="30" spans="1:6">
+      <c r="A128" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B128" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="C128" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F127" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="128" ht="43.2" spans="1:6">
-      <c r="A128" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B128" s="5" t="s">
+      <c r="D128" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F128" s="16"/>
+    </row>
+    <row r="129" ht="30" spans="1:6">
+      <c r="A129" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="C129" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="D128" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F128" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="129" ht="43.2" spans="1:6">
-      <c r="A129" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B129" s="5" t="s">
+      <c r="D129" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F129" s="16"/>
+    </row>
+    <row r="130" ht="30" spans="1:6">
+      <c r="A130" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B130" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="C129" s="5" t="s">
+      <c r="C130" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="D129" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F129" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="130" ht="43.2" spans="1:6">
-      <c r="A130" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B130" s="5" t="s">
+      <c r="D130" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F130" s="16"/>
+    </row>
+    <row r="131" ht="45" spans="1:6">
+      <c r="A131" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B131" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="C131" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F130" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="131" ht="43.2" spans="1:6">
-      <c r="A131" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B131" s="5" t="s">
+      <c r="D131" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F131" s="16"/>
+    </row>
+    <row r="132" ht="30" spans="1:6">
+      <c r="A132" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="C132" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="D131" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F131" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="132" ht="43.2" spans="1:6">
-      <c r="A132" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B132" s="5" t="s">
+      <c r="D132" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F132" s="16"/>
+    </row>
+    <row r="133" ht="30" spans="1:6">
+      <c r="A133" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="C133" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F132" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="133" ht="43.2" spans="1:6">
-      <c r="A133" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B133" s="5" t="s">
+      <c r="D133" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F133" s="16"/>
+    </row>
+    <row r="134" ht="30" spans="1:6">
+      <c r="A134" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B134" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="C134" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F133" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="134" ht="43.2" spans="1:6">
-      <c r="A134" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B134" s="5" t="s">
+      <c r="D134" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F134" s="16"/>
+    </row>
+    <row r="135" ht="30" spans="1:6">
+      <c r="A135" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="C135" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F134" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="135" ht="43.2" spans="1:6">
-      <c r="A135" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B135" s="5" t="s">
+      <c r="D135" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F135" s="16"/>
+    </row>
+    <row r="136" ht="30" spans="1:6">
+      <c r="A136" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B136" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C135" s="5" t="s">
+      <c r="C136" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D135" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F135" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="136" ht="43.2" spans="1:6">
-      <c r="A136" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B136" s="5" t="s">
+      <c r="D136" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F136" s="16"/>
+    </row>
+    <row r="137" ht="30" spans="1:6">
+      <c r="A137" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="C137" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="D136" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F136" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="137" ht="43.2" spans="1:6">
-      <c r="A137" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B137" s="5" t="s">
+      <c r="D137" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F137" s="16"/>
+    </row>
+    <row r="138" ht="30" spans="1:6">
+      <c r="A138" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="C138" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="D137" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F137" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="138" ht="43.2" spans="1:6">
-      <c r="A138" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B138" s="5" t="s">
+      <c r="D138" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F138" s="16"/>
+    </row>
+    <row r="139" ht="30" spans="1:6">
+      <c r="A139" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="C139" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D138" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F138" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="139" ht="43.2" spans="1:6">
-      <c r="A139" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B139" s="5" t="s">
+      <c r="D139" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F139" s="16"/>
+    </row>
+    <row r="140" ht="30" spans="1:6">
+      <c r="A140" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="C140" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="D139" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F139" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="140" ht="43.2" spans="1:6">
-      <c r="A140" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B140" s="5" t="s">
+      <c r="D140" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F140" s="16"/>
+    </row>
+    <row r="141" ht="30" spans="1:6">
+      <c r="A141" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="C141" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="D140" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F140" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="141" ht="43.2" spans="1:6">
-      <c r="A141" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B141" s="5" t="s">
+      <c r="D141" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F141" s="16"/>
+    </row>
+    <row r="142" ht="30" spans="1:6">
+      <c r="A142" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C141" s="5" t="s">
+      <c r="C142" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="D141" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F141" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="142" ht="43.2" spans="1:6">
-      <c r="A142" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B142" s="5" t="s">
+      <c r="D142" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F142" s="16"/>
+    </row>
+    <row r="143" ht="30" spans="1:6">
+      <c r="A143" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C143" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F142" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="143" ht="43.2" spans="1:6">
-      <c r="A143" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B143" s="5" t="s">
+      <c r="D143" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F143" s="16"/>
+    </row>
+    <row r="144" ht="30" spans="1:6">
+      <c r="A144" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B144" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="C144" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="D143" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F143" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="144" ht="43.2" spans="1:6">
-      <c r="A144" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>359</v>
-      </c>
       <c r="D144" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E144" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F144" s="10" t="s">
-        <v>265</v>
-      </c>
+      <c r="F144" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F97:F144"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
   <headerFooter/>
@@ -5843,550 +5871,550 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.6296296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="73.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.8833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>379</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -539,6 +539,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t>Atlas 训练系列产品
 Atlas A2 训练系列产品
 Atlas A3 训练系列产品
@@ -656,7 +662,7 @@
     <t>npu_chip_info_utilization</t>
   </si>
   <si>
-    <t>昇腾AI处理器AI Core利用率</t>
+    <t>昇腾AI处理器AICore利用率</t>
   </si>
   <si>
     <t>单位：%</t>
@@ -665,7 +671,7 @@
     <t>npu_chip_info_aicore_current_freq</t>
   </si>
   <si>
-    <t>昇腾AI处理器的AI Core当前频率</t>
+    <t>昇腾AI处理器的AICore当前频率</t>
   </si>
   <si>
     <t>单位：MHz</t>
@@ -674,7 +680,7 @@
     <t>container_npu_utilization</t>
   </si>
   <si>
-    <t>带有容器信息的NPU的AI Core利用率。
+    <t>带有容器信息的NPU的AICore利用率。
 说明：Telegraf不支持上报该指标。</t>
   </si>
   <si>
@@ -702,7 +708,18 @@
     <t>npu_chip_info_cube_utilization</t>
   </si>
   <si>
-    <t>昇腾AI处理器AI Cube利用率</t>
+    <r>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器AICube利用率</t>
+    </r>
   </si>
   <si>
     <t>Atlas A2 训练系列产品
@@ -729,7 +746,18 @@
     <t>npu_chip_info_vector_utilization</t>
   </si>
   <si>
-    <t>昇腾AI处理器AI Vector利用率</t>
+    <r>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器AIVector利用率</t>
+    </r>
   </si>
   <si>
     <t>Atlas A2 训练系列产品
@@ -764,7 +792,7 @@
     <t>vnpu_pod_aicore_utilization</t>
   </si>
   <si>
-    <t>vNPU的AI Core利用率</t>
+    <t>vNPU的AICore利用率</t>
   </si>
   <si>
     <t>详见“标签数据信息说明”页签中“标签3”</t>
@@ -1289,13 +1317,13 @@
     <t>Atlas 850 系列硬件产品</t>
   </si>
   <si>
-    <t>npu_chip_optical_tx_power_Z_X_Y</t>
+    <t>npu_chip_info_optical_tx_power_Z_X_Y</t>
   </si>
   <si>
     <t>光模块发送功率。Z为Lane的index，取值为[0:3]，X为Udie ID，Y为Port ID。</t>
   </si>
   <si>
-    <t>npu_chip_optical_rx_power_Z_X_Y</t>
+    <t>npu_chip_info_optical_rx_power_Z_X_Y</t>
   </si>
   <si>
     <t>光模块接收功率。Z为Lane的index，取值为[0:3]，X为Udie ID，Y为Port ID。X为Udie ID，Y为Port ID。</t>
@@ -2124,6 +2152,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="方正兰亭黑简体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -2133,13 +2168,6 @@
       <sz val="11"/>
       <color rgb="FF252B3A"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2685,7 +2713,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2727,6 +2755,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3698,7 +3729,7 @@
       <c r="B32" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="14" t="s">
         <v>100</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -3738,7 +3769,7 @@
       <c r="B34" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="14" t="s">
         <v>106</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -4112,13 +4143,13 @@
       </c>
     </row>
     <row r="53" ht="45" spans="1:6">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="15" t="s">
         <v>157</v>
       </c>
       <c r="D53" s="5" t="s">
@@ -4132,13 +4163,13 @@
       </c>
     </row>
     <row r="54" ht="45" spans="1:6">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="15" t="s">
         <v>160</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -4152,13 +4183,13 @@
       </c>
     </row>
     <row r="55" ht="45" spans="1:6">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="15" t="s">
         <v>163</v>
       </c>
       <c r="D55" s="5" t="s">
@@ -4172,13 +4203,13 @@
       </c>
     </row>
     <row r="56" ht="29" customHeight="1" spans="1:6">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="15" t="s">
         <v>165</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -4192,13 +4223,13 @@
       </c>
     </row>
     <row r="57" ht="45" spans="1:6">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="15" t="s">
         <v>168</v>
       </c>
       <c r="D57" s="5" t="s">
@@ -5007,7 +5038,7 @@
       <c r="E97" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F97" s="15" t="s">
+      <c r="F97" s="16" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5027,7 +5058,7 @@
       <c r="E98" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F98" s="16"/>
+      <c r="F98" s="17"/>
     </row>
     <row r="99" ht="30" spans="1:6">
       <c r="A99" s="5" t="s">
@@ -5045,7 +5076,7 @@
       <c r="E99" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F99" s="16"/>
+      <c r="F99" s="17"/>
     </row>
     <row r="100" ht="30" spans="1:6">
       <c r="A100" s="5" t="s">
@@ -5063,7 +5094,7 @@
       <c r="E100" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F100" s="16"/>
+      <c r="F100" s="17"/>
     </row>
     <row r="101" ht="30" spans="1:6">
       <c r="A101" s="5" t="s">
@@ -5081,7 +5112,7 @@
       <c r="E101" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F101" s="16"/>
+      <c r="F101" s="17"/>
     </row>
     <row r="102" ht="30" spans="1:6">
       <c r="A102" s="5" t="s">
@@ -5099,7 +5130,7 @@
       <c r="E102" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F102" s="16"/>
+      <c r="F102" s="17"/>
     </row>
     <row r="103" ht="30" spans="1:6">
       <c r="A103" s="5" t="s">
@@ -5117,7 +5148,7 @@
       <c r="E103" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F103" s="16"/>
+      <c r="F103" s="17"/>
     </row>
     <row r="104" ht="30" spans="1:6">
       <c r="A104" s="5" t="s">
@@ -5135,7 +5166,7 @@
       <c r="E104" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F104" s="16"/>
+      <c r="F104" s="17"/>
     </row>
     <row r="105" ht="30" spans="1:6">
       <c r="A105" s="5" t="s">
@@ -5153,7 +5184,7 @@
       <c r="E105" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F105" s="16"/>
+      <c r="F105" s="17"/>
     </row>
     <row r="106" ht="30" spans="1:6">
       <c r="A106" s="5" t="s">
@@ -5171,7 +5202,7 @@
       <c r="E106" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F106" s="16"/>
+      <c r="F106" s="17"/>
     </row>
     <row r="107" ht="30" spans="1:6">
       <c r="A107" s="5" t="s">
@@ -5189,7 +5220,7 @@
       <c r="E107" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F107" s="16"/>
+      <c r="F107" s="17"/>
     </row>
     <row r="108" ht="45" spans="1:6">
       <c r="A108" s="5" t="s">
@@ -5207,7 +5238,7 @@
       <c r="E108" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F108" s="16"/>
+      <c r="F108" s="17"/>
     </row>
     <row r="109" ht="45" spans="1:6">
       <c r="A109" s="5" t="s">
@@ -5225,7 +5256,7 @@
       <c r="E109" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F109" s="16"/>
+      <c r="F109" s="17"/>
     </row>
     <row r="110" ht="45" spans="1:6">
       <c r="A110" s="5" t="s">
@@ -5243,7 +5274,7 @@
       <c r="E110" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F110" s="16"/>
+      <c r="F110" s="17"/>
     </row>
     <row r="111" ht="45" spans="1:6">
       <c r="A111" s="5" t="s">
@@ -5261,7 +5292,7 @@
       <c r="E111" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F111" s="16"/>
+      <c r="F111" s="17"/>
     </row>
     <row r="112" ht="45" spans="1:6">
       <c r="A112" s="5" t="s">
@@ -5279,7 +5310,7 @@
       <c r="E112" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F112" s="16"/>
+      <c r="F112" s="17"/>
     </row>
     <row r="113" ht="45" spans="1:6">
       <c r="A113" s="5" t="s">
@@ -5297,7 +5328,7 @@
       <c r="E113" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F113" s="16"/>
+      <c r="F113" s="17"/>
     </row>
     <row r="114" ht="45" spans="1:6">
       <c r="A114" s="5" t="s">
@@ -5315,7 +5346,7 @@
       <c r="E114" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F114" s="16"/>
+      <c r="F114" s="17"/>
     </row>
     <row r="115" ht="45" spans="1:6">
       <c r="A115" s="5" t="s">
@@ -5333,7 +5364,7 @@
       <c r="E115" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F115" s="16"/>
+      <c r="F115" s="17"/>
     </row>
     <row r="116" ht="30" spans="1:6">
       <c r="A116" s="5" t="s">
@@ -5351,7 +5382,7 @@
       <c r="E116" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F116" s="16"/>
+      <c r="F116" s="17"/>
     </row>
     <row r="117" ht="30" spans="1:6">
       <c r="A117" s="5" t="s">
@@ -5369,7 +5400,7 @@
       <c r="E117" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F117" s="16"/>
+      <c r="F117" s="17"/>
     </row>
     <row r="118" ht="30" spans="1:6">
       <c r="A118" s="5" t="s">
@@ -5387,7 +5418,7 @@
       <c r="E118" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F118" s="16"/>
+      <c r="F118" s="17"/>
     </row>
     <row r="119" ht="30" spans="1:6">
       <c r="A119" s="5" t="s">
@@ -5405,7 +5436,7 @@
       <c r="E119" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F119" s="16"/>
+      <c r="F119" s="17"/>
     </row>
     <row r="120" ht="30" spans="1:6">
       <c r="A120" s="5" t="s">
@@ -5423,7 +5454,7 @@
       <c r="E120" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F120" s="16"/>
+      <c r="F120" s="17"/>
     </row>
     <row r="121" ht="30" spans="1:6">
       <c r="A121" s="5" t="s">
@@ -5441,7 +5472,7 @@
       <c r="E121" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F121" s="16"/>
+      <c r="F121" s="17"/>
     </row>
     <row r="122" ht="30" spans="1:6">
       <c r="A122" s="5" t="s">
@@ -5459,7 +5490,7 @@
       <c r="E122" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F122" s="16"/>
+      <c r="F122" s="17"/>
     </row>
     <row r="123" ht="30" spans="1:6">
       <c r="A123" s="5" t="s">
@@ -5477,7 +5508,7 @@
       <c r="E123" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F123" s="16"/>
+      <c r="F123" s="17"/>
     </row>
     <row r="124" ht="30" spans="1:6">
       <c r="A124" s="5" t="s">
@@ -5495,7 +5526,7 @@
       <c r="E124" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F124" s="16"/>
+      <c r="F124" s="17"/>
     </row>
     <row r="125" ht="30" spans="1:6">
       <c r="A125" s="5" t="s">
@@ -5513,7 +5544,7 @@
       <c r="E125" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F125" s="16"/>
+      <c r="F125" s="17"/>
     </row>
     <row r="126" ht="30" spans="1:6">
       <c r="A126" s="5" t="s">
@@ -5531,7 +5562,7 @@
       <c r="E126" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F126" s="16"/>
+      <c r="F126" s="17"/>
     </row>
     <row r="127" ht="30" spans="1:6">
       <c r="A127" s="5" t="s">
@@ -5549,7 +5580,7 @@
       <c r="E127" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F127" s="16"/>
+      <c r="F127" s="17"/>
     </row>
     <row r="128" ht="30" spans="1:6">
       <c r="A128" s="5" t="s">
@@ -5567,7 +5598,7 @@
       <c r="E128" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F128" s="16"/>
+      <c r="F128" s="17"/>
     </row>
     <row r="129" ht="30" spans="1:6">
       <c r="A129" s="5" t="s">
@@ -5585,7 +5616,7 @@
       <c r="E129" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F129" s="16"/>
+      <c r="F129" s="17"/>
     </row>
     <row r="130" ht="30" spans="1:6">
       <c r="A130" s="5" t="s">
@@ -5603,7 +5634,7 @@
       <c r="E130" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F130" s="16"/>
+      <c r="F130" s="17"/>
     </row>
     <row r="131" ht="45" spans="1:6">
       <c r="A131" s="5" t="s">
@@ -5621,7 +5652,7 @@
       <c r="E131" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F131" s="16"/>
+      <c r="F131" s="17"/>
     </row>
     <row r="132" ht="30" spans="1:6">
       <c r="A132" s="5" t="s">
@@ -5639,7 +5670,7 @@
       <c r="E132" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F132" s="16"/>
+      <c r="F132" s="17"/>
     </row>
     <row r="133" ht="30" spans="1:6">
       <c r="A133" s="5" t="s">
@@ -5657,7 +5688,7 @@
       <c r="E133" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F133" s="16"/>
+      <c r="F133" s="17"/>
     </row>
     <row r="134" ht="30" spans="1:6">
       <c r="A134" s="5" t="s">
@@ -5675,7 +5706,7 @@
       <c r="E134" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F134" s="16"/>
+      <c r="F134" s="17"/>
     </row>
     <row r="135" ht="30" spans="1:6">
       <c r="A135" s="5" t="s">
@@ -5693,7 +5724,7 @@
       <c r="E135" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F135" s="16"/>
+      <c r="F135" s="17"/>
     </row>
     <row r="136" ht="30" spans="1:6">
       <c r="A136" s="5" t="s">
@@ -5711,7 +5742,7 @@
       <c r="E136" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F136" s="16"/>
+      <c r="F136" s="17"/>
     </row>
     <row r="137" ht="30" spans="1:6">
       <c r="A137" s="5" t="s">
@@ -5729,7 +5760,7 @@
       <c r="E137" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F137" s="16"/>
+      <c r="F137" s="17"/>
     </row>
     <row r="138" ht="30" spans="1:6">
       <c r="A138" s="5" t="s">
@@ -5747,7 +5778,7 @@
       <c r="E138" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F138" s="16"/>
+      <c r="F138" s="17"/>
     </row>
     <row r="139" ht="30" spans="1:6">
       <c r="A139" s="5" t="s">
@@ -5765,7 +5796,7 @@
       <c r="E139" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F139" s="16"/>
+      <c r="F139" s="17"/>
     </row>
     <row r="140" ht="30" spans="1:6">
       <c r="A140" s="5" t="s">
@@ -5783,7 +5814,7 @@
       <c r="E140" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F140" s="16"/>
+      <c r="F140" s="17"/>
     </row>
     <row r="141" ht="30" spans="1:6">
       <c r="A141" s="5" t="s">
@@ -5801,7 +5832,7 @@
       <c r="E141" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F141" s="16"/>
+      <c r="F141" s="17"/>
     </row>
     <row r="142" ht="30" spans="1:6">
       <c r="A142" s="5" t="s">
@@ -5819,7 +5850,7 @@
       <c r="E142" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F142" s="16"/>
+      <c r="F142" s="17"/>
     </row>
     <row r="143" ht="30" spans="1:6">
       <c r="A143" s="5" t="s">
@@ -5837,7 +5868,7 @@
       <c r="E143" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F143" s="16"/>
+      <c r="F143" s="17"/>
     </row>
     <row r="144" ht="30" spans="1:6">
       <c r="A144" s="5" t="s">
@@ -5855,7 +5886,7 @@
       <c r="E144" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F144" s="17"/>
+      <c r="F144" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
     <sheet name="标签数据信息说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="396">
   <si>
     <t>类别</t>
   </si>
@@ -307,6 +307,21 @@
   </si>
   <si>
     <t>单位：个</t>
+  </si>
+  <si>
+    <t>machine_card_nums</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器模组数目</t>
+  </si>
+  <si>
+    <t>Atlas 训练系列产品
+Atlas A2 训练系列产品
+Atlas A3 训练系列产品
+推理服务器（插Atlas 300I 推理卡）
+Atlas 推理系列产品
+Atlas 800I A2 推理服务器
+A200I A2 Box 异构组件</t>
   </si>
   <si>
     <t>npu_chip_info_network_status</t>
@@ -709,6 +724,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>昇</t>
     </r>
     <r>
@@ -747,6 +768,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>昇</t>
     </r>
     <r>
@@ -2152,16 +2179,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3090,12 +3117,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F144"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:F145"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="42" style="7" customWidth="1"/>
-    <col min="3" max="3" width="32.6333333333333" style="7" customWidth="1"/>
+    <col min="3" max="3" width="32.6296296296296" style="7" customWidth="1"/>
     <col min="4" max="4" width="48.25" style="7" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="7" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="7" customWidth="1"/>
@@ -3182,7 +3209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="75" spans="1:6">
+    <row r="5" ht="72" spans="1:6">
       <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
@@ -3222,7 +3249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="75" spans="1:6">
+    <row r="7" ht="72" spans="1:6">
       <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
@@ -3242,7 +3269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="75" spans="1:6">
+    <row r="8" ht="72" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -3262,7 +3289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="45" spans="1:6">
+    <row r="9" ht="43.2" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -3282,7 +3309,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="1:6">
+    <row r="10" ht="43.2" spans="1:6">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -3302,7 +3329,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="45" spans="1:6">
+    <row r="11" ht="43.2" spans="1:6">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -3322,7 +3349,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="45" spans="1:6">
+    <row r="12" ht="43.2" spans="1:6">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -3362,227 +3389,227 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" ht="75" spans="1:6">
-      <c r="A14" s="7" t="s">
+    <row r="14" ht="159" customHeight="1" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" ht="210" spans="1:6">
+    </row>
+    <row r="15" ht="72" spans="1:6">
       <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" ht="149" customHeight="1" spans="1:6">
+      <c r="E15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="201.6" spans="1:6">
       <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="13" t="s">
         <v>53</v>
       </c>
+      <c r="C16" s="13" t="s">
+        <v>54</v>
+      </c>
       <c r="D16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" ht="150" spans="1:6">
+    <row r="17" ht="149" customHeight="1" spans="1:6">
       <c r="A17" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>56</v>
+      <c r="E17" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" ht="195" spans="1:6">
-      <c r="A18" s="9" t="s">
+    <row r="18" ht="144" spans="1:6">
+      <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>58</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" ht="150" spans="1:6">
+      <c r="F18" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="187.2" spans="1:6">
       <c r="A19" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" ht="153" customHeight="1" spans="1:6">
-      <c r="A20" s="7" t="s">
+    </row>
+    <row r="20" ht="144" spans="1:6">
+      <c r="A20" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" ht="151" customHeight="1" spans="1:6">
+    <row r="21" ht="153" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" ht="150" spans="1:6">
-      <c r="A22" s="9" t="s">
+    <row r="22" ht="151" customHeight="1" spans="1:6">
+      <c r="A22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="9" t="s">
+      <c r="D22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" ht="144" spans="1:6">
+      <c r="A23" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F23" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" ht="150" spans="1:6">
-      <c r="A23" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" ht="150" spans="1:6">
-      <c r="A24" s="9" t="s">
+    <row r="24" ht="144" spans="1:6">
+      <c r="A24" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="7" t="s">
         <v>77</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" ht="120" spans="1:6">
+    <row r="25" ht="144" spans="1:6">
       <c r="A25" s="9" t="s">
         <v>42</v>
       </c>
@@ -3593,16 +3620,16 @@
         <v>80</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" ht="120" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" ht="115.2" spans="1:6">
       <c r="A26" s="9" t="s">
         <v>42</v>
       </c>
@@ -3616,33 +3643,33 @@
         <v>19</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" ht="150" spans="1:6">
-      <c r="A27" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" ht="115.2" spans="1:6">
+      <c r="A27" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" ht="150" spans="1:6">
+    </row>
+    <row r="28" ht="144" spans="1:6">
       <c r="A28" s="4" t="s">
         <v>42</v>
       </c>
@@ -3662,47 +3689,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" ht="150" spans="1:6">
+    <row r="29" ht="144" spans="1:6">
       <c r="A29" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="9" t="s">
         <v>91</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="150" spans="1:6">
-      <c r="A30" s="9" t="s">
+    <row r="30" ht="144" spans="1:6">
+      <c r="A30" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" ht="39" customHeight="1" spans="1:6">
+    <row r="31" ht="144" spans="1:6">
       <c r="A31" s="9" t="s">
         <v>42</v>
       </c>
@@ -3719,98 +3746,98 @@
         <v>10</v>
       </c>
       <c r="F31" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" ht="39" customHeight="1" spans="1:6">
+      <c r="A32" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="32" ht="60" spans="1:6">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="D32" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="E32" s="9" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="33" ht="105" spans="1:6">
+    <row r="33" ht="57.6" spans="1:6">
       <c r="A33" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="14" t="s">
         <v>103</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" ht="135" spans="1:6">
+    <row r="34" ht="100.8" spans="1:6">
       <c r="A34" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="9" t="s">
         <v>106</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" ht="75" spans="1:6">
-      <c r="A35" s="7" t="s">
+    <row r="35" ht="129.6" spans="1:6">
+      <c r="A35" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C35" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" ht="75" spans="1:6">
-      <c r="A36" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B36" s="9" t="s">
+    </row>
+    <row r="36" ht="72" spans="1:6">
+      <c r="A36" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="B36" s="7" t="s">
         <v>112</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>19</v>
@@ -3822,29 +3849,29 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="5" t="s">
+    <row r="37" ht="72" spans="1:6">
+      <c r="A37" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="9" t="s">
         <v>115</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>86</v>
+        <v>19</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>117</v>
@@ -3853,18 +3880,18 @@
         <v>118</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>120</v>
@@ -3873,18 +3900,18 @@
         <v>121</v>
       </c>
       <c r="D39" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="13" t="s">
         <v>116</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" ht="45" spans="1:6">
-      <c r="A40" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>123</v>
@@ -3893,18 +3920,18 @@
         <v>124</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F40" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" ht="43.2" spans="1:6">
+      <c r="A41" s="5" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="41" ht="45" spans="1:6">
-      <c r="A41" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>126</v>
@@ -3916,15 +3943,15 @@
         <v>19</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F41" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" ht="43.2" spans="1:6">
+      <c r="A42" s="5" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="42" ht="120" spans="1:6">
-      <c r="A42" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>129</v>
@@ -3936,15 +3963,15 @@
         <v>19</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F42" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" ht="115.2" spans="1:6">
+      <c r="A43" s="5" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="43" ht="123" customHeight="1" spans="1:6">
-      <c r="A43" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>132</v>
@@ -3956,61 +3983,61 @@
         <v>19</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F43" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" ht="123" customHeight="1" spans="1:6">
+      <c r="A44" s="5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="44" ht="120" spans="1:6">
-      <c r="A44" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F44" s="10" t="s">
+    </row>
+    <row r="45" ht="115.2" spans="1:6">
+      <c r="A45" s="13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="45" ht="120" spans="1:6">
-      <c r="A45" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="13" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>45</v>
+      <c r="E45" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="F45" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" ht="115.2" spans="1:6">
+      <c r="A46" s="13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="46" ht="120" spans="1:6">
-      <c r="A46" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="B46" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>19</v>
@@ -4019,18 +4046,18 @@
         <v>45</v>
       </c>
       <c r="F46" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" ht="115.2" spans="1:6">
+      <c r="A47" s="13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="47" ht="120" spans="1:6">
-      <c r="A47" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="B47" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>19</v>
@@ -4039,18 +4066,18 @@
         <v>45</v>
       </c>
       <c r="F47" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" ht="115.2" spans="1:6">
+      <c r="A48" s="13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="48" ht="120" spans="1:6">
-      <c r="A48" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="B48" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>19</v>
@@ -4059,18 +4086,18 @@
         <v>45</v>
       </c>
       <c r="F48" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" ht="115.2" spans="1:6">
+      <c r="A49" s="13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="49" ht="119" customHeight="1" spans="1:6">
-      <c r="A49" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="B49" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>19</v>
@@ -4079,18 +4106,18 @@
         <v>45</v>
       </c>
       <c r="F49" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" ht="119" customHeight="1" spans="1:6">
+      <c r="A50" s="13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="50" ht="120" spans="1:6">
-      <c r="A50" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="B50" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>19</v>
@@ -4099,12 +4126,12 @@
         <v>45</v>
       </c>
       <c r="F50" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" ht="115.2" spans="1:6">
+      <c r="A51" s="13" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="51" ht="33" customHeight="1" spans="1:6">
-      <c r="A51" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>150</v>
@@ -4119,12 +4146,12 @@
         <v>45</v>
       </c>
       <c r="F51" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" ht="33" customHeight="1" spans="1:6">
+      <c r="A52" s="5" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="52" ht="29" customHeight="1" spans="1:6">
-      <c r="A52" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>153</v>
@@ -4142,29 +4169,29 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" ht="45" spans="1:6">
-      <c r="A53" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B53" s="15" t="s">
+    <row r="53" ht="29" customHeight="1" spans="1:6">
+      <c r="A53" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="5" t="s">
         <v>157</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F53" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="54" ht="45" spans="1:6">
+    </row>
+    <row r="54" ht="43.2" spans="1:6">
       <c r="A54" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B54" s="15" t="s">
         <v>159</v>
@@ -4179,12 +4206,12 @@
         <v>161</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="55" ht="45" spans="1:6">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" ht="43.2" spans="1:6">
       <c r="A55" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B55" s="15" t="s">
         <v>162</v>
@@ -4196,35 +4223,35 @@
         <v>19</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="56" ht="29" customHeight="1" spans="1:6">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" ht="43.2" spans="1:6">
       <c r="A56" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B56" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C56" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>161</v>
-      </c>
       <c r="F56" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="57" ht="45" spans="1:6">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" ht="29" customHeight="1" spans="1:6">
       <c r="A57" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B57" s="15" t="s">
         <v>167</v>
@@ -4236,181 +4263,181 @@
         <v>19</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="58" ht="35" customHeight="1" spans="1:6">
-      <c r="A58" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B58" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="5" t="s">
+    </row>
+    <row r="58" ht="43.2" spans="1:6">
+      <c r="A58" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B58" s="15" t="s">
         <v>170</v>
       </c>
+      <c r="C58" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="D58" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="7" t="s">
-        <v>45</v>
+      <c r="E58" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="59" ht="45" spans="1:6">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="59" ht="35" customHeight="1" spans="1:6">
       <c r="A59" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B59" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>172</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>173</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" ht="43.2" spans="1:6">
+      <c r="A60" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="C60" s="5" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="60" ht="45" spans="1:6">
-      <c r="A60" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="E60" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="F60" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" ht="43.2" spans="1:6">
+      <c r="A61" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="61" ht="45" spans="1:6">
-      <c r="A61" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="B61" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F61" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D61" s="5" t="s">
+    </row>
+    <row r="62" ht="43.2" spans="1:6">
+      <c r="A62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62" ht="45" spans="1:6">
-      <c r="A62" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="B62" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D62" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" ht="43.2" spans="1:6">
+      <c r="A63" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="63" ht="45" spans="1:6">
-      <c r="A63" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="B63" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D63" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64" ht="43.2" spans="1:6">
+      <c r="A64" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="64" ht="45" spans="1:6">
-      <c r="A64" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="B64" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D64" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="65" ht="43.2" spans="1:6">
+      <c r="A65" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="65" ht="75" spans="1:6">
-      <c r="A65" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="B65" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" ht="75" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="66" ht="72" spans="1:6">
       <c r="A66" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>19</v>
@@ -4422,15 +4449,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" ht="75" spans="1:6">
+    <row r="67" ht="72" spans="1:6">
       <c r="A67" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>19</v>
@@ -4442,15 +4469,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" ht="75" spans="1:6">
+    <row r="68" ht="72" spans="1:6">
       <c r="A68" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>19</v>
@@ -4462,15 +4489,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" ht="75" spans="1:6">
+    <row r="69" ht="72" spans="1:6">
       <c r="A69" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>19</v>
@@ -4482,15 +4509,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" ht="75" spans="1:6">
+    <row r="70" ht="72" spans="1:6">
       <c r="A70" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>19</v>
@@ -4502,15 +4529,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" ht="75" spans="1:6">
+    <row r="71" ht="72" spans="1:6">
       <c r="A71" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>19</v>
@@ -4522,15 +4549,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" ht="75" spans="1:6">
+    <row r="72" ht="72" spans="1:6">
       <c r="A72" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>19</v>
@@ -4542,15 +4569,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" ht="75" spans="1:6">
+    <row r="73" ht="72" spans="1:6">
       <c r="A73" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>19</v>
@@ -4562,15 +4589,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" ht="75" spans="1:6">
+    <row r="74" ht="72" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>19</v>
@@ -4582,15 +4609,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" ht="75" customHeight="1" spans="1:6">
+    <row r="75" ht="72" spans="1:6">
       <c r="A75" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>19</v>
@@ -4602,15 +4629,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" ht="75" spans="1:6">
+    <row r="76" ht="75" customHeight="1" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>19</v>
@@ -4622,15 +4649,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" ht="75" spans="1:6">
+    <row r="77" ht="72" spans="1:6">
       <c r="A77" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>19</v>
@@ -4642,15 +4669,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" ht="75" spans="1:6">
+    <row r="78" ht="72" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>19</v>
@@ -4662,15 +4689,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" ht="75" spans="1:6">
+    <row r="79" ht="72" spans="1:6">
       <c r="A79" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>19</v>
@@ -4682,15 +4709,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" ht="75" spans="1:6">
+    <row r="80" ht="72" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>19</v>
@@ -4702,15 +4729,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" ht="75" spans="1:6">
+    <row r="81" ht="72" spans="1:6">
       <c r="A81" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>19</v>
@@ -4722,15 +4749,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" ht="75" spans="1:6">
+    <row r="82" ht="72" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>19</v>
@@ -4742,15 +4769,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" ht="27" customHeight="1" spans="1:6">
+    <row r="83" ht="72" spans="1:6">
       <c r="A83" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>19</v>
@@ -4762,14 +4789,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1" spans="1:6">
+    <row r="84" ht="27" customHeight="1" spans="1:6">
       <c r="A84" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B84" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B84" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="5" t="s">
         <v>227</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -4779,12 +4806,12 @@
         <v>45</v>
       </c>
       <c r="F84" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1" spans="1:6">
+      <c r="A85" s="5" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="85" ht="60" spans="1:6">
-      <c r="A85" s="5" t="s">
-        <v>225</v>
       </c>
       <c r="B85" s="13" t="s">
         <v>229</v>
@@ -4799,52 +4826,52 @@
         <v>45</v>
       </c>
       <c r="F85" s="10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="86" ht="57.6" spans="1:6">
+      <c r="A86" s="5" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="86" ht="75" spans="1:6">
-      <c r="A86" s="5" t="s">
+      <c r="B86" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="13" t="s">
+    </row>
+    <row r="87" ht="72" spans="1:6">
+      <c r="A87" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F86" s="10" t="s">
+      <c r="B87" s="5" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="87" ht="75" spans="1:6">
-      <c r="A87" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B87" s="5" t="s">
+      <c r="C87" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="D87" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="D87" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87" s="5" t="s">
+      <c r="F87" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="88" ht="75" spans="1:6">
+    </row>
+    <row r="88" ht="72" spans="1:6">
       <c r="A88" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>239</v>
@@ -4856,35 +4883,35 @@
         <v>19</v>
       </c>
       <c r="E88" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F88" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="F88" s="10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="89" ht="75" spans="1:6">
+    </row>
+    <row r="89" ht="72" spans="1:6">
       <c r="A89" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>243</v>
-      </c>
       <c r="F89" s="10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="90" ht="75" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="90" ht="72" spans="1:6">
       <c r="A90" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>244</v>
@@ -4899,12 +4926,12 @@
         <v>246</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="91" ht="30" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="91" ht="72" spans="1:6">
       <c r="A91" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>247</v>
@@ -4916,15 +4943,15 @@
         <v>19</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>45</v>
+        <v>249</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="92" ht="45" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="92" ht="28.8" spans="1:6">
       <c r="A92" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>250</v>
@@ -4936,75 +4963,75 @@
         <v>19</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>238</v>
+        <v>45</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="93" ht="60" spans="1:6">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="93" ht="43.2" spans="1:6">
       <c r="A93" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B93" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F93" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="C93" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="94" ht="120" spans="1:6">
-      <c r="A94" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C94" s="9" t="s">
+    </row>
+    <row r="94" ht="57.6" spans="1:6">
+      <c r="A94" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>255</v>
       </c>
+      <c r="C94" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="D94" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E94" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F94" s="13" t="s">
+      <c r="E94" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="95" ht="115.2" spans="1:6">
+      <c r="A95" s="9" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="95" ht="120" spans="1:6">
-      <c r="A95" s="9" t="s">
-        <v>128</v>
-      </c>
       <c r="B95" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="F95" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="96" ht="115.2" spans="1:6">
+      <c r="A96" s="9" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="96" ht="120" spans="1:6">
-      <c r="A96" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>259</v>
@@ -5016,59 +5043,61 @@
         <v>19</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>86</v>
+        <v>261</v>
       </c>
       <c r="F96" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="97" ht="115.2" spans="1:6">
+      <c r="A97" s="9" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="97" ht="30" spans="1:6">
-      <c r="A97" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C97" s="9" t="s">
         <v>263</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F97" s="16" t="s">
+      <c r="E97" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F97" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="98" ht="28.8" spans="1:6">
+      <c r="A98" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F98" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="98" ht="30" spans="1:6">
-      <c r="A98" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B98" s="5" t="s">
+    <row r="99" ht="28.8" spans="1:6">
+      <c r="A99" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F98" s="17"/>
-    </row>
-    <row r="99" ht="30" spans="1:6">
-      <c r="A99" s="5" t="s">
-        <v>261</v>
-      </c>
       <c r="B99" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>19</v>
@@ -5078,15 +5107,15 @@
       </c>
       <c r="F99" s="17"/>
     </row>
-    <row r="100" ht="30" spans="1:6">
+    <row r="100" ht="28.8" spans="1:6">
       <c r="A100" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>19</v>
@@ -5096,15 +5125,15 @@
       </c>
       <c r="F100" s="17"/>
     </row>
-    <row r="101" ht="30" spans="1:6">
+    <row r="101" ht="28.8" spans="1:6">
       <c r="A101" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>19</v>
@@ -5114,15 +5143,15 @@
       </c>
       <c r="F101" s="17"/>
     </row>
-    <row r="102" ht="30" spans="1:6">
+    <row r="102" ht="28.8" spans="1:6">
       <c r="A102" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>19</v>
@@ -5132,15 +5161,15 @@
       </c>
       <c r="F102" s="17"/>
     </row>
-    <row r="103" ht="30" spans="1:6">
+    <row r="103" ht="28.8" spans="1:6">
       <c r="A103" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>19</v>
@@ -5150,15 +5179,15 @@
       </c>
       <c r="F103" s="17"/>
     </row>
-    <row r="104" ht="30" spans="1:6">
+    <row r="104" ht="28.8" spans="1:6">
       <c r="A104" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>19</v>
@@ -5168,15 +5197,15 @@
       </c>
       <c r="F104" s="17"/>
     </row>
-    <row r="105" ht="30" spans="1:6">
+    <row r="105" ht="28.8" spans="1:6">
       <c r="A105" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>19</v>
@@ -5186,15 +5215,15 @@
       </c>
       <c r="F105" s="17"/>
     </row>
-    <row r="106" ht="30" spans="1:6">
+    <row r="106" ht="28.8" spans="1:6">
       <c r="A106" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>19</v>
@@ -5204,15 +5233,15 @@
       </c>
       <c r="F106" s="17"/>
     </row>
-    <row r="107" ht="30" spans="1:6">
+    <row r="107" ht="28.8" spans="1:6">
       <c r="A107" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>19</v>
@@ -5222,15 +5251,15 @@
       </c>
       <c r="F107" s="17"/>
     </row>
-    <row r="108" ht="45" spans="1:6">
+    <row r="108" ht="28.8" spans="1:6">
       <c r="A108" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>19</v>
@@ -5240,15 +5269,15 @@
       </c>
       <c r="F108" s="17"/>
     </row>
-    <row r="109" ht="45" spans="1:6">
+    <row r="109" ht="57.6" spans="1:6">
       <c r="A109" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>19</v>
@@ -5258,15 +5287,15 @@
       </c>
       <c r="F109" s="17"/>
     </row>
-    <row r="110" ht="45" spans="1:6">
+    <row r="110" ht="43.2" spans="1:6">
       <c r="A110" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>19</v>
@@ -5276,15 +5305,15 @@
       </c>
       <c r="F110" s="17"/>
     </row>
-    <row r="111" ht="45" spans="1:6">
+    <row r="111" ht="43.2" spans="1:6">
       <c r="A111" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>19</v>
@@ -5294,15 +5323,15 @@
       </c>
       <c r="F111" s="17"/>
     </row>
-    <row r="112" ht="45" spans="1:6">
+    <row r="112" ht="43.2" spans="1:6">
       <c r="A112" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>19</v>
@@ -5312,15 +5341,15 @@
       </c>
       <c r="F112" s="17"/>
     </row>
-    <row r="113" ht="45" spans="1:6">
+    <row r="113" ht="43.2" spans="1:6">
       <c r="A113" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>19</v>
@@ -5330,15 +5359,15 @@
       </c>
       <c r="F113" s="17"/>
     </row>
-    <row r="114" ht="45" spans="1:6">
+    <row r="114" ht="43.2" spans="1:6">
       <c r="A114" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>19</v>
@@ -5348,15 +5377,15 @@
       </c>
       <c r="F114" s="17"/>
     </row>
-    <row r="115" ht="45" spans="1:6">
+    <row r="115" ht="43.2" spans="1:6">
       <c r="A115" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>19</v>
@@ -5366,15 +5395,15 @@
       </c>
       <c r="F115" s="17"/>
     </row>
-    <row r="116" ht="30" spans="1:6">
+    <row r="116" ht="43.2" spans="1:6">
       <c r="A116" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>19</v>
@@ -5384,15 +5413,15 @@
       </c>
       <c r="F116" s="17"/>
     </row>
-    <row r="117" ht="30" spans="1:6">
+    <row r="117" ht="28.8" spans="1:6">
       <c r="A117" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>19</v>
@@ -5402,15 +5431,15 @@
       </c>
       <c r="F117" s="17"/>
     </row>
-    <row r="118" ht="30" spans="1:6">
+    <row r="118" ht="28.8" spans="1:6">
       <c r="A118" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>19</v>
@@ -5420,15 +5449,15 @@
       </c>
       <c r="F118" s="17"/>
     </row>
-    <row r="119" ht="30" spans="1:6">
+    <row r="119" ht="28.8" spans="1:6">
       <c r="A119" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>19</v>
@@ -5438,15 +5467,15 @@
       </c>
       <c r="F119" s="17"/>
     </row>
-    <row r="120" ht="30" spans="1:6">
+    <row r="120" ht="28.8" spans="1:6">
       <c r="A120" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>19</v>
@@ -5456,15 +5485,15 @@
       </c>
       <c r="F120" s="17"/>
     </row>
-    <row r="121" ht="30" spans="1:6">
+    <row r="121" ht="28.8" spans="1:6">
       <c r="A121" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>19</v>
@@ -5474,15 +5503,15 @@
       </c>
       <c r="F121" s="17"/>
     </row>
-    <row r="122" ht="30" spans="1:6">
+    <row r="122" ht="28.8" spans="1:6">
       <c r="A122" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>19</v>
@@ -5492,15 +5521,15 @@
       </c>
       <c r="F122" s="17"/>
     </row>
-    <row r="123" ht="30" spans="1:6">
+    <row r="123" ht="28.8" spans="1:6">
       <c r="A123" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>19</v>
@@ -5510,15 +5539,15 @@
       </c>
       <c r="F123" s="17"/>
     </row>
-    <row r="124" ht="30" spans="1:6">
+    <row r="124" ht="28.8" spans="1:6">
       <c r="A124" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>19</v>
@@ -5528,15 +5557,15 @@
       </c>
       <c r="F124" s="17"/>
     </row>
-    <row r="125" ht="30" spans="1:6">
+    <row r="125" ht="28.8" spans="1:6">
       <c r="A125" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>19</v>
@@ -5546,15 +5575,15 @@
       </c>
       <c r="F125" s="17"/>
     </row>
-    <row r="126" ht="30" spans="1:6">
+    <row r="126" ht="28.8" spans="1:6">
       <c r="A126" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>19</v>
@@ -5564,15 +5593,15 @@
       </c>
       <c r="F126" s="17"/>
     </row>
-    <row r="127" ht="30" spans="1:6">
+    <row r="127" ht="28.8" spans="1:6">
       <c r="A127" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>19</v>
@@ -5582,15 +5611,15 @@
       </c>
       <c r="F127" s="17"/>
     </row>
-    <row r="128" ht="30" spans="1:6">
+    <row r="128" ht="28.8" spans="1:6">
       <c r="A128" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>19</v>
@@ -5600,15 +5629,15 @@
       </c>
       <c r="F128" s="17"/>
     </row>
-    <row r="129" ht="30" spans="1:6">
+    <row r="129" ht="28.8" spans="1:6">
       <c r="A129" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>19</v>
@@ -5618,15 +5647,15 @@
       </c>
       <c r="F129" s="17"/>
     </row>
-    <row r="130" ht="30" spans="1:6">
+    <row r="130" ht="28.8" spans="1:6">
       <c r="A130" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>19</v>
@@ -5636,15 +5665,15 @@
       </c>
       <c r="F130" s="17"/>
     </row>
-    <row r="131" ht="45" spans="1:6">
+    <row r="131" ht="43.2" spans="1:6">
       <c r="A131" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>19</v>
@@ -5654,15 +5683,15 @@
       </c>
       <c r="F131" s="17"/>
     </row>
-    <row r="132" ht="30" spans="1:6">
+    <row r="132" ht="43.2" spans="1:6">
       <c r="A132" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>19</v>
@@ -5672,15 +5701,15 @@
       </c>
       <c r="F132" s="17"/>
     </row>
-    <row r="133" ht="30" spans="1:6">
+    <row r="133" ht="28.8" spans="1:6">
       <c r="A133" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>19</v>
@@ -5690,15 +5719,15 @@
       </c>
       <c r="F133" s="17"/>
     </row>
-    <row r="134" ht="30" spans="1:6">
+    <row r="134" ht="28.8" spans="1:6">
       <c r="A134" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>19</v>
@@ -5708,15 +5737,15 @@
       </c>
       <c r="F134" s="17"/>
     </row>
-    <row r="135" ht="30" spans="1:6">
+    <row r="135" ht="28.8" spans="1:6">
       <c r="A135" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>19</v>
@@ -5726,15 +5755,15 @@
       </c>
       <c r="F135" s="17"/>
     </row>
-    <row r="136" ht="30" spans="1:6">
+    <row r="136" ht="28.8" spans="1:6">
       <c r="A136" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>19</v>
@@ -5744,15 +5773,15 @@
       </c>
       <c r="F136" s="17"/>
     </row>
-    <row r="137" ht="30" spans="1:6">
+    <row r="137" ht="28.8" spans="1:6">
       <c r="A137" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>19</v>
@@ -5762,15 +5791,15 @@
       </c>
       <c r="F137" s="17"/>
     </row>
-    <row r="138" ht="30" spans="1:6">
+    <row r="138" ht="28.8" spans="1:6">
       <c r="A138" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>19</v>
@@ -5780,15 +5809,15 @@
       </c>
       <c r="F138" s="17"/>
     </row>
-    <row r="139" ht="30" spans="1:6">
+    <row r="139" ht="28.8" spans="1:6">
       <c r="A139" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>19</v>
@@ -5798,15 +5827,15 @@
       </c>
       <c r="F139" s="17"/>
     </row>
-    <row r="140" ht="30" spans="1:6">
+    <row r="140" ht="28.8" spans="1:6">
       <c r="A140" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>19</v>
@@ -5816,15 +5845,15 @@
       </c>
       <c r="F140" s="17"/>
     </row>
-    <row r="141" ht="30" spans="1:6">
+    <row r="141" ht="28.8" spans="1:6">
       <c r="A141" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>19</v>
@@ -5834,15 +5863,15 @@
       </c>
       <c r="F141" s="17"/>
     </row>
-    <row r="142" ht="30" spans="1:6">
+    <row r="142" ht="28.8" spans="1:6">
       <c r="A142" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>19</v>
@@ -5852,15 +5881,15 @@
       </c>
       <c r="F142" s="17"/>
     </row>
-    <row r="143" ht="30" spans="1:6">
+    <row r="143" ht="28.8" spans="1:6">
       <c r="A143" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>19</v>
@@ -5870,15 +5899,15 @@
       </c>
       <c r="F143" s="17"/>
     </row>
-    <row r="144" ht="30" spans="1:6">
+    <row r="144" ht="28.8" spans="1:6">
       <c r="A144" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>19</v>
@@ -5886,11 +5915,29 @@
       <c r="E144" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F144" s="18"/>
+      <c r="F144" s="17"/>
+    </row>
+    <row r="145" ht="28.8" spans="1:6">
+      <c r="A145" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F145" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F97:F144"/>
+    <mergeCell ref="F98:F145"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
@@ -5902,550 +5949,550 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.6333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="73.8833333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6296296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -43,6 +43,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">数据信息标签字段及字段类型
 </t>
     </r>
@@ -570,7 +577,18 @@
     <t>npu_chip_info_utilization</t>
   </si>
   <si>
-    <t>昇腾AI处理器AI Core利用率</t>
+    <r>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器AICore利用率</t>
+    </r>
   </si>
   <si>
     <t>单位：%</t>
@@ -579,7 +597,18 @@
     <t>npu_chip_info_aicore_current_freq</t>
   </si>
   <si>
-    <t>昇腾AI处理器的AI Core当前频率</t>
+    <r>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器的AICore当前频率</t>
+    </r>
   </si>
   <si>
     <t>单位：MHz</t>
@@ -588,7 +617,7 @@
     <t>container_npu_utilization</t>
   </si>
   <si>
-    <t>带有容器信息的NPU的AI Core利用率。
+    <t>带有容器信息的NPU的AICore利用率。
 说明：Telegraf不支持上报该指标。</t>
   </si>
   <si>
@@ -616,7 +645,18 @@
     <t>npu_chip_info_cube_utilization</t>
   </si>
   <si>
-    <t>昇腾AI处理器AI Cube利用率</t>
+    <r>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器AICube利用率</t>
+    </r>
   </si>
   <si>
     <t>Atlas A2 训练系列产品
@@ -641,7 +681,18 @@
     <t>npu_chip_info_vector_utilization</t>
   </si>
   <si>
-    <t>昇腾AI处理器AI Vector利用率</t>
+    <r>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器AIVector利用率</t>
+    </r>
   </si>
   <si>
     <t>Atlas A2 训练系列产品
@@ -674,7 +725,7 @@
     <t>vnpu_pod_aicore_utilization</t>
   </si>
   <si>
-    <t>vNPU的AI Core利用率</t>
+    <t>vNPU的AICore利用率</t>
   </si>
   <si>
     <t>详见“标签数据信息说明”页签中“标签3”</t>
@@ -1882,6 +1933,12 @@
       <sz val="11"/>
       <color rgb="FF252B3A"/>
       <name val="方正兰亭黑简体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2035,22 +2092,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF252B3A"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2429,16 +2480,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2447,119 +2495,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2598,6 +2649,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3440,7 +3494,7 @@
       <c r="B26" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="13" t="s">
         <v>83</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -3460,7 +3514,7 @@
       <c r="B27" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -3540,7 +3594,7 @@
       <c r="B31" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="13" t="s">
         <v>98</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -3580,7 +3634,7 @@
       <c r="B33" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="13" t="s">
         <v>104</v>
       </c>
       <c r="D33" s="5" t="s">
@@ -3954,13 +4008,13 @@
       </c>
     </row>
     <row r="52" ht="45" spans="1:6">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>155</v>
       </c>
       <c r="D52" s="5" t="s">
@@ -3974,13 +4028,13 @@
       </c>
     </row>
     <row r="53" ht="45" spans="1:6">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>158</v>
       </c>
       <c r="D53" s="5" t="s">
@@ -3994,13 +4048,13 @@
       </c>
     </row>
     <row r="54" ht="45" spans="1:6">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="14" t="s">
         <v>161</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -4014,13 +4068,13 @@
       </c>
     </row>
     <row r="55" ht="29" customHeight="1" spans="1:6">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="14" t="s">
         <v>163</v>
       </c>
       <c r="D55" s="5" t="s">
@@ -4034,13 +4088,13 @@
       </c>
     </row>
     <row r="56" ht="45" spans="1:6">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="14" t="s">
         <v>166</v>
       </c>
       <c r="D56" s="5" t="s">

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -163,12 +163,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="方正兰亭黑简体"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -207,7 +201,8 @@
         <rFont val="方正兰亭黑简体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> 0：DOWN</t>
+      <t xml:space="preserve"> 0：DOWN
+• -1：未知(dcmi接口调用失败)</t>
     </r>
   </si>
   <si>
@@ -331,12 +326,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="方正兰亭黑简体"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -375,7 +364,8 @@
         <rFont val="方正兰亭黑简体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> 0：不健康，无法连通</t>
+      <t xml:space="preserve"> 0：不健康，无法连通
+• -1：未知，dcmi接口调用失败</t>
     </r>
   </si>
   <si>
@@ -496,13 +486,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="方正兰亭黑简体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">取值为0或1
+      <t xml:space="preserve">取值为0或1或-1
 </t>
     </r>
     <r>
@@ -540,7 +524,8 @@
         <rFont val="方正兰亭黑简体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> 0：不健康</t>
+      <t xml:space="preserve"> 0：不健康
+• -1：未知(dcmi接口调用失败)</t>
     </r>
   </si>
   <si>
@@ -2185,16 +2170,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF252B3A"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF252B3A"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3289,7 +3274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="43.2" spans="1:6">
+    <row r="9" ht="72" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -3409,7 +3394,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" ht="72" spans="1:6">
+    <row r="15" ht="86.4" spans="1:6">
       <c r="A15" s="7" t="s">
         <v>42</v>
       </c>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="397">
   <si>
     <t>类别</t>
   </si>
@@ -202,7 +202,7 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 0：DOWN
-• -1：未知(dcmi接口调用失败)</t>
+• -1：未知(hccn_tool工具调用失败)</t>
     </r>
   </si>
   <si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -486,6 +492,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为0或1或-1
 </t>
     </r>
@@ -659,6 +671,39 @@
 说明：Telegraf不支持上报该数据指标。</t>
   </si>
   <si>
+    <t>npu_chip_info_aicore_current_freq</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器的AICore当前频率</t>
+  </si>
+  <si>
+    <t>单位：MHz</t>
+  </si>
+  <si>
+    <t>npu_chip_info_serial_number</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器序列号</t>
+  </si>
+  <si>
+    <t>详见“标签数据信息说明”页签中“标签6”</t>
+  </si>
+  <si>
+    <t>npu_chip_info_product_type</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器产品形态</t>
+  </si>
+  <si>
+    <t>详见“标签数据信息说明”页签中“标签7”</t>
+  </si>
+  <si>
+    <t>Atlas 推理系列产品</t>
+  </si>
+  <si>
+    <t>utilization</t>
+  </si>
+  <si>
     <t>npu_chip_info_utilization</t>
   </si>
   <si>
@@ -666,15 +711,6 @@
   </si>
   <si>
     <t>单位：%</t>
-  </si>
-  <si>
-    <t>npu_chip_info_aicore_current_freq</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器的AICore当前频率</t>
-  </si>
-  <si>
-    <t>单位：MHz</t>
   </si>
   <si>
     <t>container_npu_utilization</t>
@@ -682,27 +718,6 @@
   <si>
     <t>带有容器信息的NPU的AICore利用率。
 说明：Telegraf不支持上报该指标。</t>
-  </si>
-  <si>
-    <t>npu_chip_info_serial_number</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器序列号</t>
-  </si>
-  <si>
-    <t>详见“标签数据信息说明”页签中“标签6”</t>
-  </si>
-  <si>
-    <t>npu_chip_info_product_type</t>
-  </si>
-  <si>
-    <t>昇腾AI处理器产品形态</t>
-  </si>
-  <si>
-    <t>详见“标签数据信息说明”页签中“标签7”</t>
-  </si>
-  <si>
-    <t>Atlas 推理系列产品</t>
   </si>
   <si>
     <t>npu_chip_info_cube_utilization</t>
@@ -2164,6 +2179,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="方正兰亭黑简体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -2173,13 +2195,6 @@
       <sz val="11"/>
       <color rgb="FF252B3A"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3254,7 +3269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="72" spans="1:6">
+    <row r="8" ht="86.4" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -3274,7 +3289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="72" spans="1:6">
+    <row r="9" ht="86.4" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -3675,27 +3690,27 @@
       </c>
     </row>
     <row r="29" ht="144" spans="1:6">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="144" spans="1:6">
-      <c r="A30" s="4" t="s">
+    <row r="30" ht="39" customHeight="1" spans="1:6">
+      <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -3705,124 +3720,124 @@
         <v>94</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" ht="144" spans="1:6">
-      <c r="A31" s="9" t="s">
-        <v>42</v>
+      <c r="A31" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" ht="39" customHeight="1" spans="1:6">
-      <c r="A32" s="9" t="s">
-        <v>42</v>
+    <row r="32" ht="144" spans="1:6">
+      <c r="A32" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="F32" s="10" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" ht="57.6" spans="1:6">
       <c r="A33" s="4" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" ht="100.8" spans="1:6">
       <c r="A34" s="4" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" ht="129.6" spans="1:6">
       <c r="A35" s="4" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" ht="72" spans="1:6">
       <c r="A36" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>19</v>
@@ -3836,13 +3851,13 @@
     </row>
     <row r="37" ht="72" spans="1:6">
       <c r="A37" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>19</v>
@@ -3856,73 +3871,73 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="E39" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="F40" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" ht="43.2" spans="1:6">
       <c r="A41" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>19</v>
@@ -3931,18 +3946,18 @@
         <v>70</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" ht="43.2" spans="1:6">
       <c r="A42" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>19</v>
@@ -3951,18 +3966,18 @@
         <v>70</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" ht="115.2" spans="1:6">
       <c r="A43" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>19</v>
@@ -3971,18 +3986,18 @@
         <v>70</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" ht="123" customHeight="1" spans="1:6">
       <c r="A44" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>19</v>
@@ -3991,38 +4006,38 @@
         <v>70</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" ht="115.2" spans="1:6">
       <c r="A45" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" ht="115.2" spans="1:6">
       <c r="A46" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>19</v>
@@ -4031,18 +4046,18 @@
         <v>45</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" ht="115.2" spans="1:6">
       <c r="A47" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>19</v>
@@ -4051,18 +4066,18 @@
         <v>45</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" ht="115.2" spans="1:6">
       <c r="A48" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>19</v>
@@ -4071,18 +4086,18 @@
         <v>45</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" ht="115.2" spans="1:6">
       <c r="A49" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>19</v>
@@ -4091,18 +4106,18 @@
         <v>45</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" ht="119" customHeight="1" spans="1:6">
       <c r="A50" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>19</v>
@@ -4111,18 +4126,18 @@
         <v>45</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" ht="115.2" spans="1:6">
       <c r="A51" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>19</v>
@@ -4131,18 +4146,18 @@
         <v>45</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" ht="33" customHeight="1" spans="1:6">
       <c r="A52" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>19</v>
@@ -4151,18 +4166,18 @@
         <v>45</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" ht="29" customHeight="1" spans="1:6">
       <c r="A53" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>19</v>
@@ -4171,118 +4186,118 @@
         <v>45</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" ht="43.2" spans="1:6">
       <c r="A54" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B54" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F54" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="55" ht="43.2" spans="1:6">
       <c r="A55" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="1:6">
       <c r="A56" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B56" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C56" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>164</v>
-      </c>
       <c r="F56" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" ht="29" customHeight="1" spans="1:6">
       <c r="A57" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" ht="43.2" spans="1:6">
       <c r="A58" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" ht="35" customHeight="1" spans="1:6">
       <c r="A59" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>19</v>
@@ -4291,138 +4306,138 @@
         <v>45</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" ht="43.2" spans="1:6">
       <c r="A60" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" ht="43.2" spans="1:6">
       <c r="A61" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F61" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="62" ht="43.2" spans="1:6">
       <c r="A62" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" ht="43.2" spans="1:6">
       <c r="A63" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" ht="43.2" spans="1:6">
       <c r="A64" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" ht="43.2" spans="1:6">
       <c r="A65" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" ht="72" spans="1:6">
       <c r="A66" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>19</v>
@@ -4436,13 +4451,13 @@
     </row>
     <row r="67" ht="72" spans="1:6">
       <c r="A67" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>19</v>
@@ -4456,13 +4471,13 @@
     </row>
     <row r="68" ht="72" spans="1:6">
       <c r="A68" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>19</v>
@@ -4476,13 +4491,13 @@
     </row>
     <row r="69" ht="72" spans="1:6">
       <c r="A69" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>19</v>
@@ -4496,13 +4511,13 @@
     </row>
     <row r="70" ht="72" spans="1:6">
       <c r="A70" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>19</v>
@@ -4516,13 +4531,13 @@
     </row>
     <row r="71" ht="72" spans="1:6">
       <c r="A71" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>19</v>
@@ -4536,13 +4551,13 @@
     </row>
     <row r="72" ht="72" spans="1:6">
       <c r="A72" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>19</v>
@@ -4556,13 +4571,13 @@
     </row>
     <row r="73" ht="72" spans="1:6">
       <c r="A73" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>19</v>
@@ -4576,13 +4591,13 @@
     </row>
     <row r="74" ht="72" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>19</v>
@@ -4596,13 +4611,13 @@
     </row>
     <row r="75" ht="72" spans="1:6">
       <c r="A75" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>19</v>
@@ -4616,13 +4631,13 @@
     </row>
     <row r="76" ht="75" customHeight="1" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>19</v>
@@ -4636,13 +4651,13 @@
     </row>
     <row r="77" ht="72" spans="1:6">
       <c r="A77" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>19</v>
@@ -4656,13 +4671,13 @@
     </row>
     <row r="78" ht="72" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>19</v>
@@ -4676,13 +4691,13 @@
     </row>
     <row r="79" ht="72" spans="1:6">
       <c r="A79" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>19</v>
@@ -4696,13 +4711,13 @@
     </row>
     <row r="80" ht="72" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>19</v>
@@ -4716,13 +4731,13 @@
     </row>
     <row r="81" ht="72" spans="1:6">
       <c r="A81" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>19</v>
@@ -4736,13 +4751,13 @@
     </row>
     <row r="82" ht="72" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>19</v>
@@ -4756,13 +4771,13 @@
     </row>
     <row r="83" ht="72" spans="1:6">
       <c r="A83" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>19</v>
@@ -4776,13 +4791,13 @@
     </row>
     <row r="84" ht="27" customHeight="1" spans="1:6">
       <c r="A84" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>19</v>
@@ -4796,13 +4811,13 @@
     </row>
     <row r="85" ht="60" customHeight="1" spans="1:6">
       <c r="A85" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>19</v>
@@ -4811,138 +4826,138 @@
         <v>45</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" ht="57.6" spans="1:6">
       <c r="A86" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B86" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="87" ht="72" spans="1:6">
       <c r="A87" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" ht="72" spans="1:6">
       <c r="A88" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B88" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F88" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="89" ht="72" spans="1:6">
       <c r="A89" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="F89" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" ht="72" spans="1:6">
       <c r="A90" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" ht="72" spans="1:6">
       <c r="A91" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" ht="28.8" spans="1:6">
       <c r="A92" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>19</v>
@@ -4951,118 +4966,118 @@
         <v>45</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" ht="43.2" spans="1:6">
       <c r="A93" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B93" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F93" s="10" t="s">
         <v>253</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="94" ht="57.6" spans="1:6">
       <c r="A94" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95" ht="115.2" spans="1:6">
       <c r="A95" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F95" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="96" ht="115.2" spans="1:6">
       <c r="A96" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="97" ht="115.2" spans="1:6">
       <c r="A97" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F97" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" ht="28.8" spans="1:6">
       <c r="A98" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>19</v>
@@ -5076,13 +5091,13 @@
     </row>
     <row r="99" ht="28.8" spans="1:6">
       <c r="A99" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>19</v>
@@ -5094,13 +5109,13 @@
     </row>
     <row r="100" ht="28.8" spans="1:6">
       <c r="A100" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>19</v>
@@ -5112,13 +5127,13 @@
     </row>
     <row r="101" ht="28.8" spans="1:6">
       <c r="A101" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>19</v>
@@ -5130,13 +5145,13 @@
     </row>
     <row r="102" ht="28.8" spans="1:6">
       <c r="A102" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>19</v>
@@ -5148,13 +5163,13 @@
     </row>
     <row r="103" ht="28.8" spans="1:6">
       <c r="A103" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>19</v>
@@ -5166,13 +5181,13 @@
     </row>
     <row r="104" ht="28.8" spans="1:6">
       <c r="A104" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>19</v>
@@ -5184,13 +5199,13 @@
     </row>
     <row r="105" ht="28.8" spans="1:6">
       <c r="A105" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>19</v>
@@ -5202,13 +5217,13 @@
     </row>
     <row r="106" ht="28.8" spans="1:6">
       <c r="A106" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>19</v>
@@ -5220,13 +5235,13 @@
     </row>
     <row r="107" ht="28.8" spans="1:6">
       <c r="A107" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>19</v>
@@ -5238,13 +5253,13 @@
     </row>
     <row r="108" ht="28.8" spans="1:6">
       <c r="A108" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>19</v>
@@ -5256,13 +5271,13 @@
     </row>
     <row r="109" ht="57.6" spans="1:6">
       <c r="A109" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>19</v>
@@ -5274,13 +5289,13 @@
     </row>
     <row r="110" ht="43.2" spans="1:6">
       <c r="A110" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>19</v>
@@ -5292,13 +5307,13 @@
     </row>
     <row r="111" ht="43.2" spans="1:6">
       <c r="A111" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>19</v>
@@ -5310,13 +5325,13 @@
     </row>
     <row r="112" ht="43.2" spans="1:6">
       <c r="A112" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>19</v>
@@ -5328,13 +5343,13 @@
     </row>
     <row r="113" ht="43.2" spans="1:6">
       <c r="A113" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>19</v>
@@ -5346,13 +5361,13 @@
     </row>
     <row r="114" ht="43.2" spans="1:6">
       <c r="A114" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>19</v>
@@ -5364,13 +5379,13 @@
     </row>
     <row r="115" ht="43.2" spans="1:6">
       <c r="A115" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>19</v>
@@ -5382,13 +5397,13 @@
     </row>
     <row r="116" ht="43.2" spans="1:6">
       <c r="A116" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>19</v>
@@ -5400,13 +5415,13 @@
     </row>
     <row r="117" ht="28.8" spans="1:6">
       <c r="A117" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>19</v>
@@ -5418,13 +5433,13 @@
     </row>
     <row r="118" ht="28.8" spans="1:6">
       <c r="A118" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>19</v>
@@ -5436,13 +5451,13 @@
     </row>
     <row r="119" ht="28.8" spans="1:6">
       <c r="A119" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>19</v>
@@ -5454,13 +5469,13 @@
     </row>
     <row r="120" ht="28.8" spans="1:6">
       <c r="A120" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>19</v>
@@ -5472,13 +5487,13 @@
     </row>
     <row r="121" ht="28.8" spans="1:6">
       <c r="A121" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>19</v>
@@ -5490,13 +5505,13 @@
     </row>
     <row r="122" ht="28.8" spans="1:6">
       <c r="A122" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>19</v>
@@ -5508,13 +5523,13 @@
     </row>
     <row r="123" ht="28.8" spans="1:6">
       <c r="A123" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>19</v>
@@ -5526,13 +5541,13 @@
     </row>
     <row r="124" ht="28.8" spans="1:6">
       <c r="A124" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>19</v>
@@ -5544,13 +5559,13 @@
     </row>
     <row r="125" ht="28.8" spans="1:6">
       <c r="A125" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>19</v>
@@ -5562,13 +5577,13 @@
     </row>
     <row r="126" ht="28.8" spans="1:6">
       <c r="A126" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>19</v>
@@ -5580,13 +5595,13 @@
     </row>
     <row r="127" ht="28.8" spans="1:6">
       <c r="A127" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>19</v>
@@ -5598,13 +5613,13 @@
     </row>
     <row r="128" ht="28.8" spans="1:6">
       <c r="A128" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>19</v>
@@ -5616,13 +5631,13 @@
     </row>
     <row r="129" ht="28.8" spans="1:6">
       <c r="A129" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>19</v>
@@ -5634,13 +5649,13 @@
     </row>
     <row r="130" ht="28.8" spans="1:6">
       <c r="A130" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>19</v>
@@ -5652,13 +5667,13 @@
     </row>
     <row r="131" ht="43.2" spans="1:6">
       <c r="A131" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>19</v>
@@ -5670,13 +5685,13 @@
     </row>
     <row r="132" ht="43.2" spans="1:6">
       <c r="A132" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>19</v>
@@ -5688,13 +5703,13 @@
     </row>
     <row r="133" ht="28.8" spans="1:6">
       <c r="A133" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>19</v>
@@ -5706,13 +5721,13 @@
     </row>
     <row r="134" ht="28.8" spans="1:6">
       <c r="A134" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>19</v>
@@ -5724,13 +5739,13 @@
     </row>
     <row r="135" ht="28.8" spans="1:6">
       <c r="A135" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>19</v>
@@ -5742,13 +5757,13 @@
     </row>
     <row r="136" ht="28.8" spans="1:6">
       <c r="A136" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>19</v>
@@ -5760,13 +5775,13 @@
     </row>
     <row r="137" ht="28.8" spans="1:6">
       <c r="A137" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>19</v>
@@ -5778,13 +5793,13 @@
     </row>
     <row r="138" ht="28.8" spans="1:6">
       <c r="A138" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>19</v>
@@ -5796,13 +5811,13 @@
     </row>
     <row r="139" ht="28.8" spans="1:6">
       <c r="A139" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>19</v>
@@ -5814,13 +5829,13 @@
     </row>
     <row r="140" ht="28.8" spans="1:6">
       <c r="A140" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>19</v>
@@ -5832,13 +5847,13 @@
     </row>
     <row r="141" ht="28.8" spans="1:6">
       <c r="A141" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>19</v>
@@ -5850,13 +5865,13 @@
     </row>
     <row r="142" ht="28.8" spans="1:6">
       <c r="A142" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>19</v>
@@ -5868,13 +5883,13 @@
     </row>
     <row r="143" ht="28.8" spans="1:6">
       <c r="A143" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>19</v>
@@ -5886,13 +5901,13 @@
     </row>
     <row r="144" ht="28.8" spans="1:6">
       <c r="A144" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>19</v>
@@ -5904,13 +5919,13 @@
     </row>
     <row r="145" ht="28.8" spans="1:6">
       <c r="A145" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>19</v>
@@ -5921,6 +5936,9 @@
       <c r="F145" s="18"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F145" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="F98:F145"/>
   </mergeCells>
@@ -5944,540 +5962,540 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="57.6" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
     <sheet name="标签数据信息说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$197</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="503">
   <si>
     <t>类别</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -229,9 +235,7 @@
     </r>
   </si>
   <si>
-    <t>Atlas 350 标卡（4Pmesh互联）
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+    <t>Atlas 350 标卡（4Pmesh互联）说明：旧版本指标</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_rx_X_Y</t>
@@ -287,6 +291,80 @@
   </si>
   <si>
     <t>单位：G</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口Link状态。</t>
+    </r>
+  </si>
+  <si>
+    <t>详见“标签数据信息说明”页签中“标签8”</t>
+  </si>
+  <si>
+    <t>Atlas 350 标卡（4Pmesh互联）
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口实时接收速率。使用的-time参数为100。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口实时发送速率。使用的-time参数为100。</t>
+    </r>
+  </si>
+  <si>
+    <t>npu_chip_info_link_speed</t>
+  </si>
+  <si>
+    <t>物理端口的速率。</t>
   </si>
   <si>
     <t>NPU</t>
@@ -1335,25 +1413,25 @@
     <t>单位：℃</t>
   </si>
   <si>
-    <t>npu_chip_info_optical_index_num_X_Y</t>
-  </si>
-  <si>
-    <t>芯片Udie Port链接的光模块Lane数量。X为Udie ID，Y为Port ID。</t>
+    <t>npu_chip_info_optical_index_num</t>
+  </si>
+  <si>
+    <t>芯片Udie Port链接的光模块Lane数量。</t>
   </si>
   <si>
     <t>Atlas 850 系列硬件产品</t>
   </si>
   <si>
-    <t>npu_chip_info_optical_tx_power_Z_X_Y</t>
-  </si>
-  <si>
-    <t>光模块发送功率。Z为Lane的index，取值为[0:3]，X为Udie ID，Y为Port ID。</t>
-  </si>
-  <si>
-    <t>npu_chip_info_optical_rx_power_Z_X_Y</t>
-  </si>
-  <si>
-    <t>光模块接收功率。Z为Lane的index，取值为[0:3]，X为Udie ID，Y为Port ID。X为Udie ID，Y为Port ID。</t>
+    <t>npu_chip_info_optical_tx_power_Z</t>
+  </si>
+  <si>
+    <t>光模块发送功率。Z为Lane的index，取值为[0:3]。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_optical_rx_power_Z</t>
+  </si>
+  <si>
+    <t>光模块接收功率。Z为Lane的index，取值为[0:3]。</t>
   </si>
   <si>
     <t>npu_chip_info_hbm_utilization</t>
@@ -1666,6 +1744,294 @@
   </si>
   <si>
     <t>TX坏包总报文字节数。X为Udie ID，Y为Port ID。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv4_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv4 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv6_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv6 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv4_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv4 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv6_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv6 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_compact_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG6报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ctph_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG7 CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ntph_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG7 非CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_mem_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的UB mem报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unknown_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的未知报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_drop_ind_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的带drop_ind的报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_err_ind_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的ERR报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_host_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后的落地报文数量（不包含枚举配置和管理报文）。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_imp_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后落地的枚举配置和管理报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_mar_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后落地的UB memory报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_link_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后转发到同Port的TX侧的报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_noc_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后的P2P报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_route_err_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后出现路由查表错误的报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_out_err_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过校验后的错误报文总数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_length_err_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过校验后的长度错误报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_rx_busi_flit_num</t>
+  </si>
+  <si>
+    <t>RX侧报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_rx_send_ack_flit</t>
+  </si>
+  <si>
+    <t>RX向对端返回响应的报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv4_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv4 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv6_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv6 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv4_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv4 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv6_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv6 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_compact_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG6报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ctph_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG7 CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ntph_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG7 非CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_mem_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的UB mem报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unknown_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的未知报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_drop_ind_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的带drop_ind的报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_err_ind_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的ERR报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_lpbk_ind_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送报文在NL环回的报文个数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_out_err_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的报文经过校验后的错误报文总数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_length_err_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的报文经过校验后的长度错误报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_tx_busi_flit_num</t>
+  </si>
+  <si>
+    <t>TX报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_tx_recv_ack_flit</t>
+  </si>
+  <si>
+    <t>TX收到对端响应的报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_retry_req_sum</t>
+  </si>
+  <si>
+    <t>发起重传次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_retry_ack_sum</t>
+  </si>
+  <si>
+    <t>响应重传次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_crc_error_sum</t>
+  </si>
+  <si>
+    <t>CRC校验错误次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxpausepkts</t>
+  </si>
+  <si>
+    <t>RX pause帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txpausepkts</t>
+  </si>
+  <si>
+    <t>TX pause帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxpfcpkts</t>
+  </si>
+  <si>
+    <t>RX PFC帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txpfcpkts</t>
+  </si>
+  <si>
+    <t>TX PFC帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxbadpkts</t>
+  </si>
+  <si>
+    <t>RX坏包总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txbadpkts</t>
+  </si>
+  <si>
+    <t>TX坏包总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxbadoctets</t>
+  </si>
+  <si>
+    <t>RX坏包总报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txbadoctets</t>
+  </si>
+  <si>
+    <t>TX坏包总报文字节数。</t>
   </si>
   <si>
     <t>名称</t>
@@ -1989,6 +2355,15 @@
   </si>
   <si>
     <t>product_type：昇腾AI处理器产品形态</t>
+  </si>
+  <si>
+    <t>标签8</t>
+  </si>
+  <si>
+    <t>port:Udie端口ID</t>
+  </si>
+  <si>
+    <t>udie:Ascend 950处理器的Udie ID</t>
   </si>
 </sst>
 </file>
@@ -2187,14 +2562,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
+      <color rgb="FF252B3A"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF252B3A"/>
-      <name val="宋体"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3117,12 +3492,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F145"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="42" style="7" customWidth="1"/>
-    <col min="3" max="3" width="32.6296296296296" style="7" customWidth="1"/>
+    <col min="3" max="3" width="32.6333333333333" style="7" customWidth="1"/>
     <col min="4" max="4" width="48.25" style="7" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="7" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="7" customWidth="1"/>
@@ -3209,7 +3584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="72" spans="1:6">
+    <row r="5" ht="67.5" spans="1:6">
       <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
@@ -3249,7 +3624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="72" spans="1:6">
+    <row r="7" ht="67.5" spans="1:6">
       <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
@@ -3269,7 +3644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="86.4" spans="1:6">
+    <row r="8" ht="84" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -3289,7 +3664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="86.4" spans="1:6">
+    <row r="9" ht="84" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -3309,7 +3684,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="43.2" spans="1:6">
+    <row r="10" ht="40.5" spans="1:6">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -3329,7 +3704,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="43.2" spans="1:6">
+    <row r="11" ht="40.5" spans="1:6">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -3349,7 +3724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="43.2" spans="1:6">
+    <row r="12" ht="27" spans="1:6">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -3370,2577 +3745,3524 @@
       </c>
     </row>
     <row r="13" ht="159" customHeight="1" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="D13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="E13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="5" t="s">
+    </row>
+    <row r="14" ht="159" customHeight="1" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="159" customHeight="1" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="D15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="159" customHeight="1" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" ht="159" customHeight="1" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" ht="159" customHeight="1" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="5" t="s">
+    <row r="18" ht="159" customHeight="1" spans="1:6">
+      <c r="A18" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" ht="86.4" spans="1:6">
-      <c r="A15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="11" t="s">
+      <c r="B18" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" ht="84" spans="1:6">
+      <c r="A19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" ht="201.6" spans="1:6">
-      <c r="A16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" ht="149" customHeight="1" spans="1:6">
-      <c r="A17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" ht="144" spans="1:6">
-      <c r="A18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" ht="187.2" spans="1:6">
-      <c r="A19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="9" t="s">
+    <row r="20" ht="175.5" spans="1:6">
+      <c r="A20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C20" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" ht="144" spans="1:6">
-      <c r="A20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="D20" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" ht="153" customHeight="1" spans="1:6">
+    <row r="21" ht="149" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" ht="135" spans="1:6">
+      <c r="A22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" ht="175.5" spans="1:6">
+      <c r="A23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C23" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F23" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="10" t="s">
+    </row>
+    <row r="24" ht="135" spans="1:6">
+      <c r="A24" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" ht="151" customHeight="1" spans="1:6">
-      <c r="A22" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" ht="144" spans="1:6">
-      <c r="A23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="9" t="s">
+    <row r="25" ht="153" customHeight="1" spans="1:6">
+      <c r="A25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C25" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" ht="144" spans="1:6">
-      <c r="A24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="9" t="s">
+      <c r="D25" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" ht="144" spans="1:6">
-      <c r="A25" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" ht="115.2" spans="1:6">
-      <c r="A26" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="9" t="s">
+    <row r="26" ht="151" customHeight="1" spans="1:6">
+      <c r="A26" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" ht="135" spans="1:6">
+      <c r="A27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" ht="135" spans="1:6">
+      <c r="A28" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26" s="10" t="s">
+      <c r="C28" s="7" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="27" ht="115.2" spans="1:6">
-      <c r="A27" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="9" t="s">
+      <c r="D28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="F28" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" ht="135" spans="1:6">
+      <c r="A29" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" ht="144" spans="1:6">
-      <c r="A28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="C29" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="D29" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" ht="144" spans="1:6">
-      <c r="A29" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="E29" s="9" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="39" customHeight="1" spans="1:6">
+    <row r="30" ht="108" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" ht="108" spans="1:6">
+      <c r="A31" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="D31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" ht="135" spans="1:6">
+      <c r="A32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="C32" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="10" t="s">
+      <c r="D32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="31" ht="144" spans="1:6">
-      <c r="A31" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" ht="144" spans="1:6">
-      <c r="A32" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" ht="57.6" spans="1:6">
-      <c r="A33" s="4" t="s">
+    <row r="33" ht="135" spans="1:6">
+      <c r="A33" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" ht="39" customHeight="1" spans="1:6">
+      <c r="A34" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="14" t="s">
+    </row>
+    <row r="35" ht="135" spans="1:6">
+      <c r="A35" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="34" ht="100.8" spans="1:6">
-      <c r="A34" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="D35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="10" t="s">
+      <c r="F35" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" ht="135" spans="1:6">
+      <c r="A36" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="35" ht="129.6" spans="1:6">
-      <c r="A35" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B35" s="9" t="s">
+      <c r="C36" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="D36" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" ht="54" spans="1:6">
+      <c r="A37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" s="10" t="s">
+      <c r="C37" s="14" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="36" ht="72" spans="1:6">
-      <c r="A36" s="7" t="s">
+      <c r="D37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="7" t="s">
+    </row>
+    <row r="38" ht="94.5" spans="1:6">
+      <c r="A38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C38" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="10" t="s">
+      <c r="D38" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" ht="121.5" spans="1:6">
+      <c r="A39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" ht="67.5" spans="1:6">
+      <c r="A40" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" ht="72" spans="1:6">
-      <c r="A37" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="10" t="s">
+    <row r="41" ht="67.5" spans="1:6">
+      <c r="A41" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="5" t="s">
+    <row r="42" spans="1:6">
+      <c r="A42" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" ht="40.5" spans="1:6">
+      <c r="A45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" ht="40.5" spans="1:6">
+      <c r="A46" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" ht="108" spans="1:6">
+      <c r="A47" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" ht="123" customHeight="1" spans="1:6">
+      <c r="A48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" ht="108" spans="1:6">
+      <c r="A49" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" ht="108" spans="1:6">
+      <c r="A50" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" ht="108" spans="1:6">
+      <c r="A51" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" ht="108" spans="1:6">
+      <c r="A52" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" ht="108" spans="1:6">
+      <c r="A53" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" ht="119" customHeight="1" spans="1:6">
+      <c r="A54" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" ht="108" spans="1:6">
+      <c r="A55" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" ht="33" customHeight="1" spans="1:6">
+      <c r="A56" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" ht="29" customHeight="1" spans="1:6">
+      <c r="A57" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" ht="40.5" spans="1:6">
+      <c r="A58" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" ht="40.5" spans="1:6">
+      <c r="A59" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" ht="40.5" spans="1:6">
+      <c r="A60" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" ht="29" customHeight="1" spans="1:6">
+      <c r="A61" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" ht="40.5" spans="1:6">
+      <c r="A62" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" ht="35" customHeight="1" spans="1:6">
+      <c r="A63" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" ht="40.5" spans="1:6">
+      <c r="A64" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="65" ht="40.5" spans="1:6">
+      <c r="A65" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" ht="40.5" spans="1:6">
+      <c r="A66" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" ht="40.5" spans="1:6">
+      <c r="A67" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="68" ht="40.5" spans="1:6">
+      <c r="A68" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" ht="40.5" spans="1:6">
+      <c r="A69" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" ht="67.5" spans="1:6">
+      <c r="A70" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" ht="43.2" spans="1:6">
-      <c r="A41" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42" ht="43.2" spans="1:6">
-      <c r="A42" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="43" ht="115.2" spans="1:6">
-      <c r="A43" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" ht="123" customHeight="1" spans="1:6">
-      <c r="A44" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" ht="115.2" spans="1:6">
-      <c r="A45" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" ht="115.2" spans="1:6">
-      <c r="A46" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" ht="115.2" spans="1:6">
-      <c r="A47" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" ht="115.2" spans="1:6">
-      <c r="A48" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" ht="115.2" spans="1:6">
-      <c r="A49" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" ht="119" customHeight="1" spans="1:6">
-      <c r="A50" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" ht="115.2" spans="1:6">
-      <c r="A51" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" ht="33" customHeight="1" spans="1:6">
-      <c r="A52" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="53" ht="29" customHeight="1" spans="1:6">
-      <c r="A53" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="54" ht="43.2" spans="1:6">
-      <c r="A54" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="55" ht="43.2" spans="1:6">
-      <c r="A55" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="56" ht="43.2" spans="1:6">
-      <c r="A56" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="57" ht="29" customHeight="1" spans="1:6">
-      <c r="A57" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="58" ht="43.2" spans="1:6">
-      <c r="A58" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="59" ht="35" customHeight="1" spans="1:6">
-      <c r="A59" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" ht="43.2" spans="1:6">
-      <c r="A60" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61" ht="43.2" spans="1:6">
-      <c r="A61" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="62" ht="43.2" spans="1:6">
-      <c r="A62" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="63" ht="43.2" spans="1:6">
-      <c r="A63" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" ht="43.2" spans="1:6">
-      <c r="A64" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="65" ht="43.2" spans="1:6">
-      <c r="A65" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" ht="72" spans="1:6">
-      <c r="A66" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" ht="72" spans="1:6">
-      <c r="A67" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" ht="72" spans="1:6">
-      <c r="A68" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" ht="72" spans="1:6">
-      <c r="A69" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C69" s="5" t="s">
+      <c r="B70" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D69" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" ht="72" spans="1:6">
-      <c r="A70" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B70" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="D70" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F70" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="71" ht="72" spans="1:6">
+    <row r="71" ht="67.5" spans="1:6">
       <c r="A71" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B71" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="D71" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="72" ht="72" spans="1:6">
+    <row r="72" ht="67.5" spans="1:6">
       <c r="A72" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="D72" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="73" ht="72" spans="1:6">
+    <row r="73" ht="67.5" spans="1:6">
       <c r="A73" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B73" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="D73" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="74" ht="72" spans="1:6">
+    <row r="74" ht="67.5" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B74" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>208</v>
-      </c>
       <c r="D74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="75" ht="72" spans="1:6">
+    <row r="75" ht="67.5" spans="1:6">
       <c r="A75" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B75" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>210</v>
-      </c>
       <c r="D75" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="76" ht="75" customHeight="1" spans="1:6">
+    <row r="76" ht="67.5" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B76" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>212</v>
-      </c>
       <c r="D76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F76" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="77" ht="72" spans="1:6">
+    <row r="77" ht="67.5" spans="1:6">
       <c r="A77" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B77" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>214</v>
-      </c>
       <c r="D77" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="78" ht="72" spans="1:6">
+    <row r="78" ht="67.5" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B78" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="D78" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F78" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="79" ht="72" spans="1:6">
+    <row r="79" ht="67.5" spans="1:6">
       <c r="A79" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B79" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>218</v>
-      </c>
       <c r="D79" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="80" ht="72" spans="1:6">
+    <row r="80" ht="75" customHeight="1" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B80" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="D80" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="81" ht="72" spans="1:6">
+    <row r="81" ht="67.5" spans="1:6">
       <c r="A81" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B81" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>222</v>
-      </c>
       <c r="D81" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="82" ht="72" spans="1:6">
+    <row r="82" ht="67.5" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B82" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>224</v>
-      </c>
       <c r="D82" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="83" ht="72" spans="1:6">
+    <row r="83" ht="67.5" spans="1:6">
       <c r="A83" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B83" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>226</v>
-      </c>
       <c r="D83" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="84" ht="27" customHeight="1" spans="1:6">
+    <row r="84" ht="67.5" spans="1:6">
       <c r="A84" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B84" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>228</v>
-      </c>
       <c r="D84" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F84" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1" spans="1:6">
+    <row r="85" ht="67.5" spans="1:6">
       <c r="A85" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="D85" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" ht="67.5" spans="1:6">
+      <c r="A86" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C86" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D85" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F85" s="10" t="s">
+      <c r="D86" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" ht="67.5" spans="1:6">
+      <c r="A87" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="86" ht="57.6" spans="1:6">
-      <c r="A86" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B86" s="13" t="s">
+      <c r="C87" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="D87" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" ht="27" customHeight="1" spans="1:6">
+      <c r="A88" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="87" ht="72" spans="1:6">
-      <c r="A87" s="5" t="s">
+      <c r="C88" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="D88" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1" spans="1:6">
+      <c r="A89" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="B89" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="D87" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87" s="13" t="s">
+      <c r="C89" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="88" ht="72" spans="1:6">
-      <c r="A88" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="89" ht="72" spans="1:6">
-      <c r="A89" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="D89" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>242</v>
+        <v>52</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="90" ht="72" spans="1:6">
+    <row r="90" ht="54" spans="1:6">
       <c r="A90" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>246</v>
+        <v>236</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>241</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>247</v>
+        <v>52</v>
       </c>
       <c r="F90" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="91" ht="72" spans="1:6">
+    <row r="91" ht="67.5" spans="1:6">
       <c r="A91" s="5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B91" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="92" ht="67.5" spans="1:6">
+      <c r="A92" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="D92" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" s="5" t="s">
+      <c r="F92" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="93" ht="67.5" spans="1:6">
+      <c r="A93" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="92" ht="28.8" spans="1:6">
-      <c r="A92" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B92" s="5" t="s">
+      <c r="C93" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="D93" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="94" ht="67.5" spans="1:6">
+      <c r="A94" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F92" s="10" t="s">
+      <c r="C94" s="5" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="93" ht="43.2" spans="1:6">
-      <c r="A93" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B93" s="5" t="s">
+      <c r="D94" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="F94" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="95" ht="67.5" spans="1:6">
+      <c r="A95" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="D93" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="5" t="s">
+      <c r="C95" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="96" ht="27" spans="1:6">
+      <c r="A96" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="94" ht="57.6" spans="1:6">
-      <c r="A94" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="5" t="s">
+      <c r="B96" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="97" ht="27" spans="1:6">
+      <c r="A97" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="F94" s="10" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="95" ht="115.2" spans="1:6">
-      <c r="A95" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F95" s="13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="96" ht="115.2" spans="1:6">
-      <c r="A96" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B96" s="9" t="s">
+      <c r="B97" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F97" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="C96" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F96" s="13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="97" ht="115.2" spans="1:6">
-      <c r="A97" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B97" s="9" t="s">
+    </row>
+    <row r="98" ht="27" spans="1:6">
+      <c r="A98" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B98" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="C97" s="9" t="s">
+      <c r="C98" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E97" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F97" s="13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="98" ht="28.8" spans="1:6">
-      <c r="A98" s="5" t="s">
+      <c r="D98" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="99" ht="108" spans="1:6">
+      <c r="A99" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B99" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="C99" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="D99" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" ht="108" spans="1:6">
+      <c r="A100" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F98" s="16" t="s">
+      <c r="C100" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="101" ht="108" spans="1:6">
+      <c r="A101" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="102" ht="27" spans="1:6">
+      <c r="A102" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F102" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="99" ht="28.8" spans="1:6">
-      <c r="A99" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F99" s="17"/>
-    </row>
-    <row r="100" ht="28.8" spans="1:6">
-      <c r="A100" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F100" s="17"/>
-    </row>
-    <row r="101" ht="28.8" spans="1:6">
-      <c r="A101" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F101" s="17"/>
-    </row>
-    <row r="102" ht="28.8" spans="1:6">
-      <c r="A102" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C102" s="5" t="s">
+    <row r="103" ht="27" spans="1:6">
+      <c r="A103" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F102" s="17"/>
-    </row>
-    <row r="103" ht="28.8" spans="1:6">
-      <c r="A103" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B103" s="5" t="s">
+      <c r="C103" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="D103" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F103" s="17"/>
+    </row>
+    <row r="104" ht="27" spans="1:6">
+      <c r="A104" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F103" s="17"/>
-    </row>
-    <row r="104" ht="28.8" spans="1:6">
-      <c r="A104" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B104" s="5" t="s">
+      <c r="C104" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="D104" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F104" s="17"/>
+    </row>
+    <row r="105" ht="27" spans="1:6">
+      <c r="A105" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F104" s="17"/>
-    </row>
-    <row r="105" ht="28.8" spans="1:6">
-      <c r="A105" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B105" s="5" t="s">
+      <c r="C105" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="D105" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F105" s="17"/>
+    </row>
+    <row r="106" ht="27" spans="1:6">
+      <c r="A106" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D105" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F105" s="17"/>
-    </row>
-    <row r="106" ht="28.8" spans="1:6">
-      <c r="A106" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B106" s="5" t="s">
+      <c r="C106" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="D106" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F106" s="17"/>
+    </row>
+    <row r="107" ht="27" spans="1:6">
+      <c r="A107" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="D106" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F106" s="17"/>
-    </row>
-    <row r="107" ht="28.8" spans="1:6">
-      <c r="A107" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B107" s="5" t="s">
+      <c r="C107" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="D107" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F107" s="17"/>
+    </row>
+    <row r="108" ht="27" spans="1:6">
+      <c r="A108" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B108" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="D107" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F107" s="17"/>
-    </row>
-    <row r="108" ht="28.8" spans="1:6">
-      <c r="A108" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B108" s="5" t="s">
+      <c r="C108" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="D108" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F108" s="17"/>
+    </row>
+    <row r="109" ht="27" spans="1:6">
+      <c r="A109" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B109" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="D108" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F108" s="17"/>
-    </row>
-    <row r="109" ht="57.6" spans="1:6">
-      <c r="A109" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B109" s="5" t="s">
+      <c r="C109" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C109" s="5" t="s">
+      <c r="D109" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F109" s="17"/>
+    </row>
+    <row r="110" ht="27" spans="1:6">
+      <c r="A110" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D109" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F109" s="17"/>
-    </row>
-    <row r="110" ht="43.2" spans="1:6">
-      <c r="A110" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B110" s="5" t="s">
+      <c r="C110" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="D110" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F110" s="17"/>
+    </row>
+    <row r="111" ht="27" spans="1:6">
+      <c r="A111" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="D110" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F110" s="17"/>
-    </row>
-    <row r="111" ht="43.2" spans="1:6">
-      <c r="A111" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B111" s="5" t="s">
+      <c r="C111" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="D111" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F111" s="17"/>
+    </row>
+    <row r="112" ht="27" spans="1:6">
+      <c r="A112" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B112" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F111" s="17"/>
-    </row>
-    <row r="112" ht="43.2" spans="1:6">
-      <c r="A112" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B112" s="5" t="s">
+      <c r="C112" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="D112" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F112" s="17"/>
+    </row>
+    <row r="113" ht="40.5" spans="1:6">
+      <c r="A113" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D112" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F112" s="17"/>
-    </row>
-    <row r="113" ht="43.2" spans="1:6">
-      <c r="A113" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B113" s="5" t="s">
+      <c r="C113" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="D113" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F113" s="17"/>
+    </row>
+    <row r="114" ht="40.5" spans="1:6">
+      <c r="A114" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="D113" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F113" s="17"/>
-    </row>
-    <row r="114" ht="43.2" spans="1:6">
-      <c r="A114" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B114" s="5" t="s">
+      <c r="C114" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="D114" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F114" s="17"/>
+    </row>
+    <row r="115" ht="40.5" spans="1:6">
+      <c r="A115" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="D114" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F114" s="17"/>
-    </row>
-    <row r="115" ht="43.2" spans="1:6">
-      <c r="A115" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B115" s="5" t="s">
+      <c r="C115" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="D115" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F115" s="17"/>
+    </row>
+    <row r="116" ht="40.5" spans="1:6">
+      <c r="A116" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="D115" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F115" s="17"/>
-    </row>
-    <row r="116" ht="43.2" spans="1:6">
-      <c r="A116" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B116" s="5" t="s">
+      <c r="C116" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="D116" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F116" s="17"/>
+    </row>
+    <row r="117" ht="27" spans="1:6">
+      <c r="A117" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="D116" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F116" s="17"/>
-    </row>
-    <row r="117" ht="28.8" spans="1:6">
-      <c r="A117" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B117" s="5" t="s">
+      <c r="C117" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="D117" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F117" s="17"/>
+    </row>
+    <row r="118" ht="40.5" spans="1:6">
+      <c r="A118" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B118" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="D117" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F117" s="17"/>
-    </row>
-    <row r="118" ht="28.8" spans="1:6">
-      <c r="A118" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B118" s="5" t="s">
+      <c r="C118" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="D118" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F118" s="17"/>
+    </row>
+    <row r="119" ht="27" spans="1:6">
+      <c r="A119" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="D118" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F118" s="17"/>
-    </row>
-    <row r="119" ht="28.8" spans="1:6">
-      <c r="A119" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B119" s="5" t="s">
+      <c r="C119" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="D119" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F119" s="17"/>
+    </row>
+    <row r="120" ht="40.5" spans="1:6">
+      <c r="A120" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D119" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F119" s="17"/>
-    </row>
-    <row r="120" ht="28.8" spans="1:6">
-      <c r="A120" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B120" s="5" t="s">
+      <c r="C120" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="D120" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F120" s="17"/>
+    </row>
+    <row r="121" ht="27" spans="1:6">
+      <c r="A121" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="D120" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F120" s="17"/>
-    </row>
-    <row r="121" ht="28.8" spans="1:6">
-      <c r="A121" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B121" s="5" t="s">
+      <c r="C121" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="C121" s="5" t="s">
+      <c r="D121" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F121" s="17"/>
+    </row>
+    <row r="122" ht="27" spans="1:6">
+      <c r="A122" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="D121" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F121" s="17"/>
-    </row>
-    <row r="122" ht="28.8" spans="1:6">
-      <c r="A122" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B122" s="5" t="s">
+      <c r="C122" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="D122" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F122" s="17"/>
+    </row>
+    <row r="123" ht="27" spans="1:6">
+      <c r="A123" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="D122" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F122" s="17"/>
-    </row>
-    <row r="123" ht="28.8" spans="1:6">
-      <c r="A123" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B123" s="5" t="s">
+      <c r="C123" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="D123" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F123" s="17"/>
+    </row>
+    <row r="124" ht="27" spans="1:6">
+      <c r="A124" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D123" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F123" s="17"/>
-    </row>
-    <row r="124" ht="28.8" spans="1:6">
-      <c r="A124" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B124" s="5" t="s">
+      <c r="C124" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="C124" s="5" t="s">
+      <c r="D124" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F124" s="17"/>
+    </row>
+    <row r="125" ht="27" spans="1:6">
+      <c r="A125" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="D124" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F124" s="17"/>
-    </row>
-    <row r="125" ht="28.8" spans="1:6">
-      <c r="A125" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B125" s="5" t="s">
+      <c r="C125" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="D125" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F125" s="17"/>
+    </row>
+    <row r="126" ht="27" spans="1:6">
+      <c r="A126" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B126" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="D125" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F125" s="17"/>
-    </row>
-    <row r="126" ht="28.8" spans="1:6">
-      <c r="A126" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B126" s="5" t="s">
+      <c r="C126" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="D126" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F126" s="17"/>
+    </row>
+    <row r="127" ht="27" spans="1:6">
+      <c r="A127" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="D126" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F126" s="17"/>
-    </row>
-    <row r="127" ht="28.8" spans="1:6">
-      <c r="A127" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B127" s="5" t="s">
+      <c r="C127" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="D127" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F127" s="17"/>
+    </row>
+    <row r="128" ht="27" spans="1:6">
+      <c r="A128" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B128" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F127" s="17"/>
-    </row>
-    <row r="128" ht="28.8" spans="1:6">
-      <c r="A128" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B128" s="5" t="s">
+      <c r="C128" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="D128" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F128" s="17"/>
+    </row>
+    <row r="129" ht="27" spans="1:6">
+      <c r="A129" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="D128" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F128" s="17"/>
-    </row>
-    <row r="129" ht="28.8" spans="1:6">
-      <c r="A129" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B129" s="5" t="s">
+      <c r="C129" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="C129" s="5" t="s">
+      <c r="D129" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F129" s="17"/>
+    </row>
+    <row r="130" ht="27" spans="1:6">
+      <c r="A130" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B130" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="D129" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F129" s="17"/>
-    </row>
-    <row r="130" ht="28.8" spans="1:6">
-      <c r="A130" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B130" s="5" t="s">
+      <c r="C130" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="D130" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F130" s="17"/>
+    </row>
+    <row r="131" ht="27" spans="1:6">
+      <c r="A131" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B131" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F130" s="17"/>
-    </row>
-    <row r="131" ht="43.2" spans="1:6">
-      <c r="A131" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B131" s="5" t="s">
+      <c r="C131" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="D131" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F131" s="17"/>
+    </row>
+    <row r="132" ht="27" spans="1:6">
+      <c r="A132" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="D131" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F131" s="17"/>
-    </row>
-    <row r="132" ht="43.2" spans="1:6">
-      <c r="A132" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B132" s="5" t="s">
+      <c r="C132" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="D132" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F132" s="17"/>
+    </row>
+    <row r="133" ht="27" spans="1:6">
+      <c r="A133" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F132" s="17"/>
-    </row>
-    <row r="133" ht="28.8" spans="1:6">
-      <c r="A133" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B133" s="5" t="s">
+      <c r="C133" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="D133" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F133" s="17"/>
+    </row>
+    <row r="134" ht="27" spans="1:6">
+      <c r="A134" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B134" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F133" s="17"/>
-    </row>
-    <row r="134" ht="28.8" spans="1:6">
-      <c r="A134" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B134" s="5" t="s">
+      <c r="C134" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="D134" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F134" s="17"/>
+    </row>
+    <row r="135" ht="27" spans="1:6">
+      <c r="A135" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F134" s="17"/>
-    </row>
-    <row r="135" ht="28.8" spans="1:6">
-      <c r="A135" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B135" s="5" t="s">
+      <c r="C135" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C135" s="5" t="s">
+      <c r="D135" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F135" s="17"/>
+    </row>
+    <row r="136" ht="40.5" spans="1:6">
+      <c r="A136" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B136" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D135" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F135" s="17"/>
-    </row>
-    <row r="136" ht="28.8" spans="1:6">
-      <c r="A136" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B136" s="5" t="s">
+      <c r="C136" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="D136" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F136" s="17"/>
+    </row>
+    <row r="137" ht="27" spans="1:6">
+      <c r="A137" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="D136" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F136" s="17"/>
-    </row>
-    <row r="137" ht="28.8" spans="1:6">
-      <c r="A137" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B137" s="5" t="s">
+      <c r="C137" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="D137" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F137" s="17"/>
+    </row>
+    <row r="138" ht="27" spans="1:6">
+      <c r="A138" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="D137" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F137" s="17"/>
-    </row>
-    <row r="138" ht="28.8" spans="1:6">
-      <c r="A138" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B138" s="5" t="s">
+      <c r="C138" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="D138" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F138" s="17"/>
+    </row>
+    <row r="139" ht="27" spans="1:6">
+      <c r="A139" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D138" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F138" s="17"/>
-    </row>
-    <row r="139" ht="28.8" spans="1:6">
-      <c r="A139" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B139" s="5" t="s">
+      <c r="C139" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="D139" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F139" s="17"/>
+    </row>
+    <row r="140" ht="27" spans="1:6">
+      <c r="A140" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="D139" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F139" s="17"/>
-    </row>
-    <row r="140" ht="28.8" spans="1:6">
-      <c r="A140" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B140" s="5" t="s">
+      <c r="C140" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="D140" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F140" s="17"/>
+    </row>
+    <row r="141" ht="27" spans="1:6">
+      <c r="A141" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="D140" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F140" s="17"/>
-    </row>
-    <row r="141" ht="28.8" spans="1:6">
-      <c r="A141" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B141" s="5" t="s">
+      <c r="C141" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C141" s="5" t="s">
+      <c r="D141" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F141" s="17"/>
+    </row>
+    <row r="142" ht="27" spans="1:6">
+      <c r="A142" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="D141" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F141" s="17"/>
-    </row>
-    <row r="142" ht="28.8" spans="1:6">
-      <c r="A142" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B142" s="5" t="s">
+      <c r="C142" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="D142" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F142" s="17"/>
+    </row>
+    <row r="143" ht="27" spans="1:6">
+      <c r="A143" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F142" s="17"/>
-    </row>
-    <row r="143" ht="28.8" spans="1:6">
-      <c r="A143" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B143" s="5" t="s">
+      <c r="C143" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="D143" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F143" s="17"/>
+    </row>
+    <row r="144" ht="27" spans="1:6">
+      <c r="A144" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B144" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="D143" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F143" s="17"/>
-    </row>
-    <row r="144" ht="28.8" spans="1:6">
-      <c r="A144" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B144" s="5" t="s">
+      <c r="C144" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="C144" s="5" t="s">
+      <c r="D144" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F144" s="17"/>
+    </row>
+    <row r="145" ht="27" spans="1:6">
+      <c r="A145" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="D144" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F144" s="17"/>
-    </row>
-    <row r="145" ht="28.8" spans="1:6">
-      <c r="A145" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B145" s="5" t="s">
+      <c r="C145" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="D145" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F145" s="17"/>
+    </row>
+    <row r="146" ht="27" spans="1:6">
+      <c r="A146" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B146" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="D145" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F145" s="18"/>
+      <c r="C146" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F146" s="17"/>
+    </row>
+    <row r="147" ht="27" spans="1:6">
+      <c r="A147" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F147" s="17"/>
+    </row>
+    <row r="148" ht="27" spans="1:6">
+      <c r="A148" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F148" s="17"/>
+    </row>
+    <row r="149" ht="27" spans="1:6">
+      <c r="A149" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F149" s="18"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F150" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F151" s="17"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F152" s="17"/>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F153" s="17"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F154" s="17"/>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F155" s="17"/>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F156" s="17"/>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F157" s="17"/>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F158" s="17"/>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F159" s="17"/>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F160" s="17"/>
+    </row>
+    <row r="161" ht="40.5" spans="1:6">
+      <c r="A161" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F161" s="17"/>
+    </row>
+    <row r="162" ht="27" spans="1:6">
+      <c r="A162" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F162" s="17"/>
+    </row>
+    <row r="163" ht="27" spans="1:6">
+      <c r="A163" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F163" s="17"/>
+    </row>
+    <row r="164" ht="27" spans="1:6">
+      <c r="A164" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F164" s="17"/>
+    </row>
+    <row r="165" ht="27" spans="1:6">
+      <c r="A165" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F165" s="17"/>
+    </row>
+    <row r="166" ht="27" spans="1:6">
+      <c r="A166" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F166" s="17"/>
+    </row>
+    <row r="167" ht="27" spans="1:6">
+      <c r="A167" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F167" s="17"/>
+    </row>
+    <row r="168" ht="27" spans="1:6">
+      <c r="A168" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F168" s="17"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F169" s="17"/>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F170" s="17"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F171" s="17"/>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F172" s="17"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F173" s="17"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F174" s="17"/>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F175" s="17"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F176" s="17"/>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F177" s="17"/>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F178" s="17"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F179" s="17"/>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F180" s="17"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F181" s="17"/>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F182" s="17"/>
+    </row>
+    <row r="183" ht="27" spans="1:6">
+      <c r="A183" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F183" s="17"/>
+    </row>
+    <row r="184" ht="27" spans="1:6">
+      <c r="A184" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F184" s="17"/>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F185" s="17"/>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F186" s="17"/>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F187" s="17"/>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F188" s="17"/>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F189" s="17"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F190" s="17"/>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F191" s="17"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F192" s="17"/>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F193" s="17"/>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F194" s="17"/>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F195" s="17"/>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F196" s="17"/>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F197" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F145" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F197" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="F98:F145"/>
+  <mergeCells count="2">
+    <mergeCell ref="F102:F149"/>
+    <mergeCell ref="F150:F197"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
@@ -5951,555 +7273,638 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:C67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.6296296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="73.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.8833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>362</v>
+        <v>465</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>363</v>
+        <v>466</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>364</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>365</v>
+        <v>468</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>373</v>
+        <v>476</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>374</v>
+        <v>477</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>375</v>
+        <v>478</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>376</v>
+        <v>479</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
-        <v>377</v>
+        <v>480</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>378</v>
+        <v>481</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>379</v>
+        <v>482</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>380</v>
+        <v>483</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>381</v>
+        <v>484</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>382</v>
+        <v>485</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>383</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>384</v>
+        <v>487</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>385</v>
+        <v>488</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>386</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>387</v>
+        <v>490</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
-        <v>377</v>
+        <v>480</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>378</v>
+        <v>481</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>379</v>
+        <v>482</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>388</v>
+        <v>491</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>389</v>
+        <v>492</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>390</v>
+        <v>493</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>391</v>
+        <v>494</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>392</v>
+        <v>495</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>373</v>
+        <v>476</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>393</v>
+        <v>496</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>373</v>
+        <v>476</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>395</v>
+        <v>498</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>396</v>
+        <v>499</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>373</v>
+        <v>476</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="61" ht="54" spans="1:3">
+      <c r="A61" s="3"/>
+      <c r="B61" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:A8"/>
     <mergeCell ref="A9:A17"/>
     <mergeCell ref="A18:A25"/>
@@ -6507,6 +7912,7 @@
     <mergeCell ref="A34:A42"/>
     <mergeCell ref="A43:A50"/>
     <mergeCell ref="A51:A58"/>
+    <mergeCell ref="A59:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
     <sheet name="标签数据信息说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$197</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="503">
   <si>
     <t>类别</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">取值为0或1
 </t>
     </r>
@@ -229,9 +235,7 @@
     </r>
   </si>
   <si>
-    <t>Atlas 350 标卡（4Pmesh互联）
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+    <t>Atlas 350 标卡（4Pmesh互联）说明：旧版本指标</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_rx_X_Y</t>
@@ -287,6 +291,80 @@
   </si>
   <si>
     <t>单位：G</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口Link状态。</t>
+    </r>
+  </si>
+  <si>
+    <t>详见“标签数据信息说明”页签中“标签8”</t>
+  </si>
+  <si>
+    <t>Atlas 350 标卡（4Pmesh互联）
+Atlas 850 系列硬件产品
+Atlas 950 SuperPoD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口实时接收速率。使用的-time参数为100。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>腾AI处理器端口实时发送速率。使用的-time参数为100。</t>
+    </r>
+  </si>
+  <si>
+    <t>npu_chip_info_link_speed</t>
+  </si>
+  <si>
+    <t>物理端口的速率。</t>
   </si>
   <si>
     <t>NPU</t>
@@ -1335,25 +1413,25 @@
     <t>单位：℃</t>
   </si>
   <si>
-    <t>npu_chip_info_optical_index_num_X_Y</t>
-  </si>
-  <si>
-    <t>芯片Udie Port链接的光模块Lane数量。X为Udie ID，Y为Port ID。</t>
+    <t>npu_chip_info_optical_index_num</t>
+  </si>
+  <si>
+    <t>芯片Udie Port链接的光模块Lane数量。</t>
   </si>
   <si>
     <t>Atlas 850 系列硬件产品</t>
   </si>
   <si>
-    <t>npu_chip_info_optical_tx_power_Z_X_Y</t>
-  </si>
-  <si>
-    <t>光模块发送功率。Z为Lane的index，取值为[0:3]，X为Udie ID，Y为Port ID。</t>
-  </si>
-  <si>
-    <t>npu_chip_info_optical_rx_power_Z_X_Y</t>
-  </si>
-  <si>
-    <t>光模块接收功率。Z为Lane的index，取值为[0:3]，X为Udie ID，Y为Port ID。X为Udie ID，Y为Port ID。</t>
+    <t>npu_chip_info_optical_tx_power_Z</t>
+  </si>
+  <si>
+    <t>光模块发送功率。Z为Lane的index，取值为[0:3]。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_optical_rx_power_Z</t>
+  </si>
+  <si>
+    <t>光模块接收功率。Z为Lane的index，取值为[0:3]。</t>
   </si>
   <si>
     <t>npu_chip_info_hbm_utilization</t>
@@ -1666,6 +1744,294 @@
   </si>
   <si>
     <t>TX坏包总报文字节数。X为Udie ID，Y为Port ID。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv4_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv4 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv6_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv6 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv4_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv4 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv6_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的IPv6 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_compact_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG6报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ctph_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG7 CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ntph_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的CFG7 非CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_mem_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的UB mem报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unknown_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的未知报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_drop_ind_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的带drop_ind的报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_err_ind_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的ERR报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_host_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后的落地报文数量（不包含枚举配置和管理报文）。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_imp_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后落地的枚举配置和管理报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_mar_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后落地的UB memory报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_link_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后转发到同Port的TX侧的报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_to_noc_pkt_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后的P2P报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_route_err_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过路由后出现路由查表错误的报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_out_err_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过校验后的错误报文总数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_length_err_cnt_rx</t>
+  </si>
+  <si>
+    <t>RX侧接收到的报文经过校验后的长度错误报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_rx_busi_flit_num</t>
+  </si>
+  <si>
+    <t>RX侧报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_rx_send_ack_flit</t>
+  </si>
+  <si>
+    <t>RX向对端返回响应的报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv4_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv4 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_ipv6_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv6 UB报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv4_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv4 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unic_ipv6_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的IPv6 UNIC报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_compact_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG6报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ctph_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG7 CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_umoc_ntph_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的CFG7 非CLAN报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_ub_mem_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的UB mem报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_unknown_pkt_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的未知报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_drop_ind_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的带drop_ind的报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_err_ind_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的ERR报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_lpbk_ind_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送报文在NL环回的报文个数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_out_err_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的报文经过校验后的错误报文总数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_length_err_cnt_tx</t>
+  </si>
+  <si>
+    <t>TX侧发送的报文经过校验后的长度错误报文数量。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_tx_busi_flit_num</t>
+  </si>
+  <si>
+    <t>TX报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_tx_recv_ack_flit</t>
+  </si>
+  <si>
+    <t>TX收到对端响应的报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_retry_req_sum</t>
+  </si>
+  <si>
+    <t>发起重传次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_retry_ack_sum</t>
+  </si>
+  <si>
+    <t>响应重传次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_crc_error_sum</t>
+  </si>
+  <si>
+    <t>CRC校验错误次数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxpausepkts</t>
+  </si>
+  <si>
+    <t>RX pause帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txpausepkts</t>
+  </si>
+  <si>
+    <t>TX pause帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxpfcpkts</t>
+  </si>
+  <si>
+    <t>RX PFC帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txpfcpkts</t>
+  </si>
+  <si>
+    <t>TX PFC帧总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxbadpkts</t>
+  </si>
+  <si>
+    <t>RX坏包总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txbadpkts</t>
+  </si>
+  <si>
+    <t>TX坏包总报文数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_rxbadoctets</t>
+  </si>
+  <si>
+    <t>RX坏包总报文字节数。</t>
+  </si>
+  <si>
+    <t>npu_chip_info_core_mib_txbadoctets</t>
+  </si>
+  <si>
+    <t>TX坏包总报文字节数。</t>
   </si>
   <si>
     <t>名称</t>
@@ -1989,6 +2355,15 @@
   </si>
   <si>
     <t>product_type：昇腾AI处理器产品形态</t>
+  </si>
+  <si>
+    <t>标签8</t>
+  </si>
+  <si>
+    <t>port:Udie端口ID</t>
+  </si>
+  <si>
+    <t>udie:Ascend 950处理器的Udie ID</t>
   </si>
 </sst>
 </file>
@@ -2179,16 +2554,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3117,12 +3492,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F145"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="42" style="7" customWidth="1"/>
-    <col min="3" max="3" width="32.6296296296296" style="7" customWidth="1"/>
+    <col min="3" max="3" width="32.6333333333333" style="7" customWidth="1"/>
     <col min="4" max="4" width="48.25" style="7" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="7" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="7" customWidth="1"/>
@@ -3209,7 +3584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="72" spans="1:6">
+    <row r="5" ht="67.5" spans="1:6">
       <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
@@ -3249,7 +3624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="72" spans="1:6">
+    <row r="7" ht="67.5" spans="1:6">
       <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
@@ -3269,7 +3644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="86.4" spans="1:6">
+    <row r="8" ht="84" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -3289,7 +3664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="86.4" spans="1:6">
+    <row r="9" ht="84" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -3309,7 +3684,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="43.2" spans="1:6">
+    <row r="10" ht="40.5" spans="1:6">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -3329,7 +3704,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="43.2" spans="1:6">
+    <row r="11" ht="40.5" spans="1:6">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -3349,7 +3724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="43.2" spans="1:6">
+    <row r="12" ht="27" spans="1:6">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -3370,2577 +3745,3524 @@
       </c>
     </row>
     <row r="13" ht="159" customHeight="1" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="D13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="E13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="5" t="s">
+    </row>
+    <row r="14" ht="159" customHeight="1" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="159" customHeight="1" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="D15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="159" customHeight="1" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" ht="159" customHeight="1" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" ht="159" customHeight="1" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="5" t="s">
+    <row r="18" ht="159" customHeight="1" spans="1:6">
+      <c r="A18" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" ht="86.4" spans="1:6">
-      <c r="A15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="11" t="s">
+      <c r="B18" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" ht="84" spans="1:6">
+      <c r="A19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" ht="201.6" spans="1:6">
-      <c r="A16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" ht="149" customHeight="1" spans="1:6">
-      <c r="A17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" ht="144" spans="1:6">
-      <c r="A18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" ht="187.2" spans="1:6">
-      <c r="A19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="9" t="s">
+    <row r="20" ht="175.5" spans="1:6">
+      <c r="A20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C20" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" ht="144" spans="1:6">
-      <c r="A20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="D20" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" ht="153" customHeight="1" spans="1:6">
+    <row r="21" ht="149" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" ht="135" spans="1:6">
+      <c r="A22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" ht="175.5" spans="1:6">
+      <c r="A23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C23" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F23" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="10" t="s">
+    </row>
+    <row r="24" ht="135" spans="1:6">
+      <c r="A24" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" ht="151" customHeight="1" spans="1:6">
-      <c r="A22" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" ht="144" spans="1:6">
-      <c r="A23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="9" t="s">
+    <row r="25" ht="153" customHeight="1" spans="1:6">
+      <c r="A25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C25" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" ht="144" spans="1:6">
-      <c r="A24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="9" t="s">
+      <c r="D25" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" ht="144" spans="1:6">
-      <c r="A25" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" ht="115.2" spans="1:6">
-      <c r="A26" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="9" t="s">
+    <row r="26" ht="151" customHeight="1" spans="1:6">
+      <c r="A26" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" ht="135" spans="1:6">
+      <c r="A27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" ht="135" spans="1:6">
+      <c r="A28" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26" s="10" t="s">
+      <c r="C28" s="7" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="27" ht="115.2" spans="1:6">
-      <c r="A27" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="9" t="s">
+      <c r="D28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="F28" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" ht="135" spans="1:6">
+      <c r="A29" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" ht="144" spans="1:6">
-      <c r="A28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="C29" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="D29" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" ht="144" spans="1:6">
-      <c r="A29" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="E29" s="9" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="39" customHeight="1" spans="1:6">
+    <row r="30" ht="108" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" ht="108" spans="1:6">
+      <c r="A31" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="D31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" ht="135" spans="1:6">
+      <c r="A32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="C32" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="10" t="s">
+      <c r="D32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="31" ht="144" spans="1:6">
-      <c r="A31" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" ht="144" spans="1:6">
-      <c r="A32" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" ht="57.6" spans="1:6">
-      <c r="A33" s="4" t="s">
+    <row r="33" ht="135" spans="1:6">
+      <c r="A33" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" ht="39" customHeight="1" spans="1:6">
+      <c r="A34" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="14" t="s">
+    </row>
+    <row r="35" ht="135" spans="1:6">
+      <c r="A35" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="34" ht="100.8" spans="1:6">
-      <c r="A34" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="D35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="10" t="s">
+      <c r="F35" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" ht="135" spans="1:6">
+      <c r="A36" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="35" ht="129.6" spans="1:6">
-      <c r="A35" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B35" s="9" t="s">
+      <c r="C36" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="D36" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" ht="54" spans="1:6">
+      <c r="A37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" s="10" t="s">
+      <c r="C37" s="14" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="36" ht="72" spans="1:6">
-      <c r="A36" s="7" t="s">
+      <c r="D37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="7" t="s">
+    </row>
+    <row r="38" ht="94.5" spans="1:6">
+      <c r="A38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C38" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="10" t="s">
+      <c r="D38" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" ht="121.5" spans="1:6">
+      <c r="A39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" ht="67.5" spans="1:6">
+      <c r="A40" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" ht="72" spans="1:6">
-      <c r="A37" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="10" t="s">
+    <row r="41" ht="67.5" spans="1:6">
+      <c r="A41" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="5" t="s">
+    <row r="42" spans="1:6">
+      <c r="A42" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" ht="40.5" spans="1:6">
+      <c r="A45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" ht="40.5" spans="1:6">
+      <c r="A46" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" ht="108" spans="1:6">
+      <c r="A47" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" ht="123" customHeight="1" spans="1:6">
+      <c r="A48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" ht="108" spans="1:6">
+      <c r="A49" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" ht="108" spans="1:6">
+      <c r="A50" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" ht="108" spans="1:6">
+      <c r="A51" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" ht="108" spans="1:6">
+      <c r="A52" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" ht="108" spans="1:6">
+      <c r="A53" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" ht="119" customHeight="1" spans="1:6">
+      <c r="A54" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" ht="108" spans="1:6">
+      <c r="A55" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" ht="33" customHeight="1" spans="1:6">
+      <c r="A56" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" ht="29" customHeight="1" spans="1:6">
+      <c r="A57" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" ht="40.5" spans="1:6">
+      <c r="A58" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" ht="40.5" spans="1:6">
+      <c r="A59" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" ht="40.5" spans="1:6">
+      <c r="A60" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" ht="29" customHeight="1" spans="1:6">
+      <c r="A61" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" ht="40.5" spans="1:6">
+      <c r="A62" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" ht="35" customHeight="1" spans="1:6">
+      <c r="A63" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" ht="40.5" spans="1:6">
+      <c r="A64" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="65" ht="40.5" spans="1:6">
+      <c r="A65" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" ht="40.5" spans="1:6">
+      <c r="A66" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" ht="40.5" spans="1:6">
+      <c r="A67" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="68" ht="40.5" spans="1:6">
+      <c r="A68" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" ht="40.5" spans="1:6">
+      <c r="A69" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" ht="67.5" spans="1:6">
+      <c r="A70" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" ht="43.2" spans="1:6">
-      <c r="A41" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42" ht="43.2" spans="1:6">
-      <c r="A42" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="43" ht="115.2" spans="1:6">
-      <c r="A43" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" ht="123" customHeight="1" spans="1:6">
-      <c r="A44" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" ht="115.2" spans="1:6">
-      <c r="A45" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" ht="115.2" spans="1:6">
-      <c r="A46" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" ht="115.2" spans="1:6">
-      <c r="A47" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" ht="115.2" spans="1:6">
-      <c r="A48" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" ht="115.2" spans="1:6">
-      <c r="A49" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" ht="119" customHeight="1" spans="1:6">
-      <c r="A50" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" ht="115.2" spans="1:6">
-      <c r="A51" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" ht="33" customHeight="1" spans="1:6">
-      <c r="A52" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="53" ht="29" customHeight="1" spans="1:6">
-      <c r="A53" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="54" ht="43.2" spans="1:6">
-      <c r="A54" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="55" ht="43.2" spans="1:6">
-      <c r="A55" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="56" ht="43.2" spans="1:6">
-      <c r="A56" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="57" ht="29" customHeight="1" spans="1:6">
-      <c r="A57" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="58" ht="43.2" spans="1:6">
-      <c r="A58" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="59" ht="35" customHeight="1" spans="1:6">
-      <c r="A59" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" ht="43.2" spans="1:6">
-      <c r="A60" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61" ht="43.2" spans="1:6">
-      <c r="A61" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="62" ht="43.2" spans="1:6">
-      <c r="A62" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="63" ht="43.2" spans="1:6">
-      <c r="A63" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" ht="43.2" spans="1:6">
-      <c r="A64" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="65" ht="43.2" spans="1:6">
-      <c r="A65" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" ht="72" spans="1:6">
-      <c r="A66" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" ht="72" spans="1:6">
-      <c r="A67" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" ht="72" spans="1:6">
-      <c r="A68" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" ht="72" spans="1:6">
-      <c r="A69" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C69" s="5" t="s">
+      <c r="B70" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D69" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" ht="72" spans="1:6">
-      <c r="A70" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B70" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="D70" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F70" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="71" ht="72" spans="1:6">
+    <row r="71" ht="67.5" spans="1:6">
       <c r="A71" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B71" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="D71" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="72" ht="72" spans="1:6">
+    <row r="72" ht="67.5" spans="1:6">
       <c r="A72" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="D72" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="73" ht="72" spans="1:6">
+    <row r="73" ht="67.5" spans="1:6">
       <c r="A73" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B73" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="D73" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="74" ht="72" spans="1:6">
+    <row r="74" ht="67.5" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B74" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>208</v>
-      </c>
       <c r="D74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="75" ht="72" spans="1:6">
+    <row r="75" ht="67.5" spans="1:6">
       <c r="A75" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B75" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>210</v>
-      </c>
       <c r="D75" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="76" ht="75" customHeight="1" spans="1:6">
+    <row r="76" ht="67.5" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B76" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>212</v>
-      </c>
       <c r="D76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F76" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="77" ht="72" spans="1:6">
+    <row r="77" ht="67.5" spans="1:6">
       <c r="A77" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B77" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>214</v>
-      </c>
       <c r="D77" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="78" ht="72" spans="1:6">
+    <row r="78" ht="67.5" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B78" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="D78" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F78" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="79" ht="72" spans="1:6">
+    <row r="79" ht="67.5" spans="1:6">
       <c r="A79" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B79" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>218</v>
-      </c>
       <c r="D79" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="80" ht="72" spans="1:6">
+    <row r="80" ht="75" customHeight="1" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B80" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="D80" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="81" ht="72" spans="1:6">
+    <row r="81" ht="67.5" spans="1:6">
       <c r="A81" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B81" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>222</v>
-      </c>
       <c r="D81" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="82" ht="72" spans="1:6">
+    <row r="82" ht="67.5" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B82" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>224</v>
-      </c>
       <c r="D82" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="83" ht="72" spans="1:6">
+    <row r="83" ht="67.5" spans="1:6">
       <c r="A83" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B83" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>226</v>
-      </c>
       <c r="D83" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="84" ht="27" customHeight="1" spans="1:6">
+    <row r="84" ht="67.5" spans="1:6">
       <c r="A84" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B84" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>228</v>
-      </c>
       <c r="D84" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F84" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1" spans="1:6">
+    <row r="85" ht="67.5" spans="1:6">
       <c r="A85" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="D85" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" ht="67.5" spans="1:6">
+      <c r="A86" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C86" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D85" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F85" s="10" t="s">
+      <c r="D86" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" ht="67.5" spans="1:6">
+      <c r="A87" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="86" ht="57.6" spans="1:6">
-      <c r="A86" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B86" s="13" t="s">
+      <c r="C87" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="D87" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" ht="27" customHeight="1" spans="1:6">
+      <c r="A88" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="87" ht="72" spans="1:6">
-      <c r="A87" s="5" t="s">
+      <c r="C88" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="D88" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1" spans="1:6">
+      <c r="A89" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="B89" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="D87" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87" s="13" t="s">
+      <c r="C89" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="88" ht="72" spans="1:6">
-      <c r="A88" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="89" ht="72" spans="1:6">
-      <c r="A89" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="D89" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>242</v>
+        <v>52</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="90" ht="72" spans="1:6">
+    <row r="90" ht="54" spans="1:6">
       <c r="A90" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>246</v>
+        <v>236</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>241</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>247</v>
+        <v>52</v>
       </c>
       <c r="F90" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="91" ht="72" spans="1:6">
+    <row r="91" ht="67.5" spans="1:6">
       <c r="A91" s="5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B91" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="92" ht="67.5" spans="1:6">
+      <c r="A92" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="D92" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" s="5" t="s">
+      <c r="F92" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="93" ht="67.5" spans="1:6">
+      <c r="A93" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="92" ht="28.8" spans="1:6">
-      <c r="A92" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B92" s="5" t="s">
+      <c r="C93" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="D93" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="94" ht="67.5" spans="1:6">
+      <c r="A94" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F92" s="10" t="s">
+      <c r="C94" s="5" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="93" ht="43.2" spans="1:6">
-      <c r="A93" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B93" s="5" t="s">
+      <c r="D94" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="F94" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="95" ht="67.5" spans="1:6">
+      <c r="A95" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="D93" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="5" t="s">
+      <c r="C95" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="96" ht="27" spans="1:6">
+      <c r="A96" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="94" ht="57.6" spans="1:6">
-      <c r="A94" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="5" t="s">
+      <c r="B96" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="97" ht="27" spans="1:6">
+      <c r="A97" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="F94" s="10" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="95" ht="115.2" spans="1:6">
-      <c r="A95" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F95" s="13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="96" ht="115.2" spans="1:6">
-      <c r="A96" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B96" s="9" t="s">
+      <c r="B97" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F97" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="C96" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F96" s="13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="97" ht="115.2" spans="1:6">
-      <c r="A97" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B97" s="9" t="s">
+    </row>
+    <row r="98" ht="27" spans="1:6">
+      <c r="A98" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B98" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="C97" s="9" t="s">
+      <c r="C98" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E97" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F97" s="13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="98" ht="28.8" spans="1:6">
-      <c r="A98" s="5" t="s">
+      <c r="D98" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="99" ht="108" spans="1:6">
+      <c r="A99" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B99" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="C99" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="D99" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" ht="108" spans="1:6">
+      <c r="A100" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F98" s="16" t="s">
+      <c r="C100" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="101" ht="108" spans="1:6">
+      <c r="A101" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="102" ht="27" spans="1:6">
+      <c r="A102" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F102" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="99" ht="28.8" spans="1:6">
-      <c r="A99" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F99" s="17"/>
-    </row>
-    <row r="100" ht="28.8" spans="1:6">
-      <c r="A100" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F100" s="17"/>
-    </row>
-    <row r="101" ht="28.8" spans="1:6">
-      <c r="A101" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F101" s="17"/>
-    </row>
-    <row r="102" ht="28.8" spans="1:6">
-      <c r="A102" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C102" s="5" t="s">
+    <row r="103" ht="27" spans="1:6">
+      <c r="A103" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F102" s="17"/>
-    </row>
-    <row r="103" ht="28.8" spans="1:6">
-      <c r="A103" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B103" s="5" t="s">
+      <c r="C103" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="D103" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F103" s="17"/>
+    </row>
+    <row r="104" ht="27" spans="1:6">
+      <c r="A104" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F103" s="17"/>
-    </row>
-    <row r="104" ht="28.8" spans="1:6">
-      <c r="A104" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B104" s="5" t="s">
+      <c r="C104" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="D104" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F104" s="17"/>
+    </row>
+    <row r="105" ht="27" spans="1:6">
+      <c r="A105" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F104" s="17"/>
-    </row>
-    <row r="105" ht="28.8" spans="1:6">
-      <c r="A105" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B105" s="5" t="s">
+      <c r="C105" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="D105" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F105" s="17"/>
+    </row>
+    <row r="106" ht="27" spans="1:6">
+      <c r="A106" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D105" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F105" s="17"/>
-    </row>
-    <row r="106" ht="28.8" spans="1:6">
-      <c r="A106" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B106" s="5" t="s">
+      <c r="C106" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="D106" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F106" s="17"/>
+    </row>
+    <row r="107" ht="27" spans="1:6">
+      <c r="A107" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="D106" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F106" s="17"/>
-    </row>
-    <row r="107" ht="28.8" spans="1:6">
-      <c r="A107" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B107" s="5" t="s">
+      <c r="C107" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="D107" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F107" s="17"/>
+    </row>
+    <row r="108" ht="27" spans="1:6">
+      <c r="A108" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B108" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="D107" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F107" s="17"/>
-    </row>
-    <row r="108" ht="28.8" spans="1:6">
-      <c r="A108" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B108" s="5" t="s">
+      <c r="C108" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="D108" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F108" s="17"/>
+    </row>
+    <row r="109" ht="27" spans="1:6">
+      <c r="A109" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B109" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="D108" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F108" s="17"/>
-    </row>
-    <row r="109" ht="57.6" spans="1:6">
-      <c r="A109" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B109" s="5" t="s">
+      <c r="C109" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C109" s="5" t="s">
+      <c r="D109" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F109" s="17"/>
+    </row>
+    <row r="110" ht="27" spans="1:6">
+      <c r="A110" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D109" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F109" s="17"/>
-    </row>
-    <row r="110" ht="43.2" spans="1:6">
-      <c r="A110" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B110" s="5" t="s">
+      <c r="C110" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="D110" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F110" s="17"/>
+    </row>
+    <row r="111" ht="27" spans="1:6">
+      <c r="A111" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="D110" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F110" s="17"/>
-    </row>
-    <row r="111" ht="43.2" spans="1:6">
-      <c r="A111" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B111" s="5" t="s">
+      <c r="C111" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="D111" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F111" s="17"/>
+    </row>
+    <row r="112" ht="27" spans="1:6">
+      <c r="A112" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B112" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F111" s="17"/>
-    </row>
-    <row r="112" ht="43.2" spans="1:6">
-      <c r="A112" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B112" s="5" t="s">
+      <c r="C112" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="D112" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F112" s="17"/>
+    </row>
+    <row r="113" ht="40.5" spans="1:6">
+      <c r="A113" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D112" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F112" s="17"/>
-    </row>
-    <row r="113" ht="43.2" spans="1:6">
-      <c r="A113" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B113" s="5" t="s">
+      <c r="C113" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="D113" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F113" s="17"/>
+    </row>
+    <row r="114" ht="40.5" spans="1:6">
+      <c r="A114" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="D113" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F113" s="17"/>
-    </row>
-    <row r="114" ht="43.2" spans="1:6">
-      <c r="A114" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B114" s="5" t="s">
+      <c r="C114" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="D114" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F114" s="17"/>
+    </row>
+    <row r="115" ht="40.5" spans="1:6">
+      <c r="A115" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="D114" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F114" s="17"/>
-    </row>
-    <row r="115" ht="43.2" spans="1:6">
-      <c r="A115" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B115" s="5" t="s">
+      <c r="C115" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="D115" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F115" s="17"/>
+    </row>
+    <row r="116" ht="40.5" spans="1:6">
+      <c r="A116" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="D115" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F115" s="17"/>
-    </row>
-    <row r="116" ht="43.2" spans="1:6">
-      <c r="A116" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B116" s="5" t="s">
+      <c r="C116" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="D116" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F116" s="17"/>
+    </row>
+    <row r="117" ht="27" spans="1:6">
+      <c r="A117" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="D116" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F116" s="17"/>
-    </row>
-    <row r="117" ht="28.8" spans="1:6">
-      <c r="A117" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B117" s="5" t="s">
+      <c r="C117" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="D117" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F117" s="17"/>
+    </row>
+    <row r="118" ht="40.5" spans="1:6">
+      <c r="A118" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B118" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="D117" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F117" s="17"/>
-    </row>
-    <row r="118" ht="28.8" spans="1:6">
-      <c r="A118" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B118" s="5" t="s">
+      <c r="C118" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="D118" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F118" s="17"/>
+    </row>
+    <row r="119" ht="27" spans="1:6">
+      <c r="A119" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="D118" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F118" s="17"/>
-    </row>
-    <row r="119" ht="28.8" spans="1:6">
-      <c r="A119" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B119" s="5" t="s">
+      <c r="C119" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="D119" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F119" s="17"/>
+    </row>
+    <row r="120" ht="40.5" spans="1:6">
+      <c r="A120" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D119" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F119" s="17"/>
-    </row>
-    <row r="120" ht="28.8" spans="1:6">
-      <c r="A120" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B120" s="5" t="s">
+      <c r="C120" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="D120" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F120" s="17"/>
+    </row>
+    <row r="121" ht="27" spans="1:6">
+      <c r="A121" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="D120" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F120" s="17"/>
-    </row>
-    <row r="121" ht="28.8" spans="1:6">
-      <c r="A121" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B121" s="5" t="s">
+      <c r="C121" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="C121" s="5" t="s">
+      <c r="D121" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F121" s="17"/>
+    </row>
+    <row r="122" ht="27" spans="1:6">
+      <c r="A122" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="D121" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F121" s="17"/>
-    </row>
-    <row r="122" ht="28.8" spans="1:6">
-      <c r="A122" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B122" s="5" t="s">
+      <c r="C122" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="D122" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F122" s="17"/>
+    </row>
+    <row r="123" ht="27" spans="1:6">
+      <c r="A123" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="D122" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F122" s="17"/>
-    </row>
-    <row r="123" ht="28.8" spans="1:6">
-      <c r="A123" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B123" s="5" t="s">
+      <c r="C123" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="D123" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F123" s="17"/>
+    </row>
+    <row r="124" ht="27" spans="1:6">
+      <c r="A124" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D123" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F123" s="17"/>
-    </row>
-    <row r="124" ht="28.8" spans="1:6">
-      <c r="A124" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B124" s="5" t="s">
+      <c r="C124" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="C124" s="5" t="s">
+      <c r="D124" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F124" s="17"/>
+    </row>
+    <row r="125" ht="27" spans="1:6">
+      <c r="A125" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="D124" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F124" s="17"/>
-    </row>
-    <row r="125" ht="28.8" spans="1:6">
-      <c r="A125" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B125" s="5" t="s">
+      <c r="C125" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="D125" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F125" s="17"/>
+    </row>
+    <row r="126" ht="27" spans="1:6">
+      <c r="A126" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B126" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="D125" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F125" s="17"/>
-    </row>
-    <row r="126" ht="28.8" spans="1:6">
-      <c r="A126" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B126" s="5" t="s">
+      <c r="C126" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="D126" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F126" s="17"/>
+    </row>
+    <row r="127" ht="27" spans="1:6">
+      <c r="A127" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="D126" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F126" s="17"/>
-    </row>
-    <row r="127" ht="28.8" spans="1:6">
-      <c r="A127" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B127" s="5" t="s">
+      <c r="C127" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="D127" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F127" s="17"/>
+    </row>
+    <row r="128" ht="27" spans="1:6">
+      <c r="A128" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B128" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F127" s="17"/>
-    </row>
-    <row r="128" ht="28.8" spans="1:6">
-      <c r="A128" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B128" s="5" t="s">
+      <c r="C128" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="D128" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F128" s="17"/>
+    </row>
+    <row r="129" ht="27" spans="1:6">
+      <c r="A129" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="D128" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F128" s="17"/>
-    </row>
-    <row r="129" ht="28.8" spans="1:6">
-      <c r="A129" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B129" s="5" t="s">
+      <c r="C129" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="C129" s="5" t="s">
+      <c r="D129" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F129" s="17"/>
+    </row>
+    <row r="130" ht="27" spans="1:6">
+      <c r="A130" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B130" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="D129" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F129" s="17"/>
-    </row>
-    <row r="130" ht="28.8" spans="1:6">
-      <c r="A130" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B130" s="5" t="s">
+      <c r="C130" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="D130" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F130" s="17"/>
+    </row>
+    <row r="131" ht="27" spans="1:6">
+      <c r="A131" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B131" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F130" s="17"/>
-    </row>
-    <row r="131" ht="43.2" spans="1:6">
-      <c r="A131" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B131" s="5" t="s">
+      <c r="C131" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="D131" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F131" s="17"/>
+    </row>
+    <row r="132" ht="27" spans="1:6">
+      <c r="A132" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="D131" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F131" s="17"/>
-    </row>
-    <row r="132" ht="43.2" spans="1:6">
-      <c r="A132" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B132" s="5" t="s">
+      <c r="C132" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="D132" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F132" s="17"/>
+    </row>
+    <row r="133" ht="27" spans="1:6">
+      <c r="A133" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F132" s="17"/>
-    </row>
-    <row r="133" ht="28.8" spans="1:6">
-      <c r="A133" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B133" s="5" t="s">
+      <c r="C133" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="D133" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F133" s="17"/>
+    </row>
+    <row r="134" ht="27" spans="1:6">
+      <c r="A134" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B134" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F133" s="17"/>
-    </row>
-    <row r="134" ht="28.8" spans="1:6">
-      <c r="A134" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B134" s="5" t="s">
+      <c r="C134" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="D134" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F134" s="17"/>
+    </row>
+    <row r="135" ht="27" spans="1:6">
+      <c r="A135" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F134" s="17"/>
-    </row>
-    <row r="135" ht="28.8" spans="1:6">
-      <c r="A135" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B135" s="5" t="s">
+      <c r="C135" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C135" s="5" t="s">
+      <c r="D135" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F135" s="17"/>
+    </row>
+    <row r="136" ht="40.5" spans="1:6">
+      <c r="A136" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B136" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D135" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F135" s="17"/>
-    </row>
-    <row r="136" ht="28.8" spans="1:6">
-      <c r="A136" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B136" s="5" t="s">
+      <c r="C136" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="D136" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F136" s="17"/>
+    </row>
+    <row r="137" ht="27" spans="1:6">
+      <c r="A137" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="D136" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F136" s="17"/>
-    </row>
-    <row r="137" ht="28.8" spans="1:6">
-      <c r="A137" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B137" s="5" t="s">
+      <c r="C137" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="D137" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F137" s="17"/>
+    </row>
+    <row r="138" ht="27" spans="1:6">
+      <c r="A138" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="D137" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F137" s="17"/>
-    </row>
-    <row r="138" ht="28.8" spans="1:6">
-      <c r="A138" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B138" s="5" t="s">
+      <c r="C138" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="D138" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F138" s="17"/>
+    </row>
+    <row r="139" ht="27" spans="1:6">
+      <c r="A139" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D138" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F138" s="17"/>
-    </row>
-    <row r="139" ht="28.8" spans="1:6">
-      <c r="A139" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B139" s="5" t="s">
+      <c r="C139" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="D139" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F139" s="17"/>
+    </row>
+    <row r="140" ht="27" spans="1:6">
+      <c r="A140" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="D139" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F139" s="17"/>
-    </row>
-    <row r="140" ht="28.8" spans="1:6">
-      <c r="A140" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B140" s="5" t="s">
+      <c r="C140" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="D140" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F140" s="17"/>
+    </row>
+    <row r="141" ht="27" spans="1:6">
+      <c r="A141" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="D140" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F140" s="17"/>
-    </row>
-    <row r="141" ht="28.8" spans="1:6">
-      <c r="A141" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B141" s="5" t="s">
+      <c r="C141" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C141" s="5" t="s">
+      <c r="D141" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F141" s="17"/>
+    </row>
+    <row r="142" ht="27" spans="1:6">
+      <c r="A142" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="D141" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F141" s="17"/>
-    </row>
-    <row r="142" ht="28.8" spans="1:6">
-      <c r="A142" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B142" s="5" t="s">
+      <c r="C142" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="D142" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F142" s="17"/>
+    </row>
+    <row r="143" ht="27" spans="1:6">
+      <c r="A143" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F142" s="17"/>
-    </row>
-    <row r="143" ht="28.8" spans="1:6">
-      <c r="A143" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B143" s="5" t="s">
+      <c r="C143" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="D143" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F143" s="17"/>
+    </row>
+    <row r="144" ht="27" spans="1:6">
+      <c r="A144" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B144" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="D143" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F143" s="17"/>
-    </row>
-    <row r="144" ht="28.8" spans="1:6">
-      <c r="A144" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B144" s="5" t="s">
+      <c r="C144" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="C144" s="5" t="s">
+      <c r="D144" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F144" s="17"/>
+    </row>
+    <row r="145" ht="27" spans="1:6">
+      <c r="A145" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="D144" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F144" s="17"/>
-    </row>
-    <row r="145" ht="28.8" spans="1:6">
-      <c r="A145" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B145" s="5" t="s">
+      <c r="C145" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="D145" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F145" s="17"/>
+    </row>
+    <row r="146" ht="27" spans="1:6">
+      <c r="A146" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B146" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="D145" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F145" s="18"/>
+      <c r="C146" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F146" s="17"/>
+    </row>
+    <row r="147" ht="27" spans="1:6">
+      <c r="A147" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F147" s="17"/>
+    </row>
+    <row r="148" ht="27" spans="1:6">
+      <c r="A148" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F148" s="17"/>
+    </row>
+    <row r="149" ht="27" spans="1:6">
+      <c r="A149" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F149" s="18"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F150" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F151" s="17"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F152" s="17"/>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F153" s="17"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F154" s="17"/>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F155" s="17"/>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F156" s="17"/>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F157" s="17"/>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F158" s="17"/>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F159" s="17"/>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F160" s="17"/>
+    </row>
+    <row r="161" ht="40.5" spans="1:6">
+      <c r="A161" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F161" s="17"/>
+    </row>
+    <row r="162" ht="27" spans="1:6">
+      <c r="A162" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F162" s="17"/>
+    </row>
+    <row r="163" ht="27" spans="1:6">
+      <c r="A163" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F163" s="17"/>
+    </row>
+    <row r="164" ht="27" spans="1:6">
+      <c r="A164" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F164" s="17"/>
+    </row>
+    <row r="165" ht="27" spans="1:6">
+      <c r="A165" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F165" s="17"/>
+    </row>
+    <row r="166" ht="27" spans="1:6">
+      <c r="A166" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F166" s="17"/>
+    </row>
+    <row r="167" ht="27" spans="1:6">
+      <c r="A167" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F167" s="17"/>
+    </row>
+    <row r="168" ht="27" spans="1:6">
+      <c r="A168" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F168" s="17"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F169" s="17"/>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F170" s="17"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F171" s="17"/>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F172" s="17"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F173" s="17"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F174" s="17"/>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F175" s="17"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F176" s="17"/>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F177" s="17"/>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F178" s="17"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F179" s="17"/>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F180" s="17"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F181" s="17"/>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F182" s="17"/>
+    </row>
+    <row r="183" ht="27" spans="1:6">
+      <c r="A183" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F183" s="17"/>
+    </row>
+    <row r="184" ht="27" spans="1:6">
+      <c r="A184" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F184" s="17"/>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F185" s="17"/>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F186" s="17"/>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F187" s="17"/>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F188" s="17"/>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F189" s="17"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F190" s="17"/>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F191" s="17"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F192" s="17"/>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F193" s="17"/>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F194" s="17"/>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F195" s="17"/>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F196" s="17"/>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F197" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F145" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F197" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="F98:F145"/>
+  <mergeCells count="2">
+    <mergeCell ref="F102:F149"/>
+    <mergeCell ref="F150:F197"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
@@ -5951,555 +7273,638 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:C67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.6296296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="73.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.8833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>362</v>
+        <v>465</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>363</v>
+        <v>466</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>364</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>365</v>
+        <v>468</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>373</v>
+        <v>476</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>374</v>
+        <v>477</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>375</v>
+        <v>478</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>376</v>
+        <v>479</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
-        <v>377</v>
+        <v>480</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>378</v>
+        <v>481</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>379</v>
+        <v>482</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>380</v>
+        <v>483</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>381</v>
+        <v>484</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>382</v>
+        <v>485</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>383</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>384</v>
+        <v>487</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>385</v>
+        <v>488</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>386</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>387</v>
+        <v>490</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
-        <v>377</v>
+        <v>480</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>378</v>
+        <v>481</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>379</v>
+        <v>482</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>388</v>
+        <v>491</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>389</v>
+        <v>492</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>390</v>
+        <v>493</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>391</v>
+        <v>494</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>392</v>
+        <v>495</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>373</v>
+        <v>476</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>393</v>
+        <v>496</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>373</v>
+        <v>476</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>395</v>
+        <v>498</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
-        <v>368</v>
+        <v>471</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="57.6" spans="1:3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>396</v>
+        <v>499</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>373</v>
+        <v>476</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>367</v>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="61" ht="54" spans="1:3">
+      <c r="A61" s="3"/>
+      <c r="B61" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:A8"/>
     <mergeCell ref="A9:A17"/>
     <mergeCell ref="A18:A25"/>
@@ -6507,6 +7912,7 @@
     <mergeCell ref="A34:A42"/>
     <mergeCell ref="A43:A50"/>
     <mergeCell ref="A51:A58"/>
+    <mergeCell ref="A59:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mind-cluster\docs\zh\resource\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
     <sheet name="标签数据信息说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">labels!$A$1:$F$200</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="509">
   <si>
     <t>类别</t>
   </si>
@@ -380,6 +385,24 @@
   </si>
   <si>
     <t>单位：个</t>
+  </si>
+  <si>
+    <t>machine_healthy_npu_nums</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器健康数目</t>
+  </si>
+  <si>
+    <t>machine_unhealthy_npu_nums</t>
+  </si>
+  <si>
+    <t>昇腾AI处理器故障数目</t>
+  </si>
+  <si>
+    <t>machine_unknown_npu_nums</t>
+  </si>
+  <si>
+    <t>无法通过DCMI接口获取健康状态的昇腾AI处理器数目</t>
   </si>
   <si>
     <t>machine_card_nums</t>
@@ -2554,10 +2577,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="方正兰亭黑简体"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2567,9 +2589,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="方正兰亭黑简体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3492,7 +3515,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F197"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
@@ -3861,167 +3884,167 @@
         <v>53</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="159" customHeight="1" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" ht="84" spans="1:6">
-      <c r="A19" s="7" t="s">
+      <c r="C19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" ht="159" customHeight="1" spans="1:6">
+      <c r="A20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B20" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" ht="175.5" spans="1:6">
-      <c r="A20" s="7" t="s">
+      <c r="D20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" ht="159" customHeight="1" spans="1:6">
+      <c r="A21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B21" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C21" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" ht="149" customHeight="1" spans="1:6">
-      <c r="A21" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="D21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" ht="135" spans="1:6">
+    </row>
+    <row r="22" ht="84" spans="1:6">
       <c r="A22" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="175.5" spans="1:6">
+      <c r="A23" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="C23" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" ht="175.5" spans="1:6">
-      <c r="A23" s="9" t="s">
+    <row r="24" ht="149" customHeight="1" spans="1:6">
+      <c r="A24" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B24" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" ht="135" spans="1:6">
-      <c r="A24" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>72</v>
-      </c>
       <c r="D24" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="10" t="s">
+      <c r="E24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" ht="153" customHeight="1" spans="1:6">
+    <row r="25" ht="135" spans="1:6">
       <c r="A25" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" ht="175.5" spans="1:6">
+      <c r="A26" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="F26" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" ht="151" customHeight="1" spans="1:6">
-      <c r="A26" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="27" ht="135" spans="1:6">
@@ -4029,524 +4052,524 @@
         <v>49</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" ht="135" spans="1:6">
+    <row r="28" ht="153" customHeight="1" spans="1:6">
       <c r="A28" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="F28" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" ht="151" customHeight="1" spans="1:6">
+      <c r="A29" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" ht="135" spans="1:6">
-      <c r="A29" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="9" t="s">
+      <c r="D29" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>52</v>
+      <c r="E29" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="108" spans="1:6">
+    <row r="30" ht="135" spans="1:6">
       <c r="A30" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" ht="135" spans="1:6">
+      <c r="A31" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C31" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="10" t="s">
+      <c r="D31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="31" ht="108" spans="1:6">
-      <c r="A31" s="9" t="s">
+      <c r="F31" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" ht="135" spans="1:6">
+      <c r="A32" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B32" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C32" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" ht="135" spans="1:6">
-      <c r="A32" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="D32" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="E32" s="9" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" ht="135" spans="1:6">
+    <row r="33" ht="108" spans="1:6">
       <c r="A33" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B33" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" ht="39" customHeight="1" spans="1:6">
+    </row>
+    <row r="34" ht="108" spans="1:6">
       <c r="A34" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" ht="135" spans="1:6">
       <c r="A35" s="4" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="36" ht="135" spans="1:6">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>109</v>
-      </c>
       <c r="D36" s="5" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="37" ht="54" spans="1:6">
-      <c r="A37" s="4" t="s">
-        <v>104</v>
+    <row r="37" ht="39" customHeight="1" spans="1:6">
+      <c r="A37" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="B37" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" ht="135" spans="1:6">
+      <c r="A38" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="B38" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F37" s="10" t="s">
+      <c r="C38" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="38" ht="94.5" spans="1:6">
-      <c r="A38" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B38" s="9" t="s">
+      <c r="D38" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="F38" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" ht="135" spans="1:6">
+      <c r="A39" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F38" s="10" t="s">
+      <c r="C39" s="13" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="39" ht="121.5" spans="1:6">
-      <c r="A39" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" s="9" t="s">
+      <c r="D39" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" ht="54" spans="1:6">
+      <c r="A40" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C40" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F39" s="10" t="s">
+      <c r="D40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="40" ht="67.5" spans="1:6">
-      <c r="A40" s="7" t="s">
+    <row r="41" ht="94.5" spans="1:6">
+      <c r="A41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="C41" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="D41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F40" s="10" t="s">
+    </row>
+    <row r="42" ht="121.5" spans="1:6">
+      <c r="A42" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" ht="67.5" spans="1:6">
+      <c r="A43" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="41" ht="67.5" spans="1:6">
-      <c r="A41" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F41" s="10" t="s">
+    <row r="44" ht="67.5" spans="1:6">
+      <c r="A44" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" s="5" t="s">
+    <row r="45" spans="1:6">
+      <c r="A45" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E44" s="5" t="s">
+      <c r="D45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" ht="40.5" spans="1:6">
-      <c r="A45" s="5" t="s">
+      <c r="B46" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F45" s="11" t="s">
+      <c r="E46" s="5" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="46" ht="40.5" spans="1:6">
-      <c r="A46" s="5" t="s">
+      <c r="F46" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F46" s="11" t="s">
+      <c r="E47" s="5" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="47" ht="108" spans="1:6">
-      <c r="A47" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="F47" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" ht="123" customHeight="1" spans="1:6">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" ht="40.5" spans="1:6">
       <c r="A48" s="5" t="s">
         <v>139</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" ht="40.5" spans="1:6">
+      <c r="A49" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F48" s="10" t="s">
+      <c r="D49" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F49" s="11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="49" ht="108" spans="1:6">
-      <c r="A49" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B49" s="13" t="s">
+    <row r="50" ht="108" spans="1:6">
+      <c r="A50" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="B50" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="13" t="s">
+      <c r="C50" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="50" ht="108" spans="1:6">
-      <c r="A50" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="D50" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C50" s="5" t="s">
+    </row>
+    <row r="51" ht="123" customHeight="1" spans="1:6">
+      <c r="A51" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" ht="108" spans="1:6">
-      <c r="A51" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>151</v>
-      </c>
       <c r="D51" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>52</v>
+      <c r="E51" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" ht="108" spans="1:6">
       <c r="A52" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>52</v>
-      </c>
       <c r="F52" s="10" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" ht="108" spans="1:6">
       <c r="A53" s="13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>154</v>
@@ -4561,12 +4584,12 @@
         <v>52</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" ht="119" customHeight="1" spans="1:6">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" ht="108" spans="1:6">
       <c r="A54" s="13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>156</v>
@@ -4581,12 +4604,12 @@
         <v>52</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" ht="108" spans="1:6">
       <c r="A55" s="13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>158</v>
@@ -4601,252 +4624,252 @@
         <v>52</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="56" ht="33" customHeight="1" spans="1:6">
-      <c r="A56" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" ht="108" spans="1:6">
+      <c r="A56" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="D56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" ht="119" customHeight="1" spans="1:6">
+      <c r="A57" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F56" s="10" t="s">
+      <c r="C57" s="5" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="57" ht="29" customHeight="1" spans="1:6">
-      <c r="A57" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B57" s="5" t="s">
+      <c r="D57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="58" ht="108" spans="1:6">
+      <c r="A58" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F57" s="10" t="s">
+      <c r="D58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" ht="33" customHeight="1" spans="1:6">
+      <c r="A59" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="58" ht="40.5" spans="1:6">
-      <c r="A58" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B58" s="15" t="s">
+      <c r="B59" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C59" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="9" t="s">
+      <c r="D59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F58" s="10" t="s">
+    </row>
+    <row r="60" ht="29" customHeight="1" spans="1:6">
+      <c r="A60" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="59" ht="40.5" spans="1:6">
-      <c r="A59" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B59" s="15" t="s">
+      <c r="B60" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C60" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="9" t="s">
+      <c r="D60" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F59" s="10" t="s">
+    </row>
+    <row r="61" ht="40.5" spans="1:6">
+      <c r="A61" s="15" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="60" ht="40.5" spans="1:6">
-      <c r="A60" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B60" s="15" t="s">
+      <c r="B61" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C61" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E60" s="9" t="s">
+      <c r="D61" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F61" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="61" ht="29" customHeight="1" spans="1:6">
-      <c r="A61" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:6">
       <c r="A62" s="15" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B62" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="F62" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" ht="40.5" spans="1:6">
+      <c r="A63" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B63" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E62" s="9" t="s">
+      <c r="C63" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F63" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F62" s="10" t="s">
+    </row>
+    <row r="64" ht="29" customHeight="1" spans="1:6">
+      <c r="A64" s="15" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="63" ht="35" customHeight="1" spans="1:6">
-      <c r="A63" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="B64" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="64" ht="40.5" spans="1:6">
-      <c r="A64" s="5" t="s">
+      <c r="C64" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="D64" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C64" s="5" t="s">
+    </row>
+    <row r="65" ht="40.5" spans="1:6">
+      <c r="A65" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="C65" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="D65" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="66" ht="35" customHeight="1" spans="1:6">
+      <c r="A66" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="C66" s="5" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="65" ht="40.5" spans="1:6">
-      <c r="A65" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="66" ht="40.5" spans="1:6">
-      <c r="A66" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>191</v>
-      </c>
       <c r="D66" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>186</v>
+        <v>19</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:6">
       <c r="A67" s="5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="F67" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:6">
       <c r="A68" s="5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>194</v>
@@ -4855,18 +4878,18 @@
         <v>195</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:6">
       <c r="A69" s="5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>196</v>
@@ -4875,18 +4898,18 @@
         <v>197</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="70" ht="67.5" spans="1:6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" ht="40.5" spans="1:6">
       <c r="A70" s="5" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>198</v>
@@ -4895,18 +4918,18 @@
         <v>199</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" ht="67.5" spans="1:6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" ht="40.5" spans="1:6">
       <c r="A71" s="5" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>200</v>
@@ -4915,18 +4938,18 @@
         <v>201</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" ht="67.5" spans="1:6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" ht="40.5" spans="1:6">
       <c r="A72" s="5" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>202</v>
@@ -4935,18 +4958,18 @@
         <v>203</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>21</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" ht="67.5" spans="1:6">
       <c r="A73" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>204</v>
@@ -4966,7 +4989,7 @@
     </row>
     <row r="74" ht="67.5" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>206</v>
@@ -4986,7 +5009,7 @@
     </row>
     <row r="75" ht="67.5" spans="1:6">
       <c r="A75" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>208</v>
@@ -5006,7 +5029,7 @@
     </row>
     <row r="76" ht="67.5" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>210</v>
@@ -5026,7 +5049,7 @@
     </row>
     <row r="77" ht="67.5" spans="1:6">
       <c r="A77" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>212</v>
@@ -5046,7 +5069,7 @@
     </row>
     <row r="78" ht="67.5" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>214</v>
@@ -5066,7 +5089,7 @@
     </row>
     <row r="79" ht="67.5" spans="1:6">
       <c r="A79" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>216</v>
@@ -5084,9 +5107,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" ht="75" customHeight="1" spans="1:6">
+    <row r="80" ht="67.5" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>218</v>
@@ -5106,7 +5129,7 @@
     </row>
     <row r="81" ht="67.5" spans="1:6">
       <c r="A81" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>220</v>
@@ -5126,7 +5149,7 @@
     </row>
     <row r="82" ht="67.5" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>222</v>
@@ -5144,9 +5167,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" ht="67.5" spans="1:6">
+    <row r="83" ht="75" customHeight="1" spans="1:6">
       <c r="A83" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>224</v>
@@ -5166,7 +5189,7 @@
     </row>
     <row r="84" ht="67.5" spans="1:6">
       <c r="A84" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>226</v>
@@ -5186,7 +5209,7 @@
     </row>
     <row r="85" ht="67.5" spans="1:6">
       <c r="A85" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>228</v>
@@ -5206,7 +5229,7 @@
     </row>
     <row r="86" ht="67.5" spans="1:6">
       <c r="A86" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>230</v>
@@ -5226,7 +5249,7 @@
     </row>
     <row r="87" ht="67.5" spans="1:6">
       <c r="A87" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>232</v>
@@ -5244,9 +5267,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" ht="27" customHeight="1" spans="1:6">
+    <row r="88" ht="67.5" spans="1:6">
       <c r="A88" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>234</v>
@@ -5264,325 +5287,329 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1" spans="1:6">
+    <row r="89" ht="67.5" spans="1:6">
       <c r="A89" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="C89" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="D89" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" ht="67.5" spans="1:6">
+      <c r="A90" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D89" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F89" s="10" t="s">
+      <c r="C90" s="5" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="90" ht="54" spans="1:6">
-      <c r="A90" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B90" s="13" t="s">
+      <c r="D90" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" ht="27" customHeight="1" spans="1:6">
+      <c r="A91" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C91" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D90" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="91" ht="67.5" spans="1:6">
-      <c r="A91" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="D91" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E91" s="13" t="s">
-        <v>245</v>
+      <c r="E91" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="92" ht="67.5" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1" spans="1:6">
       <c r="A92" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B92" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>248</v>
+      <c r="B92" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>244</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>249</v>
+        <v>52</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="93" ht="67.5" spans="1:6">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="93" ht="54" spans="1:6">
       <c r="A93" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B93" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>251</v>
+      <c r="B93" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>247</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>249</v>
+        <v>52</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" ht="67.5" spans="1:6">
       <c r="A94" s="5" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B94" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="F94" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="95" ht="67.5" spans="1:6">
       <c r="A95" s="5" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="F95" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="96" ht="67.5" spans="1:6">
+      <c r="A96" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B96" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="5" t="s">
+      <c r="C96" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="96" ht="27" spans="1:6">
-      <c r="A96" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B96" s="5" t="s">
+      <c r="D96" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="97" ht="67.5" spans="1:6">
+      <c r="A97" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C97" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D97" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="98" ht="67.5" spans="1:6">
+      <c r="A98" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="99" ht="27" spans="1:6">
+      <c r="A99" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D99" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E96" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="97" ht="27" spans="1:6">
-      <c r="A97" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D97" s="5" t="s">
+      <c r="E99" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="100" ht="27" spans="1:6">
+      <c r="A100" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D100" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="98" ht="27" spans="1:6">
-      <c r="A98" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="D98" s="5" t="s">
+      <c r="E100" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="101" ht="27" spans="1:6">
+      <c r="A101" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D101" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="99" ht="108" spans="1:6">
-      <c r="A99" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="C99" s="9" t="s">
+      <c r="E101" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F101" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F99" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="100" ht="108" spans="1:6">
-      <c r="A100" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E100" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="F100" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="101" ht="108" spans="1:6">
-      <c r="A101" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C101" s="9" t="s">
+    </row>
+    <row r="102" ht="108" spans="1:6">
+      <c r="A102" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B102" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="D101" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E101" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F101" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="102" ht="27" spans="1:6">
-      <c r="A102" s="5" t="s">
+      <c r="C102" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="D102" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F102" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="103" ht="108" spans="1:6">
+      <c r="A103" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B103" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C103" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F102" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="103" ht="27" spans="1:6">
-      <c r="A103" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="B103" s="5" t="s">
+      <c r="D103" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="F103" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="104" ht="108" spans="1:6">
+      <c r="A104" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F103" s="17"/>
-    </row>
-    <row r="104" ht="27" spans="1:6">
-      <c r="A104" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="B104" s="5" t="s">
+      <c r="C104" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="C104" s="5" t="s">
-        <v>278</v>
-      </c>
       <c r="D104" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E104" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F104" s="17"/>
+      <c r="E104" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F104" s="13" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="105" ht="27" spans="1:6">
       <c r="A105" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>279</v>
@@ -5596,11 +5623,13 @@
       <c r="E105" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F105" s="17"/>
+      <c r="F105" s="16" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="106" ht="27" spans="1:6">
       <c r="A106" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>281</v>
@@ -5618,7 +5647,7 @@
     </row>
     <row r="107" ht="27" spans="1:6">
       <c r="A107" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>283</v>
@@ -5636,7 +5665,7 @@
     </row>
     <row r="108" ht="27" spans="1:6">
       <c r="A108" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>285</v>
@@ -5654,7 +5683,7 @@
     </row>
     <row r="109" ht="27" spans="1:6">
       <c r="A109" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>287</v>
@@ -5672,7 +5701,7 @@
     </row>
     <row r="110" ht="27" spans="1:6">
       <c r="A110" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>289</v>
@@ -5690,7 +5719,7 @@
     </row>
     <row r="111" ht="27" spans="1:6">
       <c r="A111" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>291</v>
@@ -5708,7 +5737,7 @@
     </row>
     <row r="112" ht="27" spans="1:6">
       <c r="A112" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>293</v>
@@ -5724,9 +5753,9 @@
       </c>
       <c r="F112" s="17"/>
     </row>
-    <row r="113" ht="40.5" spans="1:6">
+    <row r="113" ht="27" spans="1:6">
       <c r="A113" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>295</v>
@@ -5742,9 +5771,9 @@
       </c>
       <c r="F113" s="17"/>
     </row>
-    <row r="114" ht="40.5" spans="1:6">
+    <row r="114" ht="27" spans="1:6">
       <c r="A114" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>297</v>
@@ -5760,9 +5789,9 @@
       </c>
       <c r="F114" s="17"/>
     </row>
-    <row r="115" ht="40.5" spans="1:6">
+    <row r="115" ht="27" spans="1:6">
       <c r="A115" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>299</v>
@@ -5780,7 +5809,7 @@
     </row>
     <row r="116" ht="40.5" spans="1:6">
       <c r="A116" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>301</v>
@@ -5796,9 +5825,9 @@
       </c>
       <c r="F116" s="17"/>
     </row>
-    <row r="117" ht="27" spans="1:6">
+    <row r="117" ht="40.5" spans="1:6">
       <c r="A117" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>303</v>
@@ -5816,7 +5845,7 @@
     </row>
     <row r="118" ht="40.5" spans="1:6">
       <c r="A118" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>305</v>
@@ -5832,9 +5861,9 @@
       </c>
       <c r="F118" s="17"/>
     </row>
-    <row r="119" ht="27" spans="1:6">
+    <row r="119" ht="40.5" spans="1:6">
       <c r="A119" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>307</v>
@@ -5850,9 +5879,9 @@
       </c>
       <c r="F119" s="17"/>
     </row>
-    <row r="120" ht="40.5" spans="1:6">
+    <row r="120" ht="27" spans="1:6">
       <c r="A120" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>309</v>
@@ -5868,9 +5897,9 @@
       </c>
       <c r="F120" s="17"/>
     </row>
-    <row r="121" ht="27" spans="1:6">
+    <row r="121" ht="40.5" spans="1:6">
       <c r="A121" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>311</v>
@@ -5888,7 +5917,7 @@
     </row>
     <row r="122" ht="27" spans="1:6">
       <c r="A122" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>313</v>
@@ -5904,9 +5933,9 @@
       </c>
       <c r="F122" s="17"/>
     </row>
-    <row r="123" ht="27" spans="1:6">
+    <row r="123" ht="40.5" spans="1:6">
       <c r="A123" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>315</v>
@@ -5924,7 +5953,7 @@
     </row>
     <row r="124" ht="27" spans="1:6">
       <c r="A124" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>317</v>
@@ -5942,7 +5971,7 @@
     </row>
     <row r="125" ht="27" spans="1:6">
       <c r="A125" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>319</v>
@@ -5960,7 +5989,7 @@
     </row>
     <row r="126" ht="27" spans="1:6">
       <c r="A126" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>321</v>
@@ -5978,7 +6007,7 @@
     </row>
     <row r="127" ht="27" spans="1:6">
       <c r="A127" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>323</v>
@@ -5996,7 +6025,7 @@
     </row>
     <row r="128" ht="27" spans="1:6">
       <c r="A128" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>325</v>
@@ -6014,7 +6043,7 @@
     </row>
     <row r="129" ht="27" spans="1:6">
       <c r="A129" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>327</v>
@@ -6032,7 +6061,7 @@
     </row>
     <row r="130" ht="27" spans="1:6">
       <c r="A130" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>329</v>
@@ -6050,7 +6079,7 @@
     </row>
     <row r="131" ht="27" spans="1:6">
       <c r="A131" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>331</v>
@@ -6068,7 +6097,7 @@
     </row>
     <row r="132" ht="27" spans="1:6">
       <c r="A132" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>333</v>
@@ -6086,7 +6115,7 @@
     </row>
     <row r="133" ht="27" spans="1:6">
       <c r="A133" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>335</v>
@@ -6104,7 +6133,7 @@
     </row>
     <row r="134" ht="27" spans="1:6">
       <c r="A134" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>337</v>
@@ -6122,7 +6151,7 @@
     </row>
     <row r="135" ht="27" spans="1:6">
       <c r="A135" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>339</v>
@@ -6138,9 +6167,9 @@
       </c>
       <c r="F135" s="17"/>
     </row>
-    <row r="136" ht="40.5" spans="1:6">
+    <row r="136" ht="27" spans="1:6">
       <c r="A136" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>341</v>
@@ -6158,7 +6187,7 @@
     </row>
     <row r="137" ht="27" spans="1:6">
       <c r="A137" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>343</v>
@@ -6176,7 +6205,7 @@
     </row>
     <row r="138" ht="27" spans="1:6">
       <c r="A138" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>345</v>
@@ -6192,9 +6221,9 @@
       </c>
       <c r="F138" s="17"/>
     </row>
-    <row r="139" ht="27" spans="1:6">
+    <row r="139" ht="40.5" spans="1:6">
       <c r="A139" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>347</v>
@@ -6212,7 +6241,7 @@
     </row>
     <row r="140" ht="27" spans="1:6">
       <c r="A140" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>349</v>
@@ -6230,7 +6259,7 @@
     </row>
     <row r="141" ht="27" spans="1:6">
       <c r="A141" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>351</v>
@@ -6248,7 +6277,7 @@
     </row>
     <row r="142" ht="27" spans="1:6">
       <c r="A142" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>353</v>
@@ -6266,7 +6295,7 @@
     </row>
     <row r="143" ht="27" spans="1:6">
       <c r="A143" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>355</v>
@@ -6284,7 +6313,7 @@
     </row>
     <row r="144" ht="27" spans="1:6">
       <c r="A144" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>357</v>
@@ -6302,7 +6331,7 @@
     </row>
     <row r="145" ht="27" spans="1:6">
       <c r="A145" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>359</v>
@@ -6320,7 +6349,7 @@
     </row>
     <row r="146" ht="27" spans="1:6">
       <c r="A146" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>361</v>
@@ -6338,7 +6367,7 @@
     </row>
     <row r="147" ht="27" spans="1:6">
       <c r="A147" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>363</v>
@@ -6356,7 +6385,7 @@
     </row>
     <row r="148" ht="27" spans="1:6">
       <c r="A148" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>365</v>
@@ -6374,7 +6403,7 @@
     </row>
     <row r="149" ht="27" spans="1:6">
       <c r="A149" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>367</v>
@@ -6388,11 +6417,11 @@
       <c r="E149" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F149" s="18"/>
-    </row>
-    <row r="150" spans="1:6">
+      <c r="F149" s="17"/>
+    </row>
+    <row r="150" ht="27" spans="1:6">
       <c r="A150" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>369</v>
@@ -6401,18 +6430,16 @@
         <v>370</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F150" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="F150" s="17"/>
+    </row>
+    <row r="151" ht="27" spans="1:6">
       <c r="A151" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>371</v>
@@ -6421,16 +6448,16 @@
         <v>372</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E151" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F151" s="17"/>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" ht="27" spans="1:6">
       <c r="A152" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>373</v>
@@ -6439,16 +6466,16 @@
         <v>374</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E152" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F152" s="17"/>
+      <c r="F152" s="18"/>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>375</v>
@@ -6462,11 +6489,13 @@
       <c r="E153" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F153" s="17"/>
+      <c r="F153" s="16" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>377</v>
@@ -6484,7 +6513,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>379</v>
@@ -6502,7 +6531,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>381</v>
@@ -6520,7 +6549,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>383</v>
@@ -6538,7 +6567,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>385</v>
@@ -6556,7 +6585,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>387</v>
@@ -6574,7 +6603,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>389</v>
@@ -6590,9 +6619,9 @@
       </c>
       <c r="F160" s="17"/>
     </row>
-    <row r="161" ht="40.5" spans="1:6">
+    <row r="161" spans="1:6">
       <c r="A161" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>391</v>
@@ -6608,9 +6637,9 @@
       </c>
       <c r="F161" s="17"/>
     </row>
-    <row r="162" ht="27" spans="1:6">
+    <row r="162" spans="1:6">
       <c r="A162" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>393</v>
@@ -6626,9 +6655,9 @@
       </c>
       <c r="F162" s="17"/>
     </row>
-    <row r="163" ht="27" spans="1:6">
+    <row r="163" spans="1:6">
       <c r="A163" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>395</v>
@@ -6644,9 +6673,9 @@
       </c>
       <c r="F163" s="17"/>
     </row>
-    <row r="164" ht="27" spans="1:6">
+    <row r="164" ht="40.5" spans="1:6">
       <c r="A164" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>397</v>
@@ -6664,7 +6693,7 @@
     </row>
     <row r="165" ht="27" spans="1:6">
       <c r="A165" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>399</v>
@@ -6682,7 +6711,7 @@
     </row>
     <row r="166" ht="27" spans="1:6">
       <c r="A166" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>401</v>
@@ -6700,7 +6729,7 @@
     </row>
     <row r="167" ht="27" spans="1:6">
       <c r="A167" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>403</v>
@@ -6718,7 +6747,7 @@
     </row>
     <row r="168" ht="27" spans="1:6">
       <c r="A168" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>405</v>
@@ -6734,9 +6763,9 @@
       </c>
       <c r="F168" s="17"/>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" ht="27" spans="1:6">
       <c r="A169" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>407</v>
@@ -6752,9 +6781,9 @@
       </c>
       <c r="F169" s="17"/>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" ht="27" spans="1:6">
       <c r="A170" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>409</v>
@@ -6770,9 +6799,9 @@
       </c>
       <c r="F170" s="17"/>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" ht="27" spans="1:6">
       <c r="A171" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>411</v>
@@ -6790,7 +6819,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>413</v>
@@ -6808,7 +6837,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>415</v>
@@ -6826,7 +6855,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>417</v>
@@ -6844,7 +6873,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>419</v>
@@ -6862,7 +6891,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>421</v>
@@ -6880,7 +6909,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>423</v>
@@ -6898,7 +6927,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>425</v>
@@ -6916,7 +6945,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>427</v>
@@ -6934,7 +6963,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>429</v>
@@ -6952,7 +6981,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>431</v>
@@ -6970,7 +6999,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>433</v>
@@ -6986,9 +7015,9 @@
       </c>
       <c r="F182" s="17"/>
     </row>
-    <row r="183" ht="27" spans="1:6">
+    <row r="183" spans="1:6">
       <c r="A183" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>435</v>
@@ -7004,9 +7033,9 @@
       </c>
       <c r="F183" s="17"/>
     </row>
-    <row r="184" ht="27" spans="1:6">
+    <row r="184" spans="1:6">
       <c r="A184" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>437</v>
@@ -7024,7 +7053,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>439</v>
@@ -7040,9 +7069,9 @@
       </c>
       <c r="F185" s="17"/>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" ht="27" spans="1:6">
       <c r="A186" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>441</v>
@@ -7058,9 +7087,9 @@
       </c>
       <c r="F186" s="17"/>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" ht="27" spans="1:6">
       <c r="A187" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>443</v>
@@ -7078,7 +7107,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>445</v>
@@ -7096,7 +7125,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>447</v>
@@ -7114,7 +7143,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>449</v>
@@ -7132,7 +7161,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>451</v>
@@ -7150,7 +7179,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>453</v>
@@ -7168,7 +7197,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>455</v>
@@ -7186,7 +7215,7 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>457</v>
@@ -7204,7 +7233,7 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>459</v>
@@ -7222,7 +7251,7 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>461</v>
@@ -7240,7 +7269,7 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>463</v>
@@ -7254,15 +7283,69 @@
       <c r="E197" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F197" s="18"/>
+      <c r="F197" s="17"/>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F198" s="17"/>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F199" s="17"/>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F200" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F197" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F200" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="2">
-    <mergeCell ref="F102:F149"/>
-    <mergeCell ref="F150:F197"/>
+    <mergeCell ref="F105:F152"/>
+    <mergeCell ref="F153:F200"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
@@ -7284,623 +7367,623 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="3"/>
       <c r="B60" s="4" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:3">
       <c r="A61" s="3"/>
       <c r="B61" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="3"/>
       <c r="B62" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="3"/>
       <c r="B63" s="4" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="3"/>
       <c r="B64" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="3"/>
       <c r="B65" s="4" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="3"/>
       <c r="B66" s="4" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="3"/>
       <c r="B67" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mind-cluster\docs\zh\resource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quyitong\Arbeit\0_repo\mind-cluster-qyt\docs\zh\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1170,7 +1170,8 @@
   <si>
     <t>Atlas A2 训练系列产品
 Atlas 800I A2 推理服务器
-A200I A2 Box 异构组件</t>
+A200I A2 Box 异构组件
+Atlas 350 标卡</t>
   </si>
   <si>
     <t>npu_chip_info_pcie_rx_np_bw</t>
@@ -2583,16 +2584,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF252B3A"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF252B3A"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4847,7 +4848,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="67" ht="40.5" spans="1:6">
+    <row r="67" ht="54" spans="1:6">
       <c r="A67" s="5" t="s">
         <v>188</v>
       </c>
@@ -4867,7 +4868,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="68" ht="40.5" spans="1:6">
+    <row r="68" ht="54" spans="1:6">
       <c r="A68" s="5" t="s">
         <v>188</v>
       </c>
@@ -4887,7 +4888,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="69" ht="40.5" spans="1:6">
+    <row r="69" ht="54" spans="1:6">
       <c r="A69" s="5" t="s">
         <v>188</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="70" ht="40.5" spans="1:6">
+    <row r="70" ht="54" spans="1:6">
       <c r="A70" s="5" t="s">
         <v>188</v>
       </c>
@@ -4927,7 +4928,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="71" ht="40.5" spans="1:6">
+    <row r="71" ht="54" spans="1:6">
       <c r="A71" s="5" t="s">
         <v>188</v>
       </c>
@@ -4947,7 +4948,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="72" ht="40.5" spans="1:6">
+    <row r="72" ht="54" spans="1:6">
       <c r="A72" s="5" t="s">
         <v>188</v>
       </c>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quyitong\Arbeit\0_repo\mind-cluster-qyt\docs\zh\resource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\poc\mind-cluster\docs\zh\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17055"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="511">
   <si>
     <t>类别</t>
   </si>
@@ -2070,7 +2070,7 @@
     <t>标签1</t>
   </si>
   <si>
-    <t>container_name：容器名</t>
+    <t>container_name：容器名。一张NPU卡被多个Pod挂载的场景下，该值为not_displayed_for_multi_pod。</t>
   </si>
   <si>
     <t>string</t>
@@ -2109,13 +2109,13 @@
     </r>
   </si>
   <si>
-    <t>namespace：命名空间名</t>
+    <t>namespace：命名空间名。一张NPU卡被多个Pod挂载的场景下，该值为not_displayed_for_multi_pod。</t>
   </si>
   <si>
     <t>pcie_bus_info：昇腾AI处理器的PCIe信息</t>
   </si>
   <si>
-    <t>pod_name：Pod名</t>
+    <t>pod_name：Pod名。一张NPU卡被多个Pod挂载的场景下，该值为not_displayed_for_multi_pod。</t>
   </si>
   <si>
     <t>vdie_id：昇腾AI处理器唯一标识，可作为NPU的UUID</t>
@@ -2124,7 +2124,7 @@
     <t>标签2</t>
   </si>
   <si>
-    <t>container_name：容器名，输出格式为“Pod Namespace_Pod名_容器名”。如果进程运行在宿主机上，该值为空。</t>
+    <t>container_name：容器名，输出格式为“Pod Namespace_Pod名_容器名”。如果进程运行在宿主机上，该值为空。一张NPU卡被多个Pod挂载的场景下，每个Pod只有1个业务进程时，该值正常展示；每个Pod有多个业务进程时，该值不保证准确性。</t>
   </si>
   <si>
     <t>container_id：容器ID</t>
@@ -2160,6 +2160,9 @@
     </r>
   </si>
   <si>
+    <t>namespace：命名空间名。一张NPU卡被多个Pod挂载的场景下，每个Pod只有1个业务进程时，该值正常展示；每个Pod有多个业务进程时，该值不保证准确性。</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2178,6 +2181,9 @@
       </rPr>
       <t>昇腾AI处理器的PCIe信息</t>
     </r>
+  </si>
+  <si>
+    <t>pod_name：Pod名。一张NPU卡被多个Pod挂载的场景下，每个Pod只有1个业务进程时，该值正常展示；每个Pod有多个业务进程时，该值不保证准确性。</t>
   </si>
   <si>
     <r>
@@ -7480,10 +7486,10 @@
         <v>476</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:3">
+    <row r="13" s="1" customFormat="1" ht="27" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>476</v>
@@ -7492,16 +7498,16 @@
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:3">
+    <row r="15" s="1" customFormat="1" ht="27" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>476</v>
@@ -7510,7 +7516,7 @@
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>476</v>
@@ -7519,7 +7525,7 @@
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>476</v>
@@ -7527,13 +7533,13 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
@@ -7584,7 +7590,7 @@
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>476</v>
@@ -7593,15 +7599,15 @@
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>475</v>
@@ -7640,7 +7646,7 @@
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>476</v>
@@ -7658,7 +7664,7 @@
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>476</v>
@@ -7667,7 +7673,7 @@
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>476</v>
@@ -7675,7 +7681,7 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>475</v>
@@ -7687,7 +7693,7 @@
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>476</v>
@@ -7696,7 +7702,7 @@
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>476</v>
@@ -7705,7 +7711,7 @@
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>476</v>
@@ -7758,7 +7764,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>475</v>
@@ -7815,7 +7821,7 @@
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>476</v>
@@ -7832,7 +7838,7 @@
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>475</v>
@@ -7889,7 +7895,7 @@
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>476</v>
@@ -7906,7 +7912,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>475</v>
@@ -7963,7 +7969,7 @@
     <row r="65" spans="1:3">
       <c r="A65" s="3"/>
       <c r="B65" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>476</v>
@@ -7972,7 +7978,7 @@
     <row r="66" spans="1:3">
       <c r="A66" s="3"/>
       <c r="B66" s="4" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>476</v>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
@@ -94,9 +94,10 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>nodeBase</t>
@@ -235,7 +236,8 @@
     </r>
   </si>
   <si>
-    <t>Atlas 350 标卡（4Pmesh互联）说明：旧版本指标</t>
+    <t>Atlas 350 加速卡（4Pmesh互联）
+说明：旧版本指标</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_rx_X_Y</t>
@@ -316,9 +318,10 @@
     <t>详见“标签数据信息说明”页签中“标签8”</t>
   </si>
   <si>
-    <t>Atlas 350 标卡（4Pmesh互联）
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+    <t>Atlas 350 加速卡（4Pmesh互联）
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <r>
@@ -629,12 +632,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="方正兰亭黑简体"/>
-        <charset val="134"/>
-      </rPr>
       <t>Atlas 训练系列产品
 Atlas A2 训练系列产品
 Atlas A3 训练系列产品
@@ -642,9 +639,10 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点
 说明：
 只有Atlas 推理系列产品为板卡功耗，其余产品为</t>
     </r>
@@ -737,9 +735,10 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>container_npu_used_memory</t>
@@ -837,9 +836,10 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>npu_chip_info_vector_utilization</t>
@@ -871,9 +871,10 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>RoCE</t>
@@ -952,9 +953,10 @@
 Atlas A3 训练系列产品
 A200I A2 Box 异构组件
 Atlas 800I A2 推理服务器
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>npu_chip_info_hbm_total_memory</t>
@@ -1304,9 +1306,10 @@
   </si>
   <si>
     <t>Atlas A3 训练系列产品
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>npu_chip_info_sio_crc_rx_err_cnt</t>
@@ -1419,7 +1422,8 @@
     <t>芯片Udie Port链接的光模块Lane数量。</t>
   </si>
   <si>
-    <t>Atlas 850 系列硬件产品</t>
+    <t>Atlas 850E 超节点
+Atlas 650E 服务器</t>
   </si>
   <si>
     <t>npu_chip_info_optical_tx_power_Z</t>
@@ -2056,12 +2060,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="方正兰亭黑简体"/>
-        <charset val="134"/>
-      </rPr>
       <t>model_name：</t>
     </r>
     <r>
@@ -2081,7 +2079,7 @@
         <charset val="134"/>
       </rPr>
       <t>腾AI处理器名称。该字段由芯片名称、芯片类型和芯片版本三部分组成。这三部分可通过npu-smi info -t board -i NPU ID -c Chip ID命令查询，分别对应返回信息中的Chip Name、Chip Type和Chip Version。
-说明：Atlas A3 系列产品的返回信息中无Chip Type字段。</t>
+说明：Atlas A3 推理系列产品/Atlas A3 训练系列产品的返回信息中无Chip Type字段。</t>
     </r>
   </si>
   <si>
@@ -2107,12 +2105,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="方正兰亭黑简体"/>
-        <charset val="134"/>
-      </rPr>
       <t>model_name：</t>
     </r>
     <r>
@@ -2132,7 +2124,7 @@
         <charset val="134"/>
       </rPr>
       <t>腾AI处理器名称。该字段由芯片名称、芯片类型和芯片版本三部分组成。这三部分可通过npu-smi info -t board -i NPU ID -c Chip ID命令查询，分别对应返回信息中的Chip Name、Chip Type和Chip Version。
-说明：Atlas A3 系列产品的返回信息中无Chip Type字段。</t>
+说明：Atlas A3 推理系列产品/Atlas A3 训练系列产品的返回信息中无Chip Type字段。</t>
     </r>
   </si>
   <si>
@@ -2560,16 +2552,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF252B3A"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF252B3A"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3493,7 +3485,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="42" style="7" customWidth="1"/>
@@ -3524,7 +3516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="154" customHeight="1" spans="1:6">
+    <row r="2" ht="167" customHeight="1" spans="1:6">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -3544,7 +3536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="154" customHeight="1" spans="1:6">
+    <row r="3" ht="167" customHeight="1" spans="1:6">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -3584,7 +3576,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="67.5" spans="1:6">
+    <row r="5" ht="75" spans="1:6">
       <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
@@ -3624,7 +3616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="67.5" spans="1:6">
+    <row r="7" ht="75" spans="1:6">
       <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
@@ -3644,7 +3636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="84" spans="1:6">
+    <row r="8" ht="90" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -3664,7 +3656,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="84" spans="1:6">
+    <row r="9" ht="90" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -3684,7 +3676,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="40.5" spans="1:6">
+    <row r="10" ht="36" customHeight="1" spans="1:6">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -3704,7 +3696,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="40.5" spans="1:6">
+    <row r="11" ht="35" customHeight="1" spans="1:6">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -3724,7 +3716,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:6">
+    <row r="12" ht="30" spans="1:6">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -3744,7 +3736,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" ht="159" customHeight="1" spans="1:6">
+    <row r="13" ht="86" customHeight="1" spans="1:6">
       <c r="A13" s="7" t="s">
         <v>16</v>
       </c>
@@ -3764,7 +3756,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" ht="159" customHeight="1" spans="1:6">
+    <row r="14" ht="69" customHeight="1" spans="1:6">
       <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
@@ -3784,7 +3776,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" ht="159" customHeight="1" spans="1:6">
+    <row r="15" ht="72" customHeight="1" spans="1:6">
       <c r="A15" s="7" t="s">
         <v>16</v>
       </c>
@@ -3804,7 +3796,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" ht="159" customHeight="1" spans="1:6">
+    <row r="16" ht="63" customHeight="1" spans="1:6">
       <c r="A16" s="7" t="s">
         <v>16</v>
       </c>
@@ -3824,7 +3816,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" ht="159" customHeight="1" spans="1:6">
+    <row r="17" ht="168" customHeight="1" spans="1:6">
       <c r="A17" s="5" t="s">
         <v>49</v>
       </c>
@@ -3844,7 +3836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" ht="159" customHeight="1" spans="1:6">
+    <row r="18" ht="107" customHeight="1" spans="1:6">
       <c r="A18" s="5" t="s">
         <v>49</v>
       </c>
@@ -3864,7 +3856,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" ht="84" spans="1:6">
+    <row r="19" ht="79" customHeight="1" spans="1:6">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -3884,7 +3876,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" ht="175.5" spans="1:6">
+    <row r="20" ht="170" customHeight="1" spans="1:6">
       <c r="A20" s="7" t="s">
         <v>49</v>
       </c>
@@ -3904,7 +3896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" ht="149" customHeight="1" spans="1:6">
+    <row r="21" ht="164" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
         <v>49</v>
       </c>
@@ -3924,7 +3916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" ht="135" spans="1:6">
+    <row r="22" ht="165" spans="1:6">
       <c r="A22" s="7" t="s">
         <v>49</v>
       </c>
@@ -3944,7 +3936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" ht="175.5" spans="1:6">
+    <row r="23" ht="210" spans="1:6">
       <c r="A23" s="9" t="s">
         <v>49</v>
       </c>
@@ -3964,7 +3956,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" ht="135" spans="1:6">
+    <row r="24" ht="165" spans="1:6">
       <c r="A24" s="9" t="s">
         <v>49</v>
       </c>
@@ -3984,7 +3976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" ht="153" customHeight="1" spans="1:6">
+    <row r="25" ht="164" customHeight="1" spans="1:6">
       <c r="A25" s="7" t="s">
         <v>49</v>
       </c>
@@ -4004,7 +3996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" ht="151" customHeight="1" spans="1:6">
+    <row r="26" ht="164" customHeight="1" spans="1:6">
       <c r="A26" s="7" t="s">
         <v>49</v>
       </c>
@@ -4024,7 +4016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" ht="135" spans="1:6">
+    <row r="27" ht="165" spans="1:6">
       <c r="A27" s="9" t="s">
         <v>49</v>
       </c>
@@ -4044,7 +4036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" ht="135" spans="1:6">
+    <row r="28" ht="165" spans="1:6">
       <c r="A28" s="7" t="s">
         <v>49</v>
       </c>
@@ -4064,7 +4056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" ht="135" spans="1:6">
+    <row r="29" ht="165" spans="1:6">
       <c r="A29" s="9" t="s">
         <v>49</v>
       </c>
@@ -4084,7 +4076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="108" spans="1:6">
+    <row r="30" ht="135" spans="1:6">
       <c r="A30" s="9" t="s">
         <v>49</v>
       </c>
@@ -4104,7 +4096,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" ht="108" spans="1:6">
+    <row r="31" ht="135" spans="1:6">
       <c r="A31" s="9" t="s">
         <v>49</v>
       </c>
@@ -4124,7 +4116,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" ht="135" spans="1:6">
+    <row r="32" ht="165" spans="1:6">
       <c r="A32" s="4" t="s">
         <v>49</v>
       </c>
@@ -4144,7 +4136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" ht="135" spans="1:6">
+    <row r="33" ht="165" spans="1:6">
       <c r="A33" s="9" t="s">
         <v>49</v>
       </c>
@@ -4184,7 +4176,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" ht="135" spans="1:6">
+    <row r="35" ht="165" spans="1:6">
       <c r="A35" s="4" t="s">
         <v>104</v>
       </c>
@@ -4204,7 +4196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" ht="135" spans="1:6">
+    <row r="36" ht="165" spans="1:6">
       <c r="A36" s="4" t="s">
         <v>104</v>
       </c>
@@ -4224,7 +4216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" ht="54" spans="1:6">
+    <row r="37" ht="60" spans="1:6">
       <c r="A37" s="4" t="s">
         <v>104</v>
       </c>
@@ -4244,7 +4236,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" ht="94.5" spans="1:6">
+    <row r="38" ht="120" spans="1:6">
       <c r="A38" s="4" t="s">
         <v>104</v>
       </c>
@@ -4264,7 +4256,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" ht="121.5" spans="1:6">
+    <row r="39" ht="150" spans="1:6">
       <c r="A39" s="4" t="s">
         <v>104</v>
       </c>
@@ -4284,7 +4276,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" ht="67.5" spans="1:6">
+    <row r="40" ht="75" spans="1:6">
       <c r="A40" s="7" t="s">
         <v>119</v>
       </c>
@@ -4304,7 +4296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" ht="67.5" spans="1:6">
+    <row r="41" ht="75" spans="1:6">
       <c r="A41" s="9" t="s">
         <v>119</v>
       </c>
@@ -4384,7 +4376,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" ht="40.5" spans="1:6">
+    <row r="45" ht="45" spans="1:6">
       <c r="A45" s="5" t="s">
         <v>133</v>
       </c>
@@ -4404,7 +4396,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="46" ht="40.5" spans="1:6">
+    <row r="46" ht="45" spans="1:6">
       <c r="A46" s="5" t="s">
         <v>133</v>
       </c>
@@ -4424,7 +4416,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="47" ht="108" spans="1:6">
+    <row r="47" ht="135" spans="1:6">
       <c r="A47" s="5" t="s">
         <v>139</v>
       </c>
@@ -4444,7 +4436,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" ht="123" customHeight="1" spans="1:6">
+    <row r="48" ht="135" customHeight="1" spans="1:6">
       <c r="A48" s="5" t="s">
         <v>139</v>
       </c>
@@ -4464,7 +4456,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="49" ht="108" spans="1:6">
+    <row r="49" ht="135" spans="1:6">
       <c r="A49" s="13" t="s">
         <v>139</v>
       </c>
@@ -4484,7 +4476,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" ht="108" spans="1:6">
+    <row r="50" ht="135" spans="1:6">
       <c r="A50" s="13" t="s">
         <v>139</v>
       </c>
@@ -4504,7 +4496,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="51" ht="108" spans="1:6">
+    <row r="51" ht="135" spans="1:6">
       <c r="A51" s="13" t="s">
         <v>139</v>
       </c>
@@ -4524,7 +4516,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" ht="108" spans="1:6">
+    <row r="52" ht="135" spans="1:6">
       <c r="A52" s="13" t="s">
         <v>139</v>
       </c>
@@ -4544,7 +4536,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="53" ht="108" spans="1:6">
+    <row r="53" ht="135" spans="1:6">
       <c r="A53" s="13" t="s">
         <v>139</v>
       </c>
@@ -4584,7 +4576,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="55" ht="108" spans="1:6">
+    <row r="55" ht="135" spans="1:6">
       <c r="A55" s="13" t="s">
         <v>139</v>
       </c>
@@ -4644,7 +4636,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" ht="40.5" spans="1:6">
+    <row r="58" ht="45" spans="1:6">
       <c r="A58" s="15" t="s">
         <v>160</v>
       </c>
@@ -4664,7 +4656,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" ht="40.5" spans="1:6">
+    <row r="59" ht="45" spans="1:6">
       <c r="A59" s="15" t="s">
         <v>160</v>
       </c>
@@ -4684,7 +4676,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="60" ht="40.5" spans="1:6">
+    <row r="60" ht="45" spans="1:6">
       <c r="A60" s="15" t="s">
         <v>160</v>
       </c>
@@ -4724,7 +4716,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" ht="40.5" spans="1:6">
+    <row r="62" ht="45" spans="1:6">
       <c r="A62" s="15" t="s">
         <v>160</v>
       </c>
@@ -4764,7 +4756,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="64" ht="40.5" spans="1:6">
+    <row r="64" ht="45" spans="1:6">
       <c r="A64" s="5" t="s">
         <v>182</v>
       </c>
@@ -4784,7 +4776,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="65" ht="40.5" spans="1:6">
+    <row r="65" ht="45" spans="1:6">
       <c r="A65" s="5" t="s">
         <v>182</v>
       </c>
@@ -4804,7 +4796,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="66" ht="40.5" spans="1:6">
+    <row r="66" ht="45" spans="1:6">
       <c r="A66" s="5" t="s">
         <v>182</v>
       </c>
@@ -4824,7 +4816,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="67" ht="40.5" spans="1:6">
+    <row r="67" ht="45" spans="1:6">
       <c r="A67" s="5" t="s">
         <v>182</v>
       </c>
@@ -4844,7 +4836,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="68" ht="40.5" spans="1:6">
+    <row r="68" ht="45" spans="1:6">
       <c r="A68" s="5" t="s">
         <v>182</v>
       </c>
@@ -4864,7 +4856,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="69" ht="40.5" spans="1:6">
+    <row r="69" ht="45" spans="1:6">
       <c r="A69" s="5" t="s">
         <v>182</v>
       </c>
@@ -4884,7 +4876,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="70" ht="67.5" spans="1:6">
+    <row r="70" ht="75" spans="1:6">
       <c r="A70" s="5" t="s">
         <v>119</v>
       </c>
@@ -4904,7 +4896,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" ht="67.5" spans="1:6">
+    <row r="71" ht="75" spans="1:6">
       <c r="A71" s="5" t="s">
         <v>119</v>
       </c>
@@ -4924,7 +4916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" ht="67.5" spans="1:6">
+    <row r="72" ht="75" spans="1:6">
       <c r="A72" s="5" t="s">
         <v>119</v>
       </c>
@@ -4944,7 +4936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" ht="67.5" spans="1:6">
+    <row r="73" ht="75" spans="1:6">
       <c r="A73" s="5" t="s">
         <v>119</v>
       </c>
@@ -4964,7 +4956,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" ht="67.5" spans="1:6">
+    <row r="74" ht="75" spans="1:6">
       <c r="A74" s="5" t="s">
         <v>119</v>
       </c>
@@ -4984,7 +4976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" ht="67.5" spans="1:6">
+    <row r="75" ht="75" spans="1:6">
       <c r="A75" s="5" t="s">
         <v>119</v>
       </c>
@@ -5004,7 +4996,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" ht="67.5" spans="1:6">
+    <row r="76" ht="75" spans="1:6">
       <c r="A76" s="5" t="s">
         <v>119</v>
       </c>
@@ -5024,7 +5016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" ht="67.5" spans="1:6">
+    <row r="77" ht="75" spans="1:6">
       <c r="A77" s="5" t="s">
         <v>119</v>
       </c>
@@ -5044,7 +5036,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" ht="67.5" spans="1:6">
+    <row r="78" ht="75" spans="1:6">
       <c r="A78" s="5" t="s">
         <v>119</v>
       </c>
@@ -5064,7 +5056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" ht="67.5" spans="1:6">
+    <row r="79" ht="75" spans="1:6">
       <c r="A79" s="5" t="s">
         <v>119</v>
       </c>
@@ -5104,7 +5096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" ht="67.5" spans="1:6">
+    <row r="81" ht="75" spans="1:6">
       <c r="A81" s="5" t="s">
         <v>119</v>
       </c>
@@ -5124,7 +5116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" ht="67.5" spans="1:6">
+    <row r="82" ht="75" spans="1:6">
       <c r="A82" s="5" t="s">
         <v>119</v>
       </c>
@@ -5144,7 +5136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" ht="67.5" spans="1:6">
+    <row r="83" ht="75" spans="1:6">
       <c r="A83" s="5" t="s">
         <v>119</v>
       </c>
@@ -5164,7 +5156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" ht="67.5" spans="1:6">
+    <row r="84" ht="75" spans="1:6">
       <c r="A84" s="5" t="s">
         <v>119</v>
       </c>
@@ -5184,7 +5176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" ht="67.5" spans="1:6">
+    <row r="85" ht="75" spans="1:6">
       <c r="A85" s="5" t="s">
         <v>119</v>
       </c>
@@ -5204,7 +5196,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" ht="67.5" spans="1:6">
+    <row r="86" ht="75" spans="1:6">
       <c r="A86" s="5" t="s">
         <v>119</v>
       </c>
@@ -5224,7 +5216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" ht="67.5" spans="1:6">
+    <row r="87" ht="75" spans="1:6">
       <c r="A87" s="5" t="s">
         <v>119</v>
       </c>
@@ -5244,7 +5236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" ht="27" customHeight="1" spans="1:6">
+    <row r="88" ht="84" customHeight="1" spans="1:6">
       <c r="A88" s="5" t="s">
         <v>119</v>
       </c>
@@ -5264,7 +5256,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1" spans="1:6">
+    <row r="89" ht="75" customHeight="1" spans="1:6">
       <c r="A89" s="5" t="s">
         <v>236</v>
       </c>
@@ -5284,7 +5276,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" ht="54" spans="1:6">
+    <row r="90" ht="75" spans="1:6">
       <c r="A90" s="5" t="s">
         <v>236</v>
       </c>
@@ -5304,7 +5296,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="91" ht="67.5" spans="1:6">
+    <row r="91" ht="75" spans="1:6">
       <c r="A91" s="5" t="s">
         <v>242</v>
       </c>
@@ -5324,7 +5316,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" ht="67.5" spans="1:6">
+    <row r="92" ht="75" spans="1:6">
       <c r="A92" s="5" t="s">
         <v>242</v>
       </c>
@@ -5344,7 +5336,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="93" ht="67.5" spans="1:6">
+    <row r="93" ht="75" spans="1:6">
       <c r="A93" s="5" t="s">
         <v>242</v>
       </c>
@@ -5364,7 +5356,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="94" ht="67.5" spans="1:6">
+    <row r="94" ht="75" spans="1:6">
       <c r="A94" s="5" t="s">
         <v>242</v>
       </c>
@@ -5384,7 +5376,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="95" ht="67.5" spans="1:6">
+    <row r="95" ht="75" spans="1:6">
       <c r="A95" s="5" t="s">
         <v>242</v>
       </c>
@@ -5404,7 +5396,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="96" ht="27" spans="1:6">
+    <row r="96" ht="30" spans="1:6">
       <c r="A96" s="5" t="s">
         <v>242</v>
       </c>
@@ -5424,7 +5416,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="97" ht="27" spans="1:6">
+    <row r="97" ht="30" spans="1:6">
       <c r="A97" s="5" t="s">
         <v>242</v>
       </c>
@@ -5444,7 +5436,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="98" ht="27" spans="1:6">
+    <row r="98" ht="30" spans="1:6">
       <c r="A98" s="5" t="s">
         <v>242</v>
       </c>
@@ -5464,7 +5456,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="99" ht="108" spans="1:6">
+    <row r="99" ht="135" spans="1:6">
       <c r="A99" s="9" t="s">
         <v>139</v>
       </c>
@@ -5484,7 +5476,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="100" ht="108" spans="1:6">
+    <row r="100" ht="135" spans="1:6">
       <c r="A100" s="9" t="s">
         <v>139</v>
       </c>
@@ -5504,7 +5496,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="101" ht="108" spans="1:6">
+    <row r="101" ht="135" spans="1:6">
       <c r="A101" s="9" t="s">
         <v>139</v>
       </c>
@@ -5524,7 +5516,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="102" ht="27" spans="1:6">
+    <row r="102" ht="30" spans="1:6">
       <c r="A102" s="5" t="s">
         <v>272</v>
       </c>
@@ -5544,7 +5536,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" ht="27" spans="1:6">
+    <row r="103" ht="30" spans="1:6">
       <c r="A103" s="5" t="s">
         <v>272</v>
       </c>
@@ -5562,7 +5554,7 @@
       </c>
       <c r="F103" s="17"/>
     </row>
-    <row r="104" ht="27" spans="1:6">
+    <row r="104" ht="30" spans="1:6">
       <c r="A104" s="5" t="s">
         <v>272</v>
       </c>
@@ -5580,7 +5572,7 @@
       </c>
       <c r="F104" s="17"/>
     </row>
-    <row r="105" ht="27" spans="1:6">
+    <row r="105" ht="30" spans="1:6">
       <c r="A105" s="5" t="s">
         <v>272</v>
       </c>
@@ -5598,7 +5590,7 @@
       </c>
       <c r="F105" s="17"/>
     </row>
-    <row r="106" ht="27" spans="1:6">
+    <row r="106" ht="30" spans="1:6">
       <c r="A106" s="5" t="s">
         <v>272</v>
       </c>
@@ -5616,7 +5608,7 @@
       </c>
       <c r="F106" s="17"/>
     </row>
-    <row r="107" ht="27" spans="1:6">
+    <row r="107" ht="30" spans="1:6">
       <c r="A107" s="5" t="s">
         <v>272</v>
       </c>
@@ -5634,7 +5626,7 @@
       </c>
       <c r="F107" s="17"/>
     </row>
-    <row r="108" ht="27" spans="1:6">
+    <row r="108" ht="30" spans="1:6">
       <c r="A108" s="5" t="s">
         <v>272</v>
       </c>
@@ -5652,7 +5644,7 @@
       </c>
       <c r="F108" s="17"/>
     </row>
-    <row r="109" ht="27" spans="1:6">
+    <row r="109" ht="30" spans="1:6">
       <c r="A109" s="5" t="s">
         <v>272</v>
       </c>
@@ -5670,7 +5662,7 @@
       </c>
       <c r="F109" s="17"/>
     </row>
-    <row r="110" ht="27" spans="1:6">
+    <row r="110" ht="30" spans="1:6">
       <c r="A110" s="5" t="s">
         <v>272</v>
       </c>
@@ -5688,7 +5680,7 @@
       </c>
       <c r="F110" s="17"/>
     </row>
-    <row r="111" ht="27" spans="1:6">
+    <row r="111" ht="30" spans="1:6">
       <c r="A111" s="5" t="s">
         <v>272</v>
       </c>
@@ -5706,7 +5698,7 @@
       </c>
       <c r="F111" s="17"/>
     </row>
-    <row r="112" ht="27" spans="1:6">
+    <row r="112" ht="30" spans="1:6">
       <c r="A112" s="5" t="s">
         <v>272</v>
       </c>
@@ -5724,7 +5716,7 @@
       </c>
       <c r="F112" s="17"/>
     </row>
-    <row r="113" ht="40.5" spans="1:6">
+    <row r="113" ht="45" spans="1:6">
       <c r="A113" s="5" t="s">
         <v>272</v>
       </c>
@@ -5742,7 +5734,7 @@
       </c>
       <c r="F113" s="17"/>
     </row>
-    <row r="114" ht="40.5" spans="1:6">
+    <row r="114" ht="45" spans="1:6">
       <c r="A114" s="5" t="s">
         <v>272</v>
       </c>
@@ -5760,7 +5752,7 @@
       </c>
       <c r="F114" s="17"/>
     </row>
-    <row r="115" ht="40.5" spans="1:6">
+    <row r="115" ht="45" spans="1:6">
       <c r="A115" s="5" t="s">
         <v>272</v>
       </c>
@@ -5778,7 +5770,7 @@
       </c>
       <c r="F115" s="17"/>
     </row>
-    <row r="116" ht="40.5" spans="1:6">
+    <row r="116" ht="45" spans="1:6">
       <c r="A116" s="5" t="s">
         <v>272</v>
       </c>
@@ -5796,7 +5788,7 @@
       </c>
       <c r="F116" s="17"/>
     </row>
-    <row r="117" ht="27" spans="1:6">
+    <row r="117" ht="45" spans="1:6">
       <c r="A117" s="5" t="s">
         <v>272</v>
       </c>
@@ -5814,7 +5806,7 @@
       </c>
       <c r="F117" s="17"/>
     </row>
-    <row r="118" ht="40.5" spans="1:6">
+    <row r="118" ht="45" spans="1:6">
       <c r="A118" s="5" t="s">
         <v>272</v>
       </c>
@@ -5832,7 +5824,7 @@
       </c>
       <c r="F118" s="17"/>
     </row>
-    <row r="119" ht="27" spans="1:6">
+    <row r="119" ht="45" spans="1:6">
       <c r="A119" s="5" t="s">
         <v>272</v>
       </c>
@@ -5850,7 +5842,7 @@
       </c>
       <c r="F119" s="17"/>
     </row>
-    <row r="120" ht="40.5" spans="1:6">
+    <row r="120" ht="45" spans="1:6">
       <c r="A120" s="5" t="s">
         <v>272</v>
       </c>
@@ -5868,7 +5860,7 @@
       </c>
       <c r="F120" s="17"/>
     </row>
-    <row r="121" ht="27" spans="1:6">
+    <row r="121" ht="30" spans="1:6">
       <c r="A121" s="5" t="s">
         <v>272</v>
       </c>
@@ -5886,7 +5878,7 @@
       </c>
       <c r="F121" s="17"/>
     </row>
-    <row r="122" ht="27" spans="1:6">
+    <row r="122" ht="30" spans="1:6">
       <c r="A122" s="5" t="s">
         <v>272</v>
       </c>
@@ -5904,7 +5896,7 @@
       </c>
       <c r="F122" s="17"/>
     </row>
-    <row r="123" ht="27" spans="1:6">
+    <row r="123" ht="30" spans="1:6">
       <c r="A123" s="5" t="s">
         <v>272</v>
       </c>
@@ -5922,7 +5914,7 @@
       </c>
       <c r="F123" s="17"/>
     </row>
-    <row r="124" ht="27" spans="1:6">
+    <row r="124" ht="30" spans="1:6">
       <c r="A124" s="5" t="s">
         <v>272</v>
       </c>
@@ -5940,7 +5932,7 @@
       </c>
       <c r="F124" s="17"/>
     </row>
-    <row r="125" ht="27" spans="1:6">
+    <row r="125" ht="30" spans="1:6">
       <c r="A125" s="5" t="s">
         <v>272</v>
       </c>
@@ -5958,7 +5950,7 @@
       </c>
       <c r="F125" s="17"/>
     </row>
-    <row r="126" ht="27" spans="1:6">
+    <row r="126" ht="30" spans="1:6">
       <c r="A126" s="5" t="s">
         <v>272</v>
       </c>
@@ -5976,7 +5968,7 @@
       </c>
       <c r="F126" s="17"/>
     </row>
-    <row r="127" ht="27" spans="1:6">
+    <row r="127" ht="30" spans="1:6">
       <c r="A127" s="5" t="s">
         <v>272</v>
       </c>
@@ -5994,7 +5986,7 @@
       </c>
       <c r="F127" s="17"/>
     </row>
-    <row r="128" ht="27" spans="1:6">
+    <row r="128" ht="30" spans="1:6">
       <c r="A128" s="5" t="s">
         <v>272</v>
       </c>
@@ -6012,7 +6004,7 @@
       </c>
       <c r="F128" s="17"/>
     </row>
-    <row r="129" ht="27" spans="1:6">
+    <row r="129" ht="30" spans="1:6">
       <c r="A129" s="5" t="s">
         <v>272</v>
       </c>
@@ -6030,7 +6022,7 @@
       </c>
       <c r="F129" s="17"/>
     </row>
-    <row r="130" ht="27" spans="1:6">
+    <row r="130" ht="30" spans="1:6">
       <c r="A130" s="5" t="s">
         <v>272</v>
       </c>
@@ -6048,7 +6040,7 @@
       </c>
       <c r="F130" s="17"/>
     </row>
-    <row r="131" ht="27" spans="1:6">
+    <row r="131" ht="30" spans="1:6">
       <c r="A131" s="5" t="s">
         <v>272</v>
       </c>
@@ -6066,7 +6058,7 @@
       </c>
       <c r="F131" s="17"/>
     </row>
-    <row r="132" ht="27" spans="1:6">
+    <row r="132" ht="30" spans="1:6">
       <c r="A132" s="5" t="s">
         <v>272</v>
       </c>
@@ -6084,7 +6076,7 @@
       </c>
       <c r="F132" s="17"/>
     </row>
-    <row r="133" ht="27" spans="1:6">
+    <row r="133" ht="30" spans="1:6">
       <c r="A133" s="5" t="s">
         <v>272</v>
       </c>
@@ -6102,7 +6094,7 @@
       </c>
       <c r="F133" s="17"/>
     </row>
-    <row r="134" ht="27" spans="1:6">
+    <row r="134" ht="30" spans="1:6">
       <c r="A134" s="5" t="s">
         <v>272</v>
       </c>
@@ -6120,7 +6112,7 @@
       </c>
       <c r="F134" s="17"/>
     </row>
-    <row r="135" ht="27" spans="1:6">
+    <row r="135" ht="30" spans="1:6">
       <c r="A135" s="5" t="s">
         <v>272</v>
       </c>
@@ -6138,7 +6130,7 @@
       </c>
       <c r="F135" s="17"/>
     </row>
-    <row r="136" ht="40.5" spans="1:6">
+    <row r="136" ht="45" spans="1:6">
       <c r="A136" s="5" t="s">
         <v>272</v>
       </c>
@@ -6156,7 +6148,7 @@
       </c>
       <c r="F136" s="17"/>
     </row>
-    <row r="137" ht="27" spans="1:6">
+    <row r="137" ht="30" spans="1:6">
       <c r="A137" s="5" t="s">
         <v>272</v>
       </c>
@@ -6174,7 +6166,7 @@
       </c>
       <c r="F137" s="17"/>
     </row>
-    <row r="138" ht="27" spans="1:6">
+    <row r="138" ht="30" spans="1:6">
       <c r="A138" s="5" t="s">
         <v>272</v>
       </c>
@@ -6192,7 +6184,7 @@
       </c>
       <c r="F138" s="17"/>
     </row>
-    <row r="139" ht="27" spans="1:6">
+    <row r="139" ht="30" spans="1:6">
       <c r="A139" s="5" t="s">
         <v>272</v>
       </c>
@@ -6210,7 +6202,7 @@
       </c>
       <c r="F139" s="17"/>
     </row>
-    <row r="140" ht="27" spans="1:6">
+    <row r="140" ht="30" spans="1:6">
       <c r="A140" s="5" t="s">
         <v>272</v>
       </c>
@@ -6228,7 +6220,7 @@
       </c>
       <c r="F140" s="17"/>
     </row>
-    <row r="141" ht="27" spans="1:6">
+    <row r="141" ht="30" spans="1:6">
       <c r="A141" s="5" t="s">
         <v>272</v>
       </c>
@@ -6246,7 +6238,7 @@
       </c>
       <c r="F141" s="17"/>
     </row>
-    <row r="142" ht="27" spans="1:6">
+    <row r="142" ht="30" spans="1:6">
       <c r="A142" s="5" t="s">
         <v>272</v>
       </c>
@@ -6264,7 +6256,7 @@
       </c>
       <c r="F142" s="17"/>
     </row>
-    <row r="143" ht="27" spans="1:6">
+    <row r="143" ht="30" spans="1:6">
       <c r="A143" s="5" t="s">
         <v>272</v>
       </c>
@@ -6282,7 +6274,7 @@
       </c>
       <c r="F143" s="17"/>
     </row>
-    <row r="144" ht="27" spans="1:6">
+    <row r="144" ht="30" spans="1:6">
       <c r="A144" s="5" t="s">
         <v>272</v>
       </c>
@@ -6300,7 +6292,7 @@
       </c>
       <c r="F144" s="17"/>
     </row>
-    <row r="145" ht="27" spans="1:6">
+    <row r="145" ht="30" spans="1:6">
       <c r="A145" s="5" t="s">
         <v>272</v>
       </c>
@@ -6318,7 +6310,7 @@
       </c>
       <c r="F145" s="17"/>
     </row>
-    <row r="146" ht="27" spans="1:6">
+    <row r="146" ht="30" spans="1:6">
       <c r="A146" s="5" t="s">
         <v>272</v>
       </c>
@@ -6336,7 +6328,7 @@
       </c>
       <c r="F146" s="17"/>
     </row>
-    <row r="147" ht="27" spans="1:6">
+    <row r="147" ht="30" spans="1:6">
       <c r="A147" s="5" t="s">
         <v>272</v>
       </c>
@@ -6354,7 +6346,7 @@
       </c>
       <c r="F147" s="17"/>
     </row>
-    <row r="148" ht="27" spans="1:6">
+    <row r="148" ht="30" spans="1:6">
       <c r="A148" s="5" t="s">
         <v>272</v>
       </c>
@@ -6372,7 +6364,7 @@
       </c>
       <c r="F148" s="17"/>
     </row>
-    <row r="149" ht="27" spans="1:6">
+    <row r="149" ht="30" spans="1:6">
       <c r="A149" s="5" t="s">
         <v>272</v>
       </c>
@@ -6500,7 +6492,7 @@
       </c>
       <c r="F155" s="17"/>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" ht="30" spans="1:6">
       <c r="A156" s="5" t="s">
         <v>272</v>
       </c>
@@ -6554,7 +6546,7 @@
       </c>
       <c r="F158" s="17"/>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" ht="30" spans="1:6">
       <c r="A159" s="5" t="s">
         <v>272</v>
       </c>
@@ -6590,7 +6582,7 @@
       </c>
       <c r="F160" s="17"/>
     </row>
-    <row r="161" ht="40.5" spans="1:6">
+    <row r="161" ht="45" spans="1:6">
       <c r="A161" s="5" t="s">
         <v>272</v>
       </c>
@@ -6608,7 +6600,7 @@
       </c>
       <c r="F161" s="17"/>
     </row>
-    <row r="162" ht="27" spans="1:6">
+    <row r="162" ht="30" spans="1:6">
       <c r="A162" s="5" t="s">
         <v>272</v>
       </c>
@@ -6626,7 +6618,7 @@
       </c>
       <c r="F162" s="17"/>
     </row>
-    <row r="163" ht="27" spans="1:6">
+    <row r="163" ht="30" spans="1:6">
       <c r="A163" s="5" t="s">
         <v>272</v>
       </c>
@@ -6644,7 +6636,7 @@
       </c>
       <c r="F163" s="17"/>
     </row>
-    <row r="164" ht="27" spans="1:6">
+    <row r="164" ht="30" spans="1:6">
       <c r="A164" s="5" t="s">
         <v>272</v>
       </c>
@@ -6662,7 +6654,7 @@
       </c>
       <c r="F164" s="17"/>
     </row>
-    <row r="165" ht="27" spans="1:6">
+    <row r="165" ht="30" spans="1:6">
       <c r="A165" s="5" t="s">
         <v>272</v>
       </c>
@@ -6680,7 +6672,7 @@
       </c>
       <c r="F165" s="17"/>
     </row>
-    <row r="166" ht="27" spans="1:6">
+    <row r="166" ht="30" spans="1:6">
       <c r="A166" s="5" t="s">
         <v>272</v>
       </c>
@@ -6698,7 +6690,7 @@
       </c>
       <c r="F166" s="17"/>
     </row>
-    <row r="167" ht="27" spans="1:6">
+    <row r="167" ht="30" spans="1:6">
       <c r="A167" s="5" t="s">
         <v>272</v>
       </c>
@@ -6716,7 +6708,7 @@
       </c>
       <c r="F167" s="17"/>
     </row>
-    <row r="168" ht="27" spans="1:6">
+    <row r="168" ht="30" spans="1:6">
       <c r="A168" s="5" t="s">
         <v>272</v>
       </c>
@@ -6986,7 +6978,7 @@
       </c>
       <c r="F182" s="17"/>
     </row>
-    <row r="183" ht="27" spans="1:6">
+    <row r="183" ht="30" spans="1:6">
       <c r="A183" s="5" t="s">
         <v>272</v>
       </c>
@@ -7004,7 +6996,7 @@
       </c>
       <c r="F183" s="17"/>
     </row>
-    <row r="184" ht="27" spans="1:6">
+    <row r="184" ht="30" spans="1:6">
       <c r="A184" s="5" t="s">
         <v>272</v>
       </c>
@@ -7257,9 +7249,6 @@
       <c r="F197" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F197" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="F102:F149"/>
     <mergeCell ref="F150:F197"/>
@@ -7274,7 +7263,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18.6333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="73.8833333333333" style="1" customWidth="1"/>
@@ -7313,7 +7302,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="4" s="1" customFormat="1" ht="75" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
         <v>472</v>
@@ -7387,7 +7376,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="12" s="1" customFormat="1" ht="75" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
         <v>480</v>
@@ -7470,7 +7459,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="21" s="1" customFormat="1" ht="75" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
         <v>472</v>
@@ -7535,7 +7524,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="28" s="1" customFormat="1" ht="75" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
         <v>480</v>
@@ -7627,7 +7616,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="38" s="1" customFormat="1" ht="75" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
         <v>472</v>
@@ -7692,7 +7681,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="45" s="1" customFormat="1" ht="75" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
         <v>472</v>
@@ -7766,7 +7755,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="53" s="1" customFormat="1" ht="75" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
         <v>472</v>
@@ -7840,7 +7829,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="61" ht="54" spans="1:3">
+    <row r="61" ht="75" spans="1:3">
       <c r="A61" s="3"/>
       <c r="B61" s="5" t="s">
         <v>472</v>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\poc\mind-cluster\docs\zh\resource\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
@@ -99,9 +94,10 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>nodeBase</t>
@@ -240,7 +236,8 @@
     </r>
   </si>
   <si>
-    <t>Atlas 350 标卡（4Pmesh互联）说明：旧版本指标</t>
+    <t>Atlas 350 加速卡（4Pmesh互联）
+说明：旧版本指标</t>
   </si>
   <si>
     <t>npu_chip_info_bandwidth_rx_X_Y</t>
@@ -321,9 +318,10 @@
     <t>详见“标签数据信息说明”页签中“标签8”</t>
   </si>
   <si>
-    <t>Atlas 350 标卡（4Pmesh互联）
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+    <t>Atlas 350 加速卡（4Pmesh互联）
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <r>
@@ -652,12 +650,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="方正兰亭黑简体"/>
-        <charset val="134"/>
-      </rPr>
       <t>Atlas 训练系列产品
 Atlas A2 训练系列产品
 Atlas A3 训练系列产品
@@ -665,9 +657,10 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点
 说明：
 只有Atlas 推理系列产品为板卡功耗，其余产品为</t>
     </r>
@@ -760,9 +753,10 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>container_npu_used_memory</t>
@@ -860,9 +854,10 @@
 Atlas A3 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>npu_chip_info_vector_utilization</t>
@@ -894,9 +889,10 @@
 Atlas 推理系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>RoCE</t>
@@ -975,9 +971,10 @@
 Atlas A3 训练系列产品
 A200I A2 Box 异构组件
 Atlas 800I A2 推理服务器
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>npu_chip_info_hbm_total_memory</t>
@@ -1171,7 +1168,7 @@
     <t>Atlas A2 训练系列产品
 Atlas 800I A2 推理服务器
 A200I A2 Box 异构组件
-Atlas 350 标卡</t>
+Atlas 350 加速卡</t>
   </si>
   <si>
     <t>npu_chip_info_pcie_rx_np_bw</t>
@@ -1328,9 +1325,10 @@
   </si>
   <si>
     <t>Atlas A3 训练系列产品
-Atlas 350 标卡
-Atlas 850 系列硬件产品
-Atlas 950 SuperPoD</t>
+Atlas 350 加速卡
+Atlas 850E 超节点
+Atlas 650E 服务器
+Atlas 950 SuperPoD 超节点</t>
   </si>
   <si>
     <t>npu_chip_info_sio_crc_rx_err_cnt</t>
@@ -1443,7 +1441,8 @@
     <t>芯片Udie Port链接的光模块Lane数量。</t>
   </si>
   <si>
-    <t>Atlas 850 系列硬件产品</t>
+    <t>Atlas 850E 超节点
+Atlas 650E 服务器</t>
   </si>
   <si>
     <t>npu_chip_info_optical_tx_power_Z</t>
@@ -3523,7 +3522,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="42" style="7" customWidth="1"/>
@@ -3554,7 +3553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="154" customHeight="1" spans="1:6">
+    <row r="2" ht="182" customHeight="1" spans="1:6">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -3574,7 +3573,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="154" customHeight="1" spans="1:6">
+    <row r="3" ht="171" customHeight="1" spans="1:6">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="67.5" spans="1:6">
+    <row r="5" ht="75" spans="1:6">
       <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
@@ -3654,7 +3653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="67.5" spans="1:6">
+    <row r="7" ht="75" spans="1:6">
       <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
@@ -3674,7 +3673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="84" spans="1:6">
+    <row r="8" ht="90" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -3694,7 +3693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="84" spans="1:6">
+    <row r="9" ht="90" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -3714,7 +3713,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="40.5" spans="1:6">
+    <row r="10" ht="45" spans="1:6">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -3734,7 +3733,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="40.5" spans="1:6">
+    <row r="11" ht="45" spans="1:6">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -3754,7 +3753,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:6">
+    <row r="12" ht="30" spans="1:6">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -3774,7 +3773,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" ht="159" customHeight="1" spans="1:6">
+    <row r="13" ht="100" customHeight="1" spans="1:6">
       <c r="A13" s="7" t="s">
         <v>16</v>
       </c>
@@ -3794,7 +3793,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" ht="159" customHeight="1" spans="1:6">
+    <row r="14" ht="69" customHeight="1" spans="1:6">
       <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
@@ -3814,7 +3813,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" ht="159" customHeight="1" spans="1:6">
+    <row r="15" ht="71" customHeight="1" spans="1:6">
       <c r="A15" s="7" t="s">
         <v>16</v>
       </c>
@@ -3834,7 +3833,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" ht="159" customHeight="1" spans="1:6">
+    <row r="16" ht="60" customHeight="1" spans="1:6">
       <c r="A16" s="7" t="s">
         <v>16</v>
       </c>
@@ -3854,7 +3853,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" ht="159" customHeight="1" spans="1:6">
+    <row r="17" ht="171" customHeight="1" spans="1:6">
       <c r="A17" s="5" t="s">
         <v>49</v>
       </c>
@@ -3874,7 +3873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" ht="159" customHeight="1" spans="1:6">
+    <row r="18" ht="176" customHeight="1" spans="1:6">
       <c r="A18" s="5" t="s">
         <v>49</v>
       </c>
@@ -3894,7 +3893,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" ht="159" customHeight="1" spans="1:6">
+    <row r="19" ht="168" customHeight="1" spans="1:6">
       <c r="A19" s="5" t="s">
         <v>49</v>
       </c>
@@ -3914,7 +3913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" ht="159" customHeight="1" spans="1:6">
+    <row r="20" ht="171" customHeight="1" spans="1:6">
       <c r="A20" s="5" t="s">
         <v>49</v>
       </c>
@@ -3934,7 +3933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" ht="159" customHeight="1" spans="1:6">
+    <row r="21" ht="131" customHeight="1" spans="1:6">
       <c r="A21" s="5" t="s">
         <v>49</v>
       </c>
@@ -3954,7 +3953,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" ht="84" spans="1:6">
+    <row r="22" ht="90" spans="1:6">
       <c r="A22" s="7" t="s">
         <v>49</v>
       </c>
@@ -3974,7 +3973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" ht="175.5" spans="1:6">
+    <row r="23" ht="174" customHeight="1" spans="1:6">
       <c r="A23" s="7" t="s">
         <v>49</v>
       </c>
@@ -3994,7 +3993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" ht="149" customHeight="1" spans="1:6">
+    <row r="24" ht="168" customHeight="1" spans="1:6">
       <c r="A24" s="7" t="s">
         <v>49</v>
       </c>
@@ -4014,7 +4013,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" ht="135" spans="1:6">
+    <row r="25" ht="165" spans="1:6">
       <c r="A25" s="7" t="s">
         <v>49</v>
       </c>
@@ -4034,7 +4033,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" ht="175.5" spans="1:6">
+    <row r="26" ht="210" spans="1:6">
       <c r="A26" s="9" t="s">
         <v>49</v>
       </c>
@@ -4054,7 +4053,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" ht="135" spans="1:6">
+    <row r="27" ht="165" spans="1:6">
       <c r="A27" s="9" t="s">
         <v>49</v>
       </c>
@@ -4074,7 +4073,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" ht="153" customHeight="1" spans="1:6">
+    <row r="28" ht="164" customHeight="1" spans="1:6">
       <c r="A28" s="7" t="s">
         <v>49</v>
       </c>
@@ -4094,7 +4093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" ht="151" customHeight="1" spans="1:6">
+    <row r="29" ht="165" customHeight="1" spans="1:6">
       <c r="A29" s="7" t="s">
         <v>49</v>
       </c>
@@ -4114,7 +4113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="135" spans="1:6">
+    <row r="30" ht="165" spans="1:6">
       <c r="A30" s="9" t="s">
         <v>49</v>
       </c>
@@ -4134,7 +4133,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" ht="135" spans="1:6">
+    <row r="31" ht="165" spans="1:6">
       <c r="A31" s="7" t="s">
         <v>49</v>
       </c>
@@ -4154,7 +4153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" ht="135" spans="1:6">
+    <row r="32" ht="165" spans="1:6">
       <c r="A32" s="9" t="s">
         <v>49</v>
       </c>
@@ -4174,7 +4173,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" ht="108" spans="1:6">
+    <row r="33" ht="135" spans="1:6">
       <c r="A33" s="9" t="s">
         <v>49</v>
       </c>
@@ -4194,7 +4193,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" ht="108" spans="1:6">
+    <row r="34" ht="135" spans="1:6">
       <c r="A34" s="9" t="s">
         <v>49</v>
       </c>
@@ -4214,7 +4213,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" ht="135" spans="1:6">
+    <row r="35" ht="165" spans="1:6">
       <c r="A35" s="4" t="s">
         <v>49</v>
       </c>
@@ -4234,7 +4233,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" ht="135" spans="1:6">
+    <row r="36" ht="165" spans="1:6">
       <c r="A36" s="9" t="s">
         <v>49</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" ht="135" spans="1:6">
+    <row r="38" ht="165" spans="1:6">
       <c r="A38" s="4" t="s">
         <v>110</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" ht="135" spans="1:6">
+    <row r="39" ht="165" spans="1:6">
       <c r="A39" s="4" t="s">
         <v>110</v>
       </c>
@@ -4314,7 +4313,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" ht="54" spans="1:6">
+    <row r="40" ht="60" spans="1:6">
       <c r="A40" s="4" t="s">
         <v>110</v>
       </c>
@@ -4334,7 +4333,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" ht="94.5" spans="1:6">
+    <row r="41" ht="120" spans="1:6">
       <c r="A41" s="4" t="s">
         <v>110</v>
       </c>
@@ -4354,7 +4353,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" ht="121.5" spans="1:6">
+    <row r="42" ht="150" spans="1:6">
       <c r="A42" s="4" t="s">
         <v>110</v>
       </c>
@@ -4374,7 +4373,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="43" ht="67.5" spans="1:6">
+    <row r="43" ht="75" spans="1:6">
       <c r="A43" s="7" t="s">
         <v>125</v>
       </c>
@@ -4394,7 +4393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" ht="67.5" spans="1:6">
+    <row r="44" ht="75" spans="1:6">
       <c r="A44" s="9" t="s">
         <v>125</v>
       </c>
@@ -4474,7 +4473,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" ht="40.5" spans="1:6">
+    <row r="48" ht="45" spans="1:6">
       <c r="A48" s="5" t="s">
         <v>139</v>
       </c>
@@ -4494,7 +4493,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="49" ht="40.5" spans="1:6">
+    <row r="49" ht="45" spans="1:6">
       <c r="A49" s="5" t="s">
         <v>139</v>
       </c>
@@ -4514,7 +4513,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" ht="108" spans="1:6">
+    <row r="50" ht="135" spans="1:6">
       <c r="A50" s="5" t="s">
         <v>145</v>
       </c>
@@ -4534,7 +4533,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="51" ht="123" customHeight="1" spans="1:6">
+    <row r="51" ht="136" customHeight="1" spans="1:6">
       <c r="A51" s="5" t="s">
         <v>145</v>
       </c>
@@ -4554,7 +4553,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" ht="108" spans="1:6">
+    <row r="52" ht="135" spans="1:6">
       <c r="A52" s="13" t="s">
         <v>145</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="53" ht="108" spans="1:6">
+    <row r="53" ht="135" spans="1:6">
       <c r="A53" s="13" t="s">
         <v>145</v>
       </c>
@@ -4594,7 +4593,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="54" ht="108" spans="1:6">
+    <row r="54" ht="135" spans="1:6">
       <c r="A54" s="13" t="s">
         <v>145</v>
       </c>
@@ -4614,7 +4613,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="55" ht="108" spans="1:6">
+    <row r="55" ht="135" spans="1:6">
       <c r="A55" s="13" t="s">
         <v>145</v>
       </c>
@@ -4634,7 +4633,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" ht="108" spans="1:6">
+    <row r="56" ht="135" spans="1:6">
       <c r="A56" s="13" t="s">
         <v>145</v>
       </c>
@@ -4654,7 +4653,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" ht="119" customHeight="1" spans="1:6">
+    <row r="57" ht="133" customHeight="1" spans="1:6">
       <c r="A57" s="13" t="s">
         <v>145</v>
       </c>
@@ -4674,7 +4673,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" ht="108" spans="1:6">
+    <row r="58" ht="135" spans="1:6">
       <c r="A58" s="13" t="s">
         <v>145</v>
       </c>
@@ -4734,7 +4733,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="61" ht="40.5" spans="1:6">
+    <row r="61" ht="45" spans="1:6">
       <c r="A61" s="15" t="s">
         <v>166</v>
       </c>
@@ -4754,7 +4753,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="62" ht="40.5" spans="1:6">
+    <row r="62" ht="45" spans="1:6">
       <c r="A62" s="15" t="s">
         <v>166</v>
       </c>
@@ -4774,7 +4773,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="63" ht="40.5" spans="1:6">
+    <row r="63" ht="45" spans="1:6">
       <c r="A63" s="15" t="s">
         <v>166</v>
       </c>
@@ -4814,7 +4813,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="65" ht="40.5" spans="1:6">
+    <row r="65" ht="45" spans="1:6">
       <c r="A65" s="15" t="s">
         <v>166</v>
       </c>
@@ -4854,7 +4853,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="67" ht="54" spans="1:6">
+    <row r="67" ht="60" spans="1:6">
       <c r="A67" s="5" t="s">
         <v>188</v>
       </c>
@@ -4874,7 +4873,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="68" ht="54" spans="1:6">
+    <row r="68" ht="60" spans="1:6">
       <c r="A68" s="5" t="s">
         <v>188</v>
       </c>
@@ -4894,7 +4893,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="69" ht="54" spans="1:6">
+    <row r="69" ht="60" spans="1:6">
       <c r="A69" s="5" t="s">
         <v>188</v>
       </c>
@@ -4914,7 +4913,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="70" ht="54" spans="1:6">
+    <row r="70" ht="60" spans="1:6">
       <c r="A70" s="5" t="s">
         <v>188</v>
       </c>
@@ -4934,7 +4933,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="71" ht="54" spans="1:6">
+    <row r="71" ht="60" spans="1:6">
       <c r="A71" s="5" t="s">
         <v>188</v>
       </c>
@@ -4954,7 +4953,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="72" ht="54" spans="1:6">
+    <row r="72" ht="60" spans="1:6">
       <c r="A72" s="5" t="s">
         <v>188</v>
       </c>
@@ -4974,7 +4973,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="73" ht="67.5" spans="1:6">
+    <row r="73" ht="75" spans="1:6">
       <c r="A73" s="5" t="s">
         <v>125</v>
       </c>
@@ -4994,7 +4993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" ht="67.5" spans="1:6">
+    <row r="74" ht="75" spans="1:6">
       <c r="A74" s="5" t="s">
         <v>125</v>
       </c>
@@ -5014,7 +5013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" ht="67.5" spans="1:6">
+    <row r="75" ht="75" spans="1:6">
       <c r="A75" s="5" t="s">
         <v>125</v>
       </c>
@@ -5034,7 +5033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" ht="67.5" spans="1:6">
+    <row r="76" ht="75" spans="1:6">
       <c r="A76" s="5" t="s">
         <v>125</v>
       </c>
@@ -5054,7 +5053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" ht="67.5" spans="1:6">
+    <row r="77" ht="75" spans="1:6">
       <c r="A77" s="5" t="s">
         <v>125</v>
       </c>
@@ -5074,7 +5073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" ht="67.5" spans="1:6">
+    <row r="78" ht="75" spans="1:6">
       <c r="A78" s="5" t="s">
         <v>125</v>
       </c>
@@ -5094,7 +5093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" ht="67.5" spans="1:6">
+    <row r="79" ht="75" spans="1:6">
       <c r="A79" s="5" t="s">
         <v>125</v>
       </c>
@@ -5114,7 +5113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" ht="67.5" spans="1:6">
+    <row r="80" ht="75" spans="1:6">
       <c r="A80" s="5" t="s">
         <v>125</v>
       </c>
@@ -5134,7 +5133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" ht="67.5" spans="1:6">
+    <row r="81" ht="75" spans="1:6">
       <c r="A81" s="5" t="s">
         <v>125</v>
       </c>
@@ -5154,7 +5153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" ht="67.5" spans="1:6">
+    <row r="82" ht="75" spans="1:6">
       <c r="A82" s="5" t="s">
         <v>125</v>
       </c>
@@ -5194,7 +5193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" ht="67.5" spans="1:6">
+    <row r="84" ht="75" spans="1:6">
       <c r="A84" s="5" t="s">
         <v>125</v>
       </c>
@@ -5214,7 +5213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" ht="67.5" spans="1:6">
+    <row r="85" ht="75" spans="1:6">
       <c r="A85" s="5" t="s">
         <v>125</v>
       </c>
@@ -5234,7 +5233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" ht="67.5" spans="1:6">
+    <row r="86" ht="75" spans="1:6">
       <c r="A86" s="5" t="s">
         <v>125</v>
       </c>
@@ -5254,7 +5253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" ht="67.5" spans="1:6">
+    <row r="87" ht="75" spans="1:6">
       <c r="A87" s="5" t="s">
         <v>125</v>
       </c>
@@ -5274,7 +5273,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" ht="67.5" spans="1:6">
+    <row r="88" ht="75" spans="1:6">
       <c r="A88" s="5" t="s">
         <v>125</v>
       </c>
@@ -5294,7 +5293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" ht="67.5" spans="1:6">
+    <row r="89" ht="75" spans="1:6">
       <c r="A89" s="5" t="s">
         <v>125</v>
       </c>
@@ -5314,7 +5313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" ht="67.5" spans="1:6">
+    <row r="90" ht="75" spans="1:6">
       <c r="A90" s="5" t="s">
         <v>125</v>
       </c>
@@ -5334,7 +5333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" ht="27" customHeight="1" spans="1:6">
+    <row r="91" ht="75" customHeight="1" spans="1:6">
       <c r="A91" s="5" t="s">
         <v>125</v>
       </c>
@@ -5354,7 +5353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1" spans="1:6">
+    <row r="92" ht="78" customHeight="1" spans="1:6">
       <c r="A92" s="5" t="s">
         <v>242</v>
       </c>
@@ -5374,7 +5373,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="93" ht="54" spans="1:6">
+    <row r="93" ht="75" spans="1:6">
       <c r="A93" s="5" t="s">
         <v>242</v>
       </c>
@@ -5394,7 +5393,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="94" ht="67.5" spans="1:6">
+    <row r="94" ht="75" spans="1:6">
       <c r="A94" s="5" t="s">
         <v>248</v>
       </c>
@@ -5414,7 +5413,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="95" ht="67.5" spans="1:6">
+    <row r="95" ht="75" spans="1:6">
       <c r="A95" s="5" t="s">
         <v>248</v>
       </c>
@@ -5434,7 +5433,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="96" ht="67.5" spans="1:6">
+    <row r="96" ht="75" spans="1:6">
       <c r="A96" s="5" t="s">
         <v>248</v>
       </c>
@@ -5454,7 +5453,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="97" ht="67.5" spans="1:6">
+    <row r="97" ht="75" spans="1:6">
       <c r="A97" s="5" t="s">
         <v>248</v>
       </c>
@@ -5474,7 +5473,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="98" ht="67.5" spans="1:6">
+    <row r="98" ht="75" spans="1:6">
       <c r="A98" s="5" t="s">
         <v>248</v>
       </c>
@@ -5494,7 +5493,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="99" ht="27" spans="1:6">
+    <row r="99" ht="30" spans="1:6">
       <c r="A99" s="5" t="s">
         <v>248</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="100" ht="27" spans="1:6">
+    <row r="100" ht="30" spans="1:6">
       <c r="A100" s="5" t="s">
         <v>248</v>
       </c>
@@ -5534,7 +5533,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="101" ht="27" spans="1:6">
+    <row r="101" ht="30" spans="1:6">
       <c r="A101" s="5" t="s">
         <v>248</v>
       </c>
@@ -5554,7 +5553,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="102" ht="108" spans="1:6">
+    <row r="102" ht="135" spans="1:6">
       <c r="A102" s="9" t="s">
         <v>145</v>
       </c>
@@ -5574,7 +5573,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="103" ht="108" spans="1:6">
+    <row r="103" ht="135" spans="1:6">
       <c r="A103" s="9" t="s">
         <v>145</v>
       </c>
@@ -5594,7 +5593,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="104" ht="108" spans="1:6">
+    <row r="104" ht="135" spans="1:6">
       <c r="A104" s="9" t="s">
         <v>145</v>
       </c>
@@ -5614,7 +5613,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="105" ht="27" spans="1:6">
+    <row r="105" ht="30" spans="1:6">
       <c r="A105" s="5" t="s">
         <v>278</v>
       </c>
@@ -5634,7 +5633,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106" ht="27" spans="1:6">
+    <row r="106" ht="30" spans="1:6">
       <c r="A106" s="5" t="s">
         <v>278</v>
       </c>
@@ -5652,7 +5651,7 @@
       </c>
       <c r="F106" s="17"/>
     </row>
-    <row r="107" ht="27" spans="1:6">
+    <row r="107" ht="30" spans="1:6">
       <c r="A107" s="5" t="s">
         <v>278</v>
       </c>
@@ -5670,7 +5669,7 @@
       </c>
       <c r="F107" s="17"/>
     </row>
-    <row r="108" ht="27" spans="1:6">
+    <row r="108" ht="30" spans="1:6">
       <c r="A108" s="5" t="s">
         <v>278</v>
       </c>
@@ -5688,7 +5687,7 @@
       </c>
       <c r="F108" s="17"/>
     </row>
-    <row r="109" ht="27" spans="1:6">
+    <row r="109" ht="30" spans="1:6">
       <c r="A109" s="5" t="s">
         <v>278</v>
       </c>
@@ -5706,7 +5705,7 @@
       </c>
       <c r="F109" s="17"/>
     </row>
-    <row r="110" ht="27" spans="1:6">
+    <row r="110" ht="30" spans="1:6">
       <c r="A110" s="5" t="s">
         <v>278</v>
       </c>
@@ -5724,7 +5723,7 @@
       </c>
       <c r="F110" s="17"/>
     </row>
-    <row r="111" ht="27" spans="1:6">
+    <row r="111" ht="30" spans="1:6">
       <c r="A111" s="5" t="s">
         <v>278</v>
       </c>
@@ -5742,7 +5741,7 @@
       </c>
       <c r="F111" s="17"/>
     </row>
-    <row r="112" ht="27" spans="1:6">
+    <row r="112" ht="30" spans="1:6">
       <c r="A112" s="5" t="s">
         <v>278</v>
       </c>
@@ -5760,7 +5759,7 @@
       </c>
       <c r="F112" s="17"/>
     </row>
-    <row r="113" ht="27" spans="1:6">
+    <row r="113" ht="30" spans="1:6">
       <c r="A113" s="5" t="s">
         <v>278</v>
       </c>
@@ -5778,7 +5777,7 @@
       </c>
       <c r="F113" s="17"/>
     </row>
-    <row r="114" ht="27" spans="1:6">
+    <row r="114" ht="30" spans="1:6">
       <c r="A114" s="5" t="s">
         <v>278</v>
       </c>
@@ -5796,7 +5795,7 @@
       </c>
       <c r="F114" s="17"/>
     </row>
-    <row r="115" ht="27" spans="1:6">
+    <row r="115" ht="30" spans="1:6">
       <c r="A115" s="5" t="s">
         <v>278</v>
       </c>
@@ -5814,7 +5813,7 @@
       </c>
       <c r="F115" s="17"/>
     </row>
-    <row r="116" ht="40.5" spans="1:6">
+    <row r="116" ht="45" spans="1:6">
       <c r="A116" s="5" t="s">
         <v>278</v>
       </c>
@@ -5832,7 +5831,7 @@
       </c>
       <c r="F116" s="17"/>
     </row>
-    <row r="117" ht="40.5" spans="1:6">
+    <row r="117" ht="45" spans="1:6">
       <c r="A117" s="5" t="s">
         <v>278</v>
       </c>
@@ -5850,7 +5849,7 @@
       </c>
       <c r="F117" s="17"/>
     </row>
-    <row r="118" ht="40.5" spans="1:6">
+    <row r="118" ht="45" spans="1:6">
       <c r="A118" s="5" t="s">
         <v>278</v>
       </c>
@@ -5868,7 +5867,7 @@
       </c>
       <c r="F118" s="17"/>
     </row>
-    <row r="119" ht="40.5" spans="1:6">
+    <row r="119" ht="45" spans="1:6">
       <c r="A119" s="5" t="s">
         <v>278</v>
       </c>
@@ -5886,7 +5885,7 @@
       </c>
       <c r="F119" s="17"/>
     </row>
-    <row r="120" ht="27" spans="1:6">
+    <row r="120" ht="45" spans="1:6">
       <c r="A120" s="5" t="s">
         <v>278</v>
       </c>
@@ -5904,7 +5903,7 @@
       </c>
       <c r="F120" s="17"/>
     </row>
-    <row r="121" ht="40.5" spans="1:6">
+    <row r="121" ht="45" spans="1:6">
       <c r="A121" s="5" t="s">
         <v>278</v>
       </c>
@@ -5922,7 +5921,7 @@
       </c>
       <c r="F121" s="17"/>
     </row>
-    <row r="122" ht="27" spans="1:6">
+    <row r="122" ht="45" spans="1:6">
       <c r="A122" s="5" t="s">
         <v>278</v>
       </c>
@@ -5940,7 +5939,7 @@
       </c>
       <c r="F122" s="17"/>
     </row>
-    <row r="123" ht="40.5" spans="1:6">
+    <row r="123" ht="45" spans="1:6">
       <c r="A123" s="5" t="s">
         <v>278</v>
       </c>
@@ -5958,7 +5957,7 @@
       </c>
       <c r="F123" s="17"/>
     </row>
-    <row r="124" ht="27" spans="1:6">
+    <row r="124" ht="30" spans="1:6">
       <c r="A124" s="5" t="s">
         <v>278</v>
       </c>
@@ -5976,7 +5975,7 @@
       </c>
       <c r="F124" s="17"/>
     </row>
-    <row r="125" ht="27" spans="1:6">
+    <row r="125" ht="30" spans="1:6">
       <c r="A125" s="5" t="s">
         <v>278</v>
       </c>
@@ -5994,7 +5993,7 @@
       </c>
       <c r="F125" s="17"/>
     </row>
-    <row r="126" ht="27" spans="1:6">
+    <row r="126" ht="30" spans="1:6">
       <c r="A126" s="5" t="s">
         <v>278</v>
       </c>
@@ -6012,7 +6011,7 @@
       </c>
       <c r="F126" s="17"/>
     </row>
-    <row r="127" ht="27" spans="1:6">
+    <row r="127" ht="30" spans="1:6">
       <c r="A127" s="5" t="s">
         <v>278</v>
       </c>
@@ -6030,7 +6029,7 @@
       </c>
       <c r="F127" s="17"/>
     </row>
-    <row r="128" ht="27" spans="1:6">
+    <row r="128" ht="30" spans="1:6">
       <c r="A128" s="5" t="s">
         <v>278</v>
       </c>
@@ -6048,7 +6047,7 @@
       </c>
       <c r="F128" s="17"/>
     </row>
-    <row r="129" ht="27" spans="1:6">
+    <row r="129" ht="30" spans="1:6">
       <c r="A129" s="5" t="s">
         <v>278</v>
       </c>
@@ -6066,7 +6065,7 @@
       </c>
       <c r="F129" s="17"/>
     </row>
-    <row r="130" ht="27" spans="1:6">
+    <row r="130" ht="30" spans="1:6">
       <c r="A130" s="5" t="s">
         <v>278</v>
       </c>
@@ -6084,7 +6083,7 @@
       </c>
       <c r="F130" s="17"/>
     </row>
-    <row r="131" ht="27" spans="1:6">
+    <row r="131" ht="30" spans="1:6">
       <c r="A131" s="5" t="s">
         <v>278</v>
       </c>
@@ -6102,7 +6101,7 @@
       </c>
       <c r="F131" s="17"/>
     </row>
-    <row r="132" ht="27" spans="1:6">
+    <row r="132" ht="30" spans="1:6">
       <c r="A132" s="5" t="s">
         <v>278</v>
       </c>
@@ -6120,7 +6119,7 @@
       </c>
       <c r="F132" s="17"/>
     </row>
-    <row r="133" ht="27" spans="1:6">
+    <row r="133" ht="30" spans="1:6">
       <c r="A133" s="5" t="s">
         <v>278</v>
       </c>
@@ -6138,7 +6137,7 @@
       </c>
       <c r="F133" s="17"/>
     </row>
-    <row r="134" ht="27" spans="1:6">
+    <row r="134" ht="30" spans="1:6">
       <c r="A134" s="5" t="s">
         <v>278</v>
       </c>
@@ -6156,7 +6155,7 @@
       </c>
       <c r="F134" s="17"/>
     </row>
-    <row r="135" ht="27" spans="1:6">
+    <row r="135" ht="30" spans="1:6">
       <c r="A135" s="5" t="s">
         <v>278</v>
       </c>
@@ -6174,7 +6173,7 @@
       </c>
       <c r="F135" s="17"/>
     </row>
-    <row r="136" ht="27" spans="1:6">
+    <row r="136" ht="30" spans="1:6">
       <c r="A136" s="5" t="s">
         <v>278</v>
       </c>
@@ -6192,7 +6191,7 @@
       </c>
       <c r="F136" s="17"/>
     </row>
-    <row r="137" ht="27" spans="1:6">
+    <row r="137" ht="30" spans="1:6">
       <c r="A137" s="5" t="s">
         <v>278</v>
       </c>
@@ -6210,7 +6209,7 @@
       </c>
       <c r="F137" s="17"/>
     </row>
-    <row r="138" ht="27" spans="1:6">
+    <row r="138" ht="30" spans="1:6">
       <c r="A138" s="5" t="s">
         <v>278</v>
       </c>
@@ -6228,7 +6227,7 @@
       </c>
       <c r="F138" s="17"/>
     </row>
-    <row r="139" ht="40.5" spans="1:6">
+    <row r="139" ht="45" spans="1:6">
       <c r="A139" s="5" t="s">
         <v>278</v>
       </c>
@@ -6246,7 +6245,7 @@
       </c>
       <c r="F139" s="17"/>
     </row>
-    <row r="140" ht="27" spans="1:6">
+    <row r="140" ht="30" spans="1:6">
       <c r="A140" s="5" t="s">
         <v>278</v>
       </c>
@@ -6264,7 +6263,7 @@
       </c>
       <c r="F140" s="17"/>
     </row>
-    <row r="141" ht="27" spans="1:6">
+    <row r="141" ht="30" spans="1:6">
       <c r="A141" s="5" t="s">
         <v>278</v>
       </c>
@@ -6282,7 +6281,7 @@
       </c>
       <c r="F141" s="17"/>
     </row>
-    <row r="142" ht="27" spans="1:6">
+    <row r="142" ht="30" spans="1:6">
       <c r="A142" s="5" t="s">
         <v>278</v>
       </c>
@@ -6300,7 +6299,7 @@
       </c>
       <c r="F142" s="17"/>
     </row>
-    <row r="143" ht="27" spans="1:6">
+    <row r="143" ht="30" spans="1:6">
       <c r="A143" s="5" t="s">
         <v>278</v>
       </c>
@@ -6318,7 +6317,7 @@
       </c>
       <c r="F143" s="17"/>
     </row>
-    <row r="144" ht="27" spans="1:6">
+    <row r="144" ht="30" spans="1:6">
       <c r="A144" s="5" t="s">
         <v>278</v>
       </c>
@@ -6336,7 +6335,7 @@
       </c>
       <c r="F144" s="17"/>
     </row>
-    <row r="145" ht="27" spans="1:6">
+    <row r="145" ht="30" spans="1:6">
       <c r="A145" s="5" t="s">
         <v>278</v>
       </c>
@@ -6354,7 +6353,7 @@
       </c>
       <c r="F145" s="17"/>
     </row>
-    <row r="146" ht="27" spans="1:6">
+    <row r="146" ht="30" spans="1:6">
       <c r="A146" s="5" t="s">
         <v>278</v>
       </c>
@@ -6372,7 +6371,7 @@
       </c>
       <c r="F146" s="17"/>
     </row>
-    <row r="147" ht="27" spans="1:6">
+    <row r="147" ht="30" spans="1:6">
       <c r="A147" s="5" t="s">
         <v>278</v>
       </c>
@@ -6390,7 +6389,7 @@
       </c>
       <c r="F147" s="17"/>
     </row>
-    <row r="148" ht="27" spans="1:6">
+    <row r="148" ht="30" spans="1:6">
       <c r="A148" s="5" t="s">
         <v>278</v>
       </c>
@@ -6408,7 +6407,7 @@
       </c>
       <c r="F148" s="17"/>
     </row>
-    <row r="149" ht="27" spans="1:6">
+    <row r="149" ht="30" spans="1:6">
       <c r="A149" s="5" t="s">
         <v>278</v>
       </c>
@@ -6426,7 +6425,7 @@
       </c>
       <c r="F149" s="17"/>
     </row>
-    <row r="150" ht="27" spans="1:6">
+    <row r="150" ht="30" spans="1:6">
       <c r="A150" s="5" t="s">
         <v>278</v>
       </c>
@@ -6444,7 +6443,7 @@
       </c>
       <c r="F150" s="17"/>
     </row>
-    <row r="151" ht="27" spans="1:6">
+    <row r="151" ht="30" spans="1:6">
       <c r="A151" s="5" t="s">
         <v>278</v>
       </c>
@@ -6462,7 +6461,7 @@
       </c>
       <c r="F151" s="17"/>
     </row>
-    <row r="152" ht="27" spans="1:6">
+    <row r="152" ht="30" spans="1:6">
       <c r="A152" s="5" t="s">
         <v>278</v>
       </c>
@@ -6590,7 +6589,7 @@
       </c>
       <c r="F158" s="17"/>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" ht="30" spans="1:6">
       <c r="A159" s="5" t="s">
         <v>278</v>
       </c>
@@ -6644,7 +6643,7 @@
       </c>
       <c r="F161" s="17"/>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" ht="30" spans="1:6">
       <c r="A162" s="5" t="s">
         <v>278</v>
       </c>
@@ -6680,7 +6679,7 @@
       </c>
       <c r="F163" s="17"/>
     </row>
-    <row r="164" ht="40.5" spans="1:6">
+    <row r="164" ht="45" spans="1:6">
       <c r="A164" s="5" t="s">
         <v>278</v>
       </c>
@@ -6698,7 +6697,7 @@
       </c>
       <c r="F164" s="17"/>
     </row>
-    <row r="165" ht="27" spans="1:6">
+    <row r="165" ht="30" spans="1:6">
       <c r="A165" s="5" t="s">
         <v>278</v>
       </c>
@@ -6716,7 +6715,7 @@
       </c>
       <c r="F165" s="17"/>
     </row>
-    <row r="166" ht="27" spans="1:6">
+    <row r="166" ht="30" spans="1:6">
       <c r="A166" s="5" t="s">
         <v>278</v>
       </c>
@@ -6734,7 +6733,7 @@
       </c>
       <c r="F166" s="17"/>
     </row>
-    <row r="167" ht="27" spans="1:6">
+    <row r="167" ht="30" spans="1:6">
       <c r="A167" s="5" t="s">
         <v>278</v>
       </c>
@@ -6752,7 +6751,7 @@
       </c>
       <c r="F167" s="17"/>
     </row>
-    <row r="168" ht="27" spans="1:6">
+    <row r="168" ht="30" spans="1:6">
       <c r="A168" s="5" t="s">
         <v>278</v>
       </c>
@@ -6770,7 +6769,7 @@
       </c>
       <c r="F168" s="17"/>
     </row>
-    <row r="169" ht="27" spans="1:6">
+    <row r="169" ht="30" spans="1:6">
       <c r="A169" s="5" t="s">
         <v>278</v>
       </c>
@@ -6788,7 +6787,7 @@
       </c>
       <c r="F169" s="17"/>
     </row>
-    <row r="170" ht="27" spans="1:6">
+    <row r="170" ht="30" spans="1:6">
       <c r="A170" s="5" t="s">
         <v>278</v>
       </c>
@@ -6806,7 +6805,7 @@
       </c>
       <c r="F170" s="17"/>
     </row>
-    <row r="171" ht="27" spans="1:6">
+    <row r="171" ht="30" spans="1:6">
       <c r="A171" s="5" t="s">
         <v>278</v>
       </c>
@@ -7076,7 +7075,7 @@
       </c>
       <c r="F185" s="17"/>
     </row>
-    <row r="186" ht="27" spans="1:6">
+    <row r="186" ht="30" spans="1:6">
       <c r="A186" s="5" t="s">
         <v>278</v>
       </c>
@@ -7094,7 +7093,7 @@
       </c>
       <c r="F186" s="17"/>
     </row>
-    <row r="187" ht="27" spans="1:6">
+    <row r="187" ht="30" spans="1:6">
       <c r="A187" s="5" t="s">
         <v>278</v>
       </c>
@@ -7347,9 +7346,6 @@
       <c r="F200" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F200" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="F105:F152"/>
     <mergeCell ref="F153:F200"/>
@@ -7364,7 +7360,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18.6333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="73.8833333333333" style="1" customWidth="1"/>
@@ -7403,7 +7399,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="4" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
         <v>478</v>
@@ -7477,7 +7473,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="12" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
         <v>486</v>
@@ -7486,7 +7482,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:3">
+    <row r="13" s="1" customFormat="1" ht="30" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
         <v>487</v>
@@ -7504,7 +7500,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:3">
+    <row r="15" s="1" customFormat="1" ht="30" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
         <v>489</v>
@@ -7560,7 +7556,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="21" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
         <v>478</v>
@@ -7625,7 +7621,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="28" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
         <v>486</v>
@@ -7717,7 +7713,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="38" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
         <v>478</v>
@@ -7782,7 +7778,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="45" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
         <v>478</v>
@@ -7856,7 +7852,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="54" spans="1:3">
+    <row r="53" s="1" customFormat="1" ht="60" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
         <v>478</v>
@@ -7930,7 +7926,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="61" ht="54" spans="1:3">
+    <row r="61" ht="60" spans="1:3">
       <c r="A61" s="3"/>
       <c r="B61" s="5" t="s">
         <v>478</v>

--- a/docs/zh/resource/数据信息说明.xlsx
+++ b/docs/zh/resource/数据信息说明.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\mind-cluster_new\docs\zh\resource\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="labels" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="512">
   <si>
     <t>类别</t>
   </si>
@@ -650,6 +655,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="方正兰亭黑简体"/>
+        <charset val="134"/>
+      </rPr>
       <t>Atlas 训练系列产品
 Atlas A2 训练系列产品
 Atlas A3 训练系列产品
@@ -920,6 +931,13 @@
   </si>
   <si>
     <t>详见“标签数据信息说明”页签中“标签3”</t>
+  </si>
+  <si>
+    <t>Atlas 推理系列产品
+Atlas A2 训练系列产品
+Atlas A3 训练系列产品
+Atlas A2 推理系列产品
+Atlas A3 推理系列产品</t>
   </si>
   <si>
     <t>vnpu_pod_total_memory</t>
@@ -2583,16 +2601,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="方正兰亭黑简体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3522,7 +3540,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="42" style="7" customWidth="1"/>
@@ -3613,7 +3631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="75" spans="1:6">
+    <row r="5" ht="67.5" spans="1:6">
       <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
@@ -3653,7 +3671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="75" spans="1:6">
+    <row r="7" ht="67.5" spans="1:6">
       <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
@@ -3673,7 +3691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="90" spans="1:6">
+    <row r="8" ht="84" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -3693,7 +3711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="90" spans="1:6">
+    <row r="9" ht="84" spans="1:6">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -3713,7 +3731,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="1:6">
+    <row r="10" ht="40.5" spans="1:6">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -3733,7 +3751,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="45" spans="1:6">
+    <row r="11" ht="40.5" spans="1:6">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -3753,7 +3771,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="30" spans="1:6">
+    <row r="12" ht="27" spans="1:6">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -3953,7 +3971,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" ht="90" spans="1:6">
+    <row r="22" ht="84" spans="1:6">
       <c r="A22" s="7" t="s">
         <v>49</v>
       </c>
@@ -4013,7 +4031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" ht="165" spans="1:6">
+    <row r="25" ht="148.5" spans="1:6">
       <c r="A25" s="7" t="s">
         <v>49</v>
       </c>
@@ -4033,7 +4051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" ht="210" spans="1:6">
+    <row r="26" ht="189" spans="1:6">
       <c r="A26" s="9" t="s">
         <v>49</v>
       </c>
@@ -4053,7 +4071,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" ht="165" spans="1:6">
+    <row r="27" ht="148.5" spans="1:6">
       <c r="A27" s="9" t="s">
         <v>49</v>
       </c>
@@ -4113,7 +4131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" ht="165" spans="1:6">
+    <row r="30" ht="148.5" spans="1:6">
       <c r="A30" s="9" t="s">
         <v>49</v>
       </c>
@@ -4133,7 +4151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" ht="165" spans="1:6">
+    <row r="31" ht="148.5" spans="1:6">
       <c r="A31" s="7" t="s">
         <v>49</v>
       </c>
@@ -4153,7 +4171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" ht="165" spans="1:6">
+    <row r="32" ht="148.5" spans="1:6">
       <c r="A32" s="9" t="s">
         <v>49</v>
       </c>
@@ -4173,7 +4191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" ht="135" spans="1:6">
+    <row r="33" ht="121.5" spans="1:6">
       <c r="A33" s="9" t="s">
         <v>49</v>
       </c>
@@ -4193,7 +4211,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" ht="135" spans="1:6">
+    <row r="34" ht="121.5" spans="1:6">
       <c r="A34" s="9" t="s">
         <v>49</v>
       </c>
@@ -4213,7 +4231,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" ht="165" spans="1:6">
+    <row r="35" ht="148.5" spans="1:6">
       <c r="A35" s="4" t="s">
         <v>49</v>
       </c>
@@ -4233,7 +4251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" ht="165" spans="1:6">
+    <row r="36" ht="148.5" spans="1:6">
       <c r="A36" s="9" t="s">
         <v>49</v>
       </c>
@@ -4273,7 +4291,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" ht="165" spans="1:6">
+    <row r="38" ht="148.5" spans="1:6">
       <c r="A38" s="4" t="s">
         <v>110</v>
       </c>
@@ -4293,7 +4311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" ht="165" spans="1:6">
+    <row r="39" ht="148.5" spans="1:6">
       <c r="A39" s="4" t="s">
         <v>110</v>
       </c>
@@ -4313,7 +4331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" ht="60" spans="1:6">
+    <row r="40" ht="54" spans="1:6">
       <c r="A40" s="4" t="s">
         <v>110</v>
       </c>
@@ -4333,7 +4351,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" ht="120" spans="1:6">
+    <row r="41" ht="108" spans="1:6">
       <c r="A41" s="4" t="s">
         <v>110</v>
       </c>
@@ -4353,7 +4371,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" ht="150" spans="1:6">
+    <row r="42" ht="135" spans="1:6">
       <c r="A42" s="4" t="s">
         <v>110</v>
       </c>
@@ -4373,7 +4391,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="43" ht="75" spans="1:6">
+    <row r="43" ht="67.5" spans="1:6">
       <c r="A43" s="7" t="s">
         <v>125</v>
       </c>
@@ -4393,7 +4411,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" ht="75" spans="1:6">
+    <row r="44" ht="67.5" spans="1:6">
       <c r="A44" s="9" t="s">
         <v>125</v>
       </c>
@@ -4413,7 +4431,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" ht="67.5" spans="1:6">
       <c r="A45" s="5" t="s">
         <v>130</v>
       </c>
@@ -4430,58 +4448,58 @@
         <v>113</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" ht="67.5" spans="1:6">
       <c r="A46" s="5" t="s">
         <v>130</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>133</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" ht="67.5" spans="1:6">
       <c r="A47" s="13" t="s">
         <v>130</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>133</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" ht="45" spans="1:6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" ht="40.5" spans="1:6">
       <c r="A48" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>19</v>
@@ -4490,18 +4508,18 @@
         <v>83</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="49" ht="45" spans="1:6">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" ht="40.5" spans="1:6">
       <c r="A49" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>19</v>
@@ -4510,18 +4528,18 @@
         <v>83</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="50" ht="135" spans="1:6">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" ht="121.5" spans="1:6">
       <c r="A50" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>19</v>
@@ -4530,18 +4548,18 @@
         <v>83</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" ht="136" customHeight="1" spans="1:6">
       <c r="A51" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>19</v>
@@ -4550,38 +4568,38 @@
         <v>83</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="52" ht="135" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="52" ht="121.5" spans="1:6">
       <c r="A52" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="53" ht="135" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" ht="121.5" spans="1:6">
       <c r="A53" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>19</v>
@@ -4590,18 +4608,18 @@
         <v>52</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="54" ht="135" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" ht="121.5" spans="1:6">
       <c r="A54" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>19</v>
@@ -4610,18 +4628,18 @@
         <v>52</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="55" ht="135" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" ht="121.5" spans="1:6">
       <c r="A55" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>19</v>
@@ -4630,18 +4648,18 @@
         <v>52</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="56" ht="135" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="56" ht="121.5" spans="1:6">
       <c r="A56" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>19</v>
@@ -4650,18 +4668,18 @@
         <v>52</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" ht="133" customHeight="1" spans="1:6">
       <c r="A57" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>19</v>
@@ -4670,18 +4688,18 @@
         <v>52</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="58" ht="135" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="58" ht="121.5" spans="1:6">
       <c r="A58" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>19</v>
@@ -4690,18 +4708,18 @@
         <v>52</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" ht="33" customHeight="1" spans="1:6">
       <c r="A59" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>19</v>
@@ -4710,18 +4728,18 @@
         <v>52</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" ht="29" customHeight="1" spans="1:6">
       <c r="A60" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>19</v>
@@ -4730,118 +4748,118 @@
         <v>52</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="61" ht="45" spans="1:6">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" ht="40.5" spans="1:6">
       <c r="A61" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B61" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F61" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C61" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="62" ht="45" spans="1:6">
+    </row>
+    <row r="62" ht="40.5" spans="1:6">
       <c r="A62" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="63" ht="45" spans="1:6">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" ht="40.5" spans="1:6">
       <c r="A63" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B63" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C63" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>178</v>
-      </c>
       <c r="F63" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" ht="29" customHeight="1" spans="1:6">
       <c r="A64" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="65" ht="45" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="65" ht="40.5" spans="1:6">
       <c r="A65" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" ht="35" customHeight="1" spans="1:6">
       <c r="A66" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>19</v>
@@ -4850,138 +4868,138 @@
         <v>52</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="67" ht="60" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" ht="54" spans="1:6">
       <c r="A67" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="68" ht="54" spans="1:6">
+      <c r="A68" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E67" s="5" t="s">
+      <c r="B68" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="E68" s="5" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="68" ht="60" spans="1:6">
-      <c r="A68" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B68" s="5" t="s">
+      <c r="F68" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E68" s="5" t="s">
+    </row>
+    <row r="69" ht="54" spans="1:6">
+      <c r="A69" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D69" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="E69" s="5" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="69" ht="60" spans="1:6">
-      <c r="A69" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E69" s="5" t="s">
+      <c r="F69" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="70" ht="54" spans="1:6">
+      <c r="A70" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D70" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="E70" s="5" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="70" ht="60" spans="1:6">
-      <c r="A70" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E70" s="5" t="s">
+      <c r="F70" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="71" ht="54" spans="1:6">
+      <c r="A71" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D71" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F70" s="10" t="s">
+      <c r="E71" s="5" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="71" ht="60" spans="1:6">
-      <c r="A71" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E71" s="5" t="s">
+      <c r="F71" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="72" ht="54" spans="1:6">
+      <c r="A72" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D72" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="E72" s="5" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="72" ht="60" spans="1:6">
-      <c r="A72" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>192</v>
-      </c>
       <c r="F72" s="10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="73" ht="75" spans="1:6">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" ht="67.5" spans="1:6">
       <c r="A73" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>19</v>
@@ -4993,15 +5011,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" ht="75" spans="1:6">
+    <row r="74" ht="67.5" spans="1:6">
       <c r="A74" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>19</v>
@@ -5013,15 +5031,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" ht="75" spans="1:6">
+    <row r="75" ht="67.5" spans="1:6">
       <c r="A75" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>19</v>
@@ -5033,15 +5051,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" ht="75" spans="1:6">
+    <row r="76" ht="67.5" spans="1:6">
       <c r="A76" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>19</v>
@@ -5053,15 +5071,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" ht="75" spans="1:6">
+    <row r="77" ht="67.5" spans="1:6">
       <c r="A77" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>19</v>
@@ -5073,15 +5091,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" ht="75" spans="1:6">
+    <row r="78" ht="67.5" spans="1:6">
       <c r="A78" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>19</v>
@@ -5093,15 +5111,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" ht="75" spans="1:6">
+    <row r="79" ht="67.5" spans="1:6">
       <c r="A79" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>19</v>
@@ -5113,15 +5131,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" ht="75" spans="1:6">
+    <row r="80" ht="67.5" spans="1:6">
       <c r="A80" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>19</v>
@@ -5133,15 +5151,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" ht="75" spans="1:6">
+    <row r="81" ht="67.5" spans="1:6">
       <c r="A81" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>19</v>
@@ -5153,15 +5171,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" ht="75" spans="1:6">
+    <row r="82" ht="67.5" spans="1:6">
       <c r="A82" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>19</v>
@@ -5178,10 +5196,10 @@
         <v>125</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>19</v>
@@ -5193,15 +5211,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" ht="75" spans="1:6">
+    <row r="84" ht="67.5" spans="1:6">
       <c r="A84" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>19</v>
@@ -5213,15 +5231,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" ht="75" spans="1:6">
+    <row r="85" ht="67.5" spans="1:6">
       <c r="A85" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>19</v>
@@ -5233,15 +5251,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" ht="75" spans="1:6">
+    <row r="86" ht="67.5" spans="1:6">
       <c r="A86" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>19</v>
@@ -5253,15 +5271,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" ht="75" spans="1:6">
+    <row r="87" ht="67.5" spans="1:6">
       <c r="A87" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>19</v>
@@ -5273,15 +5291,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" ht="75" spans="1:6">
+    <row r="88" ht="67.5" spans="1:6">
       <c r="A88" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>19</v>
@@ -5293,15 +5311,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" ht="75" spans="1:6">
+    <row r="89" ht="67.5" spans="1:6">
       <c r="A89" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>19</v>
@@ -5313,15 +5331,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" ht="75" spans="1:6">
+    <row r="90" ht="67.5" spans="1:6">
       <c r="A90" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>19</v>
@@ -5338,10 +5356,10 @@
         <v>125</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>19</v>
@@ -5355,153 +5373,153 @@
     </row>
     <row r="92" ht="78" customHeight="1" spans="1:6">
       <c r="A92" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B92" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="93" ht="67.5" spans="1:6">
+      <c r="A93" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="93" ht="75" spans="1:6">
-      <c r="A93" s="5" t="s">
-        <v>242</v>
-      </c>
       <c r="B93" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F93" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C93" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="94" ht="75" spans="1:6">
+    </row>
+    <row r="94" ht="67.5" spans="1:6">
       <c r="A94" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B94" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="95" ht="67.5" spans="1:6">
+      <c r="A95" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C94" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="95" ht="75" spans="1:6">
-      <c r="A95" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="B95" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="F95" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="96" ht="75" spans="1:6">
+    </row>
+    <row r="96" ht="67.5" spans="1:6">
       <c r="A96" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B96" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>255</v>
-      </c>
       <c r="F96" s="10" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="97" ht="75" spans="1:6">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="97" ht="67.5" spans="1:6">
       <c r="A97" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="98" ht="75" spans="1:6">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="98" ht="67.5" spans="1:6">
       <c r="A98" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="99" ht="30" spans="1:6">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="99" ht="27" spans="1:6">
       <c r="A99" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>43</v>
@@ -5510,58 +5528,58 @@
         <v>52</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="100" ht="30" spans="1:6">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="100" ht="27" spans="1:6">
       <c r="A100" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="101" ht="30" spans="1:6">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="101" ht="27" spans="1:6">
       <c r="A101" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="102" ht="135" spans="1:6">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" ht="121.5" spans="1:6">
       <c r="A102" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>19</v>
@@ -5570,38 +5588,38 @@
         <v>113</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="103" ht="135" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="103" ht="121.5" spans="1:6">
       <c r="A103" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F103" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="104" ht="135" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="104" ht="121.5" spans="1:6">
       <c r="A104" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>19</v>
@@ -5610,18 +5628,18 @@
         <v>113</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="105" ht="30" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="105" ht="27" spans="1:6">
       <c r="A105" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>19</v>
@@ -5633,15 +5651,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106" ht="30" spans="1:6">
+    <row r="106" ht="27" spans="1:6">
       <c r="A106" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>19</v>
@@ -5651,15 +5669,15 @@
       </c>
       <c r="F106" s="17"/>
     </row>
-    <row r="107" ht="30" spans="1:6">
+    <row r="107" ht="27" spans="1:6">
       <c r="A107" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>19</v>
@@ -5669,15 +5687,15 @@
       </c>
       <c r="F107" s="17"/>
     </row>
-    <row r="108" ht="30" spans="1:6">
+    <row r="108" ht="27" spans="1:6">
       <c r="A108" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>19</v>
@@ -5687,15 +5705,15 @@
       </c>
       <c r="F108" s="17"/>
     </row>
-    <row r="109" ht="30" spans="1:6">
+    <row r="109" ht="27" spans="1:6">
       <c r="A109" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>19</v>
@@ -5705,15 +5723,15 @@
       </c>
       <c r="F109" s="17"/>
     </row>
-    <row r="110" ht="30" spans="1:6">
+    <row r="110" ht="27" spans="1:6">
       <c r="A110" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>19</v>
@@ -5723,15 +5741,15 @@
       </c>
       <c r="F110" s="17"/>
     </row>
-    <row r="111" ht="30" spans="1:6">
+    <row r="111" ht="27" spans="1:6">
       <c r="A111" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>19</v>
@@ -5741,15 +5759,15 @@
       </c>
       <c r="F111" s="17"/>
     </row>
-    <row r="112" ht="30" spans="1:6">
+    <row r="112" ht="27" spans="1:6">
       <c r="A112" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>19</v>
@@ -5759,15 +5777,15 @@
       </c>
       <c r="F112" s="17"/>
     </row>
-    <row r="113" ht="30" spans="1:6">
+    <row r="113" ht="27" spans="1:6">
       <c r="A113" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>19</v>
@@ -5777,15 +5795,15 @@
       </c>
       <c r="F113" s="17"/>
     </row>
-    <row r="114" ht="30" spans="1:6">
+    <row r="114" ht="27" spans="1:6">
       <c r="A114" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>19</v>
@@ -5795,15 +5813,15 @@
       </c>
       <c r="F114" s="17"/>
     </row>
-    <row r="115" ht="30" spans="1:6">
+    <row r="115" ht="27" spans="1:6">
       <c r="A115" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>19</v>
@@ -5813,15 +5831,15 @@
       </c>
       <c r="F115" s="17"/>
     </row>
-    <row r="116" ht="45" spans="1:6">
+    <row r="116" ht="40.5" spans="1:6">
       <c r="A116" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>19</v>
@@ -5831,15 +5849,15 @@
       </c>
       <c r="F116" s="17"/>
     </row>
-    <row r="117" ht="45" spans="1:6">
+    <row r="117" ht="40.5" spans="1:6">
       <c r="A117" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>19</v>
@@ -5849,15 +5867,15 @@
       </c>
       <c r="F117" s="17"/>
     </row>
-    <row r="118" ht="45" spans="1:6">
+    <row r="118" ht="40.5" spans="1:6">
       <c r="A118" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>19</v>
@@ -5867,15 +5885,15 @@
       </c>
       <c r="F118" s="17"/>
     </row>
-    <row r="119" ht="45" spans="1:6">
+    <row r="119" ht="40.5" spans="1:6">
       <c r="A119" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>19</v>
@@ -5885,15 +5903,15 @@
       </c>
       <c r="F119" s="17"/>
     </row>
-    <row r="120" ht="45" spans="1:6">
+    <row r="120" ht="27" spans="1:6">
       <c r="A120" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>19</v>
@@ -5903,15 +5921,15 @@
       </c>
       <c r="F120" s="17"/>
     </row>
-    <row r="121" ht="45" spans="1:6">
+    <row r="121" ht="40.5" spans="1:6">
       <c r="A121" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>19</v>
@@ -5921,15 +5939,15 @@
       </c>
       <c r="F121" s="17"/>
     </row>
-    <row r="122" ht="45" spans="1:6">
+    <row r="122" ht="27" spans="1:6">
       <c r="A122" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>19</v>
@@ -5939,15 +5957,15 @@
       </c>
       <c r="F122" s="17"/>
     </row>
-    <row r="123" ht="45" spans="1:6">
+    <row r="123" ht="40.5" spans="1:6">
       <c r="A123" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>19</v>
@@ -5957,15 +5975,15 @@
       </c>
       <c r="F123" s="17"/>
     </row>
-    <row r="124" ht="30" spans="1:6">
+    <row r="124" ht="27" spans="1:6">
       <c r="A124" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>19</v>
@@ -5975,15 +5993,15 @@
       </c>
       <c r="F124" s="17"/>
     </row>
-    <row r="125" ht="30" spans="1:6">
+    <row r="125" ht="27" spans="1:6">
       <c r="A125" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>19</v>
@@ -5993,15 +6011,15 @@
       </c>
       <c r="F125" s="17"/>
     </row>
-    <row r="126" ht="30" spans="1:6">
+    <row r="126" ht="27" spans="1:6">
       <c r="A126" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>19</v>
@@ -6011,15 +6029,15 @@
       </c>
       <c r="F126" s="17"/>
     </row>
-    <row r="127" ht="30" spans="1:6">
+    <row r="127" ht="27" spans="1:6">
       <c r="A127" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>19</v>
@@ -6029,15 +6047,15 @@
       </c>
       <c r="F127" s="17"/>
     </row>
-    <row r="128" ht="30" spans="1:6">
+    <row r="128" ht="27" spans="1:6">
       <c r="A128" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>19</v>
@@ -6047,15 +6065,15 @@
       </c>
       <c r="F128" s="17"/>
     </row>
-    <row r="129" ht="30" spans="1:6">
+    <row r="129" ht="27" spans="1:6">
       <c r="A129" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>19</v>
@@ -6065,15 +6083,15 @@
       </c>
       <c r="F129" s="17"/>
     </row>
-    <row r="130" ht="30" spans="1:6">
+    <row r="130" ht="27" spans="1:6">
       <c r="A130" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>19</v>
@@ -6083,15 +6101,15 @@
       </c>
       <c r="F130" s="17"/>
     </row>
-    <row r="131" ht="30" spans="1:6">
+    <row r="131" ht="27" spans="1:6">
       <c r="A131" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>19</v>
@@ -6101,15 +6119,15 @@
       </c>
       <c r="F131" s="17"/>
     </row>
-    <row r="132" ht="30" spans="1:6">
+    <row r="132" ht="27" spans="1:6">
       <c r="A132" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>19</v>
@@ -6119,15 +6137,15 @@
       </c>
       <c r="F132" s="17"/>
     </row>
-    <row r="133" ht="30" spans="1:6">
+    <row r="133" ht="27" spans="1:6">
       <c r="A133" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>19</v>
@@ -6137,15 +6155,15 @@
       </c>
       <c r="F133" s="17"/>
     </row>
-    <row r="134" ht="30" spans="1:6">
+    <row r="134" ht="27" spans="1:6">
       <c r="A134" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>19</v>
@@ -6155,15 +6173,15 @@
       </c>
       <c r="F134" s="17"/>
     </row>
-    <row r="135" ht="30" spans="1:6">
+    <row r="135" ht="27" spans="1:6">
       <c r="A135" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>19</v>
@@ -6173,15 +6191,15 @@
       </c>
       <c r="F135" s="17"/>
     </row>
-    <row r="136" ht="30" spans="1:6">
+    <row r="136" ht="27" spans="1:6">
       <c r="A136" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>19</v>
@@ -6191,15 +6209,15 @@
       </c>
       <c r="F136" s="17"/>
     </row>
-    <row r="137" ht="30" spans="1:6">
+    <row r="137" ht="27" spans="1:6">
       <c r="A137" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>19</v>
@@ -6209,15 +6227,15 @@
       </c>
       <c r="F137" s="17"/>
     </row>
-    <row r="138" ht="30" spans="1:6">
+    <row r="138" ht="27" spans="1:6">
       <c r="A138" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>19</v>
@@ -6227,15 +6245,15 @@
       </c>
       <c r="F138" s="17"/>
     </row>
-    <row r="139" ht="45" spans="1:6">
+    <row r="139" ht="40.5" spans="1:6">
       <c r="A139" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>19</v>
@@ -6245,15 +6263,15 @@
       </c>
       <c r="F139" s="17"/>
     </row>
-    <row r="140" ht="30" spans="1:6">
+    <row r="140" ht="27" spans="1:6">
       <c r="A140" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>19</v>
@@ -6263,15 +6281,15 @@
       </c>
       <c r="F140" s="17"/>
     </row>
-    <row r="141" ht="30" spans="1:6">
+    <row r="141" ht="27" spans="1:6">
       <c r="A141" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>19</v>
@@ -6281,15 +6299,15 @@
       </c>
       <c r="F141" s="17"/>
     </row>
-    <row r="142" ht="30" spans="1:6">
+    <row r="142" ht="27" spans="1:6">
       <c r="A142" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>19</v>
@@ -6299,15 +6317,15 @@
       </c>
       <c r="F142" s="17"/>
     </row>
-    <row r="143" ht="30" spans="1:6">
+    <row r="143" ht="27" spans="1:6">
       <c r="A143" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>19</v>
@@ -6317,15 +6335,15 @@
       </c>
       <c r="F143" s="17"/>
     </row>
-    <row r="144" ht="30" spans="1:6">
+    <row r="144" ht="27" spans="1:6">
       <c r="A144" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>19</v>
@@ -6335,15 +6353,15 @@
       </c>
       <c r="F144" s="17"/>
     </row>
-    <row r="145" ht="30" spans="1:6">
+    <row r="145" ht="27" spans="1:6">
       <c r="A145" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>19</v>
@@ -6353,15 +6371,15 @@
       </c>
       <c r="F145" s="17"/>
     </row>
-    <row r="146" ht="30" spans="1:6">
+    <row r="146" ht="27" spans="1:6">
       <c r="A146" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>19</v>
@@ -6371,15 +6389,15 @@
       </c>
       <c r="F146" s="17"/>
     </row>
-    <row r="147" ht="30" spans="1:6">
+    <row r="147" ht="27" spans="1:6">
       <c r="A147" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>19</v>
@@ -6389,15 +6407,15 @@
       </c>
       <c r="F147" s="17"/>
     </row>
-    <row r="148" ht="30" spans="1:6">
+    <row r="148" ht="27" spans="1:6">
       <c r="A148" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>19</v>
@@ -6407,15 +6425,15 @@
       </c>
       <c r="F148" s="17"/>
     </row>
-    <row r="149" ht="30" spans="1:6">
+    <row r="149" ht="27" spans="1:6">
       <c r="A149" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>19</v>
@@ -6425,15 +6443,15 @@
       </c>
       <c r="F149" s="17"/>
     </row>
-    <row r="150" ht="30" spans="1:6">
+    <row r="150" ht="27" spans="1:6">
       <c r="A150" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>19</v>
@@ -6443,15 +6461,15 @@
       </c>
       <c r="F150" s="17"/>
     </row>
-    <row r="151" ht="30" spans="1:6">
+    <row r="151" ht="27" spans="1:6">
       <c r="A151" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>19</v>
@@ -6461,15 +6479,15 @@
       </c>
       <c r="F151" s="17"/>
     </row>
-    <row r="152" ht="30" spans="1:6">
+    <row r="152" ht="27" spans="1:6">
       <c r="A152" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>19</v>
@@ -6481,13 +6499,13 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>43</v>
@@ -6501,13 +6519,13 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>43</v>
@@ -6519,13 +6537,13 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>43</v>
@@ -6537,13 +6555,13 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>43</v>
@@ -6555,13 +6573,13 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>43</v>
@@ -6573,13 +6591,13 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>43</v>
@@ -6589,15 +6607,15 @@
       </c>
       <c r="F158" s="17"/>
     </row>
-    <row r="159" ht="30" spans="1:6">
+    <row r="159" spans="1:6">
       <c r="A159" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>43</v>
@@ -6609,13 +6627,13 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>43</v>
@@ -6627,13 +6645,13 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>43</v>
@@ -6643,15 +6661,15 @@
       </c>
       <c r="F161" s="17"/>
     </row>
-    <row r="162" ht="30" spans="1:6">
+    <row r="162" spans="1:6">
       <c r="A162" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>43</v>
@@ -6663,13 +6681,13 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>43</v>
@@ -6679,15 +6697,15 @@
       </c>
       <c r="F163" s="17"/>
     </row>
-    <row r="164" ht="45" spans="1:6">
+    <row r="164" ht="40.5" spans="1:6">
       <c r="A164" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>43</v>
@@ -6697,15 +6715,15 @@
       </c>
       <c r="F164" s="17"/>
     </row>
-    <row r="165" ht="30" spans="1:6">
+    <row r="165" ht="27" spans="1:6">
       <c r="A165" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>43</v>
@@ -6715,15 +6733,15 @@
       </c>
       <c r="F165" s="17"/>
     </row>
-    <row r="166" ht="30" spans="1:6">
+    <row r="166" ht="27" spans="1:6">
       <c r="A166" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>43</v>
@@ -6733,15 +6751,15 @@
       </c>
       <c r="F166" s="17"/>
     </row>
-    <row r="167" ht="30" spans="1:6">
+    <row r="167" ht="27" spans="1:6">
       <c r="A167" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>43</v>
@@ -6751,15 +6769,15 @@
       </c>
       <c r="F167" s="17"/>
     </row>
-    <row r="168" ht="30" spans="1:6">
+    <row r="168" ht="27" spans="1:6">
       <c r="A168" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>43</v>
@@ -6769,15 +6787,15 @@
       </c>
       <c r="F168" s="17"/>
     </row>
-    <row r="169" ht="30" spans="1:6">
+    <row r="169" ht="27" spans="1:6">
       <c r="A169" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>43</v>
@@ -6787,15 +6805,15 @@
       </c>
       <c r="F169" s="17"/>
     </row>
-    <row r="170" ht="30" spans="1:6">
+    <row r="170" ht="27" spans="1:6">
       <c r="A170" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>43</v>
@@ -6805,15 +6823,15 @@
       </c>
       <c r="F170" s="17"/>
     </row>
-    <row r="171" ht="30" spans="1:6">
+    <row r="171" ht="27" spans="1:6">
       <c r="A171" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>43</v>
@@ -6825,13 +6843,13 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>43</v>
@@ -6843,13 +6861,13 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>43</v>
@@ -6861,13 +6879,13 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>43</v>
@@ -6879,13 +6897,13 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>43</v>
@@ -6897,13 +6915,13 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>43</v>
@@ -6915,13 +6933,13 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>43</v>
@@ -6933,13 +6951,13 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>43</v>
@@ -6951,13 +6969,13 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>43</v>
@@ -6969,13 +6987,13 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>43</v>
@@ -6987,13 +7005,13 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>43</v>
@@ -7005,13 +7023,13 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>43</v>
@@ -7023,13 +7041,13 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>43</v>
@@ -7041,13 +7059,13 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>43</v>
@@ -7059,13 +7077,13 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>43</v>
@@ -7075,15 +7093,15 @@
       </c>
       <c r="F185" s="17"/>
     </row>
-    <row r="186" ht="30" spans="1:6">
+    <row r="186" ht="27" spans="1:6">
       <c r="A186" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>43</v>
@@ -7093,15 +7111,15 @@
       </c>
       <c r="F186" s="17"/>
     </row>
-    <row r="187" ht="30" spans="1:6">
+    <row r="187" ht="27" spans="1:6">
       <c r="A187" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>43</v>
@@ -7113,13 +7131,13 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>43</v>
@@ -7131,13 +7149,13 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>43</v>
@@ -7149,13 +7167,13 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>43</v>
@@ -7167,13 +7185,13 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>43</v>
@@ -7185,13 +7203,13 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>43</v>
@@ -7203,13 +7221,13 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>43</v>
@@ -7221,13 +7239,13 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>43</v>
@@ -7239,13 +7257,13 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>43</v>
@@ -7257,13 +7275,13 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>43</v>
@@ -7275,13 +7293,13 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>43</v>
@@ -7293,13 +7311,13 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>43</v>
@@ -7311,13 +7329,13 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>43</v>
@@ -7329,13 +7347,13 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>43</v>
@@ -7360,7 +7378,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18.6333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="73.8833333333333" style="1" customWidth="1"/>
@@ -7370,623 +7388,623 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="60" spans="1:3">
+    </row>
+    <row r="4" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="34" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="60" spans="1:3">
+    </row>
+    <row r="12" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="30" spans="1:3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="27" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="30" spans="1:3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="27" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="73" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="60" spans="1:3">
+    </row>
+    <row r="21" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:3">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="23" customHeight="1" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="60" spans="1:3">
+    </row>
+    <row r="28" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="66" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="60" spans="1:3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19" customHeight="1" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:3">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="60" spans="1:3">
+    </row>
+    <row r="45" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="60" spans="1:3">
+    </row>
+    <row r="53" s="1" customFormat="1" ht="54" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:3">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="3"/>
       <c r="B60" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="61" ht="60" spans="1:3">
+    </row>
+    <row r="61" ht="54" spans="1:3">
       <c r="A61" s="3"/>
       <c r="B61" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="3"/>
       <c r="B62" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="3"/>
       <c r="B63" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="3"/>
       <c r="B64" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="3"/>
       <c r="B65" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="3"/>
       <c r="B66" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="3"/>
       <c r="B67" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
